--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T413"/>
+  <dimension ref="A1:T414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="27" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="37" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3298591</v>
+        <v>3397019</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>888810</v>
+        <v>1281945</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>458366</v>
+        <v>599677</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>864086</v>
+        <v>874609</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>435473</v>
+        <v>463739</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>455510</v>
+        <v>502133</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>87339</v>
+        <v>174678</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1434,17 +1434,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>492726</v>
+        <v>528569</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>406503</v>
+        <v>430698</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>308196</v>
+        <v>320314</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>247526</v>
+        <v>250706</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>360048</v>
+        <v>363967</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>207724</v>
+        <v>259426</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>244752</v>
+        <v>270956</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>281856</v>
+        <v>328832</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3408,10 +3408,10 @@
         <v>43416</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>86832</v>
+        <v>130248</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3450,17 +3450,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>106072</v>
+        <v>147342</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>94058</v>
+        <v>133251</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>226682</v>
+        <v>262855</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>167782</v>
+        <v>178027</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>224360</v>
+        <v>235100</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>148702</v>
+        <v>156927</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>165436</v>
+        <v>183824</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>159512</v>
+        <v>175462</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>144674</v>
+        <v>173161</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>115215</v>
+        <v>137184</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>85820</v>
+        <v>113114</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>159703</v>
+        <v>178361</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>145206</v>
+        <v>165001</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>65707</v>
+        <v>91348</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>114532</v>
+        <v>121558</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>108320</v>
+        <v>131938</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>98778</v>
+        <v>102071</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>110576</v>
+        <v>121084</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>150508</v>
+        <v>153454</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>87300</v>
+        <v>108592</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7632,10 +7632,10 @@
         <v>19716</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39432</v>
+        <v>59148</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7674,17 +7674,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7728,10 +7728,10 @@
         <v>19651</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>39302</v>
+        <v>58953</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7770,17 +7770,17 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>117168</v>
+        <v>136696</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>113468</v>
+        <v>132700</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>117292</v>
+        <v>121901</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>92134</v>
+        <v>111209</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -8592,10 +8592,10 @@
         <v>18146</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>36292</v>
+        <v>54438</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8634,17 +8634,17 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -8880,10 +8880,10 @@
         <v>17393</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>34786</v>
+        <v>52179</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8922,17 +8922,17 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>79826</v>
+        <v>85131</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9072,10 +9072,10 @@
         <v>16598</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>33196</v>
+        <v>49794</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9114,17 +9114,17 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9264,10 +9264,10 @@
         <v>16531</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33062</v>
+        <v>49593</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9306,17 +9306,17 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>82054</v>
+        <v>90263</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>75652</v>
+        <v>80916</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9552,10 +9552,10 @@
         <v>16245</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>32490</v>
+        <v>48735</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9594,17 +9594,17 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S95" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>74188</v>
+        <v>79068</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -9744,10 +9744,10 @@
         <v>16043</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>32086</v>
+        <v>48129</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9786,17 +9786,17 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>76412</v>
+        <v>83286</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>68686</v>
+        <v>71979</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>69726</v>
+        <v>74619</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10512,10 +10512,10 @@
         <v>14667</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>29334</v>
+        <v>44001</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10554,17 +10554,17 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S105" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>75124</v>
+        <v>89728</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>76654</v>
+        <v>85875</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>75374</v>
+        <v>89761</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>51738</v>
+        <v>65891</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11376,10 +11376,10 @@
         <v>14114</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>28228</v>
+        <v>42342</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11418,17 +11418,17 @@
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>65100</v>
+        <v>69614</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>92301</v>
+        <v>103594</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11760,10 +11760,10 @@
         <v>13696</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>37154</v>
+        <v>42035</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -11856,10 +11856,10 @@
         <v>13666</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>39044</v>
+        <v>52710</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>75882</v>
+        <v>87453</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>54604</v>
+        <v>67390</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -12816,10 +12816,10 @@
         <v>12204</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>24408</v>
+        <v>36612</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12858,17 +12858,17 @@
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S129" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -12912,10 +12912,10 @@
         <v>12156</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>34072</v>
+        <v>46228</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>61166</v>
+        <v>72929</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -13584,10 +13584,10 @@
         <v>11698</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23396</v>
+        <v>35094</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13626,17 +13626,17 @@
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S137" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -13776,10 +13776,10 @@
         <v>11521</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>23042</v>
+        <v>34563</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13818,17 +13818,17 @@
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S139" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -13872,10 +13872,10 @@
         <v>11358</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>22716</v>
+        <v>34074</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13914,17 +13914,17 @@
       </c>
       <c r="R140" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S140" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>54166</v>
+        <v>59961</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S142" s="2" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>48852</v>
+        <v>59472</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S143" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -14352,10 +14352,10 @@
         <v>10573</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>21146</v>
+        <v>31719</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14394,17 +14394,17 @@
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S145" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>51040</v>
+        <v>61356</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -14928,10 +14928,10 @@
         <v>10127</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>30662</v>
+        <v>40789</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S151" s="2" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>45908</v>
+        <v>48730</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S152" s="2" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>42670</v>
+        <v>45112</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15312,10 +15312,10 @@
         <v>9970</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>19940</v>
+        <v>29910</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15354,17 +15354,17 @@
       </c>
       <c r="R155" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S155" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>51108</v>
+        <v>56866</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>35336</v>
+        <v>45196</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>58080</v>
+        <v>67760</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15888,10 +15888,10 @@
         <v>9608</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>22276</v>
+        <v>33414</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -15930,17 +15930,17 @@
       </c>
       <c r="R161" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S161" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>55600</v>
+        <v>59435</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16176,10 +16176,10 @@
         <v>9586</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>19172</v>
+        <v>28758</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16218,17 +16218,17 @@
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S164" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16464,10 +16464,10 @@
         <v>9403</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>30590</v>
+        <v>39993</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="R167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S167" s="2" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16656,10 +16656,10 @@
         <v>9213</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>18426</v>
+        <v>27639</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
@@ -16698,17 +16698,17 @@
       </c>
       <c r="R169" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S169" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>41410</v>
+        <v>50613</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="R170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>43484</v>
+        <v>47532</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="R172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S172" s="2" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -17040,10 +17040,10 @@
         <v>8830</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>17660</v>
+        <v>26490</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17082,17 +17082,17 @@
       </c>
       <c r="R173" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S173" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>48672</v>
+        <v>55516</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="R176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S176" s="2" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -17424,10 +17424,10 @@
         <v>8724</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>17448</v>
+        <v>26172</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17466,17 +17466,17 @@
       </c>
       <c r="R177" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S177" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>40502</v>
+        <v>43395</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S178" s="2" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -17712,10 +17712,10 @@
         <v>8643</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>26506</v>
+        <v>35149</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="R180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S180" s="2" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18000,10 +18000,10 @@
         <v>8399</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>28654</v>
+        <v>37053</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="R183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S183" s="2" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="T183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>38742</v>
+        <v>41653</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="R186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S186" s="2" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18480,10 +18480,10 @@
         <v>8151</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>16302</v>
+        <v>24453</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18522,17 +18522,17 @@
       </c>
       <c r="R188" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S188" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S188" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>42728</v>
+        <v>47870</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S189" s="2" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18864,10 +18864,10 @@
         <v>7809</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>15618</v>
+        <v>23427</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18906,17 +18906,17 @@
       </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S192" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S192" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>42408</v>
+        <v>48068</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="R193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S193" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>28373</v>
+        <v>35850</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S201" s="2" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="T201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>48810</v>
+        <v>50594</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S202" s="2" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="T202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>40522</v>
+        <v>47719</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S203" s="2" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="T203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>41408</v>
+        <v>48394</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S205" s="2" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="T205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>40690</v>
+        <v>47581</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S207" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="T207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -20688,10 +20688,10 @@
         <v>6752</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>13504</v>
+        <v>20256</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20730,17 +20730,17 @@
       </c>
       <c r="R211" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S211" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -20784,10 +20784,10 @@
         <v>6704</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>13408</v>
+        <v>20112</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -20826,17 +20826,17 @@
       </c>
       <c r="R212" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S212" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -21264,10 +21264,10 @@
         <v>6653</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>13306</v>
+        <v>19959</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21306,17 +21306,17 @@
       </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S217" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S217" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -21552,10 +21552,10 @@
         <v>6568</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>20984</v>
+        <v>27552</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S220" s="2" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="T220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22032,10 +22032,10 @@
         <v>6402</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>12804</v>
+        <v>19206</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22074,17 +22074,17 @@
       </c>
       <c r="R225" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S225" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22128,10 +22128,10 @@
         <v>6357</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>26406</v>
+        <v>32763</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="R226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S226" s="2" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="T226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>35822</v>
+        <v>41117</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
       </c>
       <c r="R227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S227" s="2" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="T227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22320,10 +22320,10 @@
         <v>6308</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>12616</v>
+        <v>18924</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22362,17 +22362,17 @@
       </c>
       <c r="R228" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S228" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22416,10 +22416,10 @@
         <v>6270</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>12540</v>
+        <v>18810</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
@@ -22458,17 +22458,17 @@
       </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S229" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>34118</v>
+        <v>38839</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S231" s="2" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="T231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>33588</v>
+        <v>38528</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="R235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S235" s="2" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="T235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>33248</v>
+        <v>38090</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S236" s="2" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="T236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>26788</v>
+        <v>32468</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="R240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S240" s="2" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="T240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23568,10 +23568,10 @@
         <v>5642</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>11284</v>
+        <v>16926</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23610,17 +23610,17 @@
       </c>
       <c r="R241" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S241" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>28180</v>
+        <v>33816</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="R242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S242" s="2" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="T242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>29818</v>
+        <v>33533</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="R243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S243" s="2" t="inlineStr">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="T243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -23856,10 +23856,10 @@
         <v>5533</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>11066</v>
+        <v>16599</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23898,17 +23898,17 @@
       </c>
       <c r="R244" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S244" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -24336,10 +24336,10 @@
         <v>5216</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>10432</v>
+        <v>15648</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
@@ -24378,17 +24378,17 @@
       </c>
       <c r="R249" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S249" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>27092</v>
+        <v>30290</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
       </c>
       <c r="R251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S251" s="2" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="T251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -24624,10 +24624,10 @@
         <v>5100</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>10200</v>
+        <v>15300</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -24666,17 +24666,17 @@
       </c>
       <c r="R252" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S252" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -24816,10 +24816,10 @@
         <v>5039</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>10078</v>
+        <v>15117</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24858,17 +24858,17 @@
       </c>
       <c r="R254" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S254" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -24912,10 +24912,10 @@
         <v>4963</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>15142</v>
+        <v>20105</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="R255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S255" s="2" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="T255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -25392,10 +25392,10 @@
         <v>4853</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>9706</v>
+        <v>14559</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25434,17 +25434,17 @@
       </c>
       <c r="R260" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S260" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -26160,10 +26160,10 @@
         <v>4704</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>9408</v>
+        <v>14112</v>
       </c>
       <c r="J268" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
@@ -26202,17 +26202,17 @@
       </c>
       <c r="R268" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S268" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -26352,10 +26352,10 @@
         <v>4697</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>9394</v>
+        <v>14091</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26394,17 +26394,17 @@
       </c>
       <c r="R270" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S270" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -26640,10 +26640,10 @@
         <v>4465</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>8930</v>
+        <v>13395</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26682,17 +26682,17 @@
       </c>
       <c r="R273" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S273" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>23734</v>
+        <v>26855</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="R274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S274" s="2" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -27024,10 +27024,10 @@
         <v>4305</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>16274</v>
+        <v>20579</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="R277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S277" s="2" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="T277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -27120,10 +27120,10 @@
         <v>4294</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>8588</v>
+        <v>12882</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27162,17 +27162,17 @@
       </c>
       <c r="R278" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S278" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -27504,10 +27504,10 @@
         <v>3938</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>7876</v>
+        <v>11814</v>
       </c>
       <c r="J282" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
@@ -27546,17 +27546,17 @@
       </c>
       <c r="R282" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S282" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -27600,10 +27600,10 @@
         <v>3927</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>23326</v>
+        <v>27253</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
       </c>
       <c r="R283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S283" s="2" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -27696,10 +27696,10 @@
         <v>3919</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>7838</v>
+        <v>11757</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27738,17 +27738,17 @@
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S284" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -28368,10 +28368,10 @@
         <v>3763</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>7526</v>
+        <v>11289</v>
       </c>
       <c r="J291" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
@@ -28410,17 +28410,17 @@
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S291" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>23971</v>
+        <v>27449</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
       </c>
       <c r="R298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S298" s="2" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -29616,10 +29616,10 @@
         <v>3355</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>6710</v>
+        <v>10065</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29658,17 +29658,17 @@
       </c>
       <c r="R304" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S304" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S304" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -29808,10 +29808,10 @@
         <v>3334</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>6668</v>
+        <v>10002</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29850,17 +29850,17 @@
       </c>
       <c r="R306" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S306" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -29904,10 +29904,10 @@
         <v>3331</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>12510</v>
+        <v>15841</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="R307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S307" s="2" t="inlineStr">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30000,10 +30000,10 @@
         <v>3321</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>19922</v>
+        <v>23241</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="R308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S308" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30192,10 +30192,10 @@
         <v>3198</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>18812</v>
+        <v>22010</v>
       </c>
       <c r="J310" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
       </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S310" s="2" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30384,10 +30384,10 @@
         <v>3154</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>18182</v>
+        <v>20965</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S312" s="2" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30576,10 +30576,10 @@
         <v>3101</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>17470</v>
+        <v>20571</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="R314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S314" s="2" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30864,10 +30864,10 @@
         <v>2946</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>5892</v>
+        <v>8838</v>
       </c>
       <c r="J317" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K317" s="2" t="inlineStr">
         <is>
@@ -30906,17 +30906,17 @@
       </c>
       <c r="R317" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S317" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S317" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -30960,10 +30960,10 @@
         <v>2946</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>5892</v>
+        <v>8838</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
@@ -31002,17 +31002,17 @@
       </c>
       <c r="R318" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S318" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S318" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -31056,10 +31056,10 @@
         <v>2945</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>5890</v>
+        <v>8835</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31098,17 +31098,17 @@
       </c>
       <c r="R319" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S319" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S319" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -31152,10 +31152,10 @@
         <v>2942</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>5884</v>
+        <v>8826</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31194,17 +31194,17 @@
       </c>
       <c r="R320" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S320" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S320" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -31440,10 +31440,10 @@
         <v>2911</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>17466</v>
+        <v>20377</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="R323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S323" s="2" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="T323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -31824,10 +31824,10 @@
         <v>2857</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>16190</v>
+        <v>18571</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
       </c>
       <c r="R327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S327" s="2" t="inlineStr">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="T327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -32208,10 +32208,10 @@
         <v>2823</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>5646</v>
+        <v>8469</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32250,17 +32250,17 @@
       </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S331" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -32688,10 +32688,10 @@
         <v>2796</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>5592</v>
+        <v>8388</v>
       </c>
       <c r="J336" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
@@ -32730,17 +32730,17 @@
       </c>
       <c r="R336" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S336" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -32784,10 +32784,10 @@
         <v>2767</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>5534</v>
+        <v>8301</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32826,17 +32826,17 @@
       </c>
       <c r="R337" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S337" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -32976,10 +32976,10 @@
         <v>2730</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>10920</v>
+        <v>13450</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="R339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S339" s="2" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="T339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -33168,10 +33168,10 @@
         <v>2700</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>5400</v>
+        <v>8100</v>
       </c>
       <c r="J341" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K341" s="2" t="inlineStr">
         <is>
@@ -33210,17 +33210,17 @@
       </c>
       <c r="R341" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S341" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -33264,10 +33264,10 @@
         <v>2699</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>5398</v>
+        <v>8097</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33306,17 +33306,17 @@
       </c>
       <c r="R342" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S342" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -33552,10 +33552,10 @@
         <v>2666</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>10648</v>
+        <v>13314</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
       </c>
       <c r="R345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S345" s="2" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="T345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -33648,10 +33648,10 @@
         <v>2635</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>5270</v>
+        <v>7905</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33690,17 +33690,17 @@
       </c>
       <c r="R346" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S346" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -33840,10 +33840,10 @@
         <v>2520</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>5040</v>
+        <v>7560</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33882,17 +33882,17 @@
       </c>
       <c r="R348" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-29</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S348" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -34224,10 +34224,10 @@
         <v>2427</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>9423</v>
+        <v>11850</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
       </c>
       <c r="R352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S352" s="2" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="T352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -36683,27 +36683,27 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>6a547a7c98b0560013013abd</t>
+          <t>665e11941fa95b00139155d6</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>user41081</t>
+          <t>breakoutsignals1</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>user41081</t>
+          <t>breakoutsignals1</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>vijaydarji667@gmail.com</t>
+          <t>ingeniousgcm5@gmail.com</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>9274267070</t>
+          <t>8668376331</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -36717,22 +36717,22 @@
         </is>
       </c>
       <c r="H378" s="2" t="n">
-        <v>1940</v>
+        <v>1953</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>7760</v>
+        <v>1953</v>
       </c>
       <c r="J378" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
-          <t>6a547ea798b0560013024205</t>
+          <t>66c6259d2daa8f0013342767</t>
         </is>
       </c>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a547ea798b0560013024205</t>
+          <t>https://superprofile.bio/vig/66c6259d2daa8f0013342767</t>
         </is>
       </c>
       <c r="M378" s="2" t="inlineStr">
@@ -36762,44 +36762,44 @@
       </c>
       <c r="R378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="T378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>647561213cbb05001faef3d3</t>
+          <t>6a547a7c98b0560013013abd</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>vksir1</t>
+          <t>user41081</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>vksir1</t>
+          <t>user41081</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>khandon.vk@gmail.com</t>
+          <t>vijaydarji667@gmail.com</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>8290092913</t>
+          <t>9274267070</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
@@ -36823,12 +36823,12 @@
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
-          <t>6475b04344677f001f08420d</t>
+          <t>6a547ea798b0560013024205</t>
         </is>
       </c>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6475b04344677f001f08420d</t>
+          <t>https://superprofile.bio/vig/6a547ea798b0560013024205</t>
         </is>
       </c>
       <c r="M379" s="2" t="inlineStr">
@@ -36875,27 +36875,27 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>65aa05f67bb5b6001d8288ed</t>
+          <t>647561213cbb05001faef3d3</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>professor2026</t>
+          <t>vksir1</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>professor2026</t>
+          <t>vksir1</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>jannat709676@gmail.com</t>
+          <t>khandon.vk@gmail.com</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>8849699811</t>
+          <t>8290092913</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -36912,19 +36912,19 @@
         <v>1940</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>1940</v>
+        <v>7760</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>69ca617e3e3e170013e99a12</t>
+          <t>6475b04344677f001f08420d</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca617e3e3e170013e99a12</t>
+          <t>https://superprofile.bio/vig/6475b04344677f001f08420d</t>
         </is>
       </c>
       <c r="M380" s="2" t="inlineStr">
@@ -36954,12 +36954,12 @@
       </c>
       <c r="R380" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S380" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T380" s="2" t="inlineStr">
@@ -36971,27 +36971,27 @@
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>65c8c3e0e0e11f001e86446f</t>
+          <t>65aa05f67bb5b6001d8288ed</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>edgeadmin</t>
+          <t>professor2026</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>edgeadmin</t>
+          <t>professor2026</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>nimmii5151@gmail.com</t>
+          <t>jannat709676@gmail.com</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>8085115151</t>
+          <t>8849699811</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
@@ -37005,22 +37005,22 @@
         </is>
       </c>
       <c r="H381" s="2" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>7752</v>
+        <v>1940</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
-          <t>66371b2d0b57770013e4942f</t>
+          <t>69ca617e3e3e170013e99a12</t>
         </is>
       </c>
       <c r="L381" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
+          <t>https://superprofile.bio/vig/69ca617e3e3e170013e99a12</t>
         </is>
       </c>
       <c r="M381" s="2" t="inlineStr">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="R381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T381" s="2" t="inlineStr">
@@ -37067,27 +37067,27 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>64bf7c27e98788001f3fa09d</t>
+          <t>65c8c3e0e0e11f001e86446f</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>chaudhary29</t>
+          <t>edgeadmin</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>chaudhary29</t>
+          <t>edgeadmin</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>mrgreenappleajay@gmail.com</t>
+          <t>nimmii5151@gmail.com</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>9557922941</t>
+          <t>8085115151</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -37101,22 +37101,22 @@
         </is>
       </c>
       <c r="H382" s="2" t="n">
-        <v>1932</v>
+        <v>1938</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>7728</v>
+        <v>7752</v>
       </c>
       <c r="J382" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
-          <t>6620be84ec6aa900121eccc4</t>
+          <t>66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6620be84ec6aa900121eccc4</t>
+          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="M382" s="2" t="inlineStr">
@@ -37163,27 +37163,27 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>64f7f2c441cc54001fbe7491</t>
+          <t>64bf7c27e98788001f3fa09d</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>xtellar</t>
+          <t>chaudhary29</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>xtellar</t>
+          <t>chaudhary29</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>theartbraingokul@gmail.com</t>
+          <t>mrgreenappleajay@gmail.com</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>8848757632</t>
+          <t>9557922941</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -37197,22 +37197,22 @@
         </is>
       </c>
       <c r="H383" s="2" t="n">
-        <v>1887</v>
+        <v>1932</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>7548</v>
+        <v>7728</v>
       </c>
       <c r="J383" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
-          <t>6a4773ece345050013f142db</t>
+          <t>6620be84ec6aa900121eccc4</t>
         </is>
       </c>
       <c r="L383" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
+          <t>https://superprofile.bio/vig/6620be84ec6aa900121eccc4</t>
         </is>
       </c>
       <c r="M383" s="2" t="inlineStr">
@@ -37259,27 +37259,27 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>6a07df7c7c5fcd00133a6e3b</t>
+          <t>64f7f2c441cc54001fbe7491</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>xtellar</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>xtellar</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>experttrading874@gmail.com</t>
+          <t>theartbraingokul@gmail.com</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>6377727003</t>
+          <t>8848757632</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -37293,22 +37293,22 @@
         </is>
       </c>
       <c r="H384" s="2" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>7524</v>
+        <v>7548</v>
       </c>
       <c r="J384" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
-          <t>6a088c367c5fcd00135ca723</t>
+          <t>6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
+          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="M384" s="2" t="inlineStr">
@@ -37355,27 +37355,27 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>6981d41125307400137323ec</t>
+          <t>6a07df7c7c5fcd00133a6e3b</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Prakash9690</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>Prakash9690</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>shreeshyam87756@gmail.com</t>
+          <t>experttrading874@gmail.com</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>6350429617</t>
+          <t>6377727003</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -37399,12 +37399,12 @@
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
-          <t>6981d57e21e30200125961df</t>
+          <t>6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6981d57e21e30200125961df</t>
+          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="M385" s="2" t="inlineStr">
@@ -37451,27 +37451,27 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>65c89053e0e11f001e822548</t>
+          <t>6981d41125307400137323ec</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>freshershunt</t>
+          <t>Prakash9690</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>freshershunt</t>
+          <t>Prakash9690</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>freshershunt.in@gmail.com</t>
+          <t>shreeshyam87756@gmail.com</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>9060803166</t>
+          <t>6350429617</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -37485,22 +37485,22 @@
         </is>
       </c>
       <c r="H386" s="2" t="n">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>7512</v>
+        <v>7524</v>
       </c>
       <c r="J386" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
-          <t>65f84c6876f3550013a2920c</t>
+          <t>6981d57e21e30200125961df</t>
         </is>
       </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
+          <t>https://superprofile.bio/vig/6981d57e21e30200125961df</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr">
@@ -37547,27 +37547,27 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>627ca99791125d5ba8a34b41</t>
+          <t>65c89053e0e11f001e822548</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>mamoon</t>
+          <t>freshershunt</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>mamoon</t>
+          <t>freshershunt</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Mamoon4sindia@gmail.com</t>
+          <t>freshershunt.in@gmail.com</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>7903542731</t>
+          <t>9060803166</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
@@ -37581,22 +37581,22 @@
         </is>
       </c>
       <c r="H387" s="2" t="n">
-        <v>1832</v>
+        <v>1878</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>7328</v>
+        <v>7512</v>
       </c>
       <c r="J387" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
-          <t>66eaae246c05200013bace75</t>
+          <t>65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
+          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
@@ -37643,27 +37643,27 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>687f538e23947700130cd9cc</t>
+          <t>627ca99791125d5ba8a34b41</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>mamoon</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>mamoon</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>mastermindteam051@gmail.com</t>
+          <t>Mamoon4sindia@gmail.com</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>9936556941</t>
+          <t>7903542731</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
@@ -37677,22 +37677,22 @@
         </is>
       </c>
       <c r="H388" s="2" t="n">
-        <v>1740</v>
+        <v>1832</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>6960</v>
+        <v>7328</v>
       </c>
       <c r="J388" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
-          <t>697998f47fac9d0013f74dfe</t>
+          <t>66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
+          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr">
@@ -37739,27 +37739,27 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>676cf61fae833e001322e4d4</t>
+          <t>687f538e23947700130cd9cc</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>rahulstock11@gmail.com</t>
+          <t>mastermindteam051@gmail.com</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>8305763595</t>
+          <t>9936556941</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
@@ -37773,22 +37773,22 @@
         </is>
       </c>
       <c r="H389" s="2" t="n">
-        <v>1646</v>
+        <v>1740</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>6584</v>
+        <v>6960</v>
       </c>
       <c r="J389" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K389" s="2" t="inlineStr">
         <is>
-          <t>676d0ccf8e79b600130eb896</t>
+          <t>697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="L389" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
+          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="M389" s="2" t="inlineStr">
@@ -37835,27 +37835,27 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>65e953798a133b0013814853</t>
+          <t>676cf61fae833e001322e4d4</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>samirpradhan</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>samirpradhan</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>samirkumarpradhan9@gmail.com</t>
+          <t>rahulstock11@gmail.com</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>9178074088</t>
+          <t>8305763595</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
@@ -37879,12 +37879,12 @@
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>65e9543e9451aa0012fe0644</t>
+          <t>676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
+          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr">
@@ -37931,27 +37931,27 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>656f190c85e895001e492ba2</t>
+          <t>65e953798a133b0013814853</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>mts3949</t>
+          <t>samirpradhan</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>mts3949</t>
+          <t>samirpradhan</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>shivaniprashant77@gmail.com</t>
+          <t>samirkumarpradhan9@gmail.com</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>9284394639</t>
+          <t>9178074088</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
@@ -37965,22 +37965,22 @@
         </is>
       </c>
       <c r="H391" s="2" t="n">
-        <v>1552</v>
+        <v>1646</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>6208</v>
+        <v>6584</v>
       </c>
       <c r="J391" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
         <is>
-          <t>698f2450859ceb00130815a3</t>
+          <t>65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="L391" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
+          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="M391" s="2" t="inlineStr">
@@ -38027,27 +38027,27 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>646373ce6cbb8200207efe77</t>
+          <t>656f190c85e895001e492ba2</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>godfather01</t>
+          <t>mts3949</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>godfather01</t>
+          <t>mts3949</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>vikkysharma4032@gmail.com</t>
+          <t>shivaniprashant77@gmail.com</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>9839384032</t>
+          <t>9284394639</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -38071,12 +38071,12 @@
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>68459b8cb2cccb0013dabf4c</t>
+          <t>698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
+          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr">
@@ -38123,27 +38123,27 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>645cb91fc8965700203aa836</t>
+          <t>646373ce6cbb8200207efe77</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>kavyatrader</t>
+          <t>godfather01</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>kavyatrader</t>
+          <t>godfather01</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Singhabhishek59942@gmail.com</t>
+          <t>vikkysharma4032@gmail.com</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>8979006726</t>
+          <t>9839384032</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
@@ -38157,22 +38157,22 @@
         </is>
       </c>
       <c r="H393" s="2" t="n">
-        <v>1534</v>
+        <v>1552</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>6136</v>
+        <v>6208</v>
       </c>
       <c r="J393" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
-          <t>69dc9e4d81ef030013e77b80</t>
+          <t>68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
+          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="M393" s="2" t="inlineStr">
@@ -38219,27 +38219,27 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>6693e8299527ae0013ffcb9e</t>
+          <t>645cb91fc8965700203aa836</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>bigbull2025</t>
+          <t>kavyatrader</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>bigbull2025</t>
+          <t>kavyatrader</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>bjisrk80@gmail.com</t>
+          <t>Singhabhishek59942@gmail.com</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>7568977191</t>
+          <t>8979006726</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -38253,22 +38253,22 @@
         </is>
       </c>
       <c r="H394" s="2" t="n">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>6096</v>
+        <v>6136</v>
       </c>
       <c r="J394" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
-          <t>66ee6de8d79b930013987bd6</t>
+          <t>69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
+          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="M394" s="2" t="inlineStr">
@@ -38315,27 +38315,27 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>647b0a76df97e200208e3c33</t>
+          <t>6693e8299527ae0013ffcb9e</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>ankitatfutureinvestor</t>
+          <t>bigbull2025</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>ankitatfutureinvestor</t>
+          <t>bigbull2025</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>digindia.aj@gmail.com</t>
+          <t>bjisrk80@gmail.com</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>8240223323</t>
+          <t>7568977191</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
@@ -38349,22 +38349,22 @@
         </is>
       </c>
       <c r="H395" s="2" t="n">
-        <v>1476</v>
+        <v>1524</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>5904</v>
+        <v>6096</v>
       </c>
       <c r="J395" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
-          <t>6915b8fa9a5b350013bb71b8</t>
+          <t>66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6915b8fa9a5b350013bb71b8</t>
+          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="M395" s="2" t="inlineStr">
@@ -38411,27 +38411,27 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>62357fa202100543e97a25fa</t>
+          <t>647b0a76df97e200208e3c33</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>harshtrading27</t>
+          <t>ankitatfutureinvestor</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>harshtrading27</t>
+          <t>ankitatfutureinvestor</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>hskatkiya2001@gmail.com</t>
+          <t>digindia.aj@gmail.com</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>6356359759</t>
+          <t>8240223323</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
@@ -38445,22 +38445,22 @@
         </is>
       </c>
       <c r="H396" s="2" t="n">
-        <v>1465</v>
+        <v>1476</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>5860</v>
+        <v>5904</v>
       </c>
       <c r="J396" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>643f8dccf6caee0020703e83</t>
+          <t>6915b8fa9a5b350013bb71b8</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/643f8dccf6caee0020703e83</t>
+          <t>https://superprofile.bio/vig/6915b8fa9a5b350013bb71b8</t>
         </is>
       </c>
       <c r="M396" s="2" t="inlineStr">
@@ -38507,27 +38507,27 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>67c94e21f8f7120014c00900</t>
+          <t>62357fa202100543e97a25fa</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>httpstme4xrkpkvzmi82mtzl</t>
+          <t>harshtrading27</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>httpstme4xrkpkvzmi82mtzl</t>
+          <t>harshtrading27</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>tradingwithvivek.87@gmail.com</t>
+          <t>hskatkiya2001@gmail.com</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>9106562524</t>
+          <t>6356359759</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
@@ -38541,22 +38541,22 @@
         </is>
       </c>
       <c r="H397" s="2" t="n">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>5828</v>
+        <v>5860</v>
       </c>
       <c r="J397" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
         <is>
-          <t>6a7ac8e844ab5300132d194a</t>
+          <t>643f8dccf6caee0020703e83</t>
         </is>
       </c>
       <c r="L397" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
+          <t>https://superprofile.bio/vig/643f8dccf6caee0020703e83</t>
         </is>
       </c>
       <c r="M397" s="2" t="inlineStr">
@@ -38603,27 +38603,27 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>69e89b0ed9ffde0013e31879</t>
+          <t>67c94e21f8f7120014c00900</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>httpstme4xrkpkvzmi82mtzl</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>httpstme4xrkpkvzmi82mtzl</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>nitindhandre42@gmail.com</t>
+          <t>tradingwithvivek.87@gmail.com</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>7977913010</t>
+          <t>9106562524</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -38637,22 +38637,22 @@
         </is>
       </c>
       <c r="H398" s="2" t="n">
-        <v>1428</v>
+        <v>1457</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>5712</v>
+        <v>5828</v>
       </c>
       <c r="J398" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>6a787fec62ca790013c3fe57</t>
+          <t>6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
+          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="M398" s="2" t="inlineStr">
@@ -38699,27 +38699,27 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>6a131bb7d14a790012e11a6f</t>
+          <t>69e89b0ed9ffde0013e31879</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>ffkatarka@gmail.com</t>
+          <t>nitindhandre42@gmail.com</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>9101299533</t>
+          <t>7977913010</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -38733,22 +38733,22 @@
         </is>
       </c>
       <c r="H399" s="2" t="n">
-        <v>1412</v>
+        <v>1428</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>5648</v>
+        <v>5712</v>
       </c>
       <c r="J399" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
-          <t>6a6d9d5033211a001319c244</t>
+          <t>6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="L399" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
+          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="M399" s="2" t="inlineStr">
@@ -38795,27 +38795,27 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>6986dbd1350e1a0014cdbba8</t>
+          <t>6a131bb7d14a790012e11a6f</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>kumarshubham857208@gmail.com</t>
+          <t>ffkatarka@gmail.com</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>9253166725</t>
+          <t>9101299533</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -38829,22 +38829,22 @@
         </is>
       </c>
       <c r="H400" s="2" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>5644</v>
+        <v>5648</v>
       </c>
       <c r="J400" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
-          <t>69a90448ce8bdc00125c31a5</t>
+          <t>6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="L400" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
+          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="M400" s="2" t="inlineStr">
@@ -38891,27 +38891,27 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>67d06a60fac4900013f6e7c8</t>
+          <t>6986dbd1350e1a0014cdbba8</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>gainyourselfofficial</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>gainyourselfofficial</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>dp540503@gmail.com</t>
+          <t>kumarshubham857208@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>8897083372</t>
+          <t>9253166725</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
@@ -38935,12 +38935,12 @@
       </c>
       <c r="K401" s="2" t="inlineStr">
         <is>
-          <t>6a4bdb749abd7300134a20f7</t>
+          <t>69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
+          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="M401" s="2" t="inlineStr">
@@ -38987,27 +38987,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>617fab8b6ffe000d0e7868a2</t>
+          <t>67d06a60fac4900013f6e7c8</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>shorttermstockss</t>
+          <t>gainyourselfofficial</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>shorttermstockss</t>
+          <t>gainyourselfofficial</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>shahsanket1708@gmail.com</t>
+          <t>dp540503@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>8866831782</t>
+          <t>8897083372</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -39021,22 +39021,22 @@
         </is>
       </c>
       <c r="H402" s="2" t="n">
-        <v>1316</v>
+        <v>1411</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>5264</v>
+        <v>5644</v>
       </c>
       <c r="J402" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>642560ad3b5510001f5c75de</t>
+          <t>6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/642560ad3b5510001f5c75de</t>
+          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="M402" s="2" t="inlineStr">
@@ -39083,27 +39083,27 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>6862347467feb80013f6f503</t>
+          <t>617fab8b6ffe000d0e7868a2</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>Zero9733</t>
+          <t>shorttermstockss</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>Zero9733</t>
+          <t>shorttermstockss</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>zeroheropremium9001@gmail.com</t>
+          <t>shahsanket1708@gmail.com</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>9001130080</t>
+          <t>8866831782</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -39117,22 +39117,22 @@
         </is>
       </c>
       <c r="H403" s="2" t="n">
-        <v>1261</v>
+        <v>1316</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>5044</v>
+        <v>5264</v>
       </c>
       <c r="J403" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
-          <t>6866566ca42647001377eff6</t>
+          <t>642560ad3b5510001f5c75de</t>
         </is>
       </c>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6866566ca42647001377eff6</t>
+          <t>https://superprofile.bio/vig/642560ad3b5510001f5c75de</t>
         </is>
       </c>
       <c r="M403" s="2" t="inlineStr">
@@ -39179,27 +39179,27 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>68f4c2d100b7a10013e082d6</t>
+          <t>6862347467feb80013f6f503</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare</t>
+          <t>Zero9733</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare</t>
+          <t>Zero9733</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare294@gmail.com</t>
+          <t>zeroheropremium9001@gmail.com</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>7385029673</t>
+          <t>9001130080</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -39213,22 +39213,22 @@
         </is>
       </c>
       <c r="H404" s="2" t="n">
-        <v>1222</v>
+        <v>1261</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>4888</v>
+        <v>5044</v>
       </c>
       <c r="J404" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>6a7c0a37542b2500148af289</t>
+          <t>6866566ca42647001377eff6</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7c0a37542b2500148af289</t>
+          <t>https://superprofile.bio/vig/6866566ca42647001377eff6</t>
         </is>
       </c>
       <c r="M404" s="2" t="inlineStr">
@@ -39275,27 +39275,27 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>6a2a3b18739da100136db6f1</t>
+          <t>68f4c2d100b7a10013e082d6</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>ishwarbhakare</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>ishwarbhakare</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>mr.perfect.official018@gmail.com</t>
+          <t>ishwarbhakare294@gmail.com</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>9116087897</t>
+          <t>7385029673</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
@@ -39309,22 +39309,22 @@
         </is>
       </c>
       <c r="H405" s="2" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>2440</v>
+        <v>4888</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
-          <t>6a3a9b9ec4f6700013489927</t>
+          <t>6a7c0a37542b2500148af289</t>
         </is>
       </c>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3a9b9ec4f6700013489927</t>
+          <t>https://superprofile.bio/vig/6a7c0a37542b2500148af289</t>
         </is>
       </c>
       <c r="M405" s="2" t="inlineStr">
@@ -39354,12 +39354,12 @@
       </c>
       <c r="R405" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S405" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T405" s="2" t="inlineStr">
@@ -39371,27 +39371,27 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>69d8e18075a32f001382a054</t>
+          <t>6a2a3b18739da100136db6f1</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>mirag69</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>mirag69</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>bhupendrakumar75698@gmail.com</t>
+          <t>mr.perfect.official018@gmail.com</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>9203710056</t>
+          <t>9116087897</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -39405,22 +39405,22 @@
         </is>
       </c>
       <c r="H406" s="2" t="n">
-        <v>1158</v>
+        <v>1220</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>4632</v>
+        <v>3660</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
-          <t>6a41f935be7a120013780d32</t>
+          <t>6a3a9b9ec4f6700013489927</t>
         </is>
       </c>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a41f935be7a120013780d32</t>
+          <t>https://superprofile.bio/vig/6a3a9b9ec4f6700013489927</t>
         </is>
       </c>
       <c r="M406" s="2" t="inlineStr">
@@ -39450,44 +39450,44 @@
       </c>
       <c r="R406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>65132965f4d0b1001eba9b70</t>
+          <t>69d8e18075a32f001382a054</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>mirag69</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>mirag69</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>biswalfc@gmail.com</t>
+          <t>bhupendrakumar75698@gmail.com</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>9658251426</t>
+          <t>9203710056</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -39501,22 +39501,22 @@
         </is>
       </c>
       <c r="H407" s="2" t="n">
-        <v>1134</v>
+        <v>1158</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>4536</v>
+        <v>4632</v>
       </c>
       <c r="J407" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
-          <t>6724fcbd76412b00139f3f43</t>
+          <t>6a41f935be7a120013780d32</t>
         </is>
       </c>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
+          <t>https://superprofile.bio/vig/6a41f935be7a120013780d32</t>
         </is>
       </c>
       <c r="M407" s="2" t="inlineStr">
@@ -39563,27 +39563,27 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>695fc2d673169a001320fcf5</t>
+          <t>65132965f4d0b1001eba9b70</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva7870@gmail.com</t>
+          <t>biswalfc@gmail.com</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>9534598557</t>
+          <t>9658251426</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -39597,22 +39597,22 @@
         </is>
       </c>
       <c r="H408" s="2" t="n">
-        <v>1080</v>
+        <v>1134</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>4320</v>
+        <v>4536</v>
       </c>
       <c r="J408" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
-          <t>6961fea2c0dd9a00126d58b1</t>
+          <t>6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
+          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="M408" s="2" t="inlineStr">
@@ -39659,27 +39659,27 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>659b990d57f865001e1efa98</t>
+          <t>695fc2d673169a001320fcf5</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>vishalgaikwad91888@gmail.com</t>
+          <t>shivamshiva7870@gmail.com</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>7040119684</t>
+          <t>9534598557</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -39693,22 +39693,22 @@
         </is>
       </c>
       <c r="H409" s="2" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="I409" s="2" t="n">
-        <v>4312</v>
+        <v>4320</v>
       </c>
       <c r="J409" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K409" s="2" t="inlineStr">
         <is>
-          <t>69f59765a8c2c60013505029</t>
+          <t>6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
+          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="M409" s="2" t="inlineStr">
@@ -39755,27 +39755,27 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>69fb20dbfae26e0013229a6c</t>
+          <t>659b990d57f865001e1efa98</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>rupeshbhagat1445@gmail.com</t>
+          <t>vishalgaikwad91888@gmail.com</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>6397113270</t>
+          <t>7040119684</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -39789,22 +39789,22 @@
         </is>
       </c>
       <c r="H410" s="2" t="n">
-        <v>1061</v>
+        <v>1078</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>4244</v>
+        <v>4312</v>
       </c>
       <c r="J410" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
-          <t>6a40e3e946bff60013350d9d</t>
+          <t>69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
+          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="M410" s="2" t="inlineStr">
@@ -39851,27 +39851,27 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>666e8a3cf52ecb0013f648c2</t>
+          <t>69fb20dbfae26e0013229a6c</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan@iplaneducation.com</t>
+          <t>rupeshbhagat1445@gmail.com</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>9999616222</t>
+          <t>6397113270</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
@@ -39885,57 +39885,57 @@
         </is>
       </c>
       <c r="H411" s="2" t="n">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>2114</v>
+        <v>4244</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M411" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N411" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N411" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O411" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Not Verified</t>
         </is>
       </c>
       <c r="P411" s="2" t="inlineStr">
         <is>
-          <t>INH000019521</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q411" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Manual Review Required</t>
         </is>
       </c>
       <c r="R411" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S411" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T411" s="2" t="inlineStr">
@@ -39947,27 +39947,27 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>6990756033447e00137abb03</t>
+          <t>666e8a3cf52ecb0013f648c2</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>sujit1661</t>
+          <t>pravinkhetan</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>sujit1661</t>
+          <t>pravinkhetan</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>sujitgarnayak99@gmail.com</t>
+          <t>pravinkhetan@iplaneducation.com</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>7325876135</t>
+          <t>9999616222</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -39981,89 +39981,89 @@
         </is>
       </c>
       <c r="H412" s="2" t="n">
-        <v>1031</v>
+        <v>1057</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>4124</v>
+        <v>3171</v>
       </c>
       <c r="J412" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>6904dfd487ea0200137ccc5b</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6904dfd487ea0200137ccc5b</t>
-        </is>
-      </c>
-      <c r="M412" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N412" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M412" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O412" s="2" t="inlineStr">
         <is>
-          <t>Not Verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="P412" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INH000019521</t>
         </is>
       </c>
       <c r="Q412" s="2" t="inlineStr">
         <is>
-          <t>Manual Review Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28, 2026-08-29</t>
         </is>
       </c>
       <c r="S412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>64e5ae617f68ef001ea74131</t>
+          <t>6990756033447e00137abb03</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>sujit1661</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>sujit1661</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81@gmail.com</t>
+          <t>sujitgarnayak99@gmail.com</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>9879558198</t>
+          <t>7325876135</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
@@ -40077,60 +40077,156 @@
         </is>
       </c>
       <c r="H413" s="2" t="n">
-        <v>1001</v>
+        <v>1031</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>4004</v>
+        <v>4124</v>
       </c>
       <c r="J413" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
         <is>
+          <t>6904dfd487ea0200137ccc5b</t>
+        </is>
+      </c>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/6904dfd487ea0200137ccc5b</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N413" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>Manual Review Required</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27, 2026-08-28</t>
+        </is>
+      </c>
+      <c r="S413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="T413" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>64e5ae617f68ef001ea74131</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81@gmail.com</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>9879558198</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="I414" s="2" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J414" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K414" s="2" t="inlineStr">
+        <is>
           <t>66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
-      <c r="L413" s="2" t="inlineStr">
+      <c r="L414" s="2" t="inlineStr">
         <is>
           <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
-      <c r="M413" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N413" s="4" t="inlineStr">
+      <c r="M414" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N414" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O413" s="2" t="inlineStr">
+      <c r="O414" s="2" t="inlineStr">
         <is>
           <t>Not Verified</t>
         </is>
       </c>
-      <c r="P413" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q413" s="2" t="inlineStr">
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
         <is>
           <t>Manual Review Required</t>
         </is>
       </c>
-      <c r="R413" s="2" t="inlineStr">
+      <c r="R414" s="2" t="inlineStr">
         <is>
           <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
-      <c r="S413" s="2" t="inlineStr">
+      <c r="S414" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="T413" s="2" t="inlineStr">
+      <c r="T414" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T414"/>
+  <dimension ref="A1:T416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
     <col width="27" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="37" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
   </cols>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3397019</v>
+        <v>3495447</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1281945</v>
+        <v>1675080</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>599677</v>
+        <v>740988</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>874609</v>
+        <v>885132</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>463739</v>
+        <v>492005</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>502133</v>
+        <v>548756</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>174678</v>
+        <v>262017</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>528569</v>
+        <v>564412</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>430698</v>
+        <v>454893</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>320314</v>
+        <v>332432</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>250706</v>
+        <v>253886</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>363967</v>
+        <v>367886</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>259426</v>
+        <v>311128</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>270956</v>
+        <v>297160</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>328832</v>
+        <v>375808</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3408,10 +3408,10 @@
         <v>43416</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>130248</v>
+        <v>173664</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>147342</v>
+        <v>188612</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>133251</v>
+        <v>172444</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>262855</v>
+        <v>299028</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>178027</v>
+        <v>188272</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>235100</v>
+        <v>245840</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>156927</v>
+        <v>165152</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>183824</v>
+        <v>202212</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>175462</v>
+        <v>191412</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>173161</v>
+        <v>201648</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>137184</v>
+        <v>159153</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>113114</v>
+        <v>140408</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>178361</v>
+        <v>197019</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>165001</v>
+        <v>184796</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>91348</v>
+        <v>116989</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>121558</v>
+        <v>128584</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>131938</v>
+        <v>155556</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>102071</v>
+        <v>105364</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>121084</v>
+        <v>131592</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>153454</v>
+        <v>156400</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>108592</v>
+        <v>129884</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7632,10 +7632,10 @@
         <v>19716</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>59148</v>
+        <v>78864</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7728,10 +7728,10 @@
         <v>19651</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>58953</v>
+        <v>78604</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>136696</v>
+        <v>156224</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>132700</v>
+        <v>151932</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>121901</v>
+        <v>126510</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>111209</v>
+        <v>130284</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8592,10 +8592,10 @@
         <v>18146</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>54438</v>
+        <v>72584</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8880,10 +8880,10 @@
         <v>17393</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>52179</v>
+        <v>69572</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>85131</v>
+        <v>90436</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9072,10 +9072,10 @@
         <v>16598</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>49794</v>
+        <v>66392</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9264,10 +9264,10 @@
         <v>16531</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>49593</v>
+        <v>66124</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>90263</v>
+        <v>98472</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>80916</v>
+        <v>86180</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9552,10 +9552,10 @@
         <v>16245</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>48735</v>
+        <v>64980</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S95" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>79068</v>
+        <v>83948</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S96" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9744,10 +9744,10 @@
         <v>16043</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>48129</v>
+        <v>64172</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>83286</v>
+        <v>90160</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="R100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S100" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>71979</v>
+        <v>75272</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="R101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S101" s="2" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>74619</v>
+        <v>79512</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10512,10 +10512,10 @@
         <v>14667</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>44001</v>
+        <v>58668</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>89728</v>
+        <v>104332</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>85875</v>
+        <v>95096</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>89761</v>
+        <v>104148</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>65891</v>
+        <v>80044</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11376,10 +11376,10 @@
         <v>14114</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>42342</v>
+        <v>56456</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>69614</v>
+        <v>74128</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>103594</v>
+        <v>114887</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11760,10 +11760,10 @@
         <v>13696</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>42035</v>
+        <v>46916</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11856,10 +11856,10 @@
         <v>13666</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>52710</v>
+        <v>66376</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>87453</v>
+        <v>99024</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>67390</v>
+        <v>80176</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12816,10 +12816,10 @@
         <v>12204</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>36612</v>
+        <v>48816</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12912,10 +12912,10 @@
         <v>12156</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46228</v>
+        <v>58384</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>72929</v>
+        <v>84692</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13584,10 +13584,10 @@
         <v>11698</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>35094</v>
+        <v>46792</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13776,10 +13776,10 @@
         <v>11521</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>34563</v>
+        <v>46084</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="R139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S139" s="2" t="inlineStr">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13872,10 +13872,10 @@
         <v>11358</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>34074</v>
+        <v>45432</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="R140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S140" s="2" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>59961</v>
+        <v>65756</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S142" s="2" t="inlineStr">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>59472</v>
+        <v>70092</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S143" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14352,10 +14352,10 @@
         <v>10573</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>31719</v>
+        <v>42292</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S145" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>61356</v>
+        <v>71672</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14928,10 +14928,10 @@
         <v>10127</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>40789</v>
+        <v>50916</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S151" s="2" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>48730</v>
+        <v>51552</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S152" s="2" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="T152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>45112</v>
+        <v>47554</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15312,10 +15312,10 @@
         <v>9970</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>29910</v>
+        <v>39880</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="R155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S155" s="2" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="T155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>56866</v>
+        <v>62624</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="T156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>45196</v>
+        <v>55056</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>67760</v>
+        <v>77440</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15888,10 +15888,10 @@
         <v>9608</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>33414</v>
+        <v>44552</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="R161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S161" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>59435</v>
+        <v>63270</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16176,10 +16176,10 @@
         <v>9586</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>28758</v>
+        <v>38344</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S164" s="2" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16464,10 +16464,10 @@
         <v>9403</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>39993</v>
+        <v>49396</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="R167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S167" s="2" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16656,10 +16656,10 @@
         <v>9213</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>27639</v>
+        <v>36852</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="R169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S169" s="2" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>50613</v>
+        <v>59816</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="R170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>47532</v>
+        <v>51580</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
       </c>
       <c r="R172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S172" s="2" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17040,10 +17040,10 @@
         <v>8830</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>26490</v>
+        <v>35320</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="R173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S173" s="2" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>55516</v>
+        <v>62360</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="R176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S176" s="2" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="T176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17424,10 +17424,10 @@
         <v>8724</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>26172</v>
+        <v>34896</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="R177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S177" s="2" t="inlineStr">
@@ -17476,7 +17476,7 @@
       </c>
       <c r="T177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>43395</v>
+        <v>46288</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S178" s="2" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17712,10 +17712,10 @@
         <v>8643</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>35149</v>
+        <v>43792</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="R180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S180" s="2" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="T180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18000,10 +18000,10 @@
         <v>8399</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>37053</v>
+        <v>45452</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="R183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S183" s="2" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="T183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18192,10 +18192,10 @@
         <v>8254</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>35412</v>
+        <v>37808</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="R185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-30</t>
         </is>
       </c>
       <c r="S185" s="2" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="T185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>41653</v>
+        <v>44564</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="R186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S186" s="2" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18480,10 +18480,10 @@
         <v>8151</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>24453</v>
+        <v>32604</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="R188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S188" s="2" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>47870</v>
+        <v>53012</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S189" s="2" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18864,10 +18864,10 @@
         <v>7809</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>23427</v>
+        <v>31236</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="R192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S192" s="2" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="T192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>48068</v>
+        <v>53728</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="R193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S193" s="2" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="T193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>35850</v>
+        <v>43327</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="R201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S201" s="2" t="inlineStr">
@@ -19780,7 +19780,7 @@
       </c>
       <c r="T201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>50594</v>
+        <v>52378</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="R202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S202" s="2" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="T202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>47719</v>
+        <v>54916</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S203" s="2" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="T203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>48394</v>
+        <v>55380</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S205" s="2" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="T205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>47581</v>
+        <v>54472</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S207" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="T207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20688,10 +20688,10 @@
         <v>6752</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>20256</v>
+        <v>27008</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
       </c>
       <c r="R211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S211" s="2" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="T211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20784,10 +20784,10 @@
         <v>6704</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>20112</v>
+        <v>26816</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="R212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S212" s="2" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="T212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -21264,10 +21264,10 @@
         <v>6653</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>19959</v>
+        <v>26612</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S217" s="2" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="T217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -21552,10 +21552,10 @@
         <v>6568</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>27552</v>
+        <v>34120</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S220" s="2" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="T220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22032,10 +22032,10 @@
         <v>6402</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>19206</v>
+        <v>25608</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
       </c>
       <c r="R225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S225" s="2" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="T225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22128,10 +22128,10 @@
         <v>6357</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>32763</v>
+        <v>39120</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="R226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S226" s="2" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="T226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>41117</v>
+        <v>46412</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
       </c>
       <c r="R227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S227" s="2" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="T227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22320,10 +22320,10 @@
         <v>6308</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>18924</v>
+        <v>25232</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="R228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S228" s="2" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="T228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22416,10 +22416,10 @@
         <v>6270</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>18810</v>
+        <v>25080</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S229" s="2" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="T229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>38839</v>
+        <v>43560</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S231" s="2" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="T231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>38528</v>
+        <v>43468</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
       </c>
       <c r="R235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S235" s="2" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="T235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>38090</v>
+        <v>42932</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S236" s="2" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="T236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>32468</v>
+        <v>38148</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23514,7 +23514,7 @@
       </c>
       <c r="R240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S240" s="2" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="T240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23568,10 +23568,10 @@
         <v>5642</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>16926</v>
+        <v>22568</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
       </c>
       <c r="R241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S241" s="2" t="inlineStr">
@@ -23620,7 +23620,7 @@
       </c>
       <c r="T241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>33816</v>
+        <v>39452</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
       </c>
       <c r="R242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S242" s="2" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="T242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>33533</v>
+        <v>37248</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="R243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S243" s="2" t="inlineStr">
@@ -23812,7 +23812,7 @@
       </c>
       <c r="T243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -23856,10 +23856,10 @@
         <v>5533</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>16599</v>
+        <v>22132</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="R244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S244" s="2" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="T244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -24336,10 +24336,10 @@
         <v>5216</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>15648</v>
+        <v>20864</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
       </c>
       <c r="R249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S249" s="2" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="T249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>30290</v>
+        <v>33488</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
       </c>
       <c r="R251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S251" s="2" t="inlineStr">
@@ -24580,7 +24580,7 @@
       </c>
       <c r="T251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -24624,10 +24624,10 @@
         <v>5100</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>15300</v>
+        <v>20400</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="R252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S252" s="2" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -24816,10 +24816,10 @@
         <v>5039</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>15117</v>
+        <v>20156</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="R254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S254" s="2" t="inlineStr">
@@ -24868,7 +24868,7 @@
       </c>
       <c r="T254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -25392,10 +25392,10 @@
         <v>4853</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>14559</v>
+        <v>19412</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
       </c>
       <c r="R260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S260" s="2" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="T260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -26160,10 +26160,10 @@
         <v>4704</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>14112</v>
+        <v>18816</v>
       </c>
       <c r="J268" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="R268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S268" s="2" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -26352,10 +26352,10 @@
         <v>4697</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>14091</v>
+        <v>18788</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
       </c>
       <c r="R270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S270" s="2" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="T270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -26640,10 +26640,10 @@
         <v>4465</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>13395</v>
+        <v>17860</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
       </c>
       <c r="R273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S273" s="2" t="inlineStr">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="T273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>26855</v>
+        <v>29976</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="R274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S274" s="2" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -27024,10 +27024,10 @@
         <v>4305</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>20579</v>
+        <v>24884</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="R277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S277" s="2" t="inlineStr">
@@ -27076,7 +27076,7 @@
       </c>
       <c r="T277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -27120,10 +27120,10 @@
         <v>4294</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>12882</v>
+        <v>17176</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="R278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S278" s="2" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="T278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -27504,10 +27504,10 @@
         <v>3938</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>11814</v>
+        <v>15752</v>
       </c>
       <c r="J282" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
       </c>
       <c r="R282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S282" s="2" t="inlineStr">
@@ -27556,7 +27556,7 @@
       </c>
       <c r="T282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -27600,10 +27600,10 @@
         <v>3927</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>27253</v>
+        <v>31180</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
       </c>
       <c r="R283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S283" s="2" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="T283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -27696,10 +27696,10 @@
         <v>3919</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>11757</v>
+        <v>15676</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S284" s="2" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -28368,10 +28368,10 @@
         <v>3763</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>11289</v>
+        <v>15052</v>
       </c>
       <c r="J291" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S291" s="2" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>27449</v>
+        <v>30927</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
       </c>
       <c r="R298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S298" s="2" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -29616,10 +29616,10 @@
         <v>3355</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>10065</v>
+        <v>13420</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="R304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S304" s="2" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -29808,10 +29808,10 @@
         <v>3334</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>10002</v>
+        <v>13336</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
       </c>
       <c r="R306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S306" s="2" t="inlineStr">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="T306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -29904,10 +29904,10 @@
         <v>3331</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>15841</v>
+        <v>19172</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
       </c>
       <c r="R307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S307" s="2" t="inlineStr">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="T307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30000,10 +30000,10 @@
         <v>3321</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>23241</v>
+        <v>26560</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="R308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S308" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30192,10 +30192,10 @@
         <v>3198</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>22010</v>
+        <v>25208</v>
       </c>
       <c r="J310" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
       </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S310" s="2" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30384,10 +30384,10 @@
         <v>3154</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>20965</v>
+        <v>23748</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S312" s="2" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30576,10 +30576,10 @@
         <v>3101</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>20571</v>
+        <v>23672</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="R314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S314" s="2" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30864,10 +30864,10 @@
         <v>2946</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>8838</v>
+        <v>11784</v>
       </c>
       <c r="J317" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K317" s="2" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="R317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S317" s="2" t="inlineStr">
@@ -30916,7 +30916,7 @@
       </c>
       <c r="T317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -30960,10 +30960,10 @@
         <v>2946</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>8838</v>
+        <v>11784</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
       </c>
       <c r="R318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S318" s="2" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="T318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -31056,10 +31056,10 @@
         <v>2945</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>8835</v>
+        <v>11780</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
       </c>
       <c r="R319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S319" s="2" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="T319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -31152,10 +31152,10 @@
         <v>2942</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>8826</v>
+        <v>11768</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="R320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S320" s="2" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -31440,10 +31440,10 @@
         <v>2911</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>20377</v>
+        <v>23288</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="R323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S323" s="2" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="T323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -32208,10 +32208,10 @@
         <v>2823</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>8469</v>
+        <v>11292</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S331" s="2" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="T331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -32688,10 +32688,10 @@
         <v>2796</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>8388</v>
+        <v>11184</v>
       </c>
       <c r="J336" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
       </c>
       <c r="R336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S336" s="2" t="inlineStr">
@@ -32740,7 +32740,7 @@
       </c>
       <c r="T336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -32784,10 +32784,10 @@
         <v>2767</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>8301</v>
+        <v>11068</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
       </c>
       <c r="R337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S337" s="2" t="inlineStr">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="T337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -32976,10 +32976,10 @@
         <v>2730</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>13450</v>
+        <v>15980</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="R339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S339" s="2" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="T339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -33168,10 +33168,10 @@
         <v>2700</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>8100</v>
+        <v>10800</v>
       </c>
       <c r="J341" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K341" s="2" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="R341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S341" s="2" t="inlineStr">
@@ -33220,7 +33220,7 @@
       </c>
       <c r="T341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -33264,10 +33264,10 @@
         <v>2699</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>8097</v>
+        <v>10796</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
       </c>
       <c r="R342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S342" s="2" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="T342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -33552,10 +33552,10 @@
         <v>2666</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>13314</v>
+        <v>15980</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
       </c>
       <c r="R345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S345" s="2" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="T345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -33648,10 +33648,10 @@
         <v>2635</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>7905</v>
+        <v>10540</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
       </c>
       <c r="R346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S346" s="2" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="T346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -33840,10 +33840,10 @@
         <v>2520</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>7560</v>
+        <v>10080</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
       </c>
       <c r="R348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S348" s="2" t="inlineStr">
@@ -33892,7 +33892,7 @@
       </c>
       <c r="T348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -34416,10 +34416,10 @@
         <v>2411</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>2411</v>
+        <v>4822</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34458,17 +34458,17 @@
       </c>
       <c r="R354" s="2" t="inlineStr">
         <is>
+          <t>2026-08-28, 2026-08-30</t>
+        </is>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="S354" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="T354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -34859,27 +34859,27 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>65f033d90c88f40013c186fb</t>
+          <t>67d837e1b44d25001392f4dc</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>isftraders</t>
+          <t>youse</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>isftraders</t>
+          <t>youse</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>tradingmvs.007@gmail.com</t>
+          <t>cozyidecor@gmail.com</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>9390159995</t>
+          <t>7012189534</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
@@ -34893,22 +34893,22 @@
         </is>
       </c>
       <c r="H359" s="2" t="n">
-        <v>2317</v>
+        <v>2328</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>9268</v>
+        <v>2328</v>
       </c>
       <c r="J359" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K359" s="2" t="inlineStr">
         <is>
-          <t>662bbbdb156db68c4ed1d2e1</t>
+          <t>69fc9eb01b03b90013541bc6</t>
         </is>
       </c>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/662bbbdb156db68c4ed1d2e1</t>
+          <t>https://superprofile.bio/vig/69fc9eb01b03b90013541bc6</t>
         </is>
       </c>
       <c r="M359" s="2" t="inlineStr">
@@ -34938,44 +34938,44 @@
       </c>
       <c r="R359" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="S359" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T359" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>6360eaa132e4cd003667b28b</t>
+          <t>65f033d90c88f40013c186fb</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>ahtrends</t>
+          <t>isftraders</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>ahtrends</t>
+          <t>isftraders</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>afjalhussainsaudi@gmail.com</t>
+          <t>tradingmvs.007@gmail.com</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>9864714356</t>
+          <t>9390159995</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr">
@@ -34989,22 +34989,22 @@
         </is>
       </c>
       <c r="H360" s="2" t="n">
-        <v>2287</v>
+        <v>2317</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>9148</v>
+        <v>9268</v>
       </c>
       <c r="J360" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
-          <t>6519c635535371001d421f8d</t>
+          <t>662bbbdb156db68c4ed1d2e1</t>
         </is>
       </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6519c635535371001d421f8d</t>
+          <t>https://superprofile.bio/vig/662bbbdb156db68c4ed1d2e1</t>
         </is>
       </c>
       <c r="M360" s="2" t="inlineStr">
@@ -35051,27 +35051,27 @@
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>66b0a52105f9600013e59686</t>
+          <t>6360eaa132e4cd003667b28b</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>swingwithdip</t>
+          <t>ahtrends</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>swingwithdip</t>
+          <t>ahtrends</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>patildipak2106@gmail.com</t>
+          <t>afjalhussainsaudi@gmail.com</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>9545849301</t>
+          <t>9864714356</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr">
@@ -35085,22 +35085,22 @@
         </is>
       </c>
       <c r="H361" s="2" t="n">
-        <v>2256</v>
+        <v>2287</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>9024</v>
+        <v>9148</v>
       </c>
       <c r="J361" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
-          <t>6a22b9a8c0c8d2001388c89e</t>
+          <t>6519c635535371001d421f8d</t>
         </is>
       </c>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a22b9a8c0c8d2001388c89e</t>
+          <t>https://superprofile.bio/vig/6519c635535371001d421f8d</t>
         </is>
       </c>
       <c r="M361" s="2" t="inlineStr">
@@ -35147,27 +35147,27 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>6867fda9d6f2420013da1953</t>
+          <t>66b0a52105f9600013e59686</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>anils007</t>
+          <t>swingwithdip</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>anils007</t>
+          <t>swingwithdip</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>sangwan007anil@gmail.com</t>
+          <t>patildipak2106@gmail.com</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>9220918007</t>
+          <t>9545849301</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
@@ -35181,22 +35181,22 @@
         </is>
       </c>
       <c r="H362" s="2" t="n">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>2250</v>
+        <v>9024</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
-          <t>69d79e92063b150013da4bc7</t>
+          <t>6a22b9a8c0c8d2001388c89e</t>
         </is>
       </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d79e92063b150013da4bc7</t>
+          <t>https://superprofile.bio/vig/6a22b9a8c0c8d2001388c89e</t>
         </is>
       </c>
       <c r="M362" s="2" t="inlineStr">
@@ -35226,12 +35226,12 @@
       </c>
       <c r="R362" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S362" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T362" s="2" t="inlineStr">
@@ -35243,27 +35243,27 @@
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>69cf57311a016000135458b0</t>
+          <t>6867fda9d6f2420013da1953</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Option7414</t>
+          <t>anils007</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Option7414</t>
+          <t>anils007</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>sureshranarana123567@gmail.com</t>
+          <t>sangwan007anil@gmail.com</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>9348919258</t>
+          <t>9220918007</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
@@ -35277,22 +35277,22 @@
         </is>
       </c>
       <c r="H363" s="2" t="n">
-        <v>2161</v>
+        <v>2250</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>8644</v>
+        <v>4500</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
-          <t>69cf5f42ede04d0013ac8aa0</t>
+          <t>69d79e92063b150013da4bc7</t>
         </is>
       </c>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69cf5f42ede04d0013ac8aa0</t>
+          <t>https://superprofile.bio/vig/69d79e92063b150013da4bc7</t>
         </is>
       </c>
       <c r="M363" s="2" t="inlineStr">
@@ -35322,44 +35322,44 @@
       </c>
       <c r="R363" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28, 2026-08-30</t>
         </is>
       </c>
       <c r="S363" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T363" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>688b56333cf8720013772d86</t>
+          <t>6550fb1348d70d0a6565e5d3</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>httpstme92k0adeytzxkymm1</t>
+          <t>vibhor-aw</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>httpstme92k0adeytzxkymm1</t>
+          <t>vibhor-aw</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>timetotrade335@gmail.com</t>
+          <t>vibhor.tomar@gmail.com</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>8758202353</t>
+          <t>9986680598</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -35373,22 +35373,22 @@
         </is>
       </c>
       <c r="H364" s="2" t="n">
-        <v>2157</v>
+        <v>2249</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>8628</v>
+        <v>2249</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
-          <t>68b6a53529fbc0001351c1cb</t>
+          <t>69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68b6a53529fbc0001351c1cb</t>
+          <t>https://superprofile.bio/vig/69db7be277163000147b374b</t>
         </is>
       </c>
       <c r="M364" s="2" t="inlineStr">
@@ -35418,44 +35418,44 @@
       </c>
       <c r="R364" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="S364" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T364" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>6798f85f9c782900139f3bb6</t>
+          <t>69cf57311a016000135458b0</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>finostocks</t>
+          <t>Option7414</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>finostocks</t>
+          <t>Option7414</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>BUSINESS.FINOMEDIA@GMAIL.COM</t>
+          <t>sureshranarana123567@gmail.com</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>8595499642</t>
+          <t>9348919258</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
@@ -35469,22 +35469,22 @@
         </is>
       </c>
       <c r="H365" s="2" t="n">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>8624</v>
+        <v>8644</v>
       </c>
       <c r="J365" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
-          <t>6841acade1ef5a0013eb5faa</t>
+          <t>69cf5f42ede04d0013ac8aa0</t>
         </is>
       </c>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6841acade1ef5a0013eb5faa</t>
+          <t>https://superprofile.bio/vig/69cf5f42ede04d0013ac8aa0</t>
         </is>
       </c>
       <c r="M365" s="2" t="inlineStr">
@@ -35531,27 +35531,27 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>64fb0ee375d3bf001ea52867</t>
+          <t>688b56333cf8720013772d86</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Dhruvtuli</t>
+          <t>httpstme92k0adeytzxkymm1</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Dhruvtuli</t>
+          <t>httpstme92k0adeytzxkymm1</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Dhruvtuli@gmail.com</t>
+          <t>timetotrade335@gmail.com</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>9971844298</t>
+          <t>8758202353</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -35565,89 +35565,89 @@
         </is>
       </c>
       <c r="H366" s="2" t="n">
-        <v>2147</v>
+        <v>2157</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>4294</v>
+        <v>8628</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>68b6a53529fbc0001351c1cb</t>
         </is>
       </c>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M366" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N366" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>https://superprofile.bio/vig/68b6a53529fbc0001351c1cb</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N366" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O366" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Not Verified</t>
         </is>
       </c>
       <c r="P366" s="2" t="inlineStr">
         <is>
-          <t>INH000014155</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q366" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Manual Review Required</t>
         </is>
       </c>
       <c r="R366" s="2" t="inlineStr">
         <is>
+          <t>2026-08-27, 2026-08-28</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="S366" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
       <c r="T366" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>6329c62b5a5d614df43dd7ab</t>
+          <t>6798f85f9c782900139f3bb6</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Premiummembership1</t>
+          <t>finostocks</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Premiummembership1</t>
+          <t>finostocks</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>sonukumar1996sonum@gmail.com</t>
+          <t>BUSINESS.FINOMEDIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>9982518948</t>
+          <t>8595499642</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
@@ -35661,22 +35661,22 @@
         </is>
       </c>
       <c r="H367" s="2" t="n">
-        <v>2121</v>
+        <v>2156</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>8484</v>
+        <v>8624</v>
       </c>
       <c r="J367" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
-          <t>65a527caafc66b001e94f528</t>
+          <t>6841acade1ef5a0013eb5faa</t>
         </is>
       </c>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65a527caafc66b001e94f528</t>
+          <t>https://superprofile.bio/vig/6841acade1ef5a0013eb5faa</t>
         </is>
       </c>
       <c r="M367" s="2" t="inlineStr">
@@ -35723,27 +35723,27 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>6a53897d6a98bd00149d8cb1</t>
+          <t>64fb0ee375d3bf001ea52867</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>merapariwar</t>
+          <t>Dhruvtuli</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>merapariwar</t>
+          <t>Dhruvtuli</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>amanchaudhary1424@gmail.com</t>
+          <t>Dhruvtuli@gmail.com</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>8869877067</t>
+          <t>9971844298</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
@@ -35757,52 +35757,52 @@
         </is>
       </c>
       <c r="H368" s="2" t="n">
-        <v>2116</v>
+        <v>2147</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>8464</v>
+        <v>4294</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
-          <t>6a5395c2602e000013831035</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a5395c2602e000013831035</t>
-        </is>
-      </c>
-      <c r="M368" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N368" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M368" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O368" s="2" t="inlineStr">
         <is>
-          <t>Not Verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="P368" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INH000014155</t>
         </is>
       </c>
       <c r="Q368" s="2" t="inlineStr">
         <is>
-          <t>Manual Review Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R368" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S368" s="2" t="inlineStr">
@@ -35812,34 +35812,34 @@
       </c>
       <c r="T368" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>64639ac36088070020344fae</t>
+          <t>6329c62b5a5d614df43dd7ab</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>fxtraderabhiii</t>
+          <t>Premiummembership1</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>fxtraderabhiii</t>
+          <t>Premiummembership1</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>abhishekdse21@gmail.com</t>
+          <t>sonukumar1996sonum@gmail.com</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>9067769136</t>
+          <t>9982518948</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
@@ -35853,22 +35853,22 @@
         </is>
       </c>
       <c r="H369" s="2" t="n">
-        <v>2050</v>
+        <v>2121</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>8200</v>
+        <v>8484</v>
       </c>
       <c r="J369" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K369" s="2" t="inlineStr">
         <is>
-          <t>67a9a286aceb240013a51341</t>
+          <t>65a527caafc66b001e94f528</t>
         </is>
       </c>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/67a9a286aceb240013a51341</t>
+          <t>https://superprofile.bio/vig/65a527caafc66b001e94f528</t>
         </is>
       </c>
       <c r="M369" s="2" t="inlineStr">
@@ -35915,27 +35915,27 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>653aa2aed87cd0001e6f4b77</t>
+          <t>6a53897d6a98bd00149d8cb1</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>SMTEDUCATION</t>
+          <t>merapariwar</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>SMTEDUCATION</t>
+          <t>merapariwar</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Nagaichsandeep088@gmail.com</t>
+          <t>amanchaudhary1424@gmail.com</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>7860426229</t>
+          <t>8869877067</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -35949,22 +35949,22 @@
         </is>
       </c>
       <c r="H370" s="2" t="n">
-        <v>2025</v>
+        <v>2116</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>8100</v>
+        <v>8464</v>
       </c>
       <c r="J370" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K370" s="2" t="inlineStr">
         <is>
-          <t>653b62f0e24744a9699b63c6</t>
+          <t>6a5395c2602e000013831035</t>
         </is>
       </c>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/653b62f0e24744a9699b63c6</t>
+          <t>https://superprofile.bio/vig/6a5395c2602e000013831035</t>
         </is>
       </c>
       <c r="M370" s="2" t="inlineStr">
@@ -36011,27 +36011,27 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>67f011fe828388001343c7a1</t>
+          <t>64639ac36088070020344fae</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>batchxpert</t>
+          <t>fxtraderabhiii</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>batchxpert</t>
+          <t>fxtraderabhiii</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>deepnarayan217@gmail.com</t>
+          <t>abhishekdse21@gmail.com</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>8840363374</t>
+          <t>9067769136</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
@@ -36045,22 +36045,22 @@
         </is>
       </c>
       <c r="H371" s="2" t="n">
-        <v>1979</v>
+        <v>2050</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>7916</v>
+        <v>8200</v>
       </c>
       <c r="J371" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
-          <t>69d7025ab02d380013a314eb</t>
+          <t>67a9a286aceb240013a51341</t>
         </is>
       </c>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69d7025ab02d380013a314eb</t>
+          <t>https://superprofile.bio/vig/67a9a286aceb240013a51341</t>
         </is>
       </c>
       <c r="M371" s="2" t="inlineStr">
@@ -36107,27 +36107,27 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>6252e1d8456e9d46fde5ea47</t>
+          <t>653aa2aed87cd0001e6f4b77</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>sog</t>
+          <t>SMTEDUCATION</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>sog</t>
+          <t>SMTEDUCATION</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>kumarpankajprasad2031@gmail.com</t>
+          <t>Nagaichsandeep088@gmail.com</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>9835853287</t>
+          <t>7860426229</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr">
@@ -36141,22 +36141,22 @@
         </is>
       </c>
       <c r="H372" s="2" t="n">
-        <v>1975</v>
+        <v>2025</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>7900</v>
+        <v>8100</v>
       </c>
       <c r="J372" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
-          <t>6478b0327a245400202caed4</t>
+          <t>653b62f0e24744a9699b63c6</t>
         </is>
       </c>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6478b0327a245400202caed4</t>
+          <t>https://superprofile.bio/vig/653b62f0e24744a9699b63c6</t>
         </is>
       </c>
       <c r="M372" s="2" t="inlineStr">
@@ -36203,27 +36203,27 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>68f5e1cdf03b9000131c0fc2</t>
+          <t>67f011fe828388001343c7a1</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>dampro4</t>
+          <t>batchxpert</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>dampro4</t>
+          <t>batchxpert</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>damu.tanishq@gmail.com</t>
+          <t>deepnarayan217@gmail.com</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>9789853922</t>
+          <t>8840363374</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr">
@@ -36237,22 +36237,22 @@
         </is>
       </c>
       <c r="H373" s="2" t="n">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>7888</v>
+        <v>7916</v>
       </c>
       <c r="J373" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
-          <t>6a1fd35f62b0ef0013c02680</t>
+          <t>69d7025ab02d380013a314eb</t>
         </is>
       </c>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a1fd35f62b0ef0013c02680</t>
+          <t>https://superprofile.bio/vig/69d7025ab02d380013a314eb</t>
         </is>
       </c>
       <c r="M373" s="2" t="inlineStr">
@@ -36299,27 +36299,27 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>6954db9e53660300131cc9bc</t>
+          <t>6252e1d8456e9d46fde5ea47</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>PAWANDEEP6799</t>
+          <t>sog</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>PAWANDEEP6799</t>
+          <t>sog</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>pm17pawandeeps@iimidr.ac.in</t>
+          <t>kumarpankajprasad2031@gmail.com</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>8225000076</t>
+          <t>9835853287</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
@@ -36333,47 +36333,47 @@
         </is>
       </c>
       <c r="H374" s="2" t="n">
-        <v>1968</v>
+        <v>1975</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>9840</v>
+        <v>7900</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>6478b0327a245400202caed4</t>
         </is>
       </c>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M374" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N374" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>https://superprofile.bio/vig/6478b0327a245400202caed4</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N374" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O374" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Not Verified</t>
         </is>
       </c>
       <c r="P374" s="2" t="inlineStr">
         <is>
-          <t>INH000023904</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q374" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Manual Review Required</t>
         </is>
       </c>
       <c r="R374" s="2" t="inlineStr">
@@ -36395,27 +36395,27 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>65d57aff5bdff5001412cd90</t>
+          <t>68f5e1cdf03b9000131c0fc2</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>finpranjal</t>
+          <t>dampro4</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>finpranjal</t>
+          <t>dampro4</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>rajan.pdy7@gmail.com</t>
+          <t>damu.tanishq@gmail.com</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>9140134121</t>
+          <t>9789853922</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
@@ -36429,22 +36429,22 @@
         </is>
       </c>
       <c r="H375" s="2" t="n">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>7856</v>
+        <v>7888</v>
       </c>
       <c r="J375" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
-          <t>69b6b0c5b8fa0b0014df6f9a</t>
+          <t>6a1fd35f62b0ef0013c02680</t>
         </is>
       </c>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69b6b0c5b8fa0b0014df6f9a</t>
+          <t>https://superprofile.bio/vig/6a1fd35f62b0ef0013c02680</t>
         </is>
       </c>
       <c r="M375" s="2" t="inlineStr">
@@ -36491,27 +36491,27 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>628dee579a6375439f68bb26</t>
+          <t>6954db9e53660300131cc9bc</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>smtpremiumservice</t>
+          <t>PAWANDEEP6799</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>smtpremiumservice</t>
+          <t>PAWANDEEP6799</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Memories12081994@gmail.com</t>
+          <t>pm17pawandeeps@iimidr.ac.in</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>8303297166</t>
+          <t>8225000076</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
@@ -36525,47 +36525,47 @@
         </is>
       </c>
       <c r="H376" s="2" t="n">
-        <v>1953</v>
+        <v>1968</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>7812</v>
+        <v>9840</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
-          <t>6308eb69bf868a04a3e8b047</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6308eb69bf868a04a3e8b047</t>
-        </is>
-      </c>
-      <c r="M376" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N376" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M376" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O376" s="2" t="inlineStr">
         <is>
-          <t>Not Verified</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="P376" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>INH000023904</t>
         </is>
       </c>
       <c r="Q376" s="2" t="inlineStr">
         <is>
-          <t>Manual Review Required</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="R376" s="2" t="inlineStr">
@@ -36587,27 +36587,27 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>65473a7f3fad8004611cb71e</t>
+          <t>65d57aff5bdff5001412cd90</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>mahesh3009</t>
+          <t>finpranjal</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>mahesh3009</t>
+          <t>finpranjal</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Wadhwahosiery@gmail.com</t>
+          <t>rajan.pdy7@gmail.com</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>9213297755</t>
+          <t>9140134121</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
@@ -36621,22 +36621,22 @@
         </is>
       </c>
       <c r="H377" s="2" t="n">
-        <v>1953</v>
+        <v>1964</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>7812</v>
+        <v>7856</v>
       </c>
       <c r="J377" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
         <is>
-          <t>6620bca29f96c2435e02b516</t>
+          <t>69b6b0c5b8fa0b0014df6f9a</t>
         </is>
       </c>
       <c r="L377" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6620bca29f96c2435e02b516</t>
+          <t>https://superprofile.bio/vig/69b6b0c5b8fa0b0014df6f9a</t>
         </is>
       </c>
       <c r="M377" s="2" t="inlineStr">
@@ -36683,27 +36683,27 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>665e11941fa95b00139155d6</t>
+          <t>628dee579a6375439f68bb26</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>breakoutsignals1</t>
+          <t>smtpremiumservice</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>breakoutsignals1</t>
+          <t>smtpremiumservice</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>ingeniousgcm5@gmail.com</t>
+          <t>Memories12081994@gmail.com</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>8668376331</t>
+          <t>8303297166</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr">
@@ -36720,19 +36720,19 @@
         <v>1953</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>1953</v>
+        <v>7812</v>
       </c>
       <c r="J378" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
-          <t>66c6259d2daa8f0013342767</t>
+          <t>6308eb69bf868a04a3e8b047</t>
         </is>
       </c>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66c6259d2daa8f0013342767</t>
+          <t>https://superprofile.bio/vig/6308eb69bf868a04a3e8b047</t>
         </is>
       </c>
       <c r="M378" s="2" t="inlineStr">
@@ -36762,44 +36762,44 @@
       </c>
       <c r="R378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>6a547a7c98b0560013013abd</t>
+          <t>65473a7f3fad8004611cb71e</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>user41081</t>
+          <t>mahesh3009</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>user41081</t>
+          <t>mahesh3009</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>vijaydarji667@gmail.com</t>
+          <t>Wadhwahosiery@gmail.com</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>9274267070</t>
+          <t>9213297755</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr">
@@ -36813,22 +36813,22 @@
         </is>
       </c>
       <c r="H379" s="2" t="n">
-        <v>1940</v>
+        <v>1953</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>7760</v>
+        <v>7812</v>
       </c>
       <c r="J379" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
-          <t>6a547ea798b0560013024205</t>
+          <t>6620bca29f96c2435e02b516</t>
         </is>
       </c>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a547ea798b0560013024205</t>
+          <t>https://superprofile.bio/vig/6620bca29f96c2435e02b516</t>
         </is>
       </c>
       <c r="M379" s="2" t="inlineStr">
@@ -36875,27 +36875,27 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>647561213cbb05001faef3d3</t>
+          <t>665e11941fa95b00139155d6</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>vksir1</t>
+          <t>breakoutsignals1</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>vksir1</t>
+          <t>breakoutsignals1</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>khandon.vk@gmail.com</t>
+          <t>ingeniousgcm5@gmail.com</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>8290092913</t>
+          <t>8668376331</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
@@ -36909,22 +36909,22 @@
         </is>
       </c>
       <c r="H380" s="2" t="n">
-        <v>1940</v>
+        <v>1953</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>7760</v>
+        <v>1953</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
-          <t>6475b04344677f001f08420d</t>
+          <t>66c6259d2daa8f0013342767</t>
         </is>
       </c>
       <c r="L380" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6475b04344677f001f08420d</t>
+          <t>https://superprofile.bio/vig/66c6259d2daa8f0013342767</t>
         </is>
       </c>
       <c r="M380" s="2" t="inlineStr">
@@ -36954,44 +36954,44 @@
       </c>
       <c r="R380" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S380" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="T380" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>65aa05f67bb5b6001d8288ed</t>
+          <t>6a547a7c98b0560013013abd</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>professor2026</t>
+          <t>user41081</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>professor2026</t>
+          <t>user41081</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>jannat709676@gmail.com</t>
+          <t>vijaydarji667@gmail.com</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>8849699811</t>
+          <t>9274267070</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
@@ -37008,19 +37008,19 @@
         <v>1940</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>1940</v>
+        <v>7760</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
-          <t>69ca617e3e3e170013e99a12</t>
+          <t>6a547ea798b0560013024205</t>
         </is>
       </c>
       <c r="L381" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69ca617e3e3e170013e99a12</t>
+          <t>https://superprofile.bio/vig/6a547ea798b0560013024205</t>
         </is>
       </c>
       <c r="M381" s="2" t="inlineStr">
@@ -37050,12 +37050,12 @@
       </c>
       <c r="R381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="T381" s="2" t="inlineStr">
@@ -37067,27 +37067,27 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>65c8c3e0e0e11f001e86446f</t>
+          <t>647561213cbb05001faef3d3</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>edgeadmin</t>
+          <t>vksir1</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>edgeadmin</t>
+          <t>vksir1</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>nimmii5151@gmail.com</t>
+          <t>khandon.vk@gmail.com</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>8085115151</t>
+          <t>8290092913</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
@@ -37101,22 +37101,22 @@
         </is>
       </c>
       <c r="H382" s="2" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>7752</v>
+        <v>7760</v>
       </c>
       <c r="J382" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
-          <t>66371b2d0b57770013e4942f</t>
+          <t>6475b04344677f001f08420d</t>
         </is>
       </c>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
+          <t>https://superprofile.bio/vig/6475b04344677f001f08420d</t>
         </is>
       </c>
       <c r="M382" s="2" t="inlineStr">
@@ -37163,27 +37163,27 @@
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>64bf7c27e98788001f3fa09d</t>
+          <t>65aa05f67bb5b6001d8288ed</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>chaudhary29</t>
+          <t>professor2026</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>chaudhary29</t>
+          <t>professor2026</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>mrgreenappleajay@gmail.com</t>
+          <t>jannat709676@gmail.com</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>9557922941</t>
+          <t>8849699811</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -37197,22 +37197,22 @@
         </is>
       </c>
       <c r="H383" s="2" t="n">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>7728</v>
+        <v>1940</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
-          <t>6620be84ec6aa900121eccc4</t>
+          <t>69ca617e3e3e170013e99a12</t>
         </is>
       </c>
       <c r="L383" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6620be84ec6aa900121eccc4</t>
+          <t>https://superprofile.bio/vig/69ca617e3e3e170013e99a12</t>
         </is>
       </c>
       <c r="M383" s="2" t="inlineStr">
@@ -37242,12 +37242,12 @@
       </c>
       <c r="R383" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="S383" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T383" s="2" t="inlineStr">
@@ -37259,27 +37259,27 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>64f7f2c441cc54001fbe7491</t>
+          <t>65c8c3e0e0e11f001e86446f</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>xtellar</t>
+          <t>edgeadmin</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>xtellar</t>
+          <t>edgeadmin</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>theartbraingokul@gmail.com</t>
+          <t>nimmii5151@gmail.com</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>8848757632</t>
+          <t>8085115151</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -37293,22 +37293,22 @@
         </is>
       </c>
       <c r="H384" s="2" t="n">
-        <v>1887</v>
+        <v>1938</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>7548</v>
+        <v>7752</v>
       </c>
       <c r="J384" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
-          <t>6a4773ece345050013f142db</t>
+          <t>66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
+          <t>https://superprofile.bio/vig/66371b2d0b57770013e4942f</t>
         </is>
       </c>
       <c r="M384" s="2" t="inlineStr">
@@ -37355,27 +37355,27 @@
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>6a07df7c7c5fcd00133a6e3b</t>
+          <t>64bf7c27e98788001f3fa09d</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>chaudhary29</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>aman565281</t>
+          <t>chaudhary29</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>experttrading874@gmail.com</t>
+          <t>mrgreenappleajay@gmail.com</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>6377727003</t>
+          <t>9557922941</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -37389,22 +37389,22 @@
         </is>
       </c>
       <c r="H385" s="2" t="n">
-        <v>1881</v>
+        <v>1932</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>7524</v>
+        <v>7728</v>
       </c>
       <c r="J385" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
-          <t>6a088c367c5fcd00135ca723</t>
+          <t>6620be84ec6aa900121eccc4</t>
         </is>
       </c>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
+          <t>https://superprofile.bio/vig/6620be84ec6aa900121eccc4</t>
         </is>
       </c>
       <c r="M385" s="2" t="inlineStr">
@@ -37451,27 +37451,27 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>6981d41125307400137323ec</t>
+          <t>64f7f2c441cc54001fbe7491</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Prakash9690</t>
+          <t>xtellar</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Prakash9690</t>
+          <t>xtellar</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>shreeshyam87756@gmail.com</t>
+          <t>theartbraingokul@gmail.com</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>6350429617</t>
+          <t>8848757632</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -37485,22 +37485,22 @@
         </is>
       </c>
       <c r="H386" s="2" t="n">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>7524</v>
+        <v>7548</v>
       </c>
       <c r="J386" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
-          <t>6981d57e21e30200125961df</t>
+          <t>6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6981d57e21e30200125961df</t>
+          <t>https://superprofile.bio/vig/6a4773ece345050013f142db</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr">
@@ -37547,27 +37547,27 @@
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>65c89053e0e11f001e822548</t>
+          <t>6a07df7c7c5fcd00133a6e3b</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>freshershunt</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>freshershunt</t>
+          <t>aman565281</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>freshershunt.in@gmail.com</t>
+          <t>experttrading874@gmail.com</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>9060803166</t>
+          <t>6377727003</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
@@ -37581,22 +37581,22 @@
         </is>
       </c>
       <c r="H387" s="2" t="n">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>7512</v>
+        <v>7524</v>
       </c>
       <c r="J387" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
-          <t>65f84c6876f3550013a2920c</t>
+          <t>6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
+          <t>https://superprofile.bio/vig/6a088c367c5fcd00135ca723</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
@@ -37643,27 +37643,27 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>627ca99791125d5ba8a34b41</t>
+          <t>6981d41125307400137323ec</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>mamoon</t>
+          <t>Prakash9690</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>mamoon</t>
+          <t>Prakash9690</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Mamoon4sindia@gmail.com</t>
+          <t>shreeshyam87756@gmail.com</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>7903542731</t>
+          <t>6350429617</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
@@ -37677,22 +37677,22 @@
         </is>
       </c>
       <c r="H388" s="2" t="n">
-        <v>1832</v>
+        <v>1881</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>7328</v>
+        <v>7524</v>
       </c>
       <c r="J388" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
-          <t>66eaae246c05200013bace75</t>
+          <t>6981d57e21e30200125961df</t>
         </is>
       </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
+          <t>https://superprofile.bio/vig/6981d57e21e30200125961df</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr">
@@ -37739,27 +37739,27 @@
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>687f538e23947700130cd9cc</t>
+          <t>65c89053e0e11f001e822548</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>freshershunt</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>mastermind987</t>
+          <t>freshershunt</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>mastermindteam051@gmail.com</t>
+          <t>freshershunt.in@gmail.com</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>9936556941</t>
+          <t>9060803166</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
@@ -37773,22 +37773,22 @@
         </is>
       </c>
       <c r="H389" s="2" t="n">
-        <v>1740</v>
+        <v>1878</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>6960</v>
+        <v>7512</v>
       </c>
       <c r="J389" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K389" s="2" t="inlineStr">
         <is>
-          <t>697998f47fac9d0013f74dfe</t>
+          <t>65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="L389" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
+          <t>https://superprofile.bio/vig/65f84c6876f3550013a2920c</t>
         </is>
       </c>
       <c r="M389" s="2" t="inlineStr">
@@ -37835,27 +37835,27 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>676cf61fae833e001322e4d4</t>
+          <t>627ca99791125d5ba8a34b41</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>mamoon</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>httpstmeherozerocall40</t>
+          <t>mamoon</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>rahulstock11@gmail.com</t>
+          <t>Mamoon4sindia@gmail.com</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>8305763595</t>
+          <t>7903542731</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
@@ -37869,22 +37869,22 @@
         </is>
       </c>
       <c r="H390" s="2" t="n">
-        <v>1646</v>
+        <v>1832</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>6584</v>
+        <v>7328</v>
       </c>
       <c r="J390" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
-          <t>676d0ccf8e79b600130eb896</t>
+          <t>66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
+          <t>https://superprofile.bio/vig/66eaae246c05200013bace75</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr">
@@ -37931,27 +37931,27 @@
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>65e953798a133b0013814853</t>
+          <t>687f538e23947700130cd9cc</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>samirpradhan</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>samirpradhan</t>
+          <t>mastermind987</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>samirkumarpradhan9@gmail.com</t>
+          <t>mastermindteam051@gmail.com</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>9178074088</t>
+          <t>9936556941</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
@@ -37965,22 +37965,22 @@
         </is>
       </c>
       <c r="H391" s="2" t="n">
-        <v>1646</v>
+        <v>1740</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>6584</v>
+        <v>6960</v>
       </c>
       <c r="J391" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
         <is>
-          <t>65e9543e9451aa0012fe0644</t>
+          <t>697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="L391" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
+          <t>https://superprofile.bio/vig/697998f47fac9d0013f74dfe</t>
         </is>
       </c>
       <c r="M391" s="2" t="inlineStr">
@@ -38027,27 +38027,27 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>656f190c85e895001e492ba2</t>
+          <t>676cf61fae833e001322e4d4</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>mts3949</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>mts3949</t>
+          <t>httpstmeherozerocall40</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>shivaniprashant77@gmail.com</t>
+          <t>rahulstock11@gmail.com</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>9284394639</t>
+          <t>8305763595</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -38061,22 +38061,22 @@
         </is>
       </c>
       <c r="H392" s="2" t="n">
-        <v>1552</v>
+        <v>1646</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>6208</v>
+        <v>6584</v>
       </c>
       <c r="J392" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
-          <t>698f2450859ceb00130815a3</t>
+          <t>676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
+          <t>https://superprofile.bio/vig/676d0ccf8e79b600130eb896</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr">
@@ -38123,27 +38123,27 @@
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>646373ce6cbb8200207efe77</t>
+          <t>65e953798a133b0013814853</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>godfather01</t>
+          <t>samirpradhan</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>godfather01</t>
+          <t>samirpradhan</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>vikkysharma4032@gmail.com</t>
+          <t>samirkumarpradhan9@gmail.com</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>9839384032</t>
+          <t>9178074088</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
@@ -38157,22 +38157,22 @@
         </is>
       </c>
       <c r="H393" s="2" t="n">
-        <v>1552</v>
+        <v>1646</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>6208</v>
+        <v>6584</v>
       </c>
       <c r="J393" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
-          <t>68459b8cb2cccb0013dabf4c</t>
+          <t>65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
+          <t>https://superprofile.bio/vig/65e9543e9451aa0012fe0644</t>
         </is>
       </c>
       <c r="M393" s="2" t="inlineStr">
@@ -38219,27 +38219,27 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>645cb91fc8965700203aa836</t>
+          <t>656f190c85e895001e492ba2</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>kavyatrader</t>
+          <t>mts3949</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>kavyatrader</t>
+          <t>mts3949</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Singhabhishek59942@gmail.com</t>
+          <t>shivaniprashant77@gmail.com</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>8979006726</t>
+          <t>9284394639</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -38253,22 +38253,22 @@
         </is>
       </c>
       <c r="H394" s="2" t="n">
-        <v>1534</v>
+        <v>1552</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>6136</v>
+        <v>6208</v>
       </c>
       <c r="J394" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
-          <t>69dc9e4d81ef030013e77b80</t>
+          <t>698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
+          <t>https://superprofile.bio/vig/698f2450859ceb00130815a3</t>
         </is>
       </c>
       <c r="M394" s="2" t="inlineStr">
@@ -38315,27 +38315,27 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>6693e8299527ae0013ffcb9e</t>
+          <t>646373ce6cbb8200207efe77</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>bigbull2025</t>
+          <t>godfather01</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>bigbull2025</t>
+          <t>godfather01</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>bjisrk80@gmail.com</t>
+          <t>vikkysharma4032@gmail.com</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>7568977191</t>
+          <t>9839384032</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
@@ -38349,22 +38349,22 @@
         </is>
       </c>
       <c r="H395" s="2" t="n">
-        <v>1524</v>
+        <v>1552</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>6096</v>
+        <v>6208</v>
       </c>
       <c r="J395" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
-          <t>66ee6de8d79b930013987bd6</t>
+          <t>68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
+          <t>https://superprofile.bio/vig/68459b8cb2cccb0013dabf4c</t>
         </is>
       </c>
       <c r="M395" s="2" t="inlineStr">
@@ -38411,27 +38411,27 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>647b0a76df97e200208e3c33</t>
+          <t>645cb91fc8965700203aa836</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>ankitatfutureinvestor</t>
+          <t>kavyatrader</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>ankitatfutureinvestor</t>
+          <t>kavyatrader</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>digindia.aj@gmail.com</t>
+          <t>Singhabhishek59942@gmail.com</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>8240223323</t>
+          <t>8979006726</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
@@ -38445,22 +38445,22 @@
         </is>
       </c>
       <c r="H396" s="2" t="n">
-        <v>1476</v>
+        <v>1534</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>5904</v>
+        <v>6136</v>
       </c>
       <c r="J396" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
-          <t>6915b8fa9a5b350013bb71b8</t>
+          <t>69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6915b8fa9a5b350013bb71b8</t>
+          <t>https://superprofile.bio/vig/69dc9e4d81ef030013e77b80</t>
         </is>
       </c>
       <c r="M396" s="2" t="inlineStr">
@@ -38507,27 +38507,27 @@
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>62357fa202100543e97a25fa</t>
+          <t>6693e8299527ae0013ffcb9e</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>harshtrading27</t>
+          <t>bigbull2025</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>harshtrading27</t>
+          <t>bigbull2025</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>hskatkiya2001@gmail.com</t>
+          <t>bjisrk80@gmail.com</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>6356359759</t>
+          <t>7568977191</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
@@ -38541,22 +38541,22 @@
         </is>
       </c>
       <c r="H397" s="2" t="n">
-        <v>1465</v>
+        <v>1524</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>5860</v>
+        <v>6096</v>
       </c>
       <c r="J397" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
         <is>
-          <t>643f8dccf6caee0020703e83</t>
+          <t>66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="L397" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/643f8dccf6caee0020703e83</t>
+          <t>https://superprofile.bio/vig/66ee6de8d79b930013987bd6</t>
         </is>
       </c>
       <c r="M397" s="2" t="inlineStr">
@@ -38603,27 +38603,27 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>67c94e21f8f7120014c00900</t>
+          <t>647b0a76df97e200208e3c33</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>httpstme4xrkpkvzmi82mtzl</t>
+          <t>ankitatfutureinvestor</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>httpstme4xrkpkvzmi82mtzl</t>
+          <t>ankitatfutureinvestor</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>tradingwithvivek.87@gmail.com</t>
+          <t>digindia.aj@gmail.com</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>9106562524</t>
+          <t>8240223323</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
@@ -38637,22 +38637,22 @@
         </is>
       </c>
       <c r="H398" s="2" t="n">
-        <v>1457</v>
+        <v>1476</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>5828</v>
+        <v>5904</v>
       </c>
       <c r="J398" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
-          <t>6a7ac8e844ab5300132d194a</t>
+          <t>6915b8fa9a5b350013bb71b8</t>
         </is>
       </c>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
+          <t>https://superprofile.bio/vig/6915b8fa9a5b350013bb71b8</t>
         </is>
       </c>
       <c r="M398" s="2" t="inlineStr">
@@ -38699,27 +38699,27 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>69e89b0ed9ffde0013e31879</t>
+          <t>62357fa202100543e97a25fa</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>harshtrading27</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>riskytrader92</t>
+          <t>harshtrading27</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>nitindhandre42@gmail.com</t>
+          <t>hskatkiya2001@gmail.com</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>7977913010</t>
+          <t>6356359759</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -38733,22 +38733,22 @@
         </is>
       </c>
       <c r="H399" s="2" t="n">
-        <v>1428</v>
+        <v>1465</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>5712</v>
+        <v>5860</v>
       </c>
       <c r="J399" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
-          <t>6a787fec62ca790013c3fe57</t>
+          <t>643f8dccf6caee0020703e83</t>
         </is>
       </c>
       <c r="L399" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
+          <t>https://superprofile.bio/vig/643f8dccf6caee0020703e83</t>
         </is>
       </c>
       <c r="M399" s="2" t="inlineStr">
@@ -38795,27 +38795,27 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>6a131bb7d14a790012e11a6f</t>
+          <t>67c94e21f8f7120014c00900</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>httpstme4xrkpkvzmi82mtzl</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>gawkatrader</t>
+          <t>httpstme4xrkpkvzmi82mtzl</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>ffkatarka@gmail.com</t>
+          <t>tradingwithvivek.87@gmail.com</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>9101299533</t>
+          <t>9106562524</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -38829,22 +38829,22 @@
         </is>
       </c>
       <c r="H400" s="2" t="n">
-        <v>1412</v>
+        <v>1457</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>5648</v>
+        <v>5828</v>
       </c>
       <c r="J400" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
-          <t>6a6d9d5033211a001319c244</t>
+          <t>6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="L400" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
+          <t>https://superprofile.bio/vig/6a7ac8e844ab5300132d194a</t>
         </is>
       </c>
       <c r="M400" s="2" t="inlineStr">
@@ -38891,27 +38891,27 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>6986dbd1350e1a0014cdbba8</t>
+          <t>69e89b0ed9ffde0013e31879</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>skrankboost</t>
+          <t>riskytrader92</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>kumarshubham857208@gmail.com</t>
+          <t>nitindhandre42@gmail.com</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>9253166725</t>
+          <t>7977913010</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
@@ -38925,22 +38925,22 @@
         </is>
       </c>
       <c r="H401" s="2" t="n">
-        <v>1411</v>
+        <v>1428</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>5644</v>
+        <v>5712</v>
       </c>
       <c r="J401" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K401" s="2" t="inlineStr">
         <is>
-          <t>69a90448ce8bdc00125c31a5</t>
+          <t>6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
+          <t>https://superprofile.bio/vig/6a787fec62ca790013c3fe57</t>
         </is>
       </c>
       <c r="M401" s="2" t="inlineStr">
@@ -38987,27 +38987,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>67d06a60fac4900013f6e7c8</t>
+          <t>6a131bb7d14a790012e11a6f</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>gainyourselfofficial</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>gainyourselfofficial</t>
+          <t>gawkatrader</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>dp540503@gmail.com</t>
+          <t>ffkatarka@gmail.com</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>8897083372</t>
+          <t>9101299533</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
@@ -39021,22 +39021,22 @@
         </is>
       </c>
       <c r="H402" s="2" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>5644</v>
+        <v>5648</v>
       </c>
       <c r="J402" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K402" s="2" t="inlineStr">
         <is>
-          <t>6a4bdb749abd7300134a20f7</t>
+          <t>6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
+          <t>https://superprofile.bio/vig/6a6d9d5033211a001319c244</t>
         </is>
       </c>
       <c r="M402" s="2" t="inlineStr">
@@ -39083,27 +39083,27 @@
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>617fab8b6ffe000d0e7868a2</t>
+          <t>6986dbd1350e1a0014cdbba8</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>shorttermstockss</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>shorttermstockss</t>
+          <t>skrankboost</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>shahsanket1708@gmail.com</t>
+          <t>kumarshubham857208@gmail.com</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>8866831782</t>
+          <t>9253166725</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -39117,22 +39117,22 @@
         </is>
       </c>
       <c r="H403" s="2" t="n">
-        <v>1316</v>
+        <v>1411</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>5264</v>
+        <v>5644</v>
       </c>
       <c r="J403" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
-          <t>642560ad3b5510001f5c75de</t>
+          <t>69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/642560ad3b5510001f5c75de</t>
+          <t>https://superprofile.bio/vig/69a90448ce8bdc00125c31a5</t>
         </is>
       </c>
       <c r="M403" s="2" t="inlineStr">
@@ -39179,27 +39179,27 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>6862347467feb80013f6f503</t>
+          <t>67d06a60fac4900013f6e7c8</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Zero9733</t>
+          <t>gainyourselfofficial</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Zero9733</t>
+          <t>gainyourselfofficial</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>zeroheropremium9001@gmail.com</t>
+          <t>dp540503@gmail.com</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>9001130080</t>
+          <t>8897083372</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -39213,22 +39213,22 @@
         </is>
       </c>
       <c r="H404" s="2" t="n">
-        <v>1261</v>
+        <v>1411</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>5044</v>
+        <v>5644</v>
       </c>
       <c r="J404" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
-          <t>6866566ca42647001377eff6</t>
+          <t>6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6866566ca42647001377eff6</t>
+          <t>https://superprofile.bio/vig/6a4bdb749abd7300134a20f7</t>
         </is>
       </c>
       <c r="M404" s="2" t="inlineStr">
@@ -39275,27 +39275,27 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>68f4c2d100b7a10013e082d6</t>
+          <t>617fab8b6ffe000d0e7868a2</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare</t>
+          <t>shorttermstockss</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare</t>
+          <t>shorttermstockss</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>ishwarbhakare294@gmail.com</t>
+          <t>shahsanket1708@gmail.com</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>7385029673</t>
+          <t>8866831782</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
@@ -39309,22 +39309,22 @@
         </is>
       </c>
       <c r="H405" s="2" t="n">
-        <v>1222</v>
+        <v>1316</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>4888</v>
+        <v>5264</v>
       </c>
       <c r="J405" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
-          <t>6a7c0a37542b2500148af289</t>
+          <t>642560ad3b5510001f5c75de</t>
         </is>
       </c>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a7c0a37542b2500148af289</t>
+          <t>https://superprofile.bio/vig/642560ad3b5510001f5c75de</t>
         </is>
       </c>
       <c r="M405" s="2" t="inlineStr">
@@ -39371,27 +39371,27 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>6a2a3b18739da100136db6f1</t>
+          <t>6862347467feb80013f6f503</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>Zero9733</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>mr-perfectofficial</t>
+          <t>Zero9733</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>mr.perfect.official018@gmail.com</t>
+          <t>zeroheropremium9001@gmail.com</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>9116087897</t>
+          <t>9001130080</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -39405,22 +39405,22 @@
         </is>
       </c>
       <c r="H406" s="2" t="n">
-        <v>1220</v>
+        <v>1261</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>3660</v>
+        <v>5044</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
-          <t>6a3a9b9ec4f6700013489927</t>
+          <t>6866566ca42647001377eff6</t>
         </is>
       </c>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a3a9b9ec4f6700013489927</t>
+          <t>https://superprofile.bio/vig/6866566ca42647001377eff6</t>
         </is>
       </c>
       <c r="M406" s="2" t="inlineStr">
@@ -39450,44 +39450,44 @@
       </c>
       <c r="R406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S406" s="2" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="T406" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>69d8e18075a32f001382a054</t>
+          <t>68f4c2d100b7a10013e082d6</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>mirag69</t>
+          <t>ishwarbhakare</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>mirag69</t>
+          <t>ishwarbhakare</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>bhupendrakumar75698@gmail.com</t>
+          <t>ishwarbhakare294@gmail.com</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>9203710056</t>
+          <t>7385029673</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -39501,22 +39501,22 @@
         </is>
       </c>
       <c r="H407" s="2" t="n">
-        <v>1158</v>
+        <v>1222</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>4632</v>
+        <v>4888</v>
       </c>
       <c r="J407" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
-          <t>6a41f935be7a120013780d32</t>
+          <t>6a7c0a37542b2500148af289</t>
         </is>
       </c>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a41f935be7a120013780d32</t>
+          <t>https://superprofile.bio/vig/6a7c0a37542b2500148af289</t>
         </is>
       </c>
       <c r="M407" s="2" t="inlineStr">
@@ -39563,27 +39563,27 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>65132965f4d0b1001eba9b70</t>
+          <t>6a2a3b18739da100136db6f1</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>lbfcstockss</t>
+          <t>mr-perfectofficial</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>biswalfc@gmail.com</t>
+          <t>mr.perfect.official018@gmail.com</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>9658251426</t>
+          <t>9116087897</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -39597,22 +39597,22 @@
         </is>
       </c>
       <c r="H408" s="2" t="n">
-        <v>1134</v>
+        <v>1220</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>4536</v>
+        <v>4880</v>
       </c>
       <c r="J408" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
-          <t>6724fcbd76412b00139f3f43</t>
+          <t>6a3a9b9ec4f6700013489927</t>
         </is>
       </c>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
+          <t>https://superprofile.bio/vig/6a3a9b9ec4f6700013489927</t>
         </is>
       </c>
       <c r="M408" s="2" t="inlineStr">
@@ -39642,44 +39642,44 @@
       </c>
       <c r="R408" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
         </is>
       </c>
       <c r="S408" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="T408" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>695fc2d673169a001320fcf5</t>
+          <t>69d8e18075a32f001382a054</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>mirag69</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva</t>
+          <t>mirag69</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>shivamshiva7870@gmail.com</t>
+          <t>bhupendrakumar75698@gmail.com</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>9534598557</t>
+          <t>9203710056</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -39693,22 +39693,22 @@
         </is>
       </c>
       <c r="H409" s="2" t="n">
-        <v>1080</v>
+        <v>1158</v>
       </c>
       <c r="I409" s="2" t="n">
-        <v>4320</v>
+        <v>4632</v>
       </c>
       <c r="J409" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K409" s="2" t="inlineStr">
         <is>
-          <t>6961fea2c0dd9a00126d58b1</t>
+          <t>6a41f935be7a120013780d32</t>
         </is>
       </c>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
+          <t>https://superprofile.bio/vig/6a41f935be7a120013780d32</t>
         </is>
       </c>
       <c r="M409" s="2" t="inlineStr">
@@ -39755,27 +39755,27 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>659b990d57f865001e1efa98</t>
+          <t>65132965f4d0b1001eba9b70</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>marathicommunity</t>
+          <t>lbfcstockss</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>vishalgaikwad91888@gmail.com</t>
+          <t>biswalfc@gmail.com</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>7040119684</t>
+          <t>9658251426</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -39789,22 +39789,22 @@
         </is>
       </c>
       <c r="H410" s="2" t="n">
-        <v>1078</v>
+        <v>1134</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>4312</v>
+        <v>4536</v>
       </c>
       <c r="J410" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
-          <t>69f59765a8c2c60013505029</t>
+          <t>6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
+          <t>https://superprofile.bio/vig/6724fcbd76412b00139f3f43</t>
         </is>
       </c>
       <c r="M410" s="2" t="inlineStr">
@@ -39851,27 +39851,27 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>69fb20dbfae26e0013229a6c</t>
+          <t>695fc2d673169a001320fcf5</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>bhagatedits</t>
+          <t>shivamshiva</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>rupeshbhagat1445@gmail.com</t>
+          <t>shivamshiva7870@gmail.com</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>6397113270</t>
+          <t>9534598557</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
@@ -39885,22 +39885,22 @@
         </is>
       </c>
       <c r="H411" s="2" t="n">
-        <v>1061</v>
+        <v>1080</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>4244</v>
+        <v>4320</v>
       </c>
       <c r="J411" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
-          <t>6a40e3e946bff60013350d9d</t>
+          <t>6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
+          <t>https://superprofile.bio/vig/6961fea2c0dd9a00126d58b1</t>
         </is>
       </c>
       <c r="M411" s="2" t="inlineStr">
@@ -39947,27 +39947,27 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>666e8a3cf52ecb0013f648c2</t>
+          <t>659b990d57f865001e1efa98</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan</t>
+          <t>marathicommunity</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>pravinkhetan@iplaneducation.com</t>
+          <t>vishalgaikwad91888@gmail.com</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>9999616222</t>
+          <t>7040119684</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -39981,89 +39981,89 @@
         </is>
       </c>
       <c r="H412" s="2" t="n">
-        <v>1057</v>
+        <v>1078</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>3171</v>
+        <v>4312</v>
       </c>
       <c r="J412" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>69f59765a8c2c60013505029</t>
         </is>
       </c>
       <c r="L412" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M412" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N412" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>https://superprofile.bio/vig/69f59765a8c2c60013505029</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N412" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="O412" s="2" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Not Verified</t>
         </is>
       </c>
       <c r="P412" s="2" t="inlineStr">
         <is>
-          <t>INH000019521</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q412" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Manual Review Required</t>
         </is>
       </c>
       <c r="R412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28, 2026-08-29</t>
+          <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
       <c r="S412" s="2" t="inlineStr">
         <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="T412" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>6990756033447e00137abb03</t>
+          <t>69fb20dbfae26e0013229a6c</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>sujit1661</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>sujit1661</t>
+          <t>bhagatedits</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>sujitgarnayak99@gmail.com</t>
+          <t>rupeshbhagat1445@gmail.com</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>7325876135</t>
+          <t>6397113270</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
@@ -40077,22 +40077,22 @@
         </is>
       </c>
       <c r="H413" s="2" t="n">
-        <v>1031</v>
+        <v>1061</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>4124</v>
+        <v>4244</v>
       </c>
       <c r="J413" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
         <is>
-          <t>6904dfd487ea0200137ccc5b</t>
+          <t>6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="L413" s="2" t="inlineStr">
         <is>
-          <t>https://superprofile.bio/vig/6904dfd487ea0200137ccc5b</t>
+          <t>https://superprofile.bio/vig/6a40e3e946bff60013350d9d</t>
         </is>
       </c>
       <c r="M413" s="2" t="inlineStr">
@@ -40139,27 +40139,27 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>64e5ae617f68ef001ea74131</t>
+          <t>666e8a3cf52ecb0013f648c2</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>pravinkhetan</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81</t>
+          <t>pravinkhetan</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>dalalmihir81@gmail.com</t>
+          <t>pravinkhetan@iplaneducation.com</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>9879558198</t>
+          <t>9999616222</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -40173,60 +40173,252 @@
         </is>
       </c>
       <c r="H414" s="2" t="n">
-        <v>1001</v>
+        <v>1057</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>4004</v>
+        <v>4228</v>
       </c>
       <c r="J414" s="2" t="n">
         <v>4</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M414" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>INH000019521</t>
+        </is>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28, 2026-08-29, 2026-08-30</t>
+        </is>
+      </c>
+      <c r="S414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>6990756033447e00137abb03</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>sujit1661</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>sujit1661</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>sujitgarnayak99@gmail.com</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>7325876135</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="I415" s="2" t="n">
+        <v>4124</v>
+      </c>
+      <c r="J415" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K415" s="2" t="inlineStr">
+        <is>
+          <t>6904dfd487ea0200137ccc5b</t>
+        </is>
+      </c>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>https://superprofile.bio/vig/6904dfd487ea0200137ccc5b</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N415" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>Not Verified</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>Manual Review Required</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27, 2026-08-28</t>
+        </is>
+      </c>
+      <c r="S415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="T415" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>64e5ae617f68ef001ea74131</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>dalalmihir81@gmail.com</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>9879558198</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="I416" s="2" t="n">
+        <v>4004</v>
+      </c>
+      <c r="J416" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K416" s="2" t="inlineStr">
+        <is>
           <t>66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
-      <c r="L414" s="2" t="inlineStr">
+      <c r="L416" s="2" t="inlineStr">
         <is>
           <t>https://superprofile.bio/vig/66c871cfc6acc2001368e5a3</t>
         </is>
       </c>
-      <c r="M414" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N414" s="4" t="inlineStr">
+      <c r="M416" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N416" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O414" s="2" t="inlineStr">
+      <c r="O416" s="2" t="inlineStr">
         <is>
           <t>Not Verified</t>
         </is>
       </c>
-      <c r="P414" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q414" s="2" t="inlineStr">
+      <c r="P416" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q416" s="2" t="inlineStr">
         <is>
           <t>Manual Review Required</t>
         </is>
       </c>
-      <c r="R414" s="2" t="inlineStr">
+      <c r="R416" s="2" t="inlineStr">
         <is>
           <t>2026-08-27, 2026-08-28</t>
         </is>
       </c>
-      <c r="S414" s="2" t="inlineStr">
+      <c r="S416" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="T414" s="2" t="inlineStr">
+      <c r="T416" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3200163</v>
+        <v>4338705</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>495675</v>
+        <v>546945</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1184012</v>
+        <v>1776018</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>317055</v>
+        <v>404927</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>853563</v>
+        <v>1047803</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>96829</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>484145</v>
+        <v>677803</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>407207</v>
+        <v>483517</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>408887</v>
+        <v>590019</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>84208</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>456883</v>
+        <v>625299</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>82618</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>488512</v>
+        <v>653748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1584,10 +1584,10 @@
         <v>75729</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>382308</v>
+        <v>464970</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>74332</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>297328</v>
+        <v>445992</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1776,10 +1776,10 @@
         <v>70990</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>296078</v>
+        <v>438058</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>69541</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>278164</v>
+        <v>417246</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -1968,10 +1968,10 @@
         <v>69234</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>276936</v>
+        <v>415404</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2064,10 +2064,10 @@
         <v>65193</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>260772</v>
+        <v>391158</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2160,10 +2160,10 @@
         <v>64401</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>257604</v>
+        <v>386406</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2256,10 +2256,10 @@
         <v>62983</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>244346</v>
+        <v>290426</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>59566</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>238264</v>
+        <v>357396</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2448,10 +2448,10 @@
         <v>54825</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>219300</v>
+        <v>328950</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2544,10 +2544,10 @@
         <v>53890</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>356129</v>
+        <v>453901</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>53653</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>214612</v>
+        <v>321918</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2736,10 +2736,10 @@
         <v>51702</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>156022</v>
+        <v>208182</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>50722</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>136419</v>
+        <v>150409</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -2928,10 +2928,10 @@
         <v>48086</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>218548</v>
+        <v>314720</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>47876</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>192749</v>
+        <v>288501</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>46976</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>234880</v>
+        <v>328832</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>46318</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>185272</v>
+        <v>277908</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3408,10 +3408,10 @@
         <v>42364</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>169456</v>
+        <v>254184</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3504,10 +3504,10 @@
         <v>41270</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>64802</v>
+        <v>76568</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>40719</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>162876</v>
+        <v>244314</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3696,10 +3696,10 @@
         <v>39334</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>157336</v>
+        <v>236004</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -3792,10 +3792,10 @@
         <v>39193</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>54865</v>
+        <v>62701</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>38584</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>190509</v>
+        <v>267677</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>38479</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>220608</v>
+        <v>278068</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4080,10 +4080,10 @@
         <v>37610</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>150440</v>
+        <v>225660</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4176,10 +4176,10 @@
         <v>36823</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>157537</v>
+        <v>231183</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>34868</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>139472</v>
+        <v>209208</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4368,10 +4368,10 @@
         <v>33180</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>213620</v>
+        <v>268228</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>33063</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>140477</v>
+        <v>206603</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>32165</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>147048</v>
+        <v>211378</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>31903</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>143562</v>
+        <v>207368</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>31814</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>127256</v>
+        <v>190884</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4848,10 +4848,10 @@
         <v>31494</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>168922</v>
+        <v>231910</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4944,10 +4944,10 @@
         <v>31368</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>156840</v>
+        <v>219576</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5040,10 +5040,10 @@
         <v>29237</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>116948</v>
+        <v>175422</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5136,10 +5136,10 @@
         <v>28487</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>116187</v>
+        <v>160037</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>28316</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>93246</v>
+        <v>99104</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>28241</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>112964</v>
+        <v>169446</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5424,10 +5424,10 @@
         <v>28162</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>112648</v>
+        <v>168972</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5520,10 +5520,10 @@
         <v>27760</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>111040</v>
+        <v>166560</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5616,10 +5616,10 @@
         <v>27645</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>110580</v>
+        <v>165870</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5712,10 +5712,10 @@
         <v>27294</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>58526</v>
+        <v>74142</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>27192</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>108768</v>
+        <v>163152</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -5904,10 +5904,10 @@
         <v>26961</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>141045</v>
+        <v>168431</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>26611</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>106444</v>
+        <v>159666</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6096,10 +6096,10 @@
         <v>26404</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>125411</v>
+        <v>178219</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>26168</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104672</v>
+        <v>157008</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6288,10 +6288,10 @@
         <v>25641</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>40066</v>
+        <v>45836</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>25401</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>101604</v>
+        <v>152406</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6480,10 +6480,10 @@
         <v>25120</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>107506</v>
+        <v>157746</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>24939</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>153127</v>
+        <v>203005</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6672,10 +6672,10 @@
         <v>24370</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>97480</v>
+        <v>146220</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -6768,10 +6768,10 @@
         <v>23618</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>84702</v>
+        <v>115244</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>23048</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>95485</v>
+        <v>141581</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>22390</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>100068</v>
+        <v>144848</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>21874</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>147562</v>
+        <v>191310</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>21393</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>85572</v>
+        <v>128358</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -7248,10 +7248,10 @@
         <v>21292</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>66008</v>
+        <v>88366</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>20958</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>83832</v>
+        <v>125748</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -7728,10 +7728,10 @@
         <v>19528</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>97640</v>
+        <v>136696</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>19232</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>94236</v>
+        <v>131738</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>19174</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>76696</v>
+        <v>115044</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8016,10 +8016,10 @@
         <v>19126</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>112683</v>
+        <v>150935</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>19075</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>73059</v>
+        <v>100051</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>18900</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>116100</v>
+        <v>153900</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8304,10 +8304,10 @@
         <v>18615</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>74460</v>
+        <v>111690</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8400,10 +8400,10 @@
         <v>18215</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>91075</v>
+        <v>127505</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8592,10 +8592,10 @@
         <v>17860</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>71440</v>
+        <v>107160</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8688,10 +8688,10 @@
         <v>17484</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>69936</v>
+        <v>104904</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -8880,10 +8880,10 @@
         <v>17304</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>74521</v>
+        <v>109129</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>16561</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>110141</v>
+        <v>143263</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9264,10 +9264,10 @@
         <v>16409</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>73845</v>
+        <v>106663</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>16281</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>70388</v>
+        <v>102950</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>16107</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>69308</v>
+        <v>101522</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>15997</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>63988</v>
+        <v>95982</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S97" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9840,10 +9840,10 @@
         <v>15807</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>86939</v>
+        <v>118553</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="R98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S98" s="2" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -9936,10 +9936,10 @@
         <v>15666</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>69538</v>
+        <v>100870</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>15525</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>65393</v>
+        <v>96443</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>15119</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>62445</v>
+        <v>92683</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>14985</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>64833</v>
+        <v>94803</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>14915</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>60883</v>
+        <v>90713</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>14604</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>60520</v>
+        <v>83478</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>14553</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>67433</v>
+        <v>96539</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>14396</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>57584</v>
+        <v>86376</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="R108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S108" s="2" t="inlineStr">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -10896,10 +10896,10 @@
         <v>14387</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>60987</v>
+        <v>84287</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>14380</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>57520</v>
+        <v>86280</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11088,10 +11088,10 @@
         <v>14153</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>37585</v>
+        <v>49301</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>14149</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>56596</v>
+        <v>84894</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11376,10 +11376,10 @@
         <v>14018</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>60586</v>
+        <v>88622</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>13943</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>81008</v>
+        <v>108894</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>13912</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>55648</v>
+        <v>83472</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11760,10 +11760,10 @@
         <v>13666</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>25378</v>
+        <v>31234</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>13645</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>54580</v>
+        <v>81870</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -11952,10 +11952,10 @@
         <v>13490</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>53960</v>
+        <v>80940</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12048,10 +12048,10 @@
         <v>13185</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>64311</v>
+        <v>90681</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>13172</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>52688</v>
+        <v>79032</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12240,10 +12240,10 @@
         <v>13093</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46461</v>
+        <v>54571</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12336,10 +12336,10 @@
         <v>13071</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>52284</v>
+        <v>78426</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12432,10 +12432,10 @@
         <v>12946</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>51784</v>
+        <v>77676</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12528,10 +12528,10 @@
         <v>12786</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>41818</v>
+        <v>56334</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>12513</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>50052</v>
+        <v>75078</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -12816,10 +12816,10 @@
         <v>12156</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>21916</v>
+        <v>26796</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>12088</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>48352</v>
+        <v>72528</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13008,10 +13008,10 @@
         <v>11974</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>49864</v>
+        <v>73812</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>11788</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>47152</v>
+        <v>70728</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13200,10 +13200,10 @@
         <v>11763</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>47052</v>
+        <v>70578</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S133" s="2" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13296,10 +13296,10 @@
         <v>11763</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>49403</v>
+        <v>68223</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>11717</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46868</v>
+        <v>70302</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13584,10 +13584,10 @@
         <v>11598</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46392</v>
+        <v>69588</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -13968,10 +13968,10 @@
         <v>10644</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>48371</v>
+        <v>69659</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>10620</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>38232</v>
+        <v>52038</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>10582</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>43667</v>
+        <v>64831</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>10432</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>41728</v>
+        <v>62592</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S145" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -14448,10 +14448,10 @@
         <v>10431</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>41724</v>
+        <v>62586</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S146" s="2" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -14544,10 +14544,10 @@
         <v>10316</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>40724</v>
+        <v>55928</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>10190</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>40760</v>
+        <v>61140</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -14736,10 +14736,10 @@
         <v>10165</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>40660</v>
+        <v>60990</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S149" s="2" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -14832,10 +14832,10 @@
         <v>10127</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20535</v>
+        <v>25739</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>10066</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>43086</v>
+        <v>63218</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>10057</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>42670</v>
+        <v>62784</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>9973</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>39892</v>
+        <v>59838</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="T153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -15312,10 +15312,10 @@
         <v>9898</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>45350</v>
+        <v>65146</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>9860</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>25476</v>
+        <v>33284</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>9704</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>38816</v>
+        <v>58224</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -15600,10 +15600,10 @@
         <v>9703</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>38812</v>
+        <v>58218</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S158" s="2" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -15696,10 +15696,10 @@
         <v>9680</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>48400</v>
+        <v>67760</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>9586</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>51765</v>
+        <v>70937</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>38344</v>
+        <v>57516</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16176,10 +16176,10 @@
         <v>9524</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>38096</v>
+        <v>57144</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="R164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S164" s="2" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16272,10 +16272,10 @@
         <v>9470</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>40137</v>
+        <v>59077</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>9403</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>21187</v>
+        <v>27079</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>9348</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>37392</v>
+        <v>56088</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="R167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S167" s="2" t="inlineStr">
@@ -16516,7 +16516,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16656,10 +16656,10 @@
         <v>9203</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>32207</v>
+        <v>43709</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>9152</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>36608</v>
+        <v>54912</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="R170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S170" s="2" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -16848,10 +16848,10 @@
         <v>8847</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>39436</v>
+        <v>57130</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>8819</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>35276</v>
+        <v>52914</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="R173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S173" s="2" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -17136,10 +17136,10 @@
         <v>8777</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>35108</v>
+        <v>52662</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="R174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S174" s="2" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -17232,10 +17232,10 @@
         <v>8746</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>41828</v>
+        <v>59320</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>8679</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>37609</v>
+        <v>54967</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>8653</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>34612</v>
+        <v>51918</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="R178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S178" s="2" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="T178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -17616,10 +17616,10 @@
         <v>8643</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>17863</v>
+        <v>22473</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>8610</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>35852</v>
+        <v>53072</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>8561</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>34244</v>
+        <v>51366</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="R181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S181" s="2" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="T181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -17904,10 +17904,10 @@
         <v>8399</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>20255</v>
+        <v>26183</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>8299</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>33196</v>
+        <v>49794</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="R183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S183" s="2" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="T183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -18096,10 +18096,10 @@
         <v>8254</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>35412</v>
+        <v>51920</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>8230</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>35831</v>
+        <v>52291</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>8199</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>32796</v>
+        <v>49194</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
       </c>
       <c r="R186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S186" s="2" t="inlineStr">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="T186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -18480,10 +18480,10 @@
         <v>8111</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>37586</v>
+        <v>53808</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>8010</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>32040</v>
+        <v>48060</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
       </c>
       <c r="R189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S189" s="2" t="inlineStr">
@@ -18628,7 +18628,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -18672,10 +18672,10 @@
         <v>7858</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>39290</v>
+        <v>55006</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="R190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S190" s="2" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="T190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -18864,10 +18864,10 @@
         <v>7772</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>36748</v>
+        <v>52292</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>7713</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>30852</v>
+        <v>46278</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="R194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S194" s="2" t="inlineStr">
@@ -19108,7 +19108,7 @@
       </c>
       <c r="T194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19152,10 +19152,10 @@
         <v>7618</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>30472</v>
+        <v>45708</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
       </c>
       <c r="R195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S195" s="2" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="T195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19248,10 +19248,10 @@
         <v>7594</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>30376</v>
+        <v>45564</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="R196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S196" s="2" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="T196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19344,10 +19344,10 @@
         <v>7556</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>30224</v>
+        <v>45336</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
       </c>
       <c r="R197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S197" s="2" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="T197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19440,10 +19440,10 @@
         <v>7525</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>30100</v>
+        <v>45150</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="R198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S198" s="2" t="inlineStr">
@@ -19492,7 +19492,7 @@
       </c>
       <c r="T198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19536,10 +19536,10 @@
         <v>7520</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>30080</v>
+        <v>45120</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="R199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S199" s="2" t="inlineStr">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -19632,10 +19632,10 @@
         <v>7477</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>20896</v>
+        <v>24730</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>7464</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>47026</v>
+        <v>61954</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>7197</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>33325</v>
+        <v>46389</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>7074</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>28296</v>
+        <v>42444</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="R203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S203" s="2" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="T203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20016,10 +20016,10 @@
         <v>6986</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>34422</v>
+        <v>48140</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>6963</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>27852</v>
+        <v>41778</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="R205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S205" s="2" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="T205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20208,10 +20208,10 @@
         <v>6891</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>33799</v>
+        <v>47253</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>6843</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>27372</v>
+        <v>41058</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="R207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S207" s="2" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="T207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20400,10 +20400,10 @@
         <v>6796</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>27184</v>
+        <v>40776</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="R208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S208" s="2" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="T208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20496,10 +20496,10 @@
         <v>6771</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>27084</v>
+        <v>40626</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
       </c>
       <c r="R209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S209" s="2" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="T209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20784,10 +20784,10 @@
         <v>6684</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>26736</v>
+        <v>40104</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
       </c>
       <c r="R212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S212" s="2" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="T212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20880,10 +20880,10 @@
         <v>6677</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>36919</v>
+        <v>46345</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
       </c>
       <c r="R213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S213" s="2" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="T213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -20976,10 +20976,10 @@
         <v>6670</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>26680</v>
+        <v>40020</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="R214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S214" s="2" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="T214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21072,10 +21072,10 @@
         <v>6662</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>26648</v>
+        <v>39972</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="R215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S215" s="2" t="inlineStr">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="T215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21264,10 +21264,10 @@
         <v>6627</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>26508</v>
+        <v>39762</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="R217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S217" s="2" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="T217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21360,10 +21360,10 @@
         <v>6585</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>26340</v>
+        <v>39510</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="R218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S218" s="2" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="T218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21456,10 +21456,10 @@
         <v>6568</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>14416</v>
+        <v>18340</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>6522</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>36602</v>
+        <v>49646</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="R220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S220" s="2" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="T220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21648,10 +21648,10 @@
         <v>6471</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>25884</v>
+        <v>38826</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
       </c>
       <c r="R221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S221" s="2" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="T221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21744,10 +21744,10 @@
         <v>6469</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>25876</v>
+        <v>38814</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="R222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S222" s="2" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="T222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -21840,10 +21840,10 @@
         <v>6468</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>25872</v>
+        <v>38808</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="R223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S223" s="2" t="inlineStr">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="T223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -22032,10 +22032,10 @@
         <v>6357</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>20049</v>
+        <v>26895</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>6308</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>30527</v>
+        <v>43143</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22416,10 +22416,10 @@
         <v>6269</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>25076</v>
+        <v>37614</v>
       </c>
       <c r="J229" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K229" s="2" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
       </c>
       <c r="R229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S229" s="2" t="inlineStr">
@@ -22468,7 +22468,7 @@
       </c>
       <c r="T229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -22512,10 +22512,10 @@
         <v>6169</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>29397</v>
+        <v>41735</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>6117</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>24468</v>
+        <v>36702</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="R231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S231" s="2" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="T231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -22704,10 +22704,10 @@
         <v>6022</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>26441</v>
+        <v>38485</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>6014</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>25414</v>
+        <v>37442</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>5927</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>28648</v>
+        <v>40502</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>5891</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>28406</v>
+        <v>40188</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>5853</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>23412</v>
+        <v>35118</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
       </c>
       <c r="R236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S236" s="2" t="inlineStr">
@@ -23140,7 +23140,7 @@
       </c>
       <c r="T236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -23184,10 +23184,10 @@
         <v>5834</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>23336</v>
+        <v>35004</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
       </c>
       <c r="R237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S237" s="2" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="T237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -23280,10 +23280,10 @@
         <v>5739</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>22956</v>
+        <v>34434</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
       </c>
       <c r="R238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S238" s="2" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="T238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -23376,10 +23376,10 @@
         <v>5680</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>21108</v>
+        <v>28822</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>5636</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>22544</v>
+        <v>30998</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>5597</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>26103</v>
+        <v>37297</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>5400</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>21600</v>
+        <v>32400</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="R244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S244" s="2" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="T244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -23952,10 +23952,10 @@
         <v>5399</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>21596</v>
+        <v>32394</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
       </c>
       <c r="R245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S245" s="2" t="inlineStr">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="T245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -24048,10 +24048,10 @@
         <v>5397</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>21588</v>
+        <v>32382</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
       </c>
       <c r="R246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S246" s="2" t="inlineStr">
@@ -24100,7 +24100,7 @@
       </c>
       <c r="T246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -24144,10 +24144,10 @@
         <v>5216</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>20864</v>
+        <v>31296</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
       </c>
       <c r="R247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S247" s="2" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="T247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -24336,10 +24336,10 @@
         <v>5176</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>20704</v>
+        <v>31056</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
       </c>
       <c r="R249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S249" s="2" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="T249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -24432,10 +24432,10 @@
         <v>5174</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>23894</v>
+        <v>34242</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24624,10 +24624,10 @@
         <v>5079</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>20316</v>
+        <v>30474</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
       </c>
       <c r="R252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S252" s="2" t="inlineStr">
@@ -24676,7 +24676,7 @@
       </c>
       <c r="T252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -24816,10 +24816,10 @@
         <v>4963</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>10179</v>
+        <v>12787</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>4882</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>19528</v>
+        <v>29292</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="R256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S256" s="2" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="T256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25104,10 +25104,10 @@
         <v>4863</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>19452</v>
+        <v>29178</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
       </c>
       <c r="R257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S257" s="2" t="inlineStr">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="T257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25200,10 +25200,10 @@
         <v>4853</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>19412</v>
+        <v>29118</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
       </c>
       <c r="R258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S258" s="2" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="T258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25392,10 +25392,10 @@
         <v>4852</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>19408</v>
+        <v>29112</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
       </c>
       <c r="R260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S260" s="2" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="T260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25488,10 +25488,10 @@
         <v>4822</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>19288</v>
+        <v>28932</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="R261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S261" s="2" t="inlineStr">
@@ -25540,7 +25540,7 @@
       </c>
       <c r="T261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25584,10 +25584,10 @@
         <v>4798</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>20759</v>
+        <v>30355</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>4794</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>23970</v>
+        <v>33558</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
       </c>
       <c r="R263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S263" s="2" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="T263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25776,10 +25776,10 @@
         <v>4793</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>19172</v>
+        <v>28758</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="R264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S264" s="2" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="T264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25872,10 +25872,10 @@
         <v>4749</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>18996</v>
+        <v>28494</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
       </c>
       <c r="R265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S265" s="2" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="T265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -25968,10 +25968,10 @@
         <v>4705</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>18820</v>
+        <v>28230</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
       </c>
       <c r="R266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S266" s="2" t="inlineStr">
@@ -26020,7 +26020,7 @@
       </c>
       <c r="T266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -26160,10 +26160,10 @@
         <v>4703</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>18812</v>
+        <v>28218</v>
       </c>
       <c r="J268" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
       </c>
       <c r="R268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S268" s="2" t="inlineStr">
@@ -26212,7 +26212,7 @@
       </c>
       <c r="T268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -26352,10 +26352,10 @@
         <v>4657</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>20054</v>
+        <v>29368</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>4517</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>18068</v>
+        <v>27102</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="R271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S271" s="2" t="inlineStr">
@@ -26500,7 +26500,7 @@
       </c>
       <c r="T271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -26640,10 +26640,10 @@
         <v>4373</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>20613</v>
+        <v>29359</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>4357</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>17428</v>
+        <v>26142</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="R274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S274" s="2" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="T274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -26832,10 +26832,10 @@
         <v>4313</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>17252</v>
+        <v>25878</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
       </c>
       <c r="R275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S275" s="2" t="inlineStr">
@@ -26884,7 +26884,7 @@
       </c>
       <c r="T275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -26928,10 +26928,10 @@
         <v>4305</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>11969</v>
+        <v>15801</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>4286</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>19049</v>
+        <v>27621</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>4027</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>16108</v>
+        <v>24162</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
       </c>
       <c r="R279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S279" s="2" t="inlineStr">
@@ -27268,7 +27268,7 @@
       </c>
       <c r="T279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -27312,10 +27312,10 @@
         <v>3952</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>15808</v>
+        <v>23712</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="R280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S280" s="2" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="T280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -27504,10 +27504,10 @@
         <v>3927</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>19399</v>
+        <v>27135</v>
       </c>
       <c r="J282" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K282" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>3882</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>15528</v>
+        <v>23292</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
       </c>
       <c r="R284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S284" s="2" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="T284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -27792,10 +27792,10 @@
         <v>3878</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>15512</v>
+        <v>23268</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
       </c>
       <c r="R285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S285" s="2" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="T285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -27888,10 +27888,10 @@
         <v>3870</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>17730</v>
+        <v>25470</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>3856</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>15424</v>
+        <v>23136</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
       </c>
       <c r="R287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S287" s="2" t="inlineStr">
@@ -28036,7 +28036,7 @@
       </c>
       <c r="T287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28080,10 +28080,10 @@
         <v>3775</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>15100</v>
+        <v>22650</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
       </c>
       <c r="R288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S288" s="2" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="T288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28176,10 +28176,10 @@
         <v>3764</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>15056</v>
+        <v>22584</v>
       </c>
       <c r="J289" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
       </c>
       <c r="R289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S289" s="2" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="T289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28368,10 +28368,10 @@
         <v>3762</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>15048</v>
+        <v>22572</v>
       </c>
       <c r="J291" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
       </c>
       <c r="R291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S291" s="2" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="T291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28464,10 +28464,10 @@
         <v>3736</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>14944</v>
+        <v>22416</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
       </c>
       <c r="R292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S292" s="2" t="inlineStr">
@@ -28516,7 +28516,7 @@
       </c>
       <c r="T292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28560,10 +28560,10 @@
         <v>3723</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>18615</v>
+        <v>26061</v>
       </c>
       <c r="J293" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
       </c>
       <c r="R293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S293" s="2" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="T293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28656,10 +28656,10 @@
         <v>3663</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>14652</v>
+        <v>21978</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28698,7 +28698,7 @@
       </c>
       <c r="R294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S294" s="2" t="inlineStr">
@@ -28708,7 +28708,7 @@
       </c>
       <c r="T294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28752,10 +28752,10 @@
         <v>3513</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>15809</v>
+        <v>22835</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>3504</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>17520</v>
+        <v>24528</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
       </c>
       <c r="R296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S296" s="2" t="inlineStr">
@@ -28900,7 +28900,7 @@
       </c>
       <c r="T296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -28944,10 +28944,10 @@
         <v>3478</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>20493</v>
+        <v>27299</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>3427</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>13708</v>
+        <v>20562</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
       </c>
       <c r="R298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S298" s="2" t="inlineStr">
@@ -29092,7 +29092,7 @@
       </c>
       <c r="T298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -29136,10 +29136,10 @@
         <v>3420</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>13680</v>
+        <v>20520</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
       </c>
       <c r="R299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S299" s="2" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="T299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -29232,10 +29232,10 @@
         <v>3417</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>15132</v>
+        <v>21966</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>3376</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>13504</v>
+        <v>20256</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
       </c>
       <c r="R301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S301" s="2" t="inlineStr">
@@ -29380,7 +29380,7 @@
       </c>
       <c r="T301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -29424,10 +29424,10 @@
         <v>3375</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>13500</v>
+        <v>20250</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="R302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S302" s="2" t="inlineStr">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="T302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -29616,10 +29616,10 @@
         <v>3334</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>13336</v>
+        <v>20004</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="R304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S304" s="2" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="T304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -29808,10 +29808,10 @@
         <v>3331</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>9179</v>
+        <v>12103</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>3321</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>16603</v>
+        <v>23245</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>3293</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>13172</v>
+        <v>19758</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="R308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S308" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="T308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -30096,10 +30096,10 @@
         <v>3198</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>15614</v>
+        <v>21822</v>
       </c>
       <c r="J309" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
@@ -30192,10 +30192,10 @@
         <v>3154</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>12616</v>
+        <v>18924</v>
       </c>
       <c r="J310" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
       </c>
       <c r="R310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S310" s="2" t="inlineStr">
@@ -30244,7 +30244,7 @@
       </c>
       <c r="T310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -30288,10 +30288,10 @@
         <v>3154</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>15399</v>
+        <v>21707</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>3149</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>12596</v>
+        <v>18894</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
       </c>
       <c r="R312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S312" s="2" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="T312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -30480,10 +30480,10 @@
         <v>3101</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>14369</v>
+        <v>20003</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>3056</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>12224</v>
+        <v>18336</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
       </c>
       <c r="R314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S314" s="2" t="inlineStr">
@@ -30628,7 +30628,7 @@
       </c>
       <c r="T314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -30672,10 +30672,10 @@
         <v>3045</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>12180</v>
+        <v>18270</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
       </c>
       <c r="R315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S315" s="2" t="inlineStr">
@@ -30724,7 +30724,7 @@
       </c>
       <c r="T315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31152,10 +31152,10 @@
         <v>2928</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>11712</v>
+        <v>17568</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
       </c>
       <c r="R320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S320" s="2" t="inlineStr">
@@ -31204,7 +31204,7 @@
       </c>
       <c r="T320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31248,10 +31248,10 @@
         <v>2911</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>11644</v>
+        <v>17466</v>
       </c>
       <c r="J321" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K321" s="2" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
       </c>
       <c r="R321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S321" s="2" t="inlineStr">
@@ -31300,7 +31300,7 @@
       </c>
       <c r="T321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31344,10 +31344,10 @@
         <v>2911</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>14555</v>
+        <v>20377</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>2879</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>11516</v>
+        <v>17274</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
       </c>
       <c r="R323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S323" s="2" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="T323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31536,10 +31536,10 @@
         <v>2875</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>11500</v>
+        <v>17250</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
       </c>
       <c r="R324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S324" s="2" t="inlineStr">
@@ -31588,7 +31588,7 @@
       </c>
       <c r="T324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31632,10 +31632,10 @@
         <v>2865</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>11460</v>
+        <v>17190</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="R325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S325" s="2" t="inlineStr">
@@ -31684,7 +31684,7 @@
       </c>
       <c r="T325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31728,10 +31728,10 @@
         <v>2857</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>13809</v>
+        <v>19523</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>2857</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>11428</v>
+        <v>17142</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
       </c>
       <c r="R327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S327" s="2" t="inlineStr">
@@ -31876,7 +31876,7 @@
       </c>
       <c r="T327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -31920,10 +31920,10 @@
         <v>2823</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>11292</v>
+        <v>16938</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
       </c>
       <c r="R328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S328" s="2" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="T328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32016,10 +32016,10 @@
         <v>2823</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>12704</v>
+        <v>18350</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>2822</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>11288</v>
+        <v>16932</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
       </c>
       <c r="R331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S331" s="2" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="T331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32304,10 +32304,10 @@
         <v>2822</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>11288</v>
+        <v>16932</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
       </c>
       <c r="R332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S332" s="2" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="T332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32400,10 +32400,10 @@
         <v>2822</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>11288</v>
+        <v>16932</v>
       </c>
       <c r="J333" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K333" s="2" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
       </c>
       <c r="R333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S333" s="2" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="T333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32496,10 +32496,10 @@
         <v>2821</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>11284</v>
+        <v>16926</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
       </c>
       <c r="R334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S334" s="2" t="inlineStr">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="T334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32784,10 +32784,10 @@
         <v>2744</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>10976</v>
+        <v>16464</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
       </c>
       <c r="R337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S337" s="2" t="inlineStr">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="T337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -32880,10 +32880,10 @@
         <v>2730</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>13450</v>
+        <v>18910</v>
       </c>
       <c r="J338" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K338" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>2717</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>10868</v>
+        <v>16302</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
       </c>
       <c r="R339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S339" s="2" t="inlineStr">
@@ -33028,7 +33028,7 @@
       </c>
       <c r="T339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -33264,10 +33264,10 @@
         <v>2698</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>12141</v>
+        <v>17537</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>2666</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>10664</v>
+        <v>15996</v>
       </c>
       <c r="J343" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
       </c>
       <c r="R343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S343" s="2" t="inlineStr">
@@ -33412,7 +33412,7 @@
       </c>
       <c r="T343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -33456,10 +33456,10 @@
         <v>2666</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>7982</v>
+        <v>10640</v>
       </c>
       <c r="J344" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>2530</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>10120</v>
+        <v>15180</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
       </c>
       <c r="R346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S346" s="2" t="inlineStr">
@@ -33700,7 +33700,7 @@
       </c>
       <c r="T346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -33936,10 +33936,10 @@
         <v>2491</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>9964</v>
+        <v>14946</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -33978,7 +33978,7 @@
       </c>
       <c r="R349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S349" s="2" t="inlineStr">
@@ -33988,7 +33988,7 @@
       </c>
       <c r="T349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -34032,10 +34032,10 @@
         <v>2440</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>9760</v>
+        <v>14640</v>
       </c>
       <c r="J350" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
       </c>
       <c r="R350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S350" s="2" t="inlineStr">
@@ -34084,7 +34084,7 @@
       </c>
       <c r="T350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -34224,10 +34224,10 @@
         <v>2427</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>9423</v>
+        <v>12921</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>2425</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>9700</v>
+        <v>14550</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
       </c>
       <c r="R353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S353" s="2" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="T353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -34512,10 +34512,10 @@
         <v>2353</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>9412</v>
+        <v>14118</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
       </c>
       <c r="R355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S355" s="2" t="inlineStr">
@@ -34564,7 +34564,7 @@
       </c>
       <c r="T355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -34608,10 +34608,10 @@
         <v>2352</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>9408</v>
+        <v>14112</v>
       </c>
       <c r="J356" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
       </c>
       <c r="R356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S356" s="2" t="inlineStr">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="T356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -34800,10 +34800,10 @@
         <v>2348</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>7984</v>
+        <v>10802</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>2317</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>9268</v>
+        <v>13902</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
       </c>
       <c r="R360" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S360" s="2" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="T360" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -35088,10 +35088,10 @@
         <v>2287</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>9148</v>
+        <v>13722</v>
       </c>
       <c r="J361" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
       </c>
       <c r="R361" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S361" s="2" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="T361" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -35184,10 +35184,10 @@
         <v>2256</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>9024</v>
+        <v>13536</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35226,7 +35226,7 @@
       </c>
       <c r="R362" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S362" s="2" t="inlineStr">
@@ -35236,7 +35236,7 @@
       </c>
       <c r="T362" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -35472,10 +35472,10 @@
         <v>2161</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>8644</v>
+        <v>12966</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35514,7 +35514,7 @@
       </c>
       <c r="R365" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S365" s="2" t="inlineStr">
@@ -35524,7 +35524,7 @@
       </c>
       <c r="T365" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -35568,10 +35568,10 @@
         <v>2157</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>10785</v>
+        <v>15099</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>2156</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>8624</v>
+        <v>12936</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="R367" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S367" s="2" t="inlineStr">
@@ -35716,7 +35716,7 @@
       </c>
       <c r="T367" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -35952,10 +35952,10 @@
         <v>2121</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>8484</v>
+        <v>12726</v>
       </c>
       <c r="J370" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K370" s="2" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
       </c>
       <c r="R370" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S370" s="2" t="inlineStr">
@@ -36004,7 +36004,7 @@
       </c>
       <c r="T370" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -36048,10 +36048,10 @@
         <v>2116</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>10580</v>
+        <v>14812</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>2050</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>8200</v>
+        <v>12300</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
       </c>
       <c r="R373" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S373" s="2" t="inlineStr">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="T373" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -36336,10 +36336,10 @@
         <v>2025</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>9257</v>
+        <v>13307</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>1979</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>9003</v>
+        <v>12961</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>1975</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>7900</v>
+        <v>11850</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
       </c>
       <c r="R376" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S376" s="2" t="inlineStr">
@@ -36580,7 +36580,7 @@
       </c>
       <c r="T376" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -36624,10 +36624,10 @@
         <v>1972</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>7888</v>
+        <v>11832</v>
       </c>
       <c r="J377" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
       </c>
       <c r="R377" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S377" s="2" t="inlineStr">
@@ -36676,7 +36676,7 @@
       </c>
       <c r="T377" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -36720,10 +36720,10 @@
         <v>1968</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>9840</v>
+        <v>13776</v>
       </c>
       <c r="J378" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
@@ -36762,7 +36762,7 @@
       </c>
       <c r="R378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S378" s="2" t="inlineStr">
@@ -36772,7 +36772,7 @@
       </c>
       <c r="T378" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -36816,10 +36816,10 @@
         <v>1964</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>7856</v>
+        <v>11784</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
       </c>
       <c r="R379" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S379" s="2" t="inlineStr">
@@ -36868,7 +36868,7 @@
       </c>
       <c r="T379" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -37008,10 +37008,10 @@
         <v>1953</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>7812</v>
+        <v>11718</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
       </c>
       <c r="R381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S381" s="2" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="T381" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -37104,10 +37104,10 @@
         <v>1953</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>7812</v>
+        <v>11718</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
       </c>
       <c r="R382" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S382" s="2" t="inlineStr">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="T382" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -37392,10 +37392,10 @@
         <v>1940</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>9700</v>
+        <v>13580</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37488,10 +37488,10 @@
         <v>1940</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>7760</v>
+        <v>11640</v>
       </c>
       <c r="J386" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
       </c>
       <c r="R386" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S386" s="2" t="inlineStr">
@@ -37540,7 +37540,7 @@
       </c>
       <c r="T386" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -37776,10 +37776,10 @@
         <v>1938</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>9690</v>
+        <v>13566</v>
       </c>
       <c r="J389" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K389" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>1932</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>7728</v>
+        <v>11592</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
       </c>
       <c r="R390" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S390" s="2" t="inlineStr">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="T390" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -38160,10 +38160,10 @@
         <v>1887</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>7548</v>
+        <v>11322</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
       </c>
       <c r="R393" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S393" s="2" t="inlineStr">
@@ -38212,7 +38212,7 @@
       </c>
       <c r="T393" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -38256,10 +38256,10 @@
         <v>1881</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>7524</v>
+        <v>11286</v>
       </c>
       <c r="J394" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
       </c>
       <c r="R394" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S394" s="2" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="T394" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -38352,10 +38352,10 @@
         <v>1881</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>7524</v>
+        <v>11286</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
       </c>
       <c r="R395" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S395" s="2" t="inlineStr">
@@ -38404,7 +38404,7 @@
       </c>
       <c r="T395" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -38448,10 +38448,10 @@
         <v>1878</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>7512</v>
+        <v>11268</v>
       </c>
       <c r="J396" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
       </c>
       <c r="R396" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S396" s="2" t="inlineStr">
@@ -38500,7 +38500,7 @@
       </c>
       <c r="T396" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -38544,10 +38544,10 @@
         <v>1832</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>7328</v>
+        <v>10992</v>
       </c>
       <c r="J397" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
       </c>
       <c r="R397" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S397" s="2" t="inlineStr">
@@ -38596,7 +38596,7 @@
       </c>
       <c r="T397" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39024,10 +39024,10 @@
         <v>1740</v>
       </c>
       <c r="I402" s="2" t="n">
-        <v>6960</v>
+        <v>10440</v>
       </c>
       <c r="J402" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K402" s="2" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
       </c>
       <c r="R402" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S402" s="2" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="T402" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39120,10 +39120,10 @@
         <v>1714</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>7810</v>
+        <v>10858</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39216,10 +39216,10 @@
         <v>1688</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>5932</v>
+        <v>8054</v>
       </c>
       <c r="J404" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>1646</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>6584</v>
+        <v>9876</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
       </c>
       <c r="R405" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S405" s="2" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="T405" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39408,10 +39408,10 @@
         <v>1646</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>6584</v>
+        <v>9876</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39450,7 +39450,7 @@
       </c>
       <c r="R406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S406" s="2" t="inlineStr">
@@ -39460,7 +39460,7 @@
       </c>
       <c r="T406" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39504,10 +39504,10 @@
         <v>1641</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>7849</v>
+        <v>10953</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39696,10 +39696,10 @@
         <v>1552</v>
       </c>
       <c r="I409" s="2" t="n">
-        <v>6208</v>
+        <v>9312</v>
       </c>
       <c r="J409" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K409" s="2" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
       </c>
       <c r="R409" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S409" s="2" t="inlineStr">
@@ -39748,7 +39748,7 @@
       </c>
       <c r="T409" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39792,10 +39792,10 @@
         <v>1534</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>6136</v>
+        <v>9204</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
       </c>
       <c r="R410" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S410" s="2" t="inlineStr">
@@ -39844,7 +39844,7 @@
       </c>
       <c r="T410" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -39984,10 +39984,10 @@
         <v>1476</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>5904</v>
+        <v>8856</v>
       </c>
       <c r="J412" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
@@ -40026,7 +40026,7 @@
       </c>
       <c r="R412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S412" s="2" t="inlineStr">
@@ -40036,7 +40036,7 @@
       </c>
       <c r="T412" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40080,10 +40080,10 @@
         <v>1465</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>5860</v>
+        <v>8790</v>
       </c>
       <c r="J413" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
       </c>
       <c r="R413" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S413" s="2" t="inlineStr">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="T413" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40176,10 +40176,10 @@
         <v>1457</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>6898</v>
+        <v>9812</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>1428</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>5712</v>
+        <v>8568</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
       </c>
       <c r="R417" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S417" s="2" t="inlineStr">
@@ -40516,7 +40516,7 @@
       </c>
       <c r="T417" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40560,10 +40560,10 @@
         <v>1412</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>5648</v>
+        <v>8472</v>
       </c>
       <c r="J418" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
       </c>
       <c r="R418" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S418" s="2" t="inlineStr">
@@ -40612,7 +40612,7 @@
       </c>
       <c r="T418" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40656,10 +40656,10 @@
         <v>1411</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
       </c>
       <c r="R419" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S419" s="2" t="inlineStr">
@@ -40708,7 +40708,7 @@
       </c>
       <c r="T419" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40752,10 +40752,10 @@
         <v>1411</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="R420" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S420" s="2" t="inlineStr">
@@ -40804,7 +40804,7 @@
       </c>
       <c r="T420" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -40848,10 +40848,10 @@
         <v>1401</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>5937</v>
+        <v>8205</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -40944,10 +40944,10 @@
         <v>1316</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>5264</v>
+        <v>7896</v>
       </c>
       <c r="J422" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K422" s="2" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
       </c>
       <c r="R422" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S422" s="2" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="T422" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -41040,10 +41040,10 @@
         <v>1261</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>6193</v>
+        <v>8715</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41328,10 +41328,10 @@
         <v>1222</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>4888</v>
+        <v>7332</v>
       </c>
       <c r="J426" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K426" s="2" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
       </c>
       <c r="R426" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S426" s="2" t="inlineStr">
@@ -41380,7 +41380,7 @@
       </c>
       <c r="T426" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -41616,10 +41616,10 @@
         <v>1158</v>
       </c>
       <c r="I429" s="2" t="n">
-        <v>4632</v>
+        <v>6948</v>
       </c>
       <c r="J429" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K429" s="2" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
       </c>
       <c r="R429" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S429" s="2" t="inlineStr">
@@ -41668,7 +41668,7 @@
       </c>
       <c r="T429" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -41808,10 +41808,10 @@
         <v>1080</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>5400</v>
+        <v>7560</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42096,10 +42096,10 @@
         <v>1078</v>
       </c>
       <c r="I434" s="2" t="n">
-        <v>4312</v>
+        <v>6468</v>
       </c>
       <c r="J434" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K434" s="2" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
       </c>
       <c r="R434" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S434" s="2" t="inlineStr">
@@ -42148,7 +42148,7 @@
       </c>
       <c r="T434" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -42288,10 +42288,10 @@
         <v>1031</v>
       </c>
       <c r="I436" s="2" t="n">
-        <v>4124</v>
+        <v>6186</v>
       </c>
       <c r="J436" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K436" s="2" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
       </c>
       <c r="R436" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S436" s="2" t="inlineStr">
@@ -42340,7 +42340,7 @@
       </c>
       <c r="T436" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -42384,10 +42384,10 @@
         <v>1001</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>4004</v>
+        <v>6006</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
       </c>
       <c r="R437" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27, 2026-08-28</t>
+          <t>2026-08-27, 2026-08-28, 2026-08-31</t>
         </is>
       </c>
       <c r="S437" s="2" t="inlineStr">
@@ -42436,7 +42436,7 @@
       </c>
       <c r="T437" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4907976</v>
+        <v>5477247</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>572580</v>
+        <v>598215</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2072021</v>
+        <v>2368024</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>448863</v>
+        <v>492799</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1144923</v>
+        <v>1242043</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>96829</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>774632</v>
+        <v>871461</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>521672</v>
+        <v>559827</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>680585</v>
+        <v>771151</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>87339</v>
+        <v>116919</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>709507</v>
+        <v>793715</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>82618</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>736366</v>
+        <v>818984</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>506301</v>
+        <v>547632</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>74332</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>520324</v>
+        <v>594656</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>509048</v>
+        <v>580038</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>69541</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>486787</v>
+        <v>556328</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>69234</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>484638</v>
+        <v>553872</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>65193</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>456351</v>
+        <v>521544</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>64401</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>450807</v>
+        <v>515208</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>313466</v>
+        <v>336506</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>59566</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>416962</v>
+        <v>476528</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>54825</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>383775</v>
+        <v>438600</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>502787</v>
+        <v>551673</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>53653</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>375571</v>
+        <v>429224</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>234262</v>
+        <v>260342</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>50722</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>157404</v>
+        <v>164399</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>362806</v>
+        <v>410892</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>47876</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>336377</v>
+        <v>384253</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>375808</v>
+        <v>422784</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>46318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>324226</v>
+        <v>370544</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>42364</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>296548</v>
+        <v>338912</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>82451</v>
+        <v>88334</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>40719</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>285033</v>
+        <v>325752</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>39334</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>275338</v>
+        <v>314672</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>66619</v>
+        <v>70537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>306261</v>
+        <v>344845</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>38479</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>306798</v>
+        <v>335528</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>37610</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>263270</v>
+        <v>300880</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>268006</v>
+        <v>304829</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>34868</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>244076</v>
+        <v>278944</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>295532</v>
+        <v>322836</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>239666</v>
+        <v>272729</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>243543</v>
+        <v>275708</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>239271</v>
+        <v>271174</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>31814</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>222698</v>
+        <v>254512</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>31494</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>263404</v>
+        <v>294898</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>31368</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>250944</v>
+        <v>282312</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>29237</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>204659</v>
+        <v>233896</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>181962</v>
+        <v>203887</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>102033</v>
+        <v>104962</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>28241</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>197687</v>
+        <v>225928</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>28162</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>197134</v>
+        <v>225296</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>27760</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>194320</v>
+        <v>222080</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>27645</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>193515</v>
+        <v>221160</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>81950</v>
+        <v>89758</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>27192</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>190344</v>
+        <v>217536</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>182124</v>
+        <v>195817</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>26611</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>186277</v>
+        <v>212888</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>204623</v>
+        <v>231027</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>26168</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>183176</v>
+        <v>209344</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>48721</v>
+        <v>51606</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>25401</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>177807</v>
+        <v>203208</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>182866</v>
+        <v>207986</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>24939</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>227944</v>
+        <v>252883</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>24370</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>170590</v>
+        <v>194960</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>130515</v>
+        <v>145786</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>164629</v>
+        <v>187677</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>167238</v>
+        <v>189628</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>213184</v>
+        <v>235058</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>21393</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>149751</v>
+        <v>171144</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>99545</v>
+        <v>110724</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>20958</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>146706</v>
+        <v>167664</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>156224</v>
+        <v>175752</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>150489</v>
+        <v>169240</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>19174</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>134218</v>
+        <v>153392</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>170061</v>
+        <v>189187</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>113547</v>
+        <v>127043</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>18900</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>172800</v>
+        <v>191700</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>18615</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>130305</v>
+        <v>148920</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>18215</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>145720</v>
+        <v>163935</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>17860</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>125020</v>
+        <v>142880</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>17484</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>122388</v>
+        <v>139872</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>126433</v>
+        <v>143737</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>16561</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>159824</v>
+        <v>176385</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>123072</v>
+        <v>139481</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>119231</v>
+        <v>135512</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>117629</v>
+        <v>133736</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>15997</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>111979</v>
+        <v>127976</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>15807</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>134360</v>
+        <v>150167</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>116536</v>
+        <v>132202</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>111968</v>
+        <v>127493</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>15119</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>107802</v>
+        <v>122921</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>109788</v>
+        <v>124773</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>14915</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>105628</v>
+        <v>120543</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>94957</v>
+        <v>106436</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>111092</v>
+        <v>125645</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>14396</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>100772</v>
+        <v>115168</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>95937</v>
+        <v>107587</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>14380</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>100660</v>
+        <v>115040</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>55159</v>
+        <v>61017</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>14149</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>99043</v>
+        <v>113192</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>102640</v>
+        <v>116658</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>122837</v>
+        <v>136780</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>13912</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>97384</v>
+        <v>111296</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>13645</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>95515</v>
+        <v>109160</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>13490</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>94430</v>
+        <v>107920</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>103866</v>
+        <v>117051</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>13172</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>92204</v>
+        <v>105376</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>13093</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>58626</v>
+        <v>62681</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>13071</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>91497</v>
+        <v>104568</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>12946</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>90622</v>
+        <v>103568</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>63592</v>
+        <v>70850</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>12513</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>87591</v>
+        <v>100104</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>12088</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>84616</v>
+        <v>96704</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>11974</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>85786</v>
+        <v>97760</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>11788</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>82516</v>
+        <v>94304</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>11763</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>82341</v>
+        <v>94104</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>77633</v>
+        <v>87043</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>11717</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>82019</v>
+        <v>93736</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>11598</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>81186</v>
+        <v>92784</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>80303</v>
+        <v>90947</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>58941</v>
+        <v>65844</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>10582</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>75413</v>
+        <v>85995</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>10432</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>73024</v>
+        <v>83456</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>10431</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>73017</v>
+        <v>83448</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>63530</v>
+        <v>71132</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>10190</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>71330</v>
+        <v>81520</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>10165</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>71155</v>
+        <v>81320</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>73284</v>
+        <v>83350</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>72841</v>
+        <v>82898</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>9973</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>69811</v>
+        <v>79784</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>75044</v>
+        <v>84942</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>37188</v>
+        <v>41092</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>9704</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>67928</v>
+        <v>77632</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>9703</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>67921</v>
+        <v>77624</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>77440</v>
+        <v>87120</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>80523</v>
+        <v>90109</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>9586</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>67102</v>
+        <v>76688</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>9524</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>66668</v>
+        <v>76192</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>9470</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>68547</v>
+        <v>78017</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>9348</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>65436</v>
+        <v>74784</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>49460</v>
+        <v>55211</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>9152</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>64064</v>
+        <v>73216</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>65977</v>
+        <v>74824</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>8819</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>61733</v>
+        <v>70552</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>8777</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>61439</v>
+        <v>70216</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>68066</v>
+        <v>76812</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>63646</v>
+        <v>72325</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>8653</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>60571</v>
+        <v>69224</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>8610</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>61682</v>
+        <v>70292</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>8561</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>59927</v>
+        <v>68488</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>8399</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>29147</v>
+        <v>32111</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>8299</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>58093</v>
+        <v>66392</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>8254</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>60174</v>
+        <v>68428</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>60521</v>
+        <v>68751</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>8199</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>57393</v>
+        <v>65592</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>61919</v>
+        <v>70030</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>8010</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>56070</v>
+        <v>64080</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>7858</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>62864</v>
+        <v>70722</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>60064</v>
+        <v>67836</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>7713</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>53991</v>
+        <v>61704</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>7618</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>53326</v>
+        <v>60944</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>7594</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>53158</v>
+        <v>60752</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>7556</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>52892</v>
+        <v>60448</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>7525</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>52675</v>
+        <v>60200</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>7520</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>52640</v>
+        <v>60160</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>26647</v>
+        <v>28564</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>69418</v>
+        <v>76882</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>52921</v>
+        <v>59453</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>7074</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>49518</v>
+        <v>56592</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>54999</v>
+        <v>61858</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>6963</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>48741</v>
+        <v>55704</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>53980</v>
+        <v>60707</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>6843</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>47901</v>
+        <v>54744</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>6796</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>47572</v>
+        <v>54368</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>6771</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>47397</v>
+        <v>54168</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>6684</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>46788</v>
+        <v>53472</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>6677</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>51058</v>
+        <v>55771</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>6670</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>46690</v>
+        <v>53360</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>6662</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>46634</v>
+        <v>53296</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>6627</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>46389</v>
+        <v>53016</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>6585</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>46095</v>
+        <v>52680</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>6522</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>56168</v>
+        <v>62690</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>6471</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>45297</v>
+        <v>51768</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>6469</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>45283</v>
+        <v>51752</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>6468</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>45276</v>
+        <v>51744</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>49451</v>
+        <v>55759</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>6269</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>43883</v>
+        <v>50152</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>47904</v>
+        <v>54073</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>6117</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>42819</v>
+        <v>48936</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>6022</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>44507</v>
+        <v>50529</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>6014</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>43456</v>
+        <v>49470</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>46429</v>
+        <v>52356</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>46079</v>
+        <v>51970</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>5853</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>40971</v>
+        <v>46824</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>5834</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>40838</v>
+        <v>46672</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>5739</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>40173</v>
+        <v>45912</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>32679</v>
+        <v>36536</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>35225</v>
+        <v>39452</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>42894</v>
+        <v>48491</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>5400</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>37800</v>
+        <v>43200</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>5399</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>37793</v>
+        <v>43192</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>5397</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>37779</v>
+        <v>43176</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>5216</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>36512</v>
+        <v>41728</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>5176</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>36232</v>
+        <v>41408</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>39416</v>
+        <v>44590</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>5079</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>35553</v>
+        <v>40632</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>4882</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>34174</v>
+        <v>39056</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>4863</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>34041</v>
+        <v>38904</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>4853</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>33971</v>
+        <v>38824</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>4852</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>33964</v>
+        <v>38816</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>4822</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>33754</v>
+        <v>38576</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>4798</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>35153</v>
+        <v>39951</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>4794</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>38352</v>
+        <v>43146</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>4793</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>33551</v>
+        <v>38344</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>4749</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>33243</v>
+        <v>37992</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>4705</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>32935</v>
+        <v>37640</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>4703</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>32921</v>
+        <v>37624</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>4657</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>34025</v>
+        <v>38682</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>4517</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>31619</v>
+        <v>36136</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>33732</v>
+        <v>38105</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>4357</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>30499</v>
+        <v>34856</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>4313</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>30191</v>
+        <v>34504</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>4286</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>31907</v>
+        <v>36193</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>4027</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>28189</v>
+        <v>32216</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>3952</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>27664</v>
+        <v>31616</v>
       </c>
       <c r="J281" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>3927</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>31003</v>
+        <v>34871</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>3882</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>27174</v>
+        <v>31056</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>3878</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>27146</v>
+        <v>31024</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>3870</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>29340</v>
+        <v>33210</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>3764</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>26348</v>
+        <v>30112</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>3762</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>26334</v>
+        <v>30096</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28560,10 +28560,10 @@
         <v>3736</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>26152</v>
+        <v>29888</v>
       </c>
       <c r="J293" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>3723</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>29784</v>
+        <v>33507</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>3513</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>26348</v>
+        <v>29861</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>3504</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>28032</v>
+        <v>31536</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>30702</v>
+        <v>34105</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>3427</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>23989</v>
+        <v>27416</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>3376</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>23632</v>
+        <v>27008</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>3375</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>23625</v>
+        <v>27000</v>
       </c>
       <c r="J303" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>3154</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>22078</v>
+        <v>25232</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>3154</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>24861</v>
+        <v>28015</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>2911</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>23288</v>
+        <v>26199</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -32112,10 +32112,10 @@
         <v>2823</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>21173</v>
+        <v>23996</v>
       </c>
       <c r="J330" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>1968</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>15744</v>
+        <v>17712</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4907976</v>
+        <v>5477247</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>572580</v>
+        <v>598215</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2072021</v>
+        <v>2368024</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>448863</v>
+        <v>492799</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1144923</v>
+        <v>1242043</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>96829</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>774632</v>
+        <v>871461</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>521672</v>
+        <v>559827</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>680585</v>
+        <v>771151</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>87339</v>
+        <v>102129</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>709507</v>
+        <v>793715</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>82618</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>736366</v>
+        <v>818984</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>506301</v>
+        <v>547632</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>74332</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>520324</v>
+        <v>594656</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>509048</v>
+        <v>580038</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>69541</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>486787</v>
+        <v>556328</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>69234</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>484638</v>
+        <v>553872</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>65193</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>456351</v>
+        <v>521544</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>64401</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>450807</v>
+        <v>515208</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>313466</v>
+        <v>336506</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>59566</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>416962</v>
+        <v>476528</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>54825</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>383775</v>
+        <v>438600</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>502787</v>
+        <v>551673</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>53653</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>375571</v>
+        <v>429224</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>234262</v>
+        <v>260342</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>50722</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>157404</v>
+        <v>164399</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>362806</v>
+        <v>410892</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>47876</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>336377</v>
+        <v>384253</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>375808</v>
+        <v>422784</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>46318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>324226</v>
+        <v>370544</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>42364</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>296548</v>
+        <v>338912</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>82451</v>
+        <v>88334</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>40719</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>285033</v>
+        <v>325752</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>39334</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>275338</v>
+        <v>314672</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>66619</v>
+        <v>70537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>306261</v>
+        <v>344845</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>38479</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>306798</v>
+        <v>335528</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>37610</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>263270</v>
+        <v>300880</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>268006</v>
+        <v>304829</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>34868</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>244076</v>
+        <v>278944</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>295532</v>
+        <v>322836</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>239666</v>
+        <v>272729</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>243543</v>
+        <v>275708</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>239271</v>
+        <v>271174</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>31814</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>222698</v>
+        <v>254512</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>31494</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>263404</v>
+        <v>294898</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>31368</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>250944</v>
+        <v>282312</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>29237</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>204659</v>
+        <v>233896</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>181962</v>
+        <v>203887</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>102033</v>
+        <v>104962</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>28241</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>197687</v>
+        <v>225928</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>28162</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>197134</v>
+        <v>225296</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>27760</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>194320</v>
+        <v>222080</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>27645</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>193515</v>
+        <v>221160</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>81950</v>
+        <v>89758</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>27192</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>190344</v>
+        <v>217536</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>182124</v>
+        <v>195817</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>26611</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>186277</v>
+        <v>212888</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>204623</v>
+        <v>231027</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>26168</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>183176</v>
+        <v>209344</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>48721</v>
+        <v>51606</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>25401</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>177807</v>
+        <v>203208</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>182866</v>
+        <v>207986</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>24939</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>227944</v>
+        <v>252883</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>24370</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>170590</v>
+        <v>194960</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>130515</v>
+        <v>145786</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>164629</v>
+        <v>187677</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>167238</v>
+        <v>189628</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>213184</v>
+        <v>235058</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>21393</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>149751</v>
+        <v>171144</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>99545</v>
+        <v>110724</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>20958</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>146706</v>
+        <v>167664</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>156224</v>
+        <v>175752</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>150489</v>
+        <v>169240</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>19174</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>134218</v>
+        <v>153392</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>170061</v>
+        <v>189187</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>113547</v>
+        <v>127043</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>18900</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>172800</v>
+        <v>191700</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>18615</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>130305</v>
+        <v>148920</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>18215</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>145720</v>
+        <v>163935</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>17860</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>125020</v>
+        <v>142880</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>17484</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>122388</v>
+        <v>139872</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>126433</v>
+        <v>143737</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>16561</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>159824</v>
+        <v>176385</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>123072</v>
+        <v>139481</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>119231</v>
+        <v>135512</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>117629</v>
+        <v>133736</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>15997</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>111979</v>
+        <v>127976</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>15807</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>134360</v>
+        <v>150167</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>116536</v>
+        <v>132202</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>111968</v>
+        <v>127493</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>15119</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>107802</v>
+        <v>122921</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>109788</v>
+        <v>124773</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>14915</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>105628</v>
+        <v>120543</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>94957</v>
+        <v>106436</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>111092</v>
+        <v>125645</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>14396</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>100772</v>
+        <v>115168</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>95937</v>
+        <v>107587</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>14380</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>100660</v>
+        <v>115040</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>55159</v>
+        <v>61017</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>14149</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>99043</v>
+        <v>113192</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>102640</v>
+        <v>116658</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>122837</v>
+        <v>136780</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>13912</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>97384</v>
+        <v>111296</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>13666</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>34162</v>
+        <v>37090</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>13645</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>95515</v>
+        <v>109160</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>13490</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>94430</v>
+        <v>107920</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>103866</v>
+        <v>117051</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>13172</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>92204</v>
+        <v>105376</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>13093</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>58626</v>
+        <v>62681</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>13071</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>91497</v>
+        <v>104568</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>12946</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>90622</v>
+        <v>103568</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>63592</v>
+        <v>70850</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>12513</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>87591</v>
+        <v>100104</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>12156</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>29236</v>
+        <v>31676</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>12088</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>84616</v>
+        <v>96704</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>11974</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>85786</v>
+        <v>97760</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>11788</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>82516</v>
+        <v>94304</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>11763</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>82341</v>
+        <v>94104</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>77633</v>
+        <v>87043</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>11717</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>82019</v>
+        <v>93736</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>11598</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>81186</v>
+        <v>92784</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>80303</v>
+        <v>90947</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>58941</v>
+        <v>65844</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>10582</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>75413</v>
+        <v>85995</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>10432</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>73024</v>
+        <v>83456</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>10431</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>73017</v>
+        <v>83448</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>63530</v>
+        <v>71132</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>10190</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>71330</v>
+        <v>81520</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>10165</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>71155</v>
+        <v>81320</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>10127</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>28341</v>
+        <v>30943</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>73284</v>
+        <v>83350</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>72841</v>
+        <v>82898</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>9973</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>69811</v>
+        <v>79784</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>75044</v>
+        <v>84942</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>37188</v>
+        <v>41092</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>9704</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>67928</v>
+        <v>77632</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>9703</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>67921</v>
+        <v>77624</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>77440</v>
+        <v>87120</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>80523</v>
+        <v>90109</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>9586</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>67102</v>
+        <v>76688</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>9524</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>66668</v>
+        <v>76192</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>9470</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>68547</v>
+        <v>78017</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>9403</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>30025</v>
+        <v>32971</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>9348</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>65436</v>
+        <v>74784</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>49460</v>
+        <v>55211</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>9152</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>64064</v>
+        <v>73216</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>65977</v>
+        <v>74824</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>8819</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>61733</v>
+        <v>70552</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>8777</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>61439</v>
+        <v>70216</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>68066</v>
+        <v>76812</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>63646</v>
+        <v>72325</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>8653</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>60571</v>
+        <v>69224</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>8643</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>24778</v>
+        <v>27083</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>8610</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>61682</v>
+        <v>70292</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>8561</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>59927</v>
+        <v>68488</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>8399</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>29147</v>
+        <v>32111</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>8299</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>58093</v>
+        <v>66392</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>8254</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>60174</v>
+        <v>68428</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>60521</v>
+        <v>68751</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>8199</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>57393</v>
+        <v>65592</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>61919</v>
+        <v>70030</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>8010</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>56070</v>
+        <v>64080</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>7858</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>62864</v>
+        <v>70722</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>60064</v>
+        <v>67836</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>7713</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>53991</v>
+        <v>61704</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>7618</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>53326</v>
+        <v>60944</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>7594</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>53158</v>
+        <v>60752</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>7556</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>52892</v>
+        <v>60448</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>7525</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>52675</v>
+        <v>60200</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>7520</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>52640</v>
+        <v>60160</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>26647</v>
+        <v>28564</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>69418</v>
+        <v>76882</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>52921</v>
+        <v>59453</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>7074</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>49518</v>
+        <v>56592</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>54999</v>
+        <v>61858</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>6963</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>48741</v>
+        <v>55704</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>53980</v>
+        <v>60707</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>6843</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>47901</v>
+        <v>54744</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>6796</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>47572</v>
+        <v>54368</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>6771</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>47397</v>
+        <v>54168</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>6684</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>46788</v>
+        <v>53472</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>6677</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>51058</v>
+        <v>55771</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>6670</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>46690</v>
+        <v>53360</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>6662</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>46634</v>
+        <v>53296</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>6627</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>46389</v>
+        <v>53016</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>6585</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>46095</v>
+        <v>52680</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>6568</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>20302</v>
+        <v>22264</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>6522</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>56168</v>
+        <v>62690</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>6471</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>45297</v>
+        <v>51768</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>6469</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>45283</v>
+        <v>51752</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>6468</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>45276</v>
+        <v>51744</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>6357</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>30318</v>
+        <v>33741</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>49451</v>
+        <v>55759</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>6269</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>43883</v>
+        <v>50152</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>47904</v>
+        <v>54073</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>6117</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>42819</v>
+        <v>48936</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>6022</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>44507</v>
+        <v>50529</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>6014</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>43456</v>
+        <v>49470</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>46429</v>
+        <v>52356</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>46079</v>
+        <v>51970</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>5853</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>40971</v>
+        <v>46824</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>5834</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>40838</v>
+        <v>46672</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>5739</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>40173</v>
+        <v>45912</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>32679</v>
+        <v>36536</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>35225</v>
+        <v>39452</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>42894</v>
+        <v>48491</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>5400</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>37800</v>
+        <v>43200</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>5399</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>37793</v>
+        <v>43192</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>5397</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>37779</v>
+        <v>43176</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>5216</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>36512</v>
+        <v>41728</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>5176</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>36232</v>
+        <v>41408</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>39416</v>
+        <v>44590</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>5079</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>35553</v>
+        <v>40632</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>4963</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>14091</v>
+        <v>15395</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>4882</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>34174</v>
+        <v>39056</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>4863</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>34041</v>
+        <v>38904</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>4853</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>33971</v>
+        <v>38824</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>4852</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>33964</v>
+        <v>38816</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>4822</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>33754</v>
+        <v>38576</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>4798</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>35153</v>
+        <v>39951</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>4794</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>38352</v>
+        <v>43146</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>4793</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>33551</v>
+        <v>38344</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>4749</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>33243</v>
+        <v>37992</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>4705</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>32935</v>
+        <v>37640</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>4703</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>32921</v>
+        <v>37624</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>4657</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>34025</v>
+        <v>38682</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>4517</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>31619</v>
+        <v>36136</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>33732</v>
+        <v>38105</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>4357</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>30499</v>
+        <v>34856</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>4313</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>30191</v>
+        <v>34504</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>4305</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>17717</v>
+        <v>19633</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>4286</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>31907</v>
+        <v>36193</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>4027</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>28189</v>
+        <v>32216</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>3952</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>27664</v>
+        <v>31616</v>
       </c>
       <c r="J281" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>3927</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>31003</v>
+        <v>34871</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>3882</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>27174</v>
+        <v>31056</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>3878</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>27146</v>
+        <v>31024</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>3870</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>29340</v>
+        <v>33210</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>3856</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>26992</v>
+        <v>30848</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28176,10 +28176,10 @@
         <v>3775</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>26425</v>
+        <v>30200</v>
       </c>
       <c r="J289" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>3764</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>26348</v>
+        <v>30112</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>3762</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>26334</v>
+        <v>30096</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28560,10 +28560,10 @@
         <v>3736</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>26152</v>
+        <v>29888</v>
       </c>
       <c r="J293" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K293" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>3723</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>29784</v>
+        <v>33507</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>3663</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>25641</v>
+        <v>29304</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>3513</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>26348</v>
+        <v>29861</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>3504</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>28032</v>
+        <v>31536</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>30702</v>
+        <v>34105</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>3427</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>23989</v>
+        <v>27416</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>3420</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>23940</v>
+        <v>27360</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>3417</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>25383</v>
+        <v>28800</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>3376</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>23632</v>
+        <v>27008</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>3375</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>23625</v>
+        <v>27000</v>
       </c>
       <c r="J303" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>3334</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>23338</v>
+        <v>26672</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>3331</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>13565</v>
+        <v>15027</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>3321</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>26566</v>
+        <v>29887</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>3293</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>23051</v>
+        <v>26344</v>
       </c>
       <c r="J309" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
@@ -30192,10 +30192,10 @@
         <v>3198</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>24926</v>
+        <v>28030</v>
       </c>
       <c r="J310" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K310" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>3154</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>22078</v>
+        <v>25232</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>3154</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>24861</v>
+        <v>28015</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>3149</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>22043</v>
+        <v>25192</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>3101</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>22820</v>
+        <v>25637</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>3056</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>21392</v>
+        <v>24448</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>3045</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>21315</v>
+        <v>24360</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -31248,10 +31248,10 @@
         <v>2928</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>20496</v>
+        <v>23424</v>
       </c>
       <c r="J321" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K321" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>2911</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>20377</v>
+        <v>23288</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>2911</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>23288</v>
+        <v>26199</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>2879</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>20153</v>
+        <v>23032</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>2875</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>20125</v>
+        <v>23000</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>2865</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>20055</v>
+        <v>22920</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>2857</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>22380</v>
+        <v>25237</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>2857</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>19999</v>
+        <v>22856</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>2823</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>19761</v>
+        <v>22584</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32112,10 +32112,10 @@
         <v>2823</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>21173</v>
+        <v>23996</v>
       </c>
       <c r="J330" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>2822</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>19754</v>
+        <v>22576</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32400,10 +32400,10 @@
         <v>2822</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>19754</v>
+        <v>22576</v>
       </c>
       <c r="J333" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K333" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>2822</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>19754</v>
+        <v>22576</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>2821</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>19747</v>
+        <v>22568</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32880,10 +32880,10 @@
         <v>2744</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>19208</v>
+        <v>21952</v>
       </c>
       <c r="J338" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K338" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>2730</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>21640</v>
+        <v>24370</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>2717</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>19019</v>
+        <v>21736</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>2698</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>20235</v>
+        <v>22933</v>
       </c>
       <c r="J343" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>2666</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>18662</v>
+        <v>21328</v>
       </c>
       <c r="J344" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>2666</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>11969</v>
+        <v>13298</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>2530</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>17710</v>
+        <v>20240</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>2491</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>17437</v>
+        <v>19928</v>
       </c>
       <c r="J350" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>2440</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>17080</v>
+        <v>19520</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>2427</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>14670</v>
+        <v>16419</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>2425</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>16975</v>
+        <v>19400</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>2353</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>16471</v>
+        <v>18824</v>
       </c>
       <c r="J356" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>2352</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>16464</v>
+        <v>18816</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34896,10 +34896,10 @@
         <v>2348</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>12211</v>
+        <v>13620</v>
       </c>
       <c r="J359" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K359" s="2" t="inlineStr">
         <is>
@@ -35088,10 +35088,10 @@
         <v>2317</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>16219</v>
+        <v>18536</v>
       </c>
       <c r="J361" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K361" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>2287</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>16009</v>
+        <v>18296</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>2256</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>15792</v>
+        <v>18048</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>2161</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>15127</v>
+        <v>17288</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>2157</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>17256</v>
+        <v>19413</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>2156</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>15092</v>
+        <v>17248</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>2121</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>14847</v>
+        <v>16968</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>2116</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>16928</v>
+        <v>19044</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>2050</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>14350</v>
+        <v>16400</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>2025</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>15332</v>
+        <v>17357</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>1979</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>14940</v>
+        <v>16919</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36624,10 +36624,10 @@
         <v>1975</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>13825</v>
+        <v>15800</v>
       </c>
       <c r="J377" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
         <is>
@@ -36720,10 +36720,10 @@
         <v>1972</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>13804</v>
+        <v>15776</v>
       </c>
       <c r="J378" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>1968</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>15744</v>
+        <v>17712</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>1964</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>13748</v>
+        <v>15712</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>1953</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>13671</v>
+        <v>15624</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>1953</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>13671</v>
+        <v>15624</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37488,10 +37488,10 @@
         <v>1940</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>15520</v>
+        <v>17460</v>
       </c>
       <c r="J386" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>1940</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>13580</v>
+        <v>15520</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>1938</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>15504</v>
+        <v>17442</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -37968,10 +37968,10 @@
         <v>1932</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>13524</v>
+        <v>15456</v>
       </c>
       <c r="J391" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
         <is>
@@ -38256,10 +38256,10 @@
         <v>1887</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>13209</v>
+        <v>15096</v>
       </c>
       <c r="J394" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>1881</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>13167</v>
+        <v>15048</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38448,10 +38448,10 @@
         <v>1881</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>13167</v>
+        <v>15048</v>
       </c>
       <c r="J396" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
@@ -38544,10 +38544,10 @@
         <v>1878</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>13146</v>
+        <v>15024</v>
       </c>
       <c r="J397" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>1832</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>12824</v>
+        <v>14656</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>1740</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>12180</v>
+        <v>13920</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39216,10 +39216,10 @@
         <v>1714</v>
       </c>
       <c r="I404" s="2" t="n">
-        <v>12382</v>
+        <v>13906</v>
       </c>
       <c r="J404" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>1688</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>9115</v>
+        <v>10176</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>1646</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>11522</v>
+        <v>13168</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>1646</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>11522</v>
+        <v>13168</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>1641</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>12505</v>
+        <v>14057</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>1552</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>10864</v>
+        <v>12416</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>1534</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>10738</v>
+        <v>12272</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40080,10 +40080,10 @@
         <v>1476</v>
       </c>
       <c r="I413" s="2" t="n">
-        <v>10332</v>
+        <v>11808</v>
       </c>
       <c r="J413" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>1465</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>10255</v>
+        <v>11720</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40272,10 +40272,10 @@
         <v>1457</v>
       </c>
       <c r="I415" s="2" t="n">
-        <v>11269</v>
+        <v>12726</v>
       </c>
       <c r="J415" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K415" s="2" t="inlineStr">
         <is>
@@ -40560,10 +40560,10 @@
         <v>1428</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>9996</v>
+        <v>11424</v>
       </c>
       <c r="J418" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>1412</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>9884</v>
+        <v>11296</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>1411</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>9877</v>
+        <v>11288</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>1411</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>9877</v>
+        <v>11288</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -40944,10 +40944,10 @@
         <v>1401</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>9339</v>
+        <v>10473</v>
       </c>
       <c r="J422" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K422" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>1316</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>9212</v>
+        <v>10528</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>1261</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>9976</v>
+        <v>11237</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>1222</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>8554</v>
+        <v>9776</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>1158</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>8106</v>
+        <v>9264</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41904,10 +41904,10 @@
         <v>1080</v>
       </c>
       <c r="I432" s="2" t="n">
-        <v>8640</v>
+        <v>9720</v>
       </c>
       <c r="J432" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K432" s="2" t="inlineStr">
         <is>
@@ -42192,10 +42192,10 @@
         <v>1078</v>
       </c>
       <c r="I435" s="2" t="n">
-        <v>7546</v>
+        <v>8624</v>
       </c>
       <c r="J435" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K435" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>1031</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>7217</v>
+        <v>8248</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42480,10 +42480,10 @@
         <v>1001</v>
       </c>
       <c r="I438" s="2" t="n">
-        <v>7007</v>
+        <v>8008</v>
       </c>
       <c r="J438" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K438" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5477247</v>
+        <v>6046518</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>598215</v>
+        <v>623850</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2368024</v>
+        <v>2664027</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>492799</v>
+        <v>536735</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1242043</v>
+        <v>1339163</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>96829</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>871461</v>
+        <v>968290</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>559827</v>
+        <v>597982</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>771151</v>
+        <v>861717</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>102129</v>
+        <v>131709</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>793715</v>
+        <v>877923</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>82618</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>818984</v>
+        <v>901602</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>547632</v>
+        <v>588963</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>74332</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>594656</v>
+        <v>668988</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>580038</v>
+        <v>651028</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>69541</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>556328</v>
+        <v>625869</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>69234</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>553872</v>
+        <v>623106</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>65193</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>521544</v>
+        <v>586737</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>64401</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>515208</v>
+        <v>579609</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>336506</v>
+        <v>359546</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>59566</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>476528</v>
+        <v>536094</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>54825</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>438600</v>
+        <v>493425</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>551673</v>
+        <v>600559</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>53653</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>429224</v>
+        <v>482877</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>260342</v>
+        <v>286422</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>50722</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>164399</v>
+        <v>171394</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>410892</v>
+        <v>458978</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>47876</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>384253</v>
+        <v>432129</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>422784</v>
+        <v>469760</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>46318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>370544</v>
+        <v>416862</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>42364</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>338912</v>
+        <v>381276</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>88334</v>
+        <v>94217</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>40719</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>325752</v>
+        <v>366471</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>39334</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>314672</v>
+        <v>354006</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>70537</v>
+        <v>74455</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>344845</v>
+        <v>383429</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>38479</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>335528</v>
+        <v>364258</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>37610</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>300880</v>
+        <v>338490</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>304829</v>
+        <v>341652</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>34868</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>278944</v>
+        <v>313812</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>322836</v>
+        <v>350140</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>272729</v>
+        <v>305792</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>275708</v>
+        <v>307873</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>271174</v>
+        <v>303077</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>31814</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>254512</v>
+        <v>286326</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>31494</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>294898</v>
+        <v>326392</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>31368</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>282312</v>
+        <v>313680</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>29237</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>233896</v>
+        <v>263133</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>203887</v>
+        <v>225812</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>104962</v>
+        <v>107891</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>28241</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>225928</v>
+        <v>254169</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>28162</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>225296</v>
+        <v>253458</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>27760</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>222080</v>
+        <v>249840</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>27645</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>221160</v>
+        <v>248805</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>89758</v>
+        <v>97566</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>27192</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>217536</v>
+        <v>244728</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>195817</v>
+        <v>209510</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>26611</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>212888</v>
+        <v>239499</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>231027</v>
+        <v>257431</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>26168</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>209344</v>
+        <v>235512</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>51606</v>
+        <v>54491</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>25401</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>203208</v>
+        <v>228609</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>207986</v>
+        <v>233106</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>24939</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>252883</v>
+        <v>277822</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>24370</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>194960</v>
+        <v>219330</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>145786</v>
+        <v>161057</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>187677</v>
+        <v>210725</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>189628</v>
+        <v>212018</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>235058</v>
+        <v>256932</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>21393</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>171144</v>
+        <v>192537</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>110724</v>
+        <v>121903</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>20958</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>167664</v>
+        <v>188622</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>175752</v>
+        <v>195280</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>169240</v>
+        <v>187991</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>19174</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>153392</v>
+        <v>172566</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>189187</v>
+        <v>208313</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>127043</v>
+        <v>140539</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>18900</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>191700</v>
+        <v>210600</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>18615</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>148920</v>
+        <v>167535</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>18215</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>163935</v>
+        <v>182150</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>17860</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>142880</v>
+        <v>160740</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>17484</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>139872</v>
+        <v>157356</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>143737</v>
+        <v>161041</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>16561</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>176385</v>
+        <v>192946</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>139481</v>
+        <v>155890</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>135512</v>
+        <v>151793</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>133736</v>
+        <v>149843</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>15997</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>127976</v>
+        <v>143973</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>15807</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>150167</v>
+        <v>165974</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>132202</v>
+        <v>147868</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>127493</v>
+        <v>143018</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>15119</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>122921</v>
+        <v>138040</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>124773</v>
+        <v>139758</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>14915</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>120543</v>
+        <v>135458</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>106436</v>
+        <v>117915</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>125645</v>
+        <v>140198</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>14396</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>115168</v>
+        <v>129564</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>107587</v>
+        <v>119237</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>14380</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>115040</v>
+        <v>129420</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>61017</v>
+        <v>66875</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>14149</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>113192</v>
+        <v>127341</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>116658</v>
+        <v>130676</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>136780</v>
+        <v>150723</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>13912</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>111296</v>
+        <v>125208</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>13645</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>109160</v>
+        <v>122805</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>13490</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>107920</v>
+        <v>121410</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>117051</v>
+        <v>130236</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>13172</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>105376</v>
+        <v>118548</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>13093</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>62681</v>
+        <v>66736</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>13071</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>104568</v>
+        <v>117639</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>12946</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>103568</v>
+        <v>116514</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>70850</v>
+        <v>78108</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>12513</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>100104</v>
+        <v>112617</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>12088</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>96704</v>
+        <v>108792</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>11974</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>97760</v>
+        <v>109734</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>11788</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>94304</v>
+        <v>106092</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>11763</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>94104</v>
+        <v>105867</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>87043</v>
+        <v>96453</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>11717</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>93736</v>
+        <v>105453</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>11598</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>92784</v>
+        <v>104382</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>90947</v>
+        <v>101591</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>65844</v>
+        <v>72747</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>10582</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>85995</v>
+        <v>96577</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>10432</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>83456</v>
+        <v>93888</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>10431</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>83448</v>
+        <v>93879</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>71132</v>
+        <v>78734</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>10190</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>81520</v>
+        <v>91710</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>10165</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>81320</v>
+        <v>91485</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>83350</v>
+        <v>93416</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>82898</v>
+        <v>92955</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>9973</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>79784</v>
+        <v>89757</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>84942</v>
+        <v>94840</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>41092</v>
+        <v>44996</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>9704</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>77632</v>
+        <v>87336</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>9703</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>77624</v>
+        <v>87327</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>87120</v>
+        <v>96800</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>90109</v>
+        <v>99695</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>9586</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>76688</v>
+        <v>86274</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>9524</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>76192</v>
+        <v>85716</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>9470</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>78017</v>
+        <v>87487</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>9348</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>74784</v>
+        <v>84132</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>55211</v>
+        <v>60962</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>9152</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>73216</v>
+        <v>82368</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>74824</v>
+        <v>83671</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>8819</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>70552</v>
+        <v>79371</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>8777</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>70216</v>
+        <v>78993</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>76812</v>
+        <v>85558</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>72325</v>
+        <v>81004</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>8653</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>69224</v>
+        <v>77877</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>8610</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>70292</v>
+        <v>78902</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>8561</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>68488</v>
+        <v>77049</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>8299</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>66392</v>
+        <v>74691</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>8254</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>68428</v>
+        <v>76682</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>68751</v>
+        <v>76981</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>8199</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>65592</v>
+        <v>73791</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>70030</v>
+        <v>78141</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>8010</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>64080</v>
+        <v>72090</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>7858</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>70722</v>
+        <v>78580</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>67836</v>
+        <v>75608</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>7713</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>61704</v>
+        <v>69417</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>7618</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>60944</v>
+        <v>68562</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>7594</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>60752</v>
+        <v>68346</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>7556</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>60448</v>
+        <v>68004</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>7525</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>60200</v>
+        <v>67725</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>7520</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>60160</v>
+        <v>67680</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>28564</v>
+        <v>30481</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>76882</v>
+        <v>84346</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>59453</v>
+        <v>65985</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>7074</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>56592</v>
+        <v>63666</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>61858</v>
+        <v>68717</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>6963</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>55704</v>
+        <v>62667</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>60707</v>
+        <v>67434</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>6843</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>54744</v>
+        <v>61587</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>6796</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>54368</v>
+        <v>61164</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>6771</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>54168</v>
+        <v>60939</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>6684</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>53472</v>
+        <v>60156</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>6677</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>55771</v>
+        <v>60484</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>6670</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>53360</v>
+        <v>60030</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>6662</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>53296</v>
+        <v>59958</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>6627</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>53016</v>
+        <v>59643</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>6585</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>52680</v>
+        <v>59265</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>6522</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>62690</v>
+        <v>69212</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>6471</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>51768</v>
+        <v>58239</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>6469</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>51752</v>
+        <v>58221</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>6468</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>51744</v>
+        <v>58212</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>6357</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>33741</v>
+        <v>37164</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>55759</v>
+        <v>62067</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>6269</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>50152</v>
+        <v>56421</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>54073</v>
+        <v>60242</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>6117</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>48936</v>
+        <v>55053</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>6022</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>50529</v>
+        <v>56551</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>6014</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>49470</v>
+        <v>55484</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>52356</v>
+        <v>58283</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>51970</v>
+        <v>57861</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>5853</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>46824</v>
+        <v>52677</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>5834</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>46672</v>
+        <v>52506</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>5739</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>45912</v>
+        <v>51651</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>36536</v>
+        <v>40393</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>39452</v>
+        <v>43679</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>48491</v>
+        <v>54088</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>5400</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>43200</v>
+        <v>48600</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>5399</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>43192</v>
+        <v>48591</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>5397</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>43176</v>
+        <v>48573</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>5216</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>41728</v>
+        <v>46944</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>5176</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>41408</v>
+        <v>46584</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>44590</v>
+        <v>49764</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>5079</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>40632</v>
+        <v>45711</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>4882</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>39056</v>
+        <v>43938</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>4863</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>38904</v>
+        <v>43767</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>4853</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>38824</v>
+        <v>43677</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>4852</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>38816</v>
+        <v>43668</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>4822</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>38576</v>
+        <v>43398</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>4798</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>39951</v>
+        <v>44749</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>4794</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>43146</v>
+        <v>47940</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>4793</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>38344</v>
+        <v>43137</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>4749</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>37992</v>
+        <v>42741</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>4705</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>37640</v>
+        <v>42345</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>4703</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>37624</v>
+        <v>42327</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>4657</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>38682</v>
+        <v>43339</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>4517</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>36136</v>
+        <v>40653</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>38105</v>
+        <v>42478</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>4357</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>34856</v>
+        <v>39213</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>4313</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>34504</v>
+        <v>38817</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>4286</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>36193</v>
+        <v>40479</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>4027</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>32216</v>
+        <v>36243</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>3952</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>31616</v>
+        <v>35568</v>
       </c>
       <c r="J281" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>3927</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>34871</v>
+        <v>38739</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>3882</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>31056</v>
+        <v>34938</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>3878</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>31024</v>
+        <v>34902</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>3870</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>33210</v>
+        <v>37080</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>3856</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>30848</v>
+        <v>34704</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>3764</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>30112</v>
+        <v>33876</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>3762</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>30096</v>
+        <v>33858</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>3723</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>33507</v>
+        <v>37230</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>3513</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>29861</v>
+        <v>33374</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>3504</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>31536</v>
+        <v>35040</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>34105</v>
+        <v>37508</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>3420</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>27360</v>
+        <v>30780</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>3417</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>28800</v>
+        <v>32217</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>3334</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>26672</v>
+        <v>30006</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>3321</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>29887</v>
+        <v>33208</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>3154</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>25232</v>
+        <v>28386</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>3101</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>25637</v>
+        <v>28454</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>1968</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>17712</v>
+        <v>19680</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6046518</v>
+        <v>6615789</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>623850</v>
+        <v>649485</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2664027</v>
+        <v>2960030</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>141311</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>536735</v>
+        <v>580671</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>98720</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1339163</v>
+        <v>1436283</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>96829</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>968290</v>
+        <v>1065119</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>94083</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>597982</v>
+        <v>636137</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>90566</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>861717</v>
+        <v>952283</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>87339</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>131709</v>
+        <v>146499</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>84208</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>877923</v>
+        <v>962131</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>82618</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>901602</v>
+        <v>984220</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>75729</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>588963</v>
+        <v>630294</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>74332</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>668988</v>
+        <v>743320</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>70990</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>651028</v>
+        <v>722018</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>69541</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>625869</v>
+        <v>695410</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>69234</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>623106</v>
+        <v>692340</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>65193</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>586737</v>
+        <v>651930</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>64401</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>579609</v>
+        <v>644010</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>62983</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>359546</v>
+        <v>382586</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>59566</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>536094</v>
+        <v>595660</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>54825</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>493425</v>
+        <v>548250</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>53890</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>600559</v>
+        <v>649445</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>53653</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>482877</v>
+        <v>536530</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>51702</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>286422</v>
+        <v>312502</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>50722</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>171394</v>
+        <v>178389</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>48086</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>458978</v>
+        <v>507064</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>47876</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>432129</v>
+        <v>480005</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>46976</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>469760</v>
+        <v>516736</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>46318</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>416862</v>
+        <v>463180</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>42364</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>381276</v>
+        <v>423640</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>41270</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>94217</v>
+        <v>100100</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>40719</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>366471</v>
+        <v>407190</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>39334</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>354006</v>
+        <v>393340</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>39193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>74455</v>
+        <v>78373</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>38584</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>383429</v>
+        <v>422013</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>38479</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>364258</v>
+        <v>392988</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>37610</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>338490</v>
+        <v>376100</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>36823</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>341652</v>
+        <v>378475</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>34868</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>313812</v>
+        <v>348680</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>33180</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>350140</v>
+        <v>377444</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>33063</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>305792</v>
+        <v>338855</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>32165</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>307873</v>
+        <v>340038</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>31903</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>303077</v>
+        <v>334980</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>31814</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>286326</v>
+        <v>318140</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>31494</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>326392</v>
+        <v>357886</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>31368</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>313680</v>
+        <v>345048</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>29237</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>263133</v>
+        <v>292370</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>28487</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>225812</v>
+        <v>247737</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>28316</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107891</v>
+        <v>110820</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>28241</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>254169</v>
+        <v>282410</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>28162</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>253458</v>
+        <v>281620</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>27760</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>249840</v>
+        <v>277600</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>27645</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>248805</v>
+        <v>276450</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>27294</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>97566</v>
+        <v>105374</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>27192</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>244728</v>
+        <v>271920</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>26961</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>209510</v>
+        <v>223203</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>26611</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>239499</v>
+        <v>266110</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>26404</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>257431</v>
+        <v>283835</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>26168</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>235512</v>
+        <v>261680</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>25641</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>54491</v>
+        <v>57376</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>25401</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>228609</v>
+        <v>254010</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>25120</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>233106</v>
+        <v>258226</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>24939</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>277822</v>
+        <v>302761</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>24370</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>219330</v>
+        <v>243700</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>23618</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>161057</v>
+        <v>176328</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>23048</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>210725</v>
+        <v>233773</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>22390</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>212018</v>
+        <v>234408</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>21874</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>256932</v>
+        <v>278806</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>21393</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>192537</v>
+        <v>213930</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>21292</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>121903</v>
+        <v>133082</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>20958</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>188622</v>
+        <v>209580</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>19528</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>195280</v>
+        <v>214808</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>19232</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>187991</v>
+        <v>206742</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>19174</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>172566</v>
+        <v>191740</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>19126</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>208313</v>
+        <v>227439</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>19075</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>140539</v>
+        <v>154035</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>18900</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>210600</v>
+        <v>229500</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>18615</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>167535</v>
+        <v>186150</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>18215</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>182150</v>
+        <v>200365</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>17860</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>160740</v>
+        <v>178600</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>17484</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>157356</v>
+        <v>174840</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>17304</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>161041</v>
+        <v>178345</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>16561</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>192946</v>
+        <v>209507</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>16409</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>155890</v>
+        <v>172299</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>16281</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>151793</v>
+        <v>168074</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>16107</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>149843</v>
+        <v>165950</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>15997</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>143973</v>
+        <v>159970</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>15807</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>165974</v>
+        <v>181781</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>15666</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>147868</v>
+        <v>163534</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>15525</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>143018</v>
+        <v>158543</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>15119</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>138040</v>
+        <v>153159</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>14985</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>139758</v>
+        <v>154743</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>14915</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>135458</v>
+        <v>150373</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>14604</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>117915</v>
+        <v>129394</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>14553</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>140198</v>
+        <v>154751</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>14396</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>129564</v>
+        <v>143960</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>14387</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>119237</v>
+        <v>130887</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>14380</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>129420</v>
+        <v>143800</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>14153</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>66875</v>
+        <v>72733</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>14149</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>127341</v>
+        <v>141490</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>14018</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>130676</v>
+        <v>144694</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>13943</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>150723</v>
+        <v>164666</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>13912</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>125208</v>
+        <v>139120</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>13645</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>122805</v>
+        <v>136450</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>13490</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>121410</v>
+        <v>134900</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>13185</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>130236</v>
+        <v>143421</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>13172</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>118548</v>
+        <v>131720</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>13093</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>66736</v>
+        <v>70791</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>13071</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>117639</v>
+        <v>130710</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>12946</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>116514</v>
+        <v>129460</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>12786</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>78108</v>
+        <v>85366</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>12513</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>112617</v>
+        <v>125130</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>12088</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>108792</v>
+        <v>120880</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>11974</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>109734</v>
+        <v>121708</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>11788</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>106092</v>
+        <v>117880</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>11763</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>105867</v>
+        <v>117630</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>11763</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>96453</v>
+        <v>105863</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>11717</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>105453</v>
+        <v>117170</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>11598</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>104382</v>
+        <v>115980</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>10644</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>101591</v>
+        <v>112235</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>10620</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>72747</v>
+        <v>79650</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>10582</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>96577</v>
+        <v>107159</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>10432</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>93888</v>
+        <v>104320</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>10431</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>93879</v>
+        <v>104310</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>10316</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>78734</v>
+        <v>86336</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>10190</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>91710</v>
+        <v>101900</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>10165</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>91485</v>
+        <v>101650</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>10066</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>93416</v>
+        <v>103482</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>10057</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>92955</v>
+        <v>103012</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>9973</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>89757</v>
+        <v>99730</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>9898</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>94840</v>
+        <v>104738</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>9860</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>44996</v>
+        <v>48900</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>9704</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>87336</v>
+        <v>97040</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>9703</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>87327</v>
+        <v>97030</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>9680</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>96800</v>
+        <v>106480</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>9586</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>99695</v>
+        <v>109281</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>9586</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>86274</v>
+        <v>95860</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>9524</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>85716</v>
+        <v>95240</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>9470</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>87487</v>
+        <v>96957</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>9403</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>32971</v>
+        <v>35917</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>9348</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>84132</v>
+        <v>93480</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>9203</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>60962</v>
+        <v>66713</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>9152</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>82368</v>
+        <v>91520</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>8847</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>83671</v>
+        <v>92518</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>8819</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>79371</v>
+        <v>88190</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>8777</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>78993</v>
+        <v>87770</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>8746</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>85558</v>
+        <v>94304</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>8679</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>81004</v>
+        <v>89683</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>8653</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>77877</v>
+        <v>86530</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>8610</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>78902</v>
+        <v>87512</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>8561</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>77049</v>
+        <v>85610</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>8299</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>74691</v>
+        <v>82990</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>8254</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>76682</v>
+        <v>84936</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>8230</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>76981</v>
+        <v>85211</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>8199</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>73791</v>
+        <v>81990</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>8111</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>78141</v>
+        <v>86252</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>8010</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>72090</v>
+        <v>80100</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>7858</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>78580</v>
+        <v>86438</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>7772</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>75608</v>
+        <v>83380</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>7713</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>69417</v>
+        <v>77130</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>7618</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>68562</v>
+        <v>76180</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>7594</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>68346</v>
+        <v>75940</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>7556</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>68004</v>
+        <v>75560</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>7525</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>67725</v>
+        <v>75250</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>7520</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>67680</v>
+        <v>75200</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>7477</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>30481</v>
+        <v>32398</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>7464</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>84346</v>
+        <v>91810</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>7197</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>65985</v>
+        <v>72517</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>7074</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>63666</v>
+        <v>70740</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>6986</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>68717</v>
+        <v>75576</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>6963</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>62667</v>
+        <v>69630</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>6891</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>67434</v>
+        <v>74161</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>6843</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>61587</v>
+        <v>68430</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>6796</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>61164</v>
+        <v>67960</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>6771</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>60939</v>
+        <v>67710</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>6684</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>60156</v>
+        <v>66840</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>6677</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>60484</v>
+        <v>65197</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>6670</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>60030</v>
+        <v>66700</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>6662</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>59958</v>
+        <v>66620</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>6627</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>59643</v>
+        <v>66270</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>6585</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>59265</v>
+        <v>65850</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>6522</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>69212</v>
+        <v>75734</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>6471</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>58239</v>
+        <v>64710</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>6469</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>58221</v>
+        <v>64690</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>6468</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>58212</v>
+        <v>64680</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>6357</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>37164</v>
+        <v>40587</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>6308</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>62067</v>
+        <v>68375</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>6269</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>56421</v>
+        <v>62690</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>6169</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>60242</v>
+        <v>66411</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>6117</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>55053</v>
+        <v>61170</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>6022</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>56551</v>
+        <v>62573</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>6014</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>55484</v>
+        <v>61498</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>5927</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>58283</v>
+        <v>64210</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>5891</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>57861</v>
+        <v>63752</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>5853</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>52677</v>
+        <v>58530</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>5834</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>52506</v>
+        <v>58340</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>5739</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>51651</v>
+        <v>57390</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>5680</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>40393</v>
+        <v>44250</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>5636</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>43679</v>
+        <v>47906</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>5597</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>54088</v>
+        <v>59685</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>5400</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>48600</v>
+        <v>54000</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>5399</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>48591</v>
+        <v>53990</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>5397</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>48573</v>
+        <v>53970</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>5216</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>46944</v>
+        <v>52160</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>5176</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>46584</v>
+        <v>51760</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>5174</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>49764</v>
+        <v>54938</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>5079</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>45711</v>
+        <v>50790</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>4882</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>43938</v>
+        <v>48820</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>4863</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>43767</v>
+        <v>48630</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>4853</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>43677</v>
+        <v>48530</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>4852</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>43668</v>
+        <v>48520</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>4822</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>43398</v>
+        <v>48220</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>4798</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>44749</v>
+        <v>49547</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>4794</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>47940</v>
+        <v>52734</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>4793</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>43137</v>
+        <v>47930</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>4749</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>42741</v>
+        <v>47490</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>4705</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>42345</v>
+        <v>47050</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>4703</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>42327</v>
+        <v>47030</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>4657</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>43339</v>
+        <v>47996</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>4517</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>40653</v>
+        <v>45170</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>4373</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>42478</v>
+        <v>46851</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>4357</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>39213</v>
+        <v>43570</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>4313</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>38817</v>
+        <v>43130</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>4286</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>40479</v>
+        <v>44765</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>4027</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>36243</v>
+        <v>40270</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>3952</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>35568</v>
+        <v>39520</v>
       </c>
       <c r="J281" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K281" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>3882</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>34938</v>
+        <v>38820</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>3878</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>34902</v>
+        <v>38780</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>3856</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>34704</v>
+        <v>38560</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28176,10 +28176,10 @@
         <v>3775</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>30200</v>
+        <v>33975</v>
       </c>
       <c r="J289" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>3764</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>33876</v>
+        <v>37640</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>3762</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>33858</v>
+        <v>37620</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>3723</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>37230</v>
+        <v>40953</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>3663</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>29304</v>
+        <v>32967</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>3513</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>33374</v>
+        <v>36887</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>3504</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>35040</v>
+        <v>38544</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>3478</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>37508</v>
+        <v>40911</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>3420</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>30780</v>
+        <v>34200</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>3321</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>33208</v>
+        <v>36529</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>3045</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>24360</v>
+        <v>27405</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>1968</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>19680</v>
+        <v>21648</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6280852</v>
+        <v>6515186</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2664027</v>
+        <v>2960030</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>158965</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>158965</v>
+        <v>317930</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>141311</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>536735</v>
+        <v>580671</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>106106</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>135044</v>
+        <v>241150</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>98720</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1369280</v>
+        <v>1399397</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>96829</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>968290</v>
+        <v>1065119</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>94083</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>628236</v>
+        <v>658490</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>93178</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>682141</v>
+        <v>775319</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>87339</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>131709</v>
+        <v>146499</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>84208</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>907171</v>
+        <v>936419</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>82618</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>901602</v>
+        <v>984220</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>74332</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>668988</v>
+        <v>743320</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>69234</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>623106</v>
+        <v>692340</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>62983</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>359546</v>
+        <v>382586</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>59566</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>536094</v>
+        <v>595660</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>54825</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>493425</v>
+        <v>548250</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>53890</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>622116</v>
+        <v>643673</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>50722</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>171394</v>
+        <v>178389</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>48086</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>458978</v>
+        <v>507064</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>46976</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>469760</v>
+        <v>516736</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>39193</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>74455</v>
+        <v>78373</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>38584</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>383429</v>
+        <v>422013</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>38479</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>364258</v>
+        <v>392988</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>37610</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>338490</v>
+        <v>376100</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>36823</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>341652</v>
+        <v>378475</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>34868</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>313812</v>
+        <v>348680</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>33180</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>374479</v>
+        <v>398818</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>31814</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>286326</v>
+        <v>318140</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>31494</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>326392</v>
+        <v>357886</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>31368</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>323762</v>
+        <v>333844</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>28316</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>121313</v>
+        <v>134735</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>27760</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>249840</v>
+        <v>277600</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>27645</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>248805</v>
+        <v>276450</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>27192</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>244728</v>
+        <v>271920</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>26961</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>213463</v>
+        <v>217416</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>26611</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>239499</v>
+        <v>266110</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>26168</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>235512</v>
+        <v>261680</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>25641</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>57440</v>
+        <v>60389</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>25401</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>228609</v>
+        <v>254010</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>24939</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>277822</v>
+        <v>302761</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>24370</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>219330</v>
+        <v>243700</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>23048</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>210725</v>
+        <v>233773</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>21874</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>262726</v>
+        <v>268520</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>21393</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>192537</v>
+        <v>213930</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>21292</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>121903</v>
+        <v>133082</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>20138</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>43169</v>
+        <v>46062</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>19528</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>195280</v>
+        <v>214808</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>19174</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>172566</v>
+        <v>191740</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>19126</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>208313</v>
+        <v>227439</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>18900</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>229420</v>
+        <v>248240</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>18615</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>167535</v>
+        <v>186150</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>18215</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>182150</v>
+        <v>200365</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>17860</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>160740</v>
+        <v>178600</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>17282</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>40324</v>
+        <v>57606</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>16561</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>192946</v>
+        <v>209507</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>15807</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>165974</v>
+        <v>181781</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>14915</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>135458</v>
+        <v>150373</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>14396</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>129564</v>
+        <v>143960</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>14380</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>129420</v>
+        <v>143800</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>13943</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>150723</v>
+        <v>164666</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>13912</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>125208</v>
+        <v>139120</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>13490</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>121410</v>
+        <v>134900</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>13172</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>118548</v>
+        <v>131720</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>13093</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>70559</v>
+        <v>74382</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>13071</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>117639</v>
+        <v>130710</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>12088</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>108792</v>
+        <v>120880</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>11977</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>30403</v>
+        <v>42380</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>11974</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>109734</v>
+        <v>121708</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>11788</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>106092</v>
+        <v>117880</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>11763</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>105867</v>
+        <v>117630</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>10582</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>96577</v>
+        <v>107159</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>10432</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>93888</v>
+        <v>104320</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>10316</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>78734</v>
+        <v>86336</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>10190</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>91710</v>
+        <v>101900</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>10165</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>91485</v>
+        <v>101650</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>9704</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>87336</v>
+        <v>97040</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>9703</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>87327</v>
+        <v>97030</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>9586</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>102379</v>
+        <v>105063</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>9586</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>86274</v>
+        <v>95860</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>9348</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>84132</v>
+        <v>93480</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>9152</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>82368</v>
+        <v>91520</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>8847</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>83671</v>
+        <v>92518</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>8819</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>79371</v>
+        <v>88190</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>8777</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>78993</v>
+        <v>87770</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>8679</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>81004</v>
+        <v>89683</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>8561</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>77049</v>
+        <v>85610</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>8299</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>74691</v>
+        <v>82990</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>8254</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>76682</v>
+        <v>84936</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>8199</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>73791</v>
+        <v>81990</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>8010</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>72090</v>
+        <v>80100</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>7858</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>78580</v>
+        <v>86438</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>7772</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>75608</v>
+        <v>83380</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>7762</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>21275</v>
+        <v>27026</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>7713</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>69417</v>
+        <v>77130</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>7594</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>68346</v>
+        <v>75940</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>7525</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>67725</v>
+        <v>75250</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>7520</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>67680</v>
+        <v>75200</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>7477</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>30481</v>
+        <v>32398</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>7464</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>88307</v>
+        <v>92268</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>6891</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>67434</v>
+        <v>74161</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>6677</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>64412</v>
+        <v>68340</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24336,10 +24336,10 @@
         <v>6670</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>60030</v>
+        <v>66700</v>
       </c>
       <c r="J249" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K249" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>6627</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>59643</v>
+        <v>66270</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24624,10 +24624,10 @@
         <v>6585</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>59265</v>
+        <v>65850</v>
       </c>
       <c r="J252" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>6522</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>71612</v>
+        <v>74012</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>6471</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>58239</v>
+        <v>64710</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>6468</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>58212</v>
+        <v>64680</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>6357</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>37164</v>
+        <v>40587</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>6269</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>56421</v>
+        <v>62690</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>6117</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>55053</v>
+        <v>61170</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>5927</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>58283</v>
+        <v>64210</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>5853</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>52677</v>
+        <v>58530</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>5739</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>51651</v>
+        <v>57390</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>5680</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>40393</v>
+        <v>44250</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>5400</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>48600</v>
+        <v>54000</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>5397</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>48573</v>
+        <v>53970</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28176,10 +28176,10 @@
         <v>5216</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>46944</v>
+        <v>52160</v>
       </c>
       <c r="J289" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K289" s="2" t="inlineStr">
         <is>
@@ -28368,10 +28368,10 @@
         <v>5176</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>46584</v>
+        <v>51760</v>
       </c>
       <c r="J291" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K291" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>5174</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>49764</v>
+        <v>54938</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>5079</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>45711</v>
+        <v>50790</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>4882</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>11228</v>
+        <v>12692</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>4882</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>43938</v>
+        <v>48820</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>4863</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>43767</v>
+        <v>48630</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>4822</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>43398</v>
+        <v>48220</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>4798</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>44749</v>
+        <v>49547</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>4794</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>47940</v>
+        <v>52734</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>4793</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>43137</v>
+        <v>47930</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>4749</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>42741</v>
+        <v>47490</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>4705</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>42345</v>
+        <v>47050</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>4657</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>43339</v>
+        <v>47996</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -30864,10 +30864,10 @@
         <v>4517</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>40653</v>
+        <v>45170</v>
       </c>
       <c r="J317" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K317" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>4027</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>36243</v>
+        <v>40270</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>3952</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>35568</v>
+        <v>39520</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -32112,10 +32112,10 @@
         <v>3882</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>34938</v>
+        <v>38820</v>
       </c>
       <c r="J330" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K330" s="2" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>3878</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>34902</v>
+        <v>38780</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>3856</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>34704</v>
+        <v>38560</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>3775</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>30200</v>
+        <v>33975</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32688,10 +32688,10 @@
         <v>3764</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>33876</v>
+        <v>37640</v>
       </c>
       <c r="J336" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K336" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>3723</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>37230</v>
+        <v>40953</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>3663</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>29304</v>
+        <v>32967</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>3504</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>38544</v>
+        <v>42048</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>3478</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>40986</v>
+        <v>44464</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>3420</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>30780</v>
+        <v>34200</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>3301</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>8311</v>
+        <v>11612</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>1968</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>19680</v>
+        <v>21648</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6515186</v>
+        <v>6749520</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>158965</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>317930</v>
+        <v>476895</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>106106</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>241150</v>
+        <v>347256</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>98720</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1399397</v>
+        <v>1429514</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>94083</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>658490</v>
+        <v>688744</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>93178</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>775319</v>
+        <v>868497</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>84208</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>936419</v>
+        <v>965667</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>53890</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>643673</v>
+        <v>665230</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>33180</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>398818</v>
+        <v>423157</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>31368</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>333844</v>
+        <v>343926</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>28316</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>134735</v>
+        <v>148157</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>26961</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>217416</v>
+        <v>221369</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>25641</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>60389</v>
+        <v>63338</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>21874</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>268520</v>
+        <v>274314</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>20138</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46062</v>
+        <v>48955</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>18900</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>248240</v>
+        <v>267060</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>17282</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>57606</v>
+        <v>74888</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>13093</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>74382</v>
+        <v>78205</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>11977</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>42380</v>
+        <v>54357</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>9586</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>105063</v>
+        <v>107747</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>7762</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>27026</v>
+        <v>32777</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>7464</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>92268</v>
+        <v>96229</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>6677</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>68340</v>
+        <v>72268</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>6522</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>74012</v>
+        <v>76412</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>4882</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>12692</v>
+        <v>14156</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>3504</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>42048</v>
+        <v>45552</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>3478</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>44464</v>
+        <v>47942</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>3301</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>11612</v>
+        <v>14913</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6616634</v>
+        <v>6952416</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>276355</v>
+        <v>393745</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>833619</v>
+        <v>985097</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1516340</v>
+        <v>1663400</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>759728</v>
+        <v>891220</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>146949</v>
+        <v>253574</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>207212</v>
+        <v>279380</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>955709</v>
+        <v>1004247</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>994042</v>
+        <v>1003864</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>310180</v>
+        <v>390940</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>459005</v>
+        <v>535424</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>665569</v>
+        <v>709022</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>53631</v>
+        <v>107262</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>421311</v>
+        <v>468143</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>421718</v>
+        <v>450448</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>361808</v>
+        <v>399854</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>363613</v>
+        <v>369340</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>257165</v>
+        <v>286891</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>28316</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>121313</v>
+        <v>148157</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>221369</v>
+        <v>229275</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>69235</v>
+        <v>81030</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>307935</v>
+        <v>313109</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>280795</v>
+        <v>298864</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>54980</v>
+        <v>66791</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>47630</v>
+        <v>74114</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>15316</v>
+        <v>30632</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>84872</v>
+        <v>99185</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>172796</v>
+        <v>281180</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>175003</v>
+        <v>185340</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>46447</v>
+        <v>55740</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>43280</v>
+        <v>56157</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>100610</v>
+        <v>112913</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>9586</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>102379</v>
+        <v>107747</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>7762</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>21275</v>
+        <v>32777</v>
       </c>
       <c r="J286" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>6522</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>71612</v>
+        <v>76412</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>6286</v>
+        <v>12572</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>8340</v>
+        <v>14566</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>5432</v>
+        <v>10864</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>45930</v>
+        <v>50874</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>16109</v>
+        <v>20990</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>44895</v>
+        <v>48837</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>3928</v>
+        <v>7856</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -41328,10 +41328,10 @@
         <v>3504</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>38544</v>
+        <v>45552</v>
       </c>
       <c r="J426" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K426" s="2" t="inlineStr">
         <is>
@@ -42672,10 +42672,10 @@
         <v>3301</v>
       </c>
       <c r="I440" s="2" t="n">
-        <v>8311</v>
+        <v>14913</v>
       </c>
       <c r="J440" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K440" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>2353</v>
+        <v>4706</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6952416</v>
+        <v>7288198</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>946886</v>
+        <v>969890</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2995288</v>
+        <v>3030546</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>262055</v>
+        <v>473578</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>393745</v>
+        <v>511135</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>985097</v>
+        <v>1136575</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1663400</v>
+        <v>1810460</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>672674</v>
+        <v>764677</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>782968</v>
+        <v>919687</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>891220</v>
+        <v>1022712</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>256063</v>
+        <v>370257</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>253574</v>
+        <v>360199</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>279380</v>
+        <v>351548</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>126578</v>
+        <v>228746</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1027788</v>
+        <v>1127274</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>610689</v>
+        <v>704642</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>431444</v>
+        <v>488420</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1004247</v>
+        <v>1052785</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1003864</v>
+        <v>1013686</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>390940</v>
+        <v>471700</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>535931</v>
+        <v>616670</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>140657</v>
+        <v>244621</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>535424</v>
+        <v>611843</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>750895</v>
+        <v>758470</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>763686</v>
+        <v>817110</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>406758</v>
+        <v>440935</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>717863</v>
+        <v>743386</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>216907</v>
+        <v>225156</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>607229</v>
+        <v>623044</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>487124</v>
+        <v>552235</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>585933</v>
+        <v>589095</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>604768</v>
+        <v>613876</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>304257</v>
+        <v>360919</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>709022</v>
+        <v>752475</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>576838</v>
+        <v>622829</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>107262</v>
+        <v>160893</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>129883</v>
+        <v>180753</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>535869</v>
+        <v>564674</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>461121</v>
+        <v>482270</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>468143</v>
+        <v>514975</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>316982</v>
+        <v>360977</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>284397</v>
+        <v>328247</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>94342</v>
+        <v>100154</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>208509</v>
+        <v>251556</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>429171</v>
+        <v>459110</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>86567</v>
+        <v>98863</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>108697</v>
+        <v>117408</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>422558</v>
+        <v>457261</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>364734</v>
+        <v>371886</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>84645</v>
+        <v>90917</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>311093</v>
+        <v>350266</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>41044</v>
+        <v>79632</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>450448</v>
+        <v>479178</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>399854</v>
+        <v>437900</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>389362</v>
+        <v>402624</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>129008</v>
+        <v>165048</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>269837</v>
+        <v>305901</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>178579</v>
+        <v>214414</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>353591</v>
+        <v>358502</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>39103</v>
+        <v>43590</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>156692</v>
+        <v>191026</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>33769</v>
+        <v>67538</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>317299</v>
+        <v>350843</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>321036</v>
+        <v>329699</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>353761</v>
+        <v>385828</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>328816</v>
+        <v>339492</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>31499</v>
+        <v>62998</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>369340</v>
+        <v>375067</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>286891</v>
+        <v>316617</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>138952</v>
+        <v>168545</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>277511</v>
+        <v>287096</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>133686</v>
+        <v>152967</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>148133</v>
+        <v>176452</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>280051</v>
+        <v>298319</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>284796</v>
+        <v>293142</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>54013</v>
+        <v>80455</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>38305</v>
+        <v>65806</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>120990</v>
+        <v>140509</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>52640</v>
+        <v>79698</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>229275</v>
+        <v>237181</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>183002</v>
+        <v>209816</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26555</v>
+        <v>53110</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27806</v>
+        <v>54092</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>188471</v>
+        <v>214705</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>279143</v>
+        <v>296606</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>25871</v>
+        <v>51742</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>81030</v>
+        <v>92825</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>255514</v>
+        <v>257018</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>253053</v>
+        <v>257933</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>313109</v>
+        <v>318283</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>175234</v>
+        <v>186244</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>105902</v>
+        <v>126267</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>255219</v>
+        <v>266738</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>47115</v>
+        <v>60631</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46003</v>
+        <v>69241</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>298864</v>
+        <v>316933</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>224864</v>
+        <v>239965</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>108626</v>
+        <v>130357</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>21730</v>
+        <v>43460</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>128051</v>
+        <v>132794</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>99431</v>
+        <v>121024</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>123046</v>
+        <v>144442</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>21379</v>
+        <v>42758</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>149128</v>
+        <v>165174</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>21220</v>
+        <v>42440</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>196432</v>
+        <v>200337</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20381</v>
+        <v>40762</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>66791</v>
+        <v>78602</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>166282</v>
+        <v>186232</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>115992</v>
+        <v>135746</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>61704</v>
+        <v>76246</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>125982</v>
+        <v>135662</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>123724</v>
+        <v>143128</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>57831</v>
+        <v>77102</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>67103</v>
+        <v>86276</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>19172</v>
+        <v>38344</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>161412</v>
+        <v>167710</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>44114</v>
+        <v>63036</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>194796</v>
+        <v>203442</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>74114</v>
+        <v>100598</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>81417</v>
+        <v>99934</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>162426</v>
+        <v>180892</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>120161</v>
+        <v>138422</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>43192</v>
+        <v>46067</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>92278</v>
+        <v>110074</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>26600</v>
+        <v>35420</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>51647</v>
+        <v>53101</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>169433</v>
+        <v>172809</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>50630</v>
+        <v>67920</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>110074</v>
+        <v>126997</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>125283</v>
+        <v>142132</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>57174</v>
+        <v>73761</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>32314</v>
+        <v>48875</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>35937</v>
+        <v>38812</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>39771</v>
+        <v>56265</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>16436</v>
+        <v>32872</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>162711</v>
+        <v>170997</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>41152</v>
+        <v>44892</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>79187</v>
+        <v>95384</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>103678</v>
+        <v>119844</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>51581</v>
+        <v>66313</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>17966</v>
+        <v>33979</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>148683</v>
+        <v>164210</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>155718</v>
+        <v>165596</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>30632</v>
+        <v>45948</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>17028</v>
+        <v>32103</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>49271</v>
+        <v>64224</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>152584</v>
+        <v>154795</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>14468</v>
+        <v>28936</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>99185</v>
+        <v>113498</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>83470</v>
+        <v>92257</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>141807</v>
+        <v>151451</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>18345</v>
+        <v>22579</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>281180</v>
+        <v>389564</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>143685</v>
+        <v>151756</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>185340</v>
+        <v>195677</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>144368</v>
+        <v>149616</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>33268</v>
+        <v>37052</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>16917</v>
+        <v>20066</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>55740</v>
+        <v>65033</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>54660</v>
+        <v>68325</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>33093</v>
+        <v>46656</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>131405</v>
+        <v>144930</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>56857</v>
+        <v>70090</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>134542</v>
+        <v>137364</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>56157</v>
+        <v>69034</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>87785</v>
+        <v>93740</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>12715</v>
+        <v>25430</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>44906</v>
+        <v>57595</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>34939</v>
+        <v>47614</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>12600</v>
+        <v>25200</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>120338</v>
+        <v>122238</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>12340</v>
+        <v>24680</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>112913</v>
+        <v>125216</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>132208</v>
+        <v>142708</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>106522</v>
+        <v>111886</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>32923</v>
+        <v>42450</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>23413</v>
+        <v>35041</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>108262</v>
+        <v>110178</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>11519</v>
+        <v>23038</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>44251</v>
+        <v>55535</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>74589</v>
+        <v>77947</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>10985</v>
+        <v>21970</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>74721</v>
+        <v>85361</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>109433</v>
+        <v>111707</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>62107</v>
+        <v>72650</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>22806</v>
+        <v>32996</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>98380</v>
+        <v>101114</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>92860</v>
+        <v>94742</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>105645</v>
+        <v>110555</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>105741</v>
+        <v>115622</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>9878</v>
+        <v>19756</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>14401</v>
+        <v>24215</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>9793</v>
+        <v>19586</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>9762</v>
+        <v>19524</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>69549</v>
+        <v>79261</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>97416</v>
+        <v>107062</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>96757</v>
+        <v>106362</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>49857</v>
+        <v>59444</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>77933</v>
+        <v>84776</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>95159</v>
+        <v>99674</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>23804</v>
+        <v>39307</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>17519</v>
+        <v>25991</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>9045</v>
+        <v>18090</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>24693</v>
+        <v>33586</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>94587</v>
+        <v>96656</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>91130</v>
+        <v>94070</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>8817</v>
+        <v>17634</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>34090</v>
+        <v>39910</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>10723</v>
+        <v>12698</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>95124</v>
+        <v>105312</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>92576</v>
+        <v>95469</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>86532</v>
+        <v>92741</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>52859</v>
+        <v>61468</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>31617</v>
+        <v>40202</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>75666</v>
+        <v>82802</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>36606</v>
+        <v>38681</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>71418</v>
+        <v>79787</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>89225</v>
+        <v>96460</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>23163</v>
+        <v>31295</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>8098</v>
+        <v>16196</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>29633</v>
+        <v>31549</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>65244</v>
+        <v>73098</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>19523</v>
+        <v>23428</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>85332</v>
+        <v>87284</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>79734</v>
+        <v>82338</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>28933</v>
+        <v>36538</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>43735</v>
+        <v>46087</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>7240</v>
+        <v>14480</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>23483</v>
+        <v>30672</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>7172</v>
+        <v>14344</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>66374</v>
+        <v>67530</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>6954</v>
+        <v>13908</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>9210</v>
+        <v>16068</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>6835</v>
+        <v>13670</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>19292</v>
+        <v>26044</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>6750</v>
+        <v>13500</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>22810</v>
+        <v>27562</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>12386</v>
+        <v>18964</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>7962</v>
+        <v>9370</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>6500</v>
+        <v>13000</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>65923</v>
+        <v>67863</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>12572</v>
+        <v>18858</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>6231</v>
+        <v>12462</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>14566</v>
+        <v>20792</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>6211</v>
+        <v>12422</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>62336</v>
+        <v>63502</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>6047</v>
+        <v>12094</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>36073</v>
+        <v>41769</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>61857</v>
+        <v>65930</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>41571</v>
+        <v>47426</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>16046</v>
+        <v>21892</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>9611</v>
+        <v>13383</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>8734</v>
+        <v>11663</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>23034</v>
+        <v>28780</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>27366</v>
+        <v>33040</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>54528</v>
+        <v>59741</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>10864</v>
+        <v>16296</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>43351</v>
+        <v>48074</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>7200</v>
+        <v>12600</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>5399</v>
+        <v>10798</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>28329</v>
+        <v>33725</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>5396</v>
+        <v>10792</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>16428</v>
+        <v>21817</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>9306</v>
+        <v>14694</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>5334</v>
+        <v>10668</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>57282</v>
+        <v>62404</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>31995</v>
+        <v>37171</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>5173</v>
+        <v>10346</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>8757</v>
+        <v>13917</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>10013</v>
+        <v>14882</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>54177</v>
+        <v>57564</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>5045</v>
+        <v>10090</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>14821</v>
+        <v>19564</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>19465</v>
+        <v>24492</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>50874</v>
+        <v>55818</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>20990</v>
+        <v>25871</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>50773</v>
+        <v>52726</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>4882</v>
+        <v>9764</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>12102</v>
+        <v>14054</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>9662</v>
+        <v>14531</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>22287</v>
+        <v>27132</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>53042</v>
+        <v>57864</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>7233</v>
+        <v>12055</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>4822</v>
+        <v>9644</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>4798</v>
+        <v>9596</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>6670</v>
+        <v>11434</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>4733</v>
+        <v>9466</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>14112</v>
+        <v>18816</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>46655</v>
+        <v>49007</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>4636</v>
+        <v>9272</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>28388</v>
+        <v>32791</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>45974</v>
+        <v>47714</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>38522</v>
+        <v>44685</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>48837</v>
+        <v>52779</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>9820</v>
+        <v>13748</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>7856</v>
+        <v>11784</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>40703</v>
+        <v>42667</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>15616</v>
+        <v>19473</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>21340</v>
+        <v>25220</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>40719</v>
+        <v>42658</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>3806</v>
+        <v>7612</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>3774</v>
+        <v>7548</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>40651</v>
+        <v>43662</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>31085</v>
+        <v>32282</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>26155</v>
+        <v>29891</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>19444</v>
+        <v>23176</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>34860</v>
+        <v>38475</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>3574</v>
+        <v>7148</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>22983</v>
+        <v>24393</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>3499</v>
+        <v>6998</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>30843</v>
+        <v>34270</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>3416</v>
+        <v>6832</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>3398</v>
+        <v>6796</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>3376</v>
+        <v>6752</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>3326</v>
+        <v>6652</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>3315</v>
+        <v>6630</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>28225</v>
+        <v>30106</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>31343</v>
+        <v>34300</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>26993</v>
+        <v>29538</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>3011</v>
+        <v>6022</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>25594</v>
+        <v>28604</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>2957</v>
+        <v>5914</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>5892</v>
+        <v>8838</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>4850</v>
+        <v>7760</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>4378</v>
+        <v>7287</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>2907</v>
+        <v>5814</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>22318</v>
+        <v>25223</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>2893</v>
+        <v>5786</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>5784</v>
+        <v>8676</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>2892</v>
+        <v>5784</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>2880</v>
+        <v>5760</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>2875</v>
+        <v>5750</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>25785</v>
+        <v>28650</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>2857</v>
+        <v>5714</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>2841</v>
+        <v>5682</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>2823</v>
+        <v>5646</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>2822</v>
+        <v>5644</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>2822</v>
+        <v>5644</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>2822</v>
+        <v>5644</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>28210</v>
+        <v>31031</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>20121</v>
+        <v>22376</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>23173</v>
+        <v>24394</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>28527</v>
+        <v>30521</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>25540</v>
+        <v>27442</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>15350</v>
+        <v>17402</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>17567</v>
+        <v>18883</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>3773</v>
+        <v>6314</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>9180</v>
+        <v>10800</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>4912</v>
+        <v>7368</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>13743</v>
+        <v>16190</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>2445</v>
+        <v>4890</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>2441</v>
+        <v>4882</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>2426</v>
+        <v>4852</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>4365</v>
+        <v>6790</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>2425</v>
+        <v>4850</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>2411</v>
+        <v>4822</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>2364</v>
+        <v>4728</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>4706</v>
+        <v>7059</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>2352</v>
+        <v>4704</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>2343</v>
+        <v>4686</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>4298</v>
+        <v>6268</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>19684</v>
+        <v>20832</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>2266</v>
+        <v>4532</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>6750</v>
+        <v>9000</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>2241</v>
+        <v>4482</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>2238</v>
+        <v>4476</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>19568</v>
+        <v>21456</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>3725</v>
+        <v>5903</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>19369</v>
+        <v>21381</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>2001</v>
+        <v>4002</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>1990</v>
+        <v>3980</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>1977</v>
+        <v>3954</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>1977</v>
+        <v>3954</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>1976</v>
+        <v>3952</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>1976</v>
+        <v>3952</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>17193</v>
+        <v>18610</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>1972</v>
+        <v>3944</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>1953</v>
+        <v>3906</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>1952</v>
+        <v>3904</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>17425</v>
+        <v>19330</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>1928</v>
+        <v>3856</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>1927</v>
+        <v>3854</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>1926</v>
+        <v>3852</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>1916</v>
+        <v>3832</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>1916</v>
+        <v>3832</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>1904</v>
+        <v>3808</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>1899</v>
+        <v>3798</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>16354</v>
+        <v>17612</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>18810</v>
+        <v>20691</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>1881</v>
+        <v>3762</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>1881</v>
+        <v>3762</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>1881</v>
+        <v>3762</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>1881</v>
+        <v>3762</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>16031</v>
+        <v>17038</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>3513</v>
+        <v>5367</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>1854</v>
+        <v>3708</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>1799</v>
+        <v>3598</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>1799</v>
+        <v>3598</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>1757</v>
+        <v>3514</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>1757</v>
+        <v>3514</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>1744</v>
+        <v>3488</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>1739</v>
+        <v>3478</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>1715</v>
+        <v>3430</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>15430</v>
+        <v>16954</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>14852</v>
+        <v>16566</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>1669</v>
+        <v>3338</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>1572</v>
+        <v>3144</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>2669</v>
+        <v>4205</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>1515</v>
+        <v>3030</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>1465</v>
+        <v>2930</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>1439</v>
+        <v>2878</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>1426</v>
+        <v>2852</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>14110</v>
+        <v>15521</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>12699</v>
+        <v>14110</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>1411</v>
+        <v>2822</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>1394</v>
+        <v>2788</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>1349</v>
+        <v>2698</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>1347</v>
+        <v>2694</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>13160</v>
+        <v>14476</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>1260</v>
+        <v>2520</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>2518</v>
+        <v>3777</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>1251</v>
+        <v>2502</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>1239</v>
+        <v>2478</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>1091</v>
+        <v>2182</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>2160</v>
+        <v>3240</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>1080</v>
+        <v>2160</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>1078</v>
+        <v>2156</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>1067</v>
+        <v>2134</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>9279</v>
+        <v>10310</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7288198</v>
+        <v>7623980</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>969890</v>
+        <v>992894</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3030546</v>
+        <v>3065804</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>473578</v>
+        <v>685101</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>511135</v>
+        <v>628525</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1136575</v>
+        <v>1288053</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1810460</v>
+        <v>1957520</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>764677</v>
+        <v>856680</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>919687</v>
+        <v>1056406</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1022712</v>
+        <v>1154204</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>370257</v>
+        <v>484451</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>360199</v>
+        <v>466824</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>351548</v>
+        <v>423716</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>228746</v>
+        <v>330914</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1127274</v>
+        <v>1226760</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>704642</v>
+        <v>798595</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>488420</v>
+        <v>545396</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1052785</v>
+        <v>1101323</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1013686</v>
+        <v>1023508</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>471700</v>
+        <v>552460</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>616670</v>
+        <v>697409</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>244621</v>
+        <v>348585</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>611843</v>
+        <v>688262</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>758470</v>
+        <v>766045</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>817110</v>
+        <v>870534</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>440935</v>
+        <v>475112</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>743386</v>
+        <v>768909</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>225156</v>
+        <v>233405</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>623044</v>
+        <v>638859</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>552235</v>
+        <v>617346</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>589095</v>
+        <v>592257</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>613876</v>
+        <v>622984</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>360919</v>
+        <v>417581</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>752475</v>
+        <v>795928</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>622829</v>
+        <v>668820</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>160893</v>
+        <v>214524</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>180753</v>
+        <v>231623</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>564674</v>
+        <v>593479</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>482270</v>
+        <v>503419</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>514975</v>
+        <v>561807</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>360977</v>
+        <v>404972</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>328247</v>
+        <v>372097</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>100154</v>
+        <v>105966</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>251556</v>
+        <v>294603</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>459110</v>
+        <v>489049</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>98863</v>
+        <v>111159</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>117408</v>
+        <v>126119</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>457261</v>
+        <v>491964</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>371886</v>
+        <v>379038</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>90917</v>
+        <v>97189</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>350266</v>
+        <v>389439</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>79632</v>
+        <v>118220</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>479178</v>
+        <v>507908</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>437900</v>
+        <v>475946</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>402624</v>
+        <v>415886</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>165048</v>
+        <v>201088</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>305901</v>
+        <v>341965</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>214414</v>
+        <v>250249</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>358502</v>
+        <v>363413</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>43590</v>
+        <v>48077</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>191026</v>
+        <v>225360</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>67538</v>
+        <v>101307</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>350843</v>
+        <v>384387</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>329699</v>
+        <v>338362</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>385828</v>
+        <v>417895</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>339492</v>
+        <v>350168</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>62998</v>
+        <v>94497</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>375067</v>
+        <v>380794</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>316617</v>
+        <v>346343</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>168545</v>
+        <v>198138</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>287096</v>
+        <v>296681</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>152967</v>
+        <v>172248</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>176452</v>
+        <v>204771</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>298319</v>
+        <v>316587</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>293142</v>
+        <v>301488</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>80455</v>
+        <v>106897</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>65806</v>
+        <v>93307</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>140509</v>
+        <v>160028</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>79698</v>
+        <v>106756</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>237181</v>
+        <v>245087</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>209816</v>
+        <v>236630</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>53110</v>
+        <v>79665</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>54092</v>
+        <v>80378</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>214705</v>
+        <v>240939</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>296606</v>
+        <v>314069</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>51742</v>
+        <v>77613</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>92825</v>
+        <v>104620</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>257018</v>
+        <v>258522</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>257933</v>
+        <v>262813</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>318283</v>
+        <v>323457</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>186244</v>
+        <v>197254</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>126267</v>
+        <v>146632</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>266738</v>
+        <v>278257</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>60631</v>
+        <v>74147</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>69241</v>
+        <v>92479</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>316933</v>
+        <v>335002</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>239965</v>
+        <v>255066</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>130357</v>
+        <v>152088</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>43460</v>
+        <v>65190</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>132794</v>
+        <v>137537</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>121024</v>
+        <v>142617</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>144442</v>
+        <v>165838</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>42758</v>
+        <v>64137</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>165174</v>
+        <v>181220</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>42440</v>
+        <v>63660</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>200337</v>
+        <v>204242</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>40762</v>
+        <v>61143</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>78602</v>
+        <v>90413</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>186232</v>
+        <v>206182</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>135746</v>
+        <v>155500</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>76246</v>
+        <v>90788</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>135662</v>
+        <v>145342</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>143128</v>
+        <v>162532</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>77102</v>
+        <v>96373</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>86276</v>
+        <v>105449</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>38344</v>
+        <v>57516</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>167710</v>
+        <v>174008</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>63036</v>
+        <v>81958</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>203442</v>
+        <v>212088</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>100598</v>
+        <v>127082</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>99934</v>
+        <v>118451</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>180892</v>
+        <v>199358</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>138422</v>
+        <v>156683</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>46067</v>
+        <v>48942</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>110074</v>
+        <v>127870</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>35420</v>
+        <v>44240</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>53101</v>
+        <v>54555</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>172809</v>
+        <v>176185</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>67920</v>
+        <v>85210</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>126997</v>
+        <v>143920</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>142132</v>
+        <v>158981</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>73761</v>
+        <v>90348</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>48875</v>
+        <v>65436</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>38812</v>
+        <v>41687</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>56265</v>
+        <v>72759</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>32872</v>
+        <v>49308</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>170997</v>
+        <v>179283</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>44892</v>
+        <v>48632</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>95384</v>
+        <v>111581</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>119844</v>
+        <v>136010</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>66313</v>
+        <v>81045</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>33979</v>
+        <v>49992</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>164210</v>
+        <v>179737</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>165596</v>
+        <v>175474</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>45948</v>
+        <v>61264</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>32103</v>
+        <v>47178</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>64224</v>
+        <v>79177</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>154795</v>
+        <v>157006</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>28936</v>
+        <v>43404</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>113498</v>
+        <v>127811</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>92257</v>
+        <v>101044</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>151451</v>
+        <v>161095</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>22579</v>
+        <v>26813</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>389564</v>
+        <v>497948</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>151756</v>
+        <v>159827</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>195677</v>
+        <v>206014</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>149616</v>
+        <v>154864</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>37052</v>
+        <v>40836</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>20066</v>
+        <v>23215</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>65033</v>
+        <v>74326</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>68325</v>
+        <v>81990</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>46656</v>
+        <v>60219</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>144930</v>
+        <v>158455</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>70090</v>
+        <v>83323</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>137364</v>
+        <v>140186</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>69034</v>
+        <v>81911</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>93740</v>
+        <v>99695</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>25430</v>
+        <v>38145</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>57595</v>
+        <v>70284</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>47614</v>
+        <v>60289</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>25200</v>
+        <v>37800</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>122238</v>
+        <v>124138</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>24680</v>
+        <v>37020</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>125216</v>
+        <v>137519</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>142708</v>
+        <v>153208</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>111886</v>
+        <v>117250</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>42450</v>
+        <v>51977</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>35041</v>
+        <v>46669</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>110178</v>
+        <v>112094</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>23038</v>
+        <v>34557</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>55535</v>
+        <v>66819</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>77947</v>
+        <v>81305</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>21970</v>
+        <v>32955</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>85361</v>
+        <v>96001</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>111707</v>
+        <v>113981</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>72650</v>
+        <v>83193</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>32996</v>
+        <v>43186</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>101114</v>
+        <v>103848</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>94742</v>
+        <v>96624</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>110555</v>
+        <v>115465</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>115622</v>
+        <v>125503</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>19756</v>
+        <v>29634</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>24215</v>
+        <v>34029</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>19586</v>
+        <v>29379</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>19524</v>
+        <v>29286</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>79261</v>
+        <v>88973</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>107062</v>
+        <v>116708</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>106362</v>
+        <v>115967</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>59444</v>
+        <v>69031</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>84776</v>
+        <v>91619</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>99674</v>
+        <v>104189</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>39307</v>
+        <v>54810</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>25991</v>
+        <v>34463</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>18090</v>
+        <v>27135</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>33586</v>
+        <v>42479</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>96656</v>
+        <v>98725</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>94070</v>
+        <v>97010</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>17634</v>
+        <v>26451</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>39910</v>
+        <v>45730</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>12698</v>
+        <v>14673</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>105312</v>
+        <v>115500</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>95469</v>
+        <v>98362</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>92741</v>
+        <v>98950</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>61468</v>
+        <v>70077</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>40202</v>
+        <v>48787</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>82802</v>
+        <v>89938</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>38681</v>
+        <v>40756</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>79787</v>
+        <v>88156</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>96460</v>
+        <v>103695</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>31295</v>
+        <v>39427</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>16196</v>
+        <v>24294</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>31549</v>
+        <v>33465</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>73098</v>
+        <v>80952</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>23428</v>
+        <v>27333</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>87284</v>
+        <v>89236</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>82338</v>
+        <v>84942</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>36538</v>
+        <v>44143</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>46087</v>
+        <v>48439</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>14480</v>
+        <v>21720</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>30672</v>
+        <v>37861</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>14344</v>
+        <v>21516</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>67530</v>
+        <v>68686</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>13908</v>
+        <v>20862</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>16068</v>
+        <v>22926</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>13670</v>
+        <v>20505</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>26044</v>
+        <v>32796</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>13500</v>
+        <v>20250</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>27562</v>
+        <v>32314</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>18964</v>
+        <v>25542</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>9370</v>
+        <v>10778</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>67863</v>
+        <v>69803</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>18858</v>
+        <v>25144</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>12462</v>
+        <v>18693</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>20792</v>
+        <v>27018</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>12422</v>
+        <v>18633</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>63502</v>
+        <v>64668</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>12094</v>
+        <v>18141</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>41769</v>
+        <v>47465</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>65930</v>
+        <v>70003</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>47426</v>
+        <v>53281</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>21892</v>
+        <v>27738</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>13383</v>
+        <v>17155</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>11663</v>
+        <v>14592</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>28780</v>
+        <v>34526</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>33040</v>
+        <v>38714</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>59741</v>
+        <v>64954</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>16296</v>
+        <v>21728</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>48074</v>
+        <v>52797</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>12600</v>
+        <v>18000</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>10798</v>
+        <v>16197</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>33725</v>
+        <v>39121</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>10792</v>
+        <v>16188</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>21817</v>
+        <v>27206</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>14694</v>
+        <v>20082</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>10668</v>
+        <v>16002</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>62404</v>
+        <v>67526</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>37171</v>
+        <v>42347</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>10346</v>
+        <v>15519</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>13917</v>
+        <v>19077</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>14882</v>
+        <v>19751</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>57564</v>
+        <v>60951</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>10090</v>
+        <v>15135</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>19564</v>
+        <v>24307</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>24492</v>
+        <v>29519</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>55818</v>
+        <v>60762</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>25871</v>
+        <v>30752</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>52726</v>
+        <v>54679</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>9764</v>
+        <v>14646</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>14054</v>
+        <v>16006</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>14531</v>
+        <v>19400</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>27132</v>
+        <v>31977</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>57864</v>
+        <v>62686</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>12055</v>
+        <v>16877</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>9644</v>
+        <v>14466</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>9596</v>
+        <v>14394</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>11434</v>
+        <v>16198</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>9466</v>
+        <v>14199</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>18816</v>
+        <v>23520</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>49007</v>
+        <v>51359</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>9272</v>
+        <v>13908</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>32791</v>
+        <v>37194</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>47714</v>
+        <v>49454</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>44685</v>
+        <v>50848</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>52779</v>
+        <v>56721</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>13748</v>
+        <v>17676</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>11784</v>
+        <v>15712</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>42667</v>
+        <v>44631</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>19473</v>
+        <v>23330</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>25220</v>
+        <v>29100</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>42658</v>
+        <v>44597</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>7612</v>
+        <v>11418</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>7548</v>
+        <v>11322</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>43662</v>
+        <v>46673</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>32282</v>
+        <v>33479</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>29891</v>
+        <v>33627</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>23176</v>
+        <v>26908</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>38475</v>
+        <v>42090</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>7148</v>
+        <v>10722</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>24393</v>
+        <v>25803</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>6998</v>
+        <v>10497</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>34270</v>
+        <v>37697</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>6832</v>
+        <v>10248</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>6796</v>
+        <v>10194</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>6752</v>
+        <v>10128</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>6652</v>
+        <v>9978</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>6630</v>
+        <v>9945</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>30106</v>
+        <v>31987</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>34300</v>
+        <v>37257</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>29538</v>
+        <v>32083</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>6022</v>
+        <v>9033</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>28604</v>
+        <v>31614</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>5914</v>
+        <v>8871</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>8838</v>
+        <v>11784</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>7760</v>
+        <v>10670</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>7287</v>
+        <v>10196</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>5814</v>
+        <v>8721</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>25223</v>
+        <v>28128</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>5786</v>
+        <v>8679</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>8676</v>
+        <v>11568</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>5784</v>
+        <v>8676</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>5760</v>
+        <v>8640</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>5750</v>
+        <v>8625</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>28650</v>
+        <v>31515</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>5714</v>
+        <v>8571</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>5682</v>
+        <v>8523</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>5646</v>
+        <v>8469</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>31031</v>
+        <v>33852</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>22376</v>
+        <v>24631</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>24394</v>
+        <v>25615</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>30521</v>
+        <v>32515</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>27442</v>
+        <v>29344</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>17402</v>
+        <v>19454</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>18883</v>
+        <v>20199</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>6314</v>
+        <v>8855</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>10800</v>
+        <v>12420</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>7368</v>
+        <v>9824</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>16190</v>
+        <v>18637</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>4890</v>
+        <v>7335</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>4882</v>
+        <v>7323</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>4852</v>
+        <v>7278</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>6790</v>
+        <v>9215</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>4850</v>
+        <v>7275</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>4822</v>
+        <v>7233</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>4728</v>
+        <v>7092</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>7059</v>
+        <v>9412</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>4704</v>
+        <v>7056</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>4686</v>
+        <v>7029</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>6268</v>
+        <v>8238</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>20832</v>
+        <v>21980</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>4532</v>
+        <v>6798</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>9000</v>
+        <v>11250</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>4482</v>
+        <v>6723</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>4476</v>
+        <v>6714</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>21456</v>
+        <v>23344</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>5903</v>
+        <v>8081</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>21381</v>
+        <v>23393</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>4002</v>
+        <v>6003</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>3980</v>
+        <v>5970</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>3954</v>
+        <v>5931</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>3954</v>
+        <v>5931</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>3952</v>
+        <v>5928</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>3952</v>
+        <v>5928</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>18610</v>
+        <v>20027</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>3944</v>
+        <v>5916</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>3906</v>
+        <v>5859</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>3904</v>
+        <v>5856</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>19330</v>
+        <v>21235</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>3856</v>
+        <v>5784</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>3854</v>
+        <v>5781</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>3852</v>
+        <v>5778</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>3832</v>
+        <v>5748</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>3832</v>
+        <v>5748</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>3808</v>
+        <v>5712</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>3798</v>
+        <v>5697</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>17612</v>
+        <v>18870</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>20691</v>
+        <v>22572</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>3762</v>
+        <v>5643</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>3762</v>
+        <v>5643</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>3762</v>
+        <v>5643</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>3762</v>
+        <v>5643</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>17038</v>
+        <v>18045</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>5367</v>
+        <v>7221</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>3708</v>
+        <v>5562</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>3598</v>
+        <v>5397</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>3598</v>
+        <v>5397</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>3514</v>
+        <v>5271</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>3514</v>
+        <v>5271</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>3488</v>
+        <v>5232</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>3478</v>
+        <v>5217</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>3430</v>
+        <v>5145</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>16954</v>
+        <v>18478</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>16566</v>
+        <v>18280</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>3338</v>
+        <v>5007</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>3144</v>
+        <v>4716</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>4205</v>
+        <v>5741</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>3030</v>
+        <v>4545</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>2930</v>
+        <v>4395</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>2878</v>
+        <v>4317</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>2852</v>
+        <v>4278</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>15521</v>
+        <v>16932</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>14110</v>
+        <v>15521</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>2822</v>
+        <v>4233</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>2788</v>
+        <v>4182</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>2698</v>
+        <v>4047</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>2694</v>
+        <v>4041</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>14476</v>
+        <v>15792</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>2520</v>
+        <v>3780</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>3777</v>
+        <v>5036</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>2502</v>
+        <v>3753</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>2478</v>
+        <v>3717</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>2182</v>
+        <v>3273</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>3240</v>
+        <v>4320</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>2160</v>
+        <v>3240</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>2156</v>
+        <v>3234</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>2134</v>
+        <v>3201</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>10310</v>
+        <v>11341</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Telegram SEBI 10-Day Audit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7623980</v>
+        <v>7959762</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>992894</v>
+        <v>1015898</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3065804</v>
+        <v>3101062</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>685101</v>
+        <v>896624</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>628525</v>
+        <v>745915</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1288053</v>
+        <v>1439531</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1957520</v>
+        <v>2104580</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>856680</v>
+        <v>948683</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1056406</v>
+        <v>1193125</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1154204</v>
+        <v>1285696</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>484451</v>
+        <v>598645</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>466824</v>
+        <v>573449</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>423716</v>
+        <v>495884</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>330914</v>
+        <v>433082</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1226760</v>
+        <v>1326246</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>798595</v>
+        <v>892548</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>545396</v>
+        <v>602372</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1101323</v>
+        <v>1149861</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1023508</v>
+        <v>1033330</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>552460</v>
+        <v>633220</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>697409</v>
+        <v>778148</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>348585</v>
+        <v>452549</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>688262</v>
+        <v>764681</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>766045</v>
+        <v>773620</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>870534</v>
+        <v>923958</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>475112</v>
+        <v>509289</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>768909</v>
+        <v>794432</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>233405</v>
+        <v>241654</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>638859</v>
+        <v>654674</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>617346</v>
+        <v>682457</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>592257</v>
+        <v>595419</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>622984</v>
+        <v>632092</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>417581</v>
+        <v>474243</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>795928</v>
+        <v>839381</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>668820</v>
+        <v>714811</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>214524</v>
+        <v>268155</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>231623</v>
+        <v>282493</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>593479</v>
+        <v>622284</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>503419</v>
+        <v>524568</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>561807</v>
+        <v>608639</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>404972</v>
+        <v>448967</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>372097</v>
+        <v>415947</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>105966</v>
+        <v>111778</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>294603</v>
+        <v>337650</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>489049</v>
+        <v>518988</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>111159</v>
+        <v>123455</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>126119</v>
+        <v>134830</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>491964</v>
+        <v>526667</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>379038</v>
+        <v>386190</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>97189</v>
+        <v>103461</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>389439</v>
+        <v>428612</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>118220</v>
+        <v>156808</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>507908</v>
+        <v>536638</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>475946</v>
+        <v>513992</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>415886</v>
+        <v>429148</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>201088</v>
+        <v>237128</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>341965</v>
+        <v>378029</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>250249</v>
+        <v>286084</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>363413</v>
+        <v>368324</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>48077</v>
+        <v>52564</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>225360</v>
+        <v>259694</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>101307</v>
+        <v>135076</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>384387</v>
+        <v>417931</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>338362</v>
+        <v>347025</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>417895</v>
+        <v>449962</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>350168</v>
+        <v>360844</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>94497</v>
+        <v>125996</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>380794</v>
+        <v>386521</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>346343</v>
+        <v>376069</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>198138</v>
+        <v>227731</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>296681</v>
+        <v>306266</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>172248</v>
+        <v>191529</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>204771</v>
+        <v>233090</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>316587</v>
+        <v>334855</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>301488</v>
+        <v>309834</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>106897</v>
+        <v>133339</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>93307</v>
+        <v>120808</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>160028</v>
+        <v>179547</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>106756</v>
+        <v>133814</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>245087</v>
+        <v>252993</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>236630</v>
+        <v>263444</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>79665</v>
+        <v>106220</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>80378</v>
+        <v>106664</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>240939</v>
+        <v>267173</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>314069</v>
+        <v>331532</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>77613</v>
+        <v>103484</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>104620</v>
+        <v>116415</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>258522</v>
+        <v>260026</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>262813</v>
+        <v>267693</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>323457</v>
+        <v>328631</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>197254</v>
+        <v>208264</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>146632</v>
+        <v>166997</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>278257</v>
+        <v>289776</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>74147</v>
+        <v>87663</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>92479</v>
+        <v>115717</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>335002</v>
+        <v>353071</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>255066</v>
+        <v>270167</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>152088</v>
+        <v>173819</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>65190</v>
+        <v>86920</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>137537</v>
+        <v>142280</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>142617</v>
+        <v>164210</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>165838</v>
+        <v>187234</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>64137</v>
+        <v>85516</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>181220</v>
+        <v>197266</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>63660</v>
+        <v>84880</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>204242</v>
+        <v>208147</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>61143</v>
+        <v>81524</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>90413</v>
+        <v>102224</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>206182</v>
+        <v>226132</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>155500</v>
+        <v>175254</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>90788</v>
+        <v>105330</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>145342</v>
+        <v>155022</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>162532</v>
+        <v>181936</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>96373</v>
+        <v>115644</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>105449</v>
+        <v>124622</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>57516</v>
+        <v>76688</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>174008</v>
+        <v>180306</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>81958</v>
+        <v>100880</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>212088</v>
+        <v>220734</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>127082</v>
+        <v>153566</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>118451</v>
+        <v>136968</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>199358</v>
+        <v>217824</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>156683</v>
+        <v>174944</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>48942</v>
+        <v>51817</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>127870</v>
+        <v>145666</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>44240</v>
+        <v>53060</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>54555</v>
+        <v>56009</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>176185</v>
+        <v>179561</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>85210</v>
+        <v>102500</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>143920</v>
+        <v>160843</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>158981</v>
+        <v>175830</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>90348</v>
+        <v>106935</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>65436</v>
+        <v>81997</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>41687</v>
+        <v>44562</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>72759</v>
+        <v>89253</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>49308</v>
+        <v>65744</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>179283</v>
+        <v>187569</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>48632</v>
+        <v>52372</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>111581</v>
+        <v>127778</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>136010</v>
+        <v>152176</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>81045</v>
+        <v>95777</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>49992</v>
+        <v>66005</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>179737</v>
+        <v>195264</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>175474</v>
+        <v>185352</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>61264</v>
+        <v>76580</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>47178</v>
+        <v>62253</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>79177</v>
+        <v>94130</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>157006</v>
+        <v>159217</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>43404</v>
+        <v>57872</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>127811</v>
+        <v>142124</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>101044</v>
+        <v>109831</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>161095</v>
+        <v>170739</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>26813</v>
+        <v>31047</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>497948</v>
+        <v>606332</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>159827</v>
+        <v>167898</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>206014</v>
+        <v>216351</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>154864</v>
+        <v>160112</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>40836</v>
+        <v>44620</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>23215</v>
+        <v>26364</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>74326</v>
+        <v>83619</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>81990</v>
+        <v>95655</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>60219</v>
+        <v>73782</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>158455</v>
+        <v>171980</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>83323</v>
+        <v>96556</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>140186</v>
+        <v>143008</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>81911</v>
+        <v>94788</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>99695</v>
+        <v>105650</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>38145</v>
+        <v>50860</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>70284</v>
+        <v>82973</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>60289</v>
+        <v>72964</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>37800</v>
+        <v>50400</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>124138</v>
+        <v>126038</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>37020</v>
+        <v>49360</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>137519</v>
+        <v>149822</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>153208</v>
+        <v>163708</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>117250</v>
+        <v>122614</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>51977</v>
+        <v>61504</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>46669</v>
+        <v>58297</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>112094</v>
+        <v>114010</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>34557</v>
+        <v>46076</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>66819</v>
+        <v>78103</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>81305</v>
+        <v>84663</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>32955</v>
+        <v>43940</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>96001</v>
+        <v>106641</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>113981</v>
+        <v>116255</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>83193</v>
+        <v>93736</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>43186</v>
+        <v>53376</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>103848</v>
+        <v>106582</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>96624</v>
+        <v>98506</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>115465</v>
+        <v>120375</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>125503</v>
+        <v>135384</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>29634</v>
+        <v>39512</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>34029</v>
+        <v>43843</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>29379</v>
+        <v>39172</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>29286</v>
+        <v>39048</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>88973</v>
+        <v>98685</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>116708</v>
+        <v>126354</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>115967</v>
+        <v>125572</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>69031</v>
+        <v>78618</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>91619</v>
+        <v>98462</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>104189</v>
+        <v>108704</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>54810</v>
+        <v>70313</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>34463</v>
+        <v>42935</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>27135</v>
+        <v>36180</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>42479</v>
+        <v>51372</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>98725</v>
+        <v>100794</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>97010</v>
+        <v>99950</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>26451</v>
+        <v>35268</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>45730</v>
+        <v>51550</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>14673</v>
+        <v>16648</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>115500</v>
+        <v>125688</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>98362</v>
+        <v>101255</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>98950</v>
+        <v>105159</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>70077</v>
+        <v>78686</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>48787</v>
+        <v>57372</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>89938</v>
+        <v>97074</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>40756</v>
+        <v>42831</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>88156</v>
+        <v>96525</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>103695</v>
+        <v>110930</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>39427</v>
+        <v>47559</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>24294</v>
+        <v>32392</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>33465</v>
+        <v>35381</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>80952</v>
+        <v>88806</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>27333</v>
+        <v>31238</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>89236</v>
+        <v>91188</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>84942</v>
+        <v>87546</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>44143</v>
+        <v>51748</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>48439</v>
+        <v>50791</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>21720</v>
+        <v>28960</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>37861</v>
+        <v>45050</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>21516</v>
+        <v>28688</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>68686</v>
+        <v>69842</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>20862</v>
+        <v>27816</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>22926</v>
+        <v>29784</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>20505</v>
+        <v>27340</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>32796</v>
+        <v>39548</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>20250</v>
+        <v>27000</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>32314</v>
+        <v>37066</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>25542</v>
+        <v>32120</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>10778</v>
+        <v>12186</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>19500</v>
+        <v>26000</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>69803</v>
+        <v>71743</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>25144</v>
+        <v>31430</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>18693</v>
+        <v>24924</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>27018</v>
+        <v>33244</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>18633</v>
+        <v>24844</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>64668</v>
+        <v>65834</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>18141</v>
+        <v>24188</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>47465</v>
+        <v>53161</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>70003</v>
+        <v>74076</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>53281</v>
+        <v>59136</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>27738</v>
+        <v>33584</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>17155</v>
+        <v>20927</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>14592</v>
+        <v>17521</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>34526</v>
+        <v>40272</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>38714</v>
+        <v>44388</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>64954</v>
+        <v>70167</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>21728</v>
+        <v>27160</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>52797</v>
+        <v>57520</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>18000</v>
+        <v>23400</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>16197</v>
+        <v>21596</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>39121</v>
+        <v>44517</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>16188</v>
+        <v>21584</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>27206</v>
+        <v>32595</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>20082</v>
+        <v>25470</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>16002</v>
+        <v>21336</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>67526</v>
+        <v>72648</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>42347</v>
+        <v>47523</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>15519</v>
+        <v>20692</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>19077</v>
+        <v>24237</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>19751</v>
+        <v>24620</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>60951</v>
+        <v>64338</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>15135</v>
+        <v>20180</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>24307</v>
+        <v>29050</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>29519</v>
+        <v>34546</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>60762</v>
+        <v>65706</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>30752</v>
+        <v>35633</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>54679</v>
+        <v>56632</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>14646</v>
+        <v>19528</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>16006</v>
+        <v>17958</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>19400</v>
+        <v>24269</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>31977</v>
+        <v>36822</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>62686</v>
+        <v>67508</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>16877</v>
+        <v>21699</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>14466</v>
+        <v>19288</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>14394</v>
+        <v>19192</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>16198</v>
+        <v>20962</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>14199</v>
+        <v>18932</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>23520</v>
+        <v>28224</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>51359</v>
+        <v>53711</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>13908</v>
+        <v>18544</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>37194</v>
+        <v>41597</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>49454</v>
+        <v>51194</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>50848</v>
+        <v>57011</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>56721</v>
+        <v>60663</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>17676</v>
+        <v>21604</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>15712</v>
+        <v>19640</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>44631</v>
+        <v>46595</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>23330</v>
+        <v>27187</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>29100</v>
+        <v>32980</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>44597</v>
+        <v>46536</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>11418</v>
+        <v>15224</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>11322</v>
+        <v>15096</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>46673</v>
+        <v>49684</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>33479</v>
+        <v>34676</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>33627</v>
+        <v>37363</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>26908</v>
+        <v>30640</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>42090</v>
+        <v>45705</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>10722</v>
+        <v>14296</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>25803</v>
+        <v>27213</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>10497</v>
+        <v>13996</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>37697</v>
+        <v>41124</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>10248</v>
+        <v>13664</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>10194</v>
+        <v>13592</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>10128</v>
+        <v>13504</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>9978</v>
+        <v>13304</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>9945</v>
+        <v>13260</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>31987</v>
+        <v>33868</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>37257</v>
+        <v>40214</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>32083</v>
+        <v>34628</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>9033</v>
+        <v>12044</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>31614</v>
+        <v>34624</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>8871</v>
+        <v>11828</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>11784</v>
+        <v>14730</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>10670</v>
+        <v>13580</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>10196</v>
+        <v>13105</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>8721</v>
+        <v>11628</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>28128</v>
+        <v>31033</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>8679</v>
+        <v>11572</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>11568</v>
+        <v>14460</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>8676</v>
+        <v>11568</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>8640</v>
+        <v>11520</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>8625</v>
+        <v>11500</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>31515</v>
+        <v>34380</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>8571</v>
+        <v>11428</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>8523</v>
+        <v>11364</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>8469</v>
+        <v>11292</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>8466</v>
+        <v>11288</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>8466</v>
+        <v>11288</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>8466</v>
+        <v>11288</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>33852</v>
+        <v>36673</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>24631</v>
+        <v>26886</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>25615</v>
+        <v>26836</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>32515</v>
+        <v>34509</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>29344</v>
+        <v>31246</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>19454</v>
+        <v>21506</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>20199</v>
+        <v>21515</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>8855</v>
+        <v>11396</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>12420</v>
+        <v>14040</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>9824</v>
+        <v>12280</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>18637</v>
+        <v>21084</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>7335</v>
+        <v>9780</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>7323</v>
+        <v>9764</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>7278</v>
+        <v>9704</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>9215</v>
+        <v>11640</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>7275</v>
+        <v>9700</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>7233</v>
+        <v>9644</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>7092</v>
+        <v>9456</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>9412</v>
+        <v>11765</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>7056</v>
+        <v>9408</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>7029</v>
+        <v>9372</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>8238</v>
+        <v>10208</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>21980</v>
+        <v>23128</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>6798</v>
+        <v>9064</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>11250</v>
+        <v>13500</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>6723</v>
+        <v>8964</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>6714</v>
+        <v>8952</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>23344</v>
+        <v>25232</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>8081</v>
+        <v>10259</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>23393</v>
+        <v>25405</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>6003</v>
+        <v>8004</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>5970</v>
+        <v>7960</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>5931</v>
+        <v>7908</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>5931</v>
+        <v>7908</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>5928</v>
+        <v>7904</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>5928</v>
+        <v>7904</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>20027</v>
+        <v>21444</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>5916</v>
+        <v>7888</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>5859</v>
+        <v>7812</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>5856</v>
+        <v>7808</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>21235</v>
+        <v>23140</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>5784</v>
+        <v>7712</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>5781</v>
+        <v>7708</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>5778</v>
+        <v>7704</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>5748</v>
+        <v>7664</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>5748</v>
+        <v>7664</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>5712</v>
+        <v>7616</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>5697</v>
+        <v>7596</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>18870</v>
+        <v>20128</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>22572</v>
+        <v>24453</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>5643</v>
+        <v>7524</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>5643</v>
+        <v>7524</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>5643</v>
+        <v>7524</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>5643</v>
+        <v>7524</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>18045</v>
+        <v>19052</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>7221</v>
+        <v>9075</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>5562</v>
+        <v>7416</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>5397</v>
+        <v>7196</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>5397</v>
+        <v>7196</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>5271</v>
+        <v>7028</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>5271</v>
+        <v>7028</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>5232</v>
+        <v>6976</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>5217</v>
+        <v>6956</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>5145</v>
+        <v>6860</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>18478</v>
+        <v>20002</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>18280</v>
+        <v>19994</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>5007</v>
+        <v>6676</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>4716</v>
+        <v>6288</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>5741</v>
+        <v>7277</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>4545</v>
+        <v>6060</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>4395</v>
+        <v>5860</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>4317</v>
+        <v>5756</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>4278</v>
+        <v>5704</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>16932</v>
+        <v>18343</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>15521</v>
+        <v>16932</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>4233</v>
+        <v>5644</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>4182</v>
+        <v>5576</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>4047</v>
+        <v>5396</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>4041</v>
+        <v>5388</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>15792</v>
+        <v>17108</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>3780</v>
+        <v>5040</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>5036</v>
+        <v>6295</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>3753</v>
+        <v>5004</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>3717</v>
+        <v>4956</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>3273</v>
+        <v>4364</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>4320</v>
+        <v>5400</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>3240</v>
+        <v>4320</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>3234</v>
+        <v>4312</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>3201</v>
+        <v>4268</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>11341</v>
+        <v>12372</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7959762</v>
+        <v>8295544</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1015898</v>
+        <v>1038902</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3101062</v>
+        <v>3136320</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>896624</v>
+        <v>1108147</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>745915</v>
+        <v>863305</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1439531</v>
+        <v>1591009</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2104580</v>
+        <v>2251640</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>948683</v>
+        <v>1040686</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1193125</v>
+        <v>1329844</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1285696</v>
+        <v>1417188</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>598645</v>
+        <v>712839</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>573449</v>
+        <v>680074</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>495884</v>
+        <v>568052</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>433082</v>
+        <v>535250</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1326246</v>
+        <v>1425732</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>892548</v>
+        <v>986501</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>602372</v>
+        <v>659348</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1149861</v>
+        <v>1198399</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1033330</v>
+        <v>1043152</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>633220</v>
+        <v>713980</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>778148</v>
+        <v>858887</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>452549</v>
+        <v>556513</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>764681</v>
+        <v>841100</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>773620</v>
+        <v>781195</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>923958</v>
+        <v>977382</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>509289</v>
+        <v>543466</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>794432</v>
+        <v>819955</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>241654</v>
+        <v>249903</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>654674</v>
+        <v>670489</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>682457</v>
+        <v>747568</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>595419</v>
+        <v>598581</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>632092</v>
+        <v>641200</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>474243</v>
+        <v>530905</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>839381</v>
+        <v>882834</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>714811</v>
+        <v>760802</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>268155</v>
+        <v>321786</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>282493</v>
+        <v>333363</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>622284</v>
+        <v>651089</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>524568</v>
+        <v>545717</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>608639</v>
+        <v>655471</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>448967</v>
+        <v>492962</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>415947</v>
+        <v>459797</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>111778</v>
+        <v>117590</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>337650</v>
+        <v>380697</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>518988</v>
+        <v>548927</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>123455</v>
+        <v>135751</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>134830</v>
+        <v>143541</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>526667</v>
+        <v>561370</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>386190</v>
+        <v>393342</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>103461</v>
+        <v>109733</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>428612</v>
+        <v>467785</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>156808</v>
+        <v>195396</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>536638</v>
+        <v>565368</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>513992</v>
+        <v>552038</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>429148</v>
+        <v>442410</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>237128</v>
+        <v>273168</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>378029</v>
+        <v>414093</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>286084</v>
+        <v>321919</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>368324</v>
+        <v>373235</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>52564</v>
+        <v>57051</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>259694</v>
+        <v>294028</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>135076</v>
+        <v>168845</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>417931</v>
+        <v>451475</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>347025</v>
+        <v>355688</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>449962</v>
+        <v>482029</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>360844</v>
+        <v>371520</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>125996</v>
+        <v>157495</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>386521</v>
+        <v>392248</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>376069</v>
+        <v>405795</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>227731</v>
+        <v>257324</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>306266</v>
+        <v>315851</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>191529</v>
+        <v>210810</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>233090</v>
+        <v>261409</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>334855</v>
+        <v>353123</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>309834</v>
+        <v>318180</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>133339</v>
+        <v>159781</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>120808</v>
+        <v>148309</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>179547</v>
+        <v>199066</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>133814</v>
+        <v>160872</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>252993</v>
+        <v>260899</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>263444</v>
+        <v>290258</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>106220</v>
+        <v>132775</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>106664</v>
+        <v>132950</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>267173</v>
+        <v>293407</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>331532</v>
+        <v>348995</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>103484</v>
+        <v>129355</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>116415</v>
+        <v>128210</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>260026</v>
+        <v>261530</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>267693</v>
+        <v>272573</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>328631</v>
+        <v>333805</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>208264</v>
+        <v>219274</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>166997</v>
+        <v>187362</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>289776</v>
+        <v>301295</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>87663</v>
+        <v>101179</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>115717</v>
+        <v>138955</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>353071</v>
+        <v>371140</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>270167</v>
+        <v>285268</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>173819</v>
+        <v>195550</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>86920</v>
+        <v>108650</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>142280</v>
+        <v>147023</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>164210</v>
+        <v>185803</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>187234</v>
+        <v>208630</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>85516</v>
+        <v>106895</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>197266</v>
+        <v>213312</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>84880</v>
+        <v>106100</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>208147</v>
+        <v>212052</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>81524</v>
+        <v>101905</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>102224</v>
+        <v>114035</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>226132</v>
+        <v>246082</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>175254</v>
+        <v>195008</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>105330</v>
+        <v>119872</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>155022</v>
+        <v>164702</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>181936</v>
+        <v>201340</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>115644</v>
+        <v>134915</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>124622</v>
+        <v>143795</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>76688</v>
+        <v>95860</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>180306</v>
+        <v>186604</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>100880</v>
+        <v>119802</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>220734</v>
+        <v>229380</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>153566</v>
+        <v>180050</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>136968</v>
+        <v>155485</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>217824</v>
+        <v>236290</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>174944</v>
+        <v>193205</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>51817</v>
+        <v>54692</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>145666</v>
+        <v>163462</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>53060</v>
+        <v>61880</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>56009</v>
+        <v>57463</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>179561</v>
+        <v>182937</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>102500</v>
+        <v>119790</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>160843</v>
+        <v>177766</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>175830</v>
+        <v>192679</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>106935</v>
+        <v>123522</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>81997</v>
+        <v>98558</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>44562</v>
+        <v>47437</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>89253</v>
+        <v>105747</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>65744</v>
+        <v>82180</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>187569</v>
+        <v>195855</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>52372</v>
+        <v>56112</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>127778</v>
+        <v>143975</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>152176</v>
+        <v>168342</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>95777</v>
+        <v>110509</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>66005</v>
+        <v>82018</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>195264</v>
+        <v>210791</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>185352</v>
+        <v>195230</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>76580</v>
+        <v>91896</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>62253</v>
+        <v>77328</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>94130</v>
+        <v>109083</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>159217</v>
+        <v>161428</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>57872</v>
+        <v>72340</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>142124</v>
+        <v>156437</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>109831</v>
+        <v>118618</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>170739</v>
+        <v>180383</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>31047</v>
+        <v>35281</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>606332</v>
+        <v>714716</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>167898</v>
+        <v>175969</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>216351</v>
+        <v>226688</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>160112</v>
+        <v>165360</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>44620</v>
+        <v>48404</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>26364</v>
+        <v>29513</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>83619</v>
+        <v>92912</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>95655</v>
+        <v>109320</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>73782</v>
+        <v>87345</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>171980</v>
+        <v>185505</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>96556</v>
+        <v>109789</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>143008</v>
+        <v>145830</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>94788</v>
+        <v>107665</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>105650</v>
+        <v>111605</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>50860</v>
+        <v>63575</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>82973</v>
+        <v>95662</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>72964</v>
+        <v>85639</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>50400</v>
+        <v>63000</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>126038</v>
+        <v>127938</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>49360</v>
+        <v>61700</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>149822</v>
+        <v>162125</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>163708</v>
+        <v>174208</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>122614</v>
+        <v>127978</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>61504</v>
+        <v>71031</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>58297</v>
+        <v>69925</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>114010</v>
+        <v>115926</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>46076</v>
+        <v>57595</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>78103</v>
+        <v>89387</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>84663</v>
+        <v>88021</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>43940</v>
+        <v>54925</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>106641</v>
+        <v>117281</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>116255</v>
+        <v>118529</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>93736</v>
+        <v>104279</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>53376</v>
+        <v>63566</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>106582</v>
+        <v>109316</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>98506</v>
+        <v>100388</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>120375</v>
+        <v>125285</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>135384</v>
+        <v>145265</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>39512</v>
+        <v>49390</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>43843</v>
+        <v>53657</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>39172</v>
+        <v>48965</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>39048</v>
+        <v>48810</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>98685</v>
+        <v>108397</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>126354</v>
+        <v>136000</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>125572</v>
+        <v>135177</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>78618</v>
+        <v>88205</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>98462</v>
+        <v>105305</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>108704</v>
+        <v>113219</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>70313</v>
+        <v>85816</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>42935</v>
+        <v>51407</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>36180</v>
+        <v>45225</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>51372</v>
+        <v>60265</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>100794</v>
+        <v>102863</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>99950</v>
+        <v>102890</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>35268</v>
+        <v>44085</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>51550</v>
+        <v>57370</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>16648</v>
+        <v>18623</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>125688</v>
+        <v>135876</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>101255</v>
+        <v>104148</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>105159</v>
+        <v>111368</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>78686</v>
+        <v>87295</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>57372</v>
+        <v>65957</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>97074</v>
+        <v>104210</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>42831</v>
+        <v>44906</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>96525</v>
+        <v>104894</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>110930</v>
+        <v>118165</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>47559</v>
+        <v>55691</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>32392</v>
+        <v>40490</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>35381</v>
+        <v>37297</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>88806</v>
+        <v>96660</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>31238</v>
+        <v>35143</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>91188</v>
+        <v>93140</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>87546</v>
+        <v>90150</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>51748</v>
+        <v>59353</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>50791</v>
+        <v>53143</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>28960</v>
+        <v>36200</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>45050</v>
+        <v>52239</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>28688</v>
+        <v>35860</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>69842</v>
+        <v>70998</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>27816</v>
+        <v>34770</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>29784</v>
+        <v>36642</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>27340</v>
+        <v>34175</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>39548</v>
+        <v>46300</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>27000</v>
+        <v>33750</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>37066</v>
+        <v>41818</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>32120</v>
+        <v>38698</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>12186</v>
+        <v>13594</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>26000</v>
+        <v>32500</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>71743</v>
+        <v>73683</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>31430</v>
+        <v>37716</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>24924</v>
+        <v>31155</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>33244</v>
+        <v>39470</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>24844</v>
+        <v>31055</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>65834</v>
+        <v>67000</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>24188</v>
+        <v>30235</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>53161</v>
+        <v>58857</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>74076</v>
+        <v>78149</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>59136</v>
+        <v>64991</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>33584</v>
+        <v>39430</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>20927</v>
+        <v>24699</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>17521</v>
+        <v>20450</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>40272</v>
+        <v>46018</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>44388</v>
+        <v>50062</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>70167</v>
+        <v>75380</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>27160</v>
+        <v>32592</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>57520</v>
+        <v>62243</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>23400</v>
+        <v>28800</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>21596</v>
+        <v>26995</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>44517</v>
+        <v>49913</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>21584</v>
+        <v>26980</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>32595</v>
+        <v>37984</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>25470</v>
+        <v>30858</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>21336</v>
+        <v>26670</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>72648</v>
+        <v>77770</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>47523</v>
+        <v>52699</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>20692</v>
+        <v>25865</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>24237</v>
+        <v>29397</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>24620</v>
+        <v>29489</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>64338</v>
+        <v>67725</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>20180</v>
+        <v>25225</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>29050</v>
+        <v>33793</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>34546</v>
+        <v>39573</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>65706</v>
+        <v>70650</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>35633</v>
+        <v>40514</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>56632</v>
+        <v>58585</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>19528</v>
+        <v>24410</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>17958</v>
+        <v>19910</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>24269</v>
+        <v>29138</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>36822</v>
+        <v>41667</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>67508</v>
+        <v>72330</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>21699</v>
+        <v>26521</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>19288</v>
+        <v>24110</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>19192</v>
+        <v>23990</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>20962</v>
+        <v>25726</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>18932</v>
+        <v>23665</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>28224</v>
+        <v>32928</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>53711</v>
+        <v>56063</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>18544</v>
+        <v>23180</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>41597</v>
+        <v>46000</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>51194</v>
+        <v>52934</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>57011</v>
+        <v>63174</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>60663</v>
+        <v>64605</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>21604</v>
+        <v>25532</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>19640</v>
+        <v>23568</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>46595</v>
+        <v>48559</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>27187</v>
+        <v>31044</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>32980</v>
+        <v>36860</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>46536</v>
+        <v>48475</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>15224</v>
+        <v>19030</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>15096</v>
+        <v>18870</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>49684</v>
+        <v>52695</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>34676</v>
+        <v>35873</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>37363</v>
+        <v>41099</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>30640</v>
+        <v>34372</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>45705</v>
+        <v>49320</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>14296</v>
+        <v>17870</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>27213</v>
+        <v>28623</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>13996</v>
+        <v>17495</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>41124</v>
+        <v>44551</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>13664</v>
+        <v>17080</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>13592</v>
+        <v>16990</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>13504</v>
+        <v>16880</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>13304</v>
+        <v>16630</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>13260</v>
+        <v>16575</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>33868</v>
+        <v>35749</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>40214</v>
+        <v>43171</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>34628</v>
+        <v>37173</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>12044</v>
+        <v>15055</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>34624</v>
+        <v>37634</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>11828</v>
+        <v>14785</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>14730</v>
+        <v>17676</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>13580</v>
+        <v>16490</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>13105</v>
+        <v>16014</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>11628</v>
+        <v>14535</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>31033</v>
+        <v>33938</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>11572</v>
+        <v>14465</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>14460</v>
+        <v>17352</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>11568</v>
+        <v>14460</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>11520</v>
+        <v>14400</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>11500</v>
+        <v>14375</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>34380</v>
+        <v>37245</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>11428</v>
+        <v>14285</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>11364</v>
+        <v>14205</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>11292</v>
+        <v>14115</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>11288</v>
+        <v>14110</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>11288</v>
+        <v>14110</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>11288</v>
+        <v>14110</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>36673</v>
+        <v>39494</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>26886</v>
+        <v>29141</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>26836</v>
+        <v>28057</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>34509</v>
+        <v>36503</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>31246</v>
+        <v>33148</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>21506</v>
+        <v>23558</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>21515</v>
+        <v>22831</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>11396</v>
+        <v>13937</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>14040</v>
+        <v>15660</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>12280</v>
+        <v>14736</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>21084</v>
+        <v>23531</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>9780</v>
+        <v>12225</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>9764</v>
+        <v>12205</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>9704</v>
+        <v>12130</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>11640</v>
+        <v>14065</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>9700</v>
+        <v>12125</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>9644</v>
+        <v>12055</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>9456</v>
+        <v>11820</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>11765</v>
+        <v>14118</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>9408</v>
+        <v>11760</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>9372</v>
+        <v>11715</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>10208</v>
+        <v>12178</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>23128</v>
+        <v>24276</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>9064</v>
+        <v>11330</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>13500</v>
+        <v>15750</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>8964</v>
+        <v>11205</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>8952</v>
+        <v>11190</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>25232</v>
+        <v>27120</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>10259</v>
+        <v>12437</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>25405</v>
+        <v>27417</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>8004</v>
+        <v>10005</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>7960</v>
+        <v>9950</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>7908</v>
+        <v>9885</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>7908</v>
+        <v>9885</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>7904</v>
+        <v>9880</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>7904</v>
+        <v>9880</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>21444</v>
+        <v>22861</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>7888</v>
+        <v>9860</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>7812</v>
+        <v>9765</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>7808</v>
+        <v>9760</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>23140</v>
+        <v>25045</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>7712</v>
+        <v>9640</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>7708</v>
+        <v>9635</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>7704</v>
+        <v>9630</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>7664</v>
+        <v>9580</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>7664</v>
+        <v>9580</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>7616</v>
+        <v>9520</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>7596</v>
+        <v>9495</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>20128</v>
+        <v>21386</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>24453</v>
+        <v>26334</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>7524</v>
+        <v>9405</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>7524</v>
+        <v>9405</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>7524</v>
+        <v>9405</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>7524</v>
+        <v>9405</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>19052</v>
+        <v>20059</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>9075</v>
+        <v>10929</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>7416</v>
+        <v>9270</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>7196</v>
+        <v>8995</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>7196</v>
+        <v>8995</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>7028</v>
+        <v>8785</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>7028</v>
+        <v>8785</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>6976</v>
+        <v>8720</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>6956</v>
+        <v>8695</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>6860</v>
+        <v>8575</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>20002</v>
+        <v>21526</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>19994</v>
+        <v>21708</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>6676</v>
+        <v>8345</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>6288</v>
+        <v>7860</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>7277</v>
+        <v>8813</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>6060</v>
+        <v>7575</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>5860</v>
+        <v>7325</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>5756</v>
+        <v>7195</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>5704</v>
+        <v>7130</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>18343</v>
+        <v>19754</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>16932</v>
+        <v>18343</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>5644</v>
+        <v>7055</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>5576</v>
+        <v>6970</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>5396</v>
+        <v>6745</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>5388</v>
+        <v>6735</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>17108</v>
+        <v>18424</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>5040</v>
+        <v>6300</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>6295</v>
+        <v>7554</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>5004</v>
+        <v>6255</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>4956</v>
+        <v>6195</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>4364</v>
+        <v>5455</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>5400</v>
+        <v>6480</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>4320</v>
+        <v>5400</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>4312</v>
+        <v>5390</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>4268</v>
+        <v>5335</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>12372</v>
+        <v>13403</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8295544</v>
+        <v>8631326</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1038902</v>
+        <v>1061906</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3136320</v>
+        <v>3171578</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1108147</v>
+        <v>1319670</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>863305</v>
+        <v>980695</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1591009</v>
+        <v>1742487</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2251640</v>
+        <v>2398700</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1040686</v>
+        <v>1132689</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1329844</v>
+        <v>1466563</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1417188</v>
+        <v>1548680</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>712839</v>
+        <v>827033</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>680074</v>
+        <v>786699</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>568052</v>
+        <v>640220</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>535250</v>
+        <v>637418</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1425732</v>
+        <v>1525218</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>986501</v>
+        <v>1080454</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>659348</v>
+        <v>716324</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1198399</v>
+        <v>1246937</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1043152</v>
+        <v>1052974</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>713980</v>
+        <v>794740</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>858887</v>
+        <v>939626</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>556513</v>
+        <v>660477</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>841100</v>
+        <v>917519</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>781195</v>
+        <v>788770</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>977382</v>
+        <v>1030806</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>543466</v>
+        <v>577643</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>819955</v>
+        <v>845478</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>249903</v>
+        <v>258152</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>670489</v>
+        <v>686304</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>747568</v>
+        <v>812679</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>598581</v>
+        <v>601743</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>641200</v>
+        <v>650308</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>530905</v>
+        <v>587567</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>882834</v>
+        <v>926287</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>760802</v>
+        <v>806793</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>321786</v>
+        <v>375417</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>333363</v>
+        <v>384233</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>651089</v>
+        <v>679894</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>545717</v>
+        <v>566866</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>655471</v>
+        <v>702303</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>492962</v>
+        <v>536957</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>459797</v>
+        <v>503647</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>117590</v>
+        <v>123402</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>380697</v>
+        <v>423744</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>548927</v>
+        <v>578866</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>135751</v>
+        <v>148047</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>143541</v>
+        <v>152252</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>561370</v>
+        <v>596073</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>393342</v>
+        <v>400494</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>109733</v>
+        <v>116005</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>467785</v>
+        <v>506958</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>195396</v>
+        <v>233984</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>565368</v>
+        <v>594098</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>552038</v>
+        <v>590084</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>442410</v>
+        <v>455672</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>273168</v>
+        <v>309208</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>414093</v>
+        <v>450157</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>321919</v>
+        <v>357754</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>373235</v>
+        <v>378146</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>57051</v>
+        <v>61538</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>294028</v>
+        <v>328362</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>168845</v>
+        <v>202614</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>451475</v>
+        <v>485019</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>355688</v>
+        <v>364351</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>482029</v>
+        <v>514096</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>371520</v>
+        <v>382196</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>157495</v>
+        <v>188994</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>392248</v>
+        <v>397975</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>405795</v>
+        <v>435521</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>257324</v>
+        <v>286917</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>315851</v>
+        <v>325436</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>210810</v>
+        <v>230091</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>261409</v>
+        <v>289728</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>353123</v>
+        <v>371391</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>318180</v>
+        <v>326526</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>159781</v>
+        <v>186223</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>148309</v>
+        <v>175810</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>199066</v>
+        <v>218585</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>160872</v>
+        <v>187930</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>260899</v>
+        <v>268805</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>290258</v>
+        <v>317072</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>132775</v>
+        <v>159330</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>132950</v>
+        <v>159236</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>293407</v>
+        <v>319641</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>348995</v>
+        <v>366458</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>129355</v>
+        <v>155226</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>128210</v>
+        <v>140005</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>261530</v>
+        <v>263034</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>272573</v>
+        <v>277453</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>333805</v>
+        <v>338979</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>219274</v>
+        <v>230284</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>187362</v>
+        <v>207727</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>301295</v>
+        <v>312814</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>101179</v>
+        <v>114695</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>138955</v>
+        <v>162193</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>371140</v>
+        <v>389209</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>285268</v>
+        <v>300369</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>195550</v>
+        <v>217281</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>108650</v>
+        <v>130380</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>147023</v>
+        <v>151766</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>185803</v>
+        <v>207396</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>208630</v>
+        <v>230026</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>106895</v>
+        <v>128274</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>213312</v>
+        <v>229358</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>106100</v>
+        <v>127320</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>212052</v>
+        <v>215957</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>101905</v>
+        <v>122286</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>114035</v>
+        <v>125846</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>246082</v>
+        <v>266032</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>195008</v>
+        <v>214762</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>119872</v>
+        <v>134414</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>164702</v>
+        <v>174382</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>201340</v>
+        <v>220744</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>134915</v>
+        <v>154186</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>143795</v>
+        <v>162968</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>95860</v>
+        <v>115032</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>186604</v>
+        <v>192902</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>119802</v>
+        <v>138724</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>229380</v>
+        <v>238026</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>180050</v>
+        <v>206534</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>155485</v>
+        <v>174002</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>236290</v>
+        <v>254756</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>193205</v>
+        <v>211466</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>54692</v>
+        <v>57567</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>163462</v>
+        <v>181258</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>61880</v>
+        <v>70700</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>57463</v>
+        <v>58917</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>182937</v>
+        <v>186313</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>119790</v>
+        <v>137080</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>177766</v>
+        <v>194689</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>192679</v>
+        <v>209528</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>123522</v>
+        <v>140109</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>98558</v>
+        <v>115119</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>47437</v>
+        <v>50312</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>105747</v>
+        <v>122241</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>82180</v>
+        <v>98616</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>195855</v>
+        <v>204141</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>56112</v>
+        <v>59852</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>143975</v>
+        <v>160172</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>168342</v>
+        <v>184508</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>110509</v>
+        <v>125241</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>82018</v>
+        <v>98031</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>210791</v>
+        <v>226318</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>195230</v>
+        <v>205108</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>91896</v>
+        <v>107212</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>77328</v>
+        <v>92403</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>109083</v>
+        <v>124036</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>161428</v>
+        <v>163639</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>72340</v>
+        <v>86808</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>156437</v>
+        <v>170750</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>118618</v>
+        <v>127405</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>180383</v>
+        <v>190027</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>35281</v>
+        <v>39515</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>714716</v>
+        <v>823100</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>175969</v>
+        <v>184040</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>226688</v>
+        <v>237025</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>165360</v>
+        <v>170608</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>48404</v>
+        <v>52188</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>29513</v>
+        <v>32662</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>92912</v>
+        <v>102205</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>109320</v>
+        <v>122985</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>87345</v>
+        <v>100908</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>185505</v>
+        <v>199030</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>109789</v>
+        <v>123022</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>145830</v>
+        <v>148652</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>107665</v>
+        <v>120542</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>111605</v>
+        <v>117560</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>63575</v>
+        <v>76290</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>95662</v>
+        <v>108351</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>85639</v>
+        <v>98314</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>63000</v>
+        <v>75600</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>127938</v>
+        <v>129838</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>61700</v>
+        <v>74040</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>162125</v>
+        <v>174428</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>174208</v>
+        <v>184708</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>127978</v>
+        <v>133342</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>71031</v>
+        <v>80558</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>69925</v>
+        <v>81553</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>115926</v>
+        <v>117842</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>57595</v>
+        <v>69114</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>89387</v>
+        <v>100671</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>88021</v>
+        <v>91379</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>54925</v>
+        <v>65910</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>117281</v>
+        <v>127921</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>118529</v>
+        <v>120803</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>104279</v>
+        <v>114822</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>63566</v>
+        <v>73756</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>109316</v>
+        <v>112050</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>100388</v>
+        <v>102270</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>125285</v>
+        <v>130195</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>145265</v>
+        <v>155146</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>49390</v>
+        <v>59268</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>53657</v>
+        <v>63471</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>48965</v>
+        <v>58758</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>48810</v>
+        <v>58572</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>108397</v>
+        <v>118109</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>136000</v>
+        <v>145646</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>135177</v>
+        <v>144782</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>88205</v>
+        <v>97792</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>105305</v>
+        <v>112148</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>113219</v>
+        <v>117734</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>85816</v>
+        <v>101319</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>51407</v>
+        <v>59879</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>45225</v>
+        <v>54270</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>60265</v>
+        <v>69158</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>102863</v>
+        <v>104932</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>102890</v>
+        <v>105830</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>44085</v>
+        <v>52902</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>57370</v>
+        <v>63190</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>18623</v>
+        <v>20598</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>135876</v>
+        <v>146064</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>104148</v>
+        <v>107041</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>111368</v>
+        <v>117577</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>87295</v>
+        <v>95904</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>65957</v>
+        <v>74542</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>104210</v>
+        <v>111346</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>44906</v>
+        <v>46981</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>104894</v>
+        <v>113263</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>118165</v>
+        <v>125400</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>55691</v>
+        <v>63823</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>40490</v>
+        <v>48588</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>37297</v>
+        <v>39213</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>96660</v>
+        <v>104514</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>35143</v>
+        <v>39048</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>93140</v>
+        <v>95092</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>90150</v>
+        <v>92754</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>59353</v>
+        <v>66958</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>53143</v>
+        <v>55495</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>36200</v>
+        <v>43440</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>52239</v>
+        <v>59428</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>35860</v>
+        <v>43032</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>70998</v>
+        <v>72154</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>34770</v>
+        <v>41724</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>36642</v>
+        <v>43500</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>34175</v>
+        <v>41010</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>46300</v>
+        <v>53052</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>33750</v>
+        <v>40500</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>41818</v>
+        <v>46570</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>38698</v>
+        <v>45276</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>13594</v>
+        <v>15002</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>32500</v>
+        <v>39000</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>73683</v>
+        <v>75623</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>37716</v>
+        <v>44002</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>31155</v>
+        <v>37386</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>39470</v>
+        <v>45696</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>31055</v>
+        <v>37266</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>67000</v>
+        <v>68166</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>30235</v>
+        <v>36282</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>58857</v>
+        <v>64553</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>78149</v>
+        <v>82222</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>64991</v>
+        <v>70846</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>39430</v>
+        <v>45276</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>24699</v>
+        <v>28471</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>20450</v>
+        <v>23379</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>46018</v>
+        <v>51764</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>50062</v>
+        <v>55736</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>75380</v>
+        <v>80593</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>32592</v>
+        <v>38024</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>62243</v>
+        <v>66966</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>28800</v>
+        <v>34200</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>26995</v>
+        <v>32394</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>49913</v>
+        <v>55309</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>26980</v>
+        <v>32376</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>37984</v>
+        <v>43373</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>30858</v>
+        <v>36246</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>26670</v>
+        <v>32004</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>77770</v>
+        <v>82892</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>52699</v>
+        <v>57875</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>25865</v>
+        <v>31038</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>29397</v>
+        <v>34557</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>29489</v>
+        <v>34358</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>67725</v>
+        <v>71112</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>25225</v>
+        <v>30270</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>33793</v>
+        <v>38536</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>39573</v>
+        <v>44600</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>70650</v>
+        <v>75594</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>40514</v>
+        <v>45395</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>58585</v>
+        <v>60538</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>24410</v>
+        <v>29292</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>19910</v>
+        <v>21862</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>29138</v>
+        <v>34007</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>41667</v>
+        <v>46512</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>72330</v>
+        <v>77152</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>26521</v>
+        <v>31343</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>24110</v>
+        <v>28932</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>23990</v>
+        <v>28788</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>25726</v>
+        <v>30490</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>23665</v>
+        <v>28398</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>32928</v>
+        <v>37632</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>56063</v>
+        <v>58415</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>23180</v>
+        <v>27816</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>46000</v>
+        <v>50403</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>52934</v>
+        <v>54674</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>63174</v>
+        <v>69337</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>64605</v>
+        <v>68547</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>25532</v>
+        <v>29460</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>23568</v>
+        <v>27496</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>48559</v>
+        <v>50523</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>31044</v>
+        <v>34901</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>36860</v>
+        <v>40740</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>48475</v>
+        <v>50414</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>19030</v>
+        <v>22836</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>18870</v>
+        <v>22644</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>52695</v>
+        <v>55706</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>35873</v>
+        <v>37070</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>41099</v>
+        <v>44835</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>34372</v>
+        <v>38104</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>49320</v>
+        <v>52935</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>17870</v>
+        <v>21444</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>28623</v>
+        <v>30033</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>17495</v>
+        <v>20994</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>44551</v>
+        <v>47978</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>17080</v>
+        <v>20496</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>16990</v>
+        <v>20388</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>16880</v>
+        <v>20256</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>16630</v>
+        <v>19956</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>16575</v>
+        <v>19890</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>35749</v>
+        <v>37630</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>43171</v>
+        <v>46128</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>37173</v>
+        <v>39718</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>15055</v>
+        <v>18066</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>37634</v>
+        <v>40644</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>14785</v>
+        <v>17742</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>17676</v>
+        <v>20622</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>16490</v>
+        <v>19400</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>16014</v>
+        <v>18923</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>14535</v>
+        <v>17442</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>33938</v>
+        <v>36843</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>14465</v>
+        <v>17358</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>17352</v>
+        <v>20244</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>14460</v>
+        <v>17352</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>14400</v>
+        <v>17280</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>14375</v>
+        <v>17250</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>37245</v>
+        <v>40110</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>14285</v>
+        <v>17142</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>14205</v>
+        <v>17046</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>14115</v>
+        <v>16938</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>14110</v>
+        <v>16932</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>14110</v>
+        <v>16932</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>14110</v>
+        <v>16932</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>39494</v>
+        <v>42315</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>29141</v>
+        <v>31396</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>28057</v>
+        <v>29278</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>36503</v>
+        <v>38497</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>33148</v>
+        <v>35050</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>23558</v>
+        <v>25610</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>22831</v>
+        <v>24147</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>13937</v>
+        <v>16478</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>15660</v>
+        <v>17280</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>14736</v>
+        <v>17192</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>23531</v>
+        <v>25978</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>12225</v>
+        <v>14670</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>12205</v>
+        <v>14646</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>12130</v>
+        <v>14556</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>14065</v>
+        <v>16490</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>12125</v>
+        <v>14550</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>12055</v>
+        <v>14466</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>11820</v>
+        <v>14184</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>14118</v>
+        <v>16471</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>11760</v>
+        <v>14112</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>11715</v>
+        <v>14058</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>12178</v>
+        <v>14148</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>24276</v>
+        <v>25424</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>11330</v>
+        <v>13596</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>15750</v>
+        <v>18000</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>11205</v>
+        <v>13446</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>11190</v>
+        <v>13428</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>27120</v>
+        <v>29008</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>12437</v>
+        <v>14615</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>27417</v>
+        <v>29429</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>10005</v>
+        <v>12006</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>9950</v>
+        <v>11940</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>9885</v>
+        <v>11862</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>9885</v>
+        <v>11862</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>9880</v>
+        <v>11856</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>9880</v>
+        <v>11856</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>22861</v>
+        <v>24278</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>9860</v>
+        <v>11832</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>9765</v>
+        <v>11718</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>9760</v>
+        <v>11712</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>25045</v>
+        <v>26950</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>9640</v>
+        <v>11568</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>9635</v>
+        <v>11562</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>9630</v>
+        <v>11556</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>9580</v>
+        <v>11496</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>9580</v>
+        <v>11496</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>9520</v>
+        <v>11424</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>9495</v>
+        <v>11394</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>21386</v>
+        <v>22644</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>26334</v>
+        <v>28215</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>9405</v>
+        <v>11286</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>9405</v>
+        <v>11286</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>9405</v>
+        <v>11286</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>9405</v>
+        <v>11286</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>20059</v>
+        <v>21066</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>10929</v>
+        <v>12783</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>9270</v>
+        <v>11124</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>8995</v>
+        <v>10794</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>8995</v>
+        <v>10794</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>8785</v>
+        <v>10542</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>8785</v>
+        <v>10542</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>8720</v>
+        <v>10464</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>8695</v>
+        <v>10434</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>8575</v>
+        <v>10290</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>21526</v>
+        <v>23050</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>21708</v>
+        <v>23422</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>8345</v>
+        <v>10014</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>7860</v>
+        <v>9432</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>8813</v>
+        <v>10349</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>7575</v>
+        <v>9090</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>7325</v>
+        <v>8790</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>7195</v>
+        <v>8634</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>7130</v>
+        <v>8556</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>19754</v>
+        <v>21165</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>18343</v>
+        <v>19754</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>7055</v>
+        <v>8466</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>6970</v>
+        <v>8364</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>6745</v>
+        <v>8094</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>6735</v>
+        <v>8082</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>18424</v>
+        <v>19740</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>6300</v>
+        <v>7560</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>7554</v>
+        <v>8813</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>6255</v>
+        <v>7506</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>6195</v>
+        <v>7434</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>5455</v>
+        <v>6546</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>6480</v>
+        <v>7560</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>5400</v>
+        <v>6480</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>5390</v>
+        <v>6468</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>5335</v>
+        <v>6402</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>13403</v>
+        <v>14434</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8631326</v>
+        <v>8967108</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1061906</v>
+        <v>1084910</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>296003</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3171578</v>
+        <v>3206836</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1319670</v>
+        <v>1531193</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>158965</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>980695</v>
+        <v>1098085</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>151478</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1742487</v>
+        <v>1893965</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>147060</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2398700</v>
+        <v>2545760</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>141311</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1132689</v>
+        <v>1224692</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1466563</v>
+        <v>1603282</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1548680</v>
+        <v>1680172</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>114194</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>827033</v>
+        <v>941227</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>106625</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>786699</v>
+        <v>893324</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>106106</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>640220</v>
+        <v>712388</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>102168</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>637418</v>
+        <v>739586</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>99486</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1525218</v>
+        <v>1624704</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>93953</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1080454</v>
+        <v>1174407</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>88046</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>716324</v>
+        <v>773300</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>84208</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1246937</v>
+        <v>1295475</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>82618</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1052974</v>
+        <v>1062796</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>80760</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>794740</v>
+        <v>875500</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>80739</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>939626</v>
+        <v>1020365</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>79502</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>660477</v>
+        <v>764441</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>76419</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>917519</v>
+        <v>993938</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>74332</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>788770</v>
+        <v>796345</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>70990</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1030806</v>
+        <v>1084230</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>69504</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>577643</v>
+        <v>611820</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>69234</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>845478</v>
+        <v>871001</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>68460</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>258152</v>
+        <v>266401</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>65193</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>686304</v>
+        <v>702119</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>65111</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>812679</v>
+        <v>877790</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>64401</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>601743</v>
+        <v>604905</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>59566</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>650308</v>
+        <v>659416</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>56662</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>587567</v>
+        <v>644229</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>53890</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>926287</v>
+        <v>969740</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>53653</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>806793</v>
+        <v>852784</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>53631</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>375417</v>
+        <v>429048</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>50870</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>384233</v>
+        <v>435103</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>48086</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>679894</v>
+        <v>708699</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>47876</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>566866</v>
+        <v>588015</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>46832</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>702303</v>
+        <v>749135</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>43995</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>536957</v>
+        <v>580952</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>43850</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>503647</v>
+        <v>547497</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>43416</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>123402</v>
+        <v>129214</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>43047</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>423744</v>
+        <v>466791</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>42364</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>578866</v>
+        <v>608805</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>41300</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>148047</v>
+        <v>160343</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>41270</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>152252</v>
+        <v>160963</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>40719</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>596073</v>
+        <v>630776</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>39334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>400494</v>
+        <v>407646</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>39193</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>116005</v>
+        <v>122277</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>39173</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>506958</v>
+        <v>546131</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>38588</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>233984</v>
+        <v>272572</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>38479</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>594098</v>
+        <v>622828</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>38046</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>590084</v>
+        <v>628130</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>37610</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>455672</v>
+        <v>468934</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>36417</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>309208</v>
+        <v>345248</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>36064</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>450157</v>
+        <v>486221</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>35835</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>357754</v>
+        <v>393589</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>34868</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>378146</v>
+        <v>383057</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>34616</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>61538</v>
+        <v>66025</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>34334</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>328362</v>
+        <v>362696</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>33769</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>202614</v>
+        <v>236383</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>33544</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>485019</v>
+        <v>518563</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>33063</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>364351</v>
+        <v>373014</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>32165</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>514096</v>
+        <v>546163</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>31814</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>382196</v>
+        <v>392872</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>31499</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>188994</v>
+        <v>220493</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>31494</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>397975</v>
+        <v>403702</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>29726</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>435521</v>
+        <v>465247</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>29593</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>286917</v>
+        <v>316510</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>29237</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>325436</v>
+        <v>335021</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>28689</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>230091</v>
+        <v>249372</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>28319</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>289728</v>
+        <v>318047</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>28162</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>371391</v>
+        <v>389659</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>27645</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>326526</v>
+        <v>334872</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>27571</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>186223</v>
+        <v>212665</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>27501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>175810</v>
+        <v>203311</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>27294</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>218585</v>
+        <v>238104</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>27058</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>187930</v>
+        <v>214988</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>26961</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>268805</v>
+        <v>276711</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>26814</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>317072</v>
+        <v>343886</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>26555</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>159330</v>
+        <v>185885</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>26286</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>159236</v>
+        <v>185522</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>26234</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>319641</v>
+        <v>345875</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>26168</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>366458</v>
+        <v>383921</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>25871</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>155226</v>
+        <v>181097</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>25641</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>140005</v>
+        <v>151800</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>25401</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>263034</v>
+        <v>264538</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>25120</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>277453</v>
+        <v>282333</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>24939</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>338979</v>
+        <v>344153</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>24466</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>230284</v>
+        <v>241294</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>24373</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>207727</v>
+        <v>228092</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>24370</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>312814</v>
+        <v>324333</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>23893</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>114695</v>
+        <v>128211</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>23238</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>162193</v>
+        <v>185431</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>21874</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>389209</v>
+        <v>407278</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>21772</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>300369</v>
+        <v>315470</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>21731</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>217281</v>
+        <v>239012</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>21730</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>130380</v>
+        <v>152110</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>21717</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>151766</v>
+        <v>156509</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>21593</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>207396</v>
+        <v>228989</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>21396</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>230026</v>
+        <v>251422</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>21379</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>128274</v>
+        <v>149653</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>21292</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>229358</v>
+        <v>245404</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>21220</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>127320</v>
+        <v>148540</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>20958</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>215957</v>
+        <v>219862</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>20381</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>122286</v>
+        <v>142667</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>20138</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>125846</v>
+        <v>137657</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>19950</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>266032</v>
+        <v>285982</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>19754</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>214762</v>
+        <v>234516</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>19651</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>134414</v>
+        <v>148956</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>19502</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>174382</v>
+        <v>184062</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>19404</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>220744</v>
+        <v>240148</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>19271</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>154186</v>
+        <v>173457</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>19173</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>162968</v>
+        <v>182141</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>19172</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>115032</v>
+        <v>134204</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>19075</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>192902</v>
+        <v>199200</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>18922</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>138724</v>
+        <v>157646</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>18615</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>238026</v>
+        <v>246672</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>18578</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>206534</v>
+        <v>233018</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>18517</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>174002</v>
+        <v>192519</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>18466</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>254756</v>
+        <v>273222</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>18261</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>211466</v>
+        <v>229727</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>18146</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>57567</v>
+        <v>60442</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>17796</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>181258</v>
+        <v>199054</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>17780</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>70700</v>
+        <v>79520</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>17393</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>58917</v>
+        <v>60371</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>17304</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>186313</v>
+        <v>189689</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>17290</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>137080</v>
+        <v>154370</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>16923</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>194689</v>
+        <v>211612</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>16849</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>209528</v>
+        <v>226377</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>16587</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>140109</v>
+        <v>156696</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>16561</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>115119</v>
+        <v>131680</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>16531</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>50312</v>
+        <v>53187</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>16494</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>122241</v>
+        <v>138735</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>16436</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>98616</v>
+        <v>115052</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>16281</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>204141</v>
+        <v>212427</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>16245</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>59852</v>
+        <v>63592</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>16197</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>160172</v>
+        <v>176369</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>16166</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>184508</v>
+        <v>200674</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>16043</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>125241</v>
+        <v>139973</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>16013</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>98031</v>
+        <v>114044</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>15527</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>226318</v>
+        <v>241845</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>15525</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>205108</v>
+        <v>214986</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>15316</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>107212</v>
+        <v>122528</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>15075</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>92403</v>
+        <v>107478</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>14953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>124036</v>
+        <v>138989</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>14915</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>163639</v>
+        <v>165850</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>14468</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>86808</v>
+        <v>101276</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>14313</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>170750</v>
+        <v>185063</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>14153</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>127405</v>
+        <v>136192</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>14149</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>190027</v>
+        <v>199671</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>14111</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>39515</v>
+        <v>43749</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>14097</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>823100</v>
+        <v>931484</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>14018</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>184040</v>
+        <v>192111</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>13943</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>237025</v>
+        <v>247362</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>13912</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>170608</v>
+        <v>175856</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>13860</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>52188</v>
+        <v>55972</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>13768</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>32662</v>
+        <v>35811</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>13696</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>102205</v>
+        <v>111498</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>13666</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>122985</v>
+        <v>136650</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>13563</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>100908</v>
+        <v>114471</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>13525</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>199030</v>
+        <v>212555</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>13233</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>123022</v>
+        <v>136255</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>13172</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>148652</v>
+        <v>151474</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>12877</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>120542</v>
+        <v>133419</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>12786</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>117560</v>
+        <v>123515</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>12715</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>76290</v>
+        <v>89005</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>12689</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>108351</v>
+        <v>121040</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>12675</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>98314</v>
+        <v>110989</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>12600</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>75600</v>
+        <v>88200</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>12513</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>129838</v>
+        <v>131738</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>12340</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>74040</v>
+        <v>86380</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>12303</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>174428</v>
+        <v>186731</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>11974</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>184708</v>
+        <v>195208</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>11763</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>133342</v>
+        <v>138706</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>11698</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>80558</v>
+        <v>90085</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>11628</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>81553</v>
+        <v>93181</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>11598</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>117842</v>
+        <v>119758</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>11519</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>69114</v>
+        <v>80633</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>11284</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>100671</v>
+        <v>111955</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>10989</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>91379</v>
+        <v>94737</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>10985</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>65910</v>
+        <v>76895</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>10640</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>127921</v>
+        <v>138561</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>10582</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>120803</v>
+        <v>123077</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>10543</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>114822</v>
+        <v>125365</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>10190</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>73756</v>
+        <v>83946</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>10057</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>112050</v>
+        <v>114784</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>9973</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>102270</v>
+        <v>104152</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>9898</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>130195</v>
+        <v>135105</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>9881</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>155146</v>
+        <v>165027</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>9878</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>59268</v>
+        <v>69146</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>9814</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>63471</v>
+        <v>73285</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>9793</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>58758</v>
+        <v>68551</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>9762</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>58572</v>
+        <v>68334</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>9712</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>118109</v>
+        <v>127821</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>9646</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>145646</v>
+        <v>155292</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>9605</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>144782</v>
+        <v>154387</v>
       </c>
       <c r="J246" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>9587</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>97792</v>
+        <v>107379</v>
       </c>
       <c r="J247" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>9503</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>112148</v>
+        <v>118991</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>9470</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>117734</v>
+        <v>122249</v>
       </c>
       <c r="J251" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>9099</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>101319</v>
+        <v>116822</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>9047</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>59879</v>
+        <v>68351</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>9045</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>54270</v>
+        <v>63315</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>8893</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>69158</v>
+        <v>78051</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>8847</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>104932</v>
+        <v>107001</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>8819</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>105830</v>
+        <v>108770</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>8817</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>52902</v>
+        <v>61719</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>8750</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>63190</v>
+        <v>69010</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>8748</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>20598</v>
+        <v>22573</v>
       </c>
       <c r="J263" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>8726</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>146064</v>
+        <v>156252</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>8679</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>107041</v>
+        <v>109934</v>
       </c>
       <c r="J266" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>8653</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>117577</v>
+        <v>123786</v>
       </c>
       <c r="J267" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>8609</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>95904</v>
+        <v>104513</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>8585</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>74542</v>
+        <v>83127</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>8572</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>111346</v>
+        <v>118482</v>
       </c>
       <c r="J271" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>8399</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>46981</v>
+        <v>49056</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>8369</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>113263</v>
+        <v>121632</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>8199</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>125400</v>
+        <v>132635</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>8132</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>63823</v>
+        <v>71955</v>
       </c>
       <c r="J278" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>8098</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>48588</v>
+        <v>56686</v>
       </c>
       <c r="J279" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>8084</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>39213</v>
+        <v>41129</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>7854</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>104514</v>
+        <v>112368</v>
       </c>
       <c r="J283" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>7809</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>39048</v>
+        <v>42953</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>7772</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>95092</v>
+        <v>97044</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>7713</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>92754</v>
+        <v>95358</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>7605</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>66958</v>
+        <v>74563</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>7525</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>55495</v>
+        <v>57847</v>
       </c>
       <c r="J290" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>7240</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>43440</v>
+        <v>50680</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>7189</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>59428</v>
+        <v>66617</v>
       </c>
       <c r="J296" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>7172</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>43032</v>
+        <v>50204</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>7074</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>72154</v>
+        <v>73310</v>
       </c>
       <c r="J298" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>6954</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>41724</v>
+        <v>48678</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6858</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>43500</v>
+        <v>50358</v>
       </c>
       <c r="J301" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6835</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>41010</v>
+        <v>47845</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6752</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>53052</v>
+        <v>59804</v>
       </c>
       <c r="J304" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6750</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>40500</v>
+        <v>47250</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>6653</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>46570</v>
+        <v>51322</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>6578</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>45276</v>
+        <v>51854</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>6554</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>15002</v>
+        <v>16410</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>6500</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>39000</v>
+        <v>45500</v>
       </c>
       <c r="J314" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>6308</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>75623</v>
+        <v>77563</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>6286</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>44002</v>
+        <v>50288</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>6231</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>37386</v>
+        <v>43617</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>6226</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>45696</v>
+        <v>51922</v>
       </c>
       <c r="J323" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>6211</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>37266</v>
+        <v>43477</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>6117</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>68166</v>
+        <v>69332</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>6047</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>36282</v>
+        <v>42329</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>6017</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>64553</v>
+        <v>70249</v>
       </c>
       <c r="J328" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>6014</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>82222</v>
+        <v>86295</v>
       </c>
       <c r="J329" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>5855</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>70846</v>
+        <v>76701</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>5846</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>45276</v>
+        <v>51122</v>
       </c>
       <c r="J334" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>5839</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>28471</v>
+        <v>32243</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>5805</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>23379</v>
+        <v>26308</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>5746</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>51764</v>
+        <v>57510</v>
       </c>
       <c r="J339" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>5674</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>55736</v>
+        <v>61410</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>5636</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>80593</v>
+        <v>85806</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>5432</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>38024</v>
+        <v>43456</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>5420</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>66966</v>
+        <v>71689</v>
       </c>
       <c r="J346" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>5400</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>34200</v>
+        <v>39600</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>5399</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>32394</v>
+        <v>37793</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>5396</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>55309</v>
+        <v>60705</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>5396</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>32376</v>
+        <v>37772</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>5389</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>43373</v>
+        <v>48762</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>5388</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>36246</v>
+        <v>41634</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>5334</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>32004</v>
+        <v>37338</v>
       </c>
       <c r="J355" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>5216</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>82892</v>
+        <v>88014</v>
       </c>
       <c r="J357" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>5176</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>57875</v>
+        <v>63051</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>5173</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>31038</v>
+        <v>36211</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>5160</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>34557</v>
+        <v>39717</v>
       </c>
       <c r="J363" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>5144</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>34358</v>
+        <v>39227</v>
       </c>
       <c r="J364" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>5079</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>71112</v>
+        <v>74499</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>5045</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>30270</v>
+        <v>35315</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>5039</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>38536</v>
+        <v>43279</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>5027</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>44600</v>
+        <v>49627</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -36048,10 +36048,10 @@
         <v>4944</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>75594</v>
+        <v>80538</v>
       </c>
       <c r="J371" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
         <is>
@@ -36144,10 +36144,10 @@
         <v>4882</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>45395</v>
+        <v>50276</v>
       </c>
       <c r="J372" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>4882</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>60538</v>
+        <v>62491</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>4882</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>29292</v>
+        <v>34174</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36432,10 +36432,10 @@
         <v>4880</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>21862</v>
+        <v>23814</v>
       </c>
       <c r="J375" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>4869</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>34007</v>
+        <v>38876</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36912,10 +36912,10 @@
         <v>4845</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>46512</v>
+        <v>51357</v>
       </c>
       <c r="J380" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>4822</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>77152</v>
+        <v>81974</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37104,10 +37104,10 @@
         <v>4822</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>31343</v>
+        <v>36165</v>
       </c>
       <c r="J382" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
         <is>
@@ -37200,10 +37200,10 @@
         <v>4822</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>28932</v>
+        <v>33754</v>
       </c>
       <c r="J383" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
@@ -37392,10 +37392,10 @@
         <v>4798</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>28788</v>
+        <v>33586</v>
       </c>
       <c r="J385" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>4764</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>30490</v>
+        <v>35254</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>4733</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>28398</v>
+        <v>33131</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         <v>4704</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>37632</v>
+        <v>42336</v>
       </c>
       <c r="J392" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
         <is>
@@ -38160,10 +38160,10 @@
         <v>4703</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>58415</v>
+        <v>60767</v>
       </c>
       <c r="J393" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>4636</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>27816</v>
+        <v>32452</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>4403</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>50403</v>
+        <v>54806</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>4373</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>54674</v>
+        <v>56414</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>4329</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>69337</v>
+        <v>75500</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>3942</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>68547</v>
+        <v>72489</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>3928</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>29460</v>
+        <v>33388</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>3928</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>27496</v>
+        <v>31424</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         <v>3927</v>
       </c>
       <c r="I407" s="2" t="n">
-        <v>50523</v>
+        <v>52487</v>
       </c>
       <c r="J407" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>3921</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>34901</v>
+        <v>38758</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>3880</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>40740</v>
+        <v>44620</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39888,10 +39888,10 @@
         <v>3878</v>
       </c>
       <c r="I411" s="2" t="n">
-        <v>50414</v>
+        <v>52353</v>
       </c>
       <c r="J411" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
         <is>
@@ -40176,10 +40176,10 @@
         <v>3806</v>
       </c>
       <c r="I414" s="2" t="n">
-        <v>22836</v>
+        <v>26642</v>
       </c>
       <c r="J414" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         <v>3774</v>
       </c>
       <c r="I416" s="2" t="n">
-        <v>22644</v>
+        <v>26418</v>
       </c>
       <c r="J416" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>3764</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>55706</v>
+        <v>58717</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40656,10 +40656,10 @@
         <v>3736</v>
       </c>
       <c r="I419" s="2" t="n">
-        <v>37070</v>
+        <v>38267</v>
       </c>
       <c r="J419" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>3736</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>44835</v>
+        <v>48571</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>3732</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>38104</v>
+        <v>41836</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>3615</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>52935</v>
+        <v>56550</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41136,10 +41136,10 @@
         <v>3574</v>
       </c>
       <c r="I424" s="2" t="n">
-        <v>21444</v>
+        <v>25018</v>
       </c>
       <c r="J424" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>3525</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>30033</v>
+        <v>31443</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41424,10 +41424,10 @@
         <v>3499</v>
       </c>
       <c r="I427" s="2" t="n">
-        <v>20994</v>
+        <v>24493</v>
       </c>
       <c r="J427" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
         <is>
@@ -41520,10 +41520,10 @@
         <v>3427</v>
       </c>
       <c r="I428" s="2" t="n">
-        <v>47978</v>
+        <v>51405</v>
       </c>
       <c r="J428" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>3416</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>20496</v>
+        <v>23912</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -41808,10 +41808,10 @@
         <v>3398</v>
       </c>
       <c r="I431" s="2" t="n">
-        <v>20388</v>
+        <v>23786</v>
       </c>
       <c r="J431" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>3376</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>20256</v>
+        <v>23632</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42384,10 +42384,10 @@
         <v>3326</v>
       </c>
       <c r="I437" s="2" t="n">
-        <v>19956</v>
+        <v>23282</v>
       </c>
       <c r="J437" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>3315</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>19890</v>
+        <v>23205</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42768,10 +42768,10 @@
         <v>3293</v>
       </c>
       <c r="I441" s="2" t="n">
-        <v>37630</v>
+        <v>39511</v>
       </c>
       <c r="J441" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
         <is>
@@ -42864,10 +42864,10 @@
         <v>3154</v>
       </c>
       <c r="I442" s="2" t="n">
-        <v>46128</v>
+        <v>49085</v>
       </c>
       <c r="J442" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>3056</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>39718</v>
+        <v>42263</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>3011</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>18066</v>
+        <v>21077</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43152,10 +43152,10 @@
         <v>3010</v>
       </c>
       <c r="I445" s="2" t="n">
-        <v>40644</v>
+        <v>43654</v>
       </c>
       <c r="J445" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>2957</v>
       </c>
       <c r="I446" s="2" t="n">
-        <v>17742</v>
+        <v>20699</v>
       </c>
       <c r="J446" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
@@ -43344,10 +43344,10 @@
         <v>2946</v>
       </c>
       <c r="I447" s="2" t="n">
-        <v>20622</v>
+        <v>23568</v>
       </c>
       <c r="J447" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
         <is>
@@ -43920,10 +43920,10 @@
         <v>2910</v>
       </c>
       <c r="I453" s="2" t="n">
-        <v>19400</v>
+        <v>22310</v>
       </c>
       <c r="J453" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>2909</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>18923</v>
+        <v>21832</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44112,10 +44112,10 @@
         <v>2907</v>
       </c>
       <c r="I455" s="2" t="n">
-        <v>17442</v>
+        <v>20349</v>
       </c>
       <c r="J455" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>2905</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>36843</v>
+        <v>39748</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>2893</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>17358</v>
+        <v>20251</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44400,10 +44400,10 @@
         <v>2892</v>
       </c>
       <c r="I458" s="2" t="n">
-        <v>20244</v>
+        <v>23136</v>
       </c>
       <c r="J458" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>2892</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>17352</v>
+        <v>20244</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>2880</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>17280</v>
+        <v>20160</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>2875</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>17250</v>
+        <v>20125</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>2865</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>40110</v>
+        <v>42975</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>2857</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>17142</v>
+        <v>19999</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45264,10 +45264,10 @@
         <v>2841</v>
       </c>
       <c r="I467" s="2" t="n">
-        <v>17046</v>
+        <v>19887</v>
       </c>
       <c r="J467" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>2823</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>16938</v>
+        <v>19761</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -45840,10 +45840,10 @@
         <v>2822</v>
       </c>
       <c r="I473" s="2" t="n">
-        <v>16932</v>
+        <v>19754</v>
       </c>
       <c r="J473" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
         <is>
@@ -45936,10 +45936,10 @@
         <v>2822</v>
       </c>
       <c r="I474" s="2" t="n">
-        <v>16932</v>
+        <v>19754</v>
       </c>
       <c r="J474" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>2822</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>16932</v>
+        <v>19754</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46128,10 +46128,10 @@
         <v>2821</v>
       </c>
       <c r="I476" s="2" t="n">
-        <v>42315</v>
+        <v>45136</v>
       </c>
       <c r="J476" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
         <is>
@@ -46224,10 +46224,10 @@
         <v>2818</v>
       </c>
       <c r="I477" s="2" t="n">
-        <v>31396</v>
+        <v>33651</v>
       </c>
       <c r="J477" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         <v>2744</v>
       </c>
       <c r="I479" s="2" t="n">
-        <v>29278</v>
+        <v>30499</v>
       </c>
       <c r="J479" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>2730</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>38497</v>
+        <v>40491</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>2717</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>35050</v>
+        <v>36952</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46896,10 +46896,10 @@
         <v>2666</v>
       </c>
       <c r="I484" s="2" t="n">
-        <v>25610</v>
+        <v>27662</v>
       </c>
       <c r="J484" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         <v>2631</v>
       </c>
       <c r="I485" s="2" t="n">
-        <v>24147</v>
+        <v>25463</v>
       </c>
       <c r="J485" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>2541</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>16478</v>
+        <v>19019</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47280,10 +47280,10 @@
         <v>2520</v>
       </c>
       <c r="I488" s="2" t="n">
-        <v>17280</v>
+        <v>18900</v>
       </c>
       <c r="J488" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>2456</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>17192</v>
+        <v>19648</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>2447</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>25978</v>
+        <v>28425</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>2445</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>14670</v>
+        <v>17115</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -47664,10 +47664,10 @@
         <v>2441</v>
       </c>
       <c r="I492" s="2" t="n">
-        <v>14646</v>
+        <v>17087</v>
       </c>
       <c r="J492" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
         <is>
@@ -47952,10 +47952,10 @@
         <v>2426</v>
       </c>
       <c r="I495" s="2" t="n">
-        <v>14556</v>
+        <v>16982</v>
       </c>
       <c r="J495" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
         <is>
@@ -48144,10 +48144,10 @@
         <v>2425</v>
       </c>
       <c r="I497" s="2" t="n">
-        <v>16490</v>
+        <v>18915</v>
       </c>
       <c r="J497" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>2425</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>14550</v>
+        <v>16975</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48336,10 +48336,10 @@
         <v>2411</v>
       </c>
       <c r="I499" s="2" t="n">
-        <v>14466</v>
+        <v>16877</v>
       </c>
       <c r="J499" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
         <is>
@@ -48432,10 +48432,10 @@
         <v>2364</v>
       </c>
       <c r="I500" s="2" t="n">
-        <v>14184</v>
+        <v>16548</v>
       </c>
       <c r="J500" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
         <is>
@@ -48624,10 +48624,10 @@
         <v>2353</v>
       </c>
       <c r="I502" s="2" t="n">
-        <v>16471</v>
+        <v>18824</v>
       </c>
       <c r="J502" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
         <is>
@@ -48816,10 +48816,10 @@
         <v>2352</v>
       </c>
       <c r="I504" s="2" t="n">
-        <v>14112</v>
+        <v>16464</v>
       </c>
       <c r="J504" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>2343</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>14058</v>
+        <v>16401</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49008,10 +49008,10 @@
         <v>2328</v>
       </c>
       <c r="I506" s="2" t="n">
-        <v>14148</v>
+        <v>16118</v>
       </c>
       <c r="J506" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>2317</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>25424</v>
+        <v>26572</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2266</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>13596</v>
+        <v>15862</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2250</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>18000</v>
+        <v>20250</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49584,10 +49584,10 @@
         <v>2241</v>
       </c>
       <c r="I512" s="2" t="n">
-        <v>13446</v>
+        <v>15687</v>
       </c>
       <c r="J512" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
         <is>
@@ -49680,10 +49680,10 @@
         <v>2238</v>
       </c>
       <c r="I513" s="2" t="n">
-        <v>13428</v>
+        <v>15666</v>
       </c>
       <c r="J513" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
         <is>
@@ -49776,10 +49776,10 @@
         <v>2224</v>
       </c>
       <c r="I514" s="2" t="n">
-        <v>29008</v>
+        <v>30896</v>
       </c>
       <c r="J514" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2178</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>14615</v>
+        <v>16793</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -50736,10 +50736,10 @@
         <v>2025</v>
       </c>
       <c r="I524" s="2" t="n">
-        <v>29429</v>
+        <v>31441</v>
       </c>
       <c r="J524" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
         <is>
@@ -50832,10 +50832,10 @@
         <v>2001</v>
       </c>
       <c r="I525" s="2" t="n">
-        <v>12006</v>
+        <v>14007</v>
       </c>
       <c r="J525" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
         <is>
@@ -50928,10 +50928,10 @@
         <v>1990</v>
       </c>
       <c r="I526" s="2" t="n">
-        <v>11940</v>
+        <v>13930</v>
       </c>
       <c r="J526" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>1977</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>11862</v>
+        <v>13839</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51120,10 +51120,10 @@
         <v>1977</v>
       </c>
       <c r="I528" s="2" t="n">
-        <v>11862</v>
+        <v>13839</v>
       </c>
       <c r="J528" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
         <is>
@@ -51216,10 +51216,10 @@
         <v>1976</v>
       </c>
       <c r="I529" s="2" t="n">
-        <v>11856</v>
+        <v>13832</v>
       </c>
       <c r="J529" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>1976</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>11856</v>
+        <v>13832</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51408,10 +51408,10 @@
         <v>1972</v>
       </c>
       <c r="I531" s="2" t="n">
-        <v>24278</v>
+        <v>25695</v>
       </c>
       <c r="J531" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
         <is>
@@ -51504,10 +51504,10 @@
         <v>1972</v>
       </c>
       <c r="I532" s="2" t="n">
-        <v>11832</v>
+        <v>13804</v>
       </c>
       <c r="J532" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
         <is>
@@ -51792,10 +51792,10 @@
         <v>1953</v>
       </c>
       <c r="I535" s="2" t="n">
-        <v>11718</v>
+        <v>13671</v>
       </c>
       <c r="J535" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
         <is>
@@ -51984,10 +51984,10 @@
         <v>1952</v>
       </c>
       <c r="I537" s="2" t="n">
-        <v>11712</v>
+        <v>13664</v>
       </c>
       <c r="J537" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>1940</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>26950</v>
+        <v>28855</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>1928</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>11568</v>
+        <v>13496</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>1927</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>11562</v>
+        <v>13489</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52464,10 +52464,10 @@
         <v>1926</v>
       </c>
       <c r="I542" s="2" t="n">
-        <v>11556</v>
+        <v>13482</v>
       </c>
       <c r="J542" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
         <is>
@@ -52560,10 +52560,10 @@
         <v>1916</v>
       </c>
       <c r="I543" s="2" t="n">
-        <v>11496</v>
+        <v>13412</v>
       </c>
       <c r="J543" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>1916</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>11496</v>
+        <v>13412</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52752,10 +52752,10 @@
         <v>1904</v>
       </c>
       <c r="I545" s="2" t="n">
-        <v>11424</v>
+        <v>13328</v>
       </c>
       <c r="J545" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>1899</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>11394</v>
+        <v>13293</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>1887</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>22644</v>
+        <v>23902</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>1881</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>28215</v>
+        <v>30096</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>1881</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>11286</v>
+        <v>13167</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>1881</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>11286</v>
+        <v>13167</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>1881</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>11286</v>
+        <v>13167</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53712,10 +53712,10 @@
         <v>1881</v>
       </c>
       <c r="I555" s="2" t="n">
-        <v>11286</v>
+        <v>13167</v>
       </c>
       <c r="J555" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>1878</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>21066</v>
+        <v>22073</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>1854</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>12783</v>
+        <v>14637</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>1854</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>11124</v>
+        <v>12978</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>1799</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>10794</v>
+        <v>12593</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54480,10 +54480,10 @@
         <v>1799</v>
       </c>
       <c r="I563" s="2" t="n">
-        <v>10794</v>
+        <v>12593</v>
       </c>
       <c r="J563" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K563" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>1757</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>10542</v>
+        <v>12299</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -54864,10 +54864,10 @@
         <v>1757</v>
       </c>
       <c r="I567" s="2" t="n">
-        <v>10542</v>
+        <v>12299</v>
       </c>
       <c r="J567" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K567" s="2" t="inlineStr">
         <is>
@@ -55056,10 +55056,10 @@
         <v>1744</v>
       </c>
       <c r="I569" s="2" t="n">
-        <v>10464</v>
+        <v>12208</v>
       </c>
       <c r="J569" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K569" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>1739</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>10434</v>
+        <v>12173</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>1715</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>10290</v>
+        <v>12005</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55440,10 +55440,10 @@
         <v>1714</v>
       </c>
       <c r="I573" s="2" t="n">
-        <v>23050</v>
+        <v>24574</v>
       </c>
       <c r="J573" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K573" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>1714</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>23422</v>
+        <v>25136</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55728,10 +55728,10 @@
         <v>1669</v>
       </c>
       <c r="I576" s="2" t="n">
-        <v>10014</v>
+        <v>11683</v>
       </c>
       <c r="J576" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K576" s="2" t="inlineStr">
         <is>
@@ -56400,10 +56400,10 @@
         <v>1572</v>
       </c>
       <c r="I583" s="2" t="n">
-        <v>9432</v>
+        <v>11004</v>
       </c>
       <c r="J583" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K583" s="2" t="inlineStr">
         <is>
@@ -56592,10 +56592,10 @@
         <v>1536</v>
       </c>
       <c r="I585" s="2" t="n">
-        <v>10349</v>
+        <v>11885</v>
       </c>
       <c r="J585" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K585" s="2" t="inlineStr">
         <is>
@@ -56784,10 +56784,10 @@
         <v>1515</v>
       </c>
       <c r="I587" s="2" t="n">
-        <v>9090</v>
+        <v>10605</v>
       </c>
       <c r="J587" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K587" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>1465</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>8790</v>
+        <v>10255</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57168,10 +57168,10 @@
         <v>1439</v>
       </c>
       <c r="I591" s="2" t="n">
-        <v>8634</v>
+        <v>10073</v>
       </c>
       <c r="J591" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K591" s="2" t="inlineStr">
         <is>
@@ -57264,10 +57264,10 @@
         <v>1426</v>
       </c>
       <c r="I592" s="2" t="n">
-        <v>8556</v>
+        <v>9982</v>
       </c>
       <c r="J592" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K592" s="2" t="inlineStr">
         <is>
@@ -57360,10 +57360,10 @@
         <v>1411</v>
       </c>
       <c r="I593" s="2" t="n">
-        <v>21165</v>
+        <v>22576</v>
       </c>
       <c r="J593" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K593" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1411</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>19754</v>
+        <v>21165</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57552,10 +57552,10 @@
         <v>1411</v>
       </c>
       <c r="I595" s="2" t="n">
-        <v>8466</v>
+        <v>9877</v>
       </c>
       <c r="J595" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K595" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1394</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>8364</v>
+        <v>9758</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57840,10 +57840,10 @@
         <v>1349</v>
       </c>
       <c r="I598" s="2" t="n">
-        <v>8094</v>
+        <v>9443</v>
       </c>
       <c r="J598" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1347</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>8082</v>
+        <v>9429</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58032,10 +58032,10 @@
         <v>1316</v>
       </c>
       <c r="I600" s="2" t="n">
-        <v>19740</v>
+        <v>21056</v>
       </c>
       <c r="J600" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
@@ -58128,10 +58128,10 @@
         <v>1260</v>
       </c>
       <c r="I601" s="2" t="n">
-        <v>7560</v>
+        <v>8820</v>
       </c>
       <c r="J601" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K601" s="2" t="inlineStr">
         <is>
@@ -58224,10 +58224,10 @@
         <v>1259</v>
       </c>
       <c r="I602" s="2" t="n">
-        <v>8813</v>
+        <v>10072</v>
       </c>
       <c r="J602" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K602" s="2" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>1251</v>
       </c>
       <c r="I603" s="2" t="n">
-        <v>7506</v>
+        <v>8757</v>
       </c>
       <c r="J603" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K603" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1239</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>7434</v>
+        <v>8673</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58992,10 +58992,10 @@
         <v>1091</v>
       </c>
       <c r="I610" s="2" t="n">
-        <v>6546</v>
+        <v>7637</v>
       </c>
       <c r="J610" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
@@ -59184,10 +59184,10 @@
         <v>1080</v>
       </c>
       <c r="I612" s="2" t="n">
-        <v>7560</v>
+        <v>8640</v>
       </c>
       <c r="J612" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K612" s="2" t="inlineStr">
         <is>
@@ -59280,10 +59280,10 @@
         <v>1080</v>
       </c>
       <c r="I613" s="2" t="n">
-        <v>6480</v>
+        <v>7560</v>
       </c>
       <c r="J613" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K613" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1078</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>6468</v>
+        <v>7546</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59568,10 +59568,10 @@
         <v>1067</v>
       </c>
       <c r="I616" s="2" t="n">
-        <v>6402</v>
+        <v>7469</v>
       </c>
       <c r="J616" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K616" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1031</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>14434</v>
+        <v>15465</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8869244</v>
+        <v>9156094</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1117288</v>
+        <v>1156481</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1255401</v>
+        <v>1329028</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>162819</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2577278</v>
+        <v>2740097</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>158965</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>886455</v>
+        <v>898030</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>151478</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1836693</v>
+        <v>1959535</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1385182</v>
+        <v>1412851</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1612736</v>
+        <v>1710510</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>127846</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1298844</v>
+        <v>1426690</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>114194</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>727981</v>
+        <v>735552</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>99486</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1502518</v>
+        <v>1540911</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>88046</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>819888</v>
+        <v>900158</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>87906</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1153194</v>
+        <v>1241100</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>85649</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>288579</v>
+        <v>374228</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>84208</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1356611</v>
+        <v>1435717</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>80760</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>726580</v>
+        <v>732880</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>79502</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>617669</v>
+        <v>648247</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>76419</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>889118</v>
+        <v>913127</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>75133</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>379646</v>
+        <v>454779</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>69504</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>595870</v>
+        <v>622072</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>69234</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>927173</v>
+        <v>980782</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>68460</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>303185</v>
+        <v>329826</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>68202</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>305249</v>
+        <v>373451</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>66703</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>394305</v>
+        <v>461008</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>65193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>698457</v>
+        <v>712441</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>65111</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>757214</v>
+        <v>762037</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>59566</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>652006</v>
+        <v>657409</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>58582</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>648069</v>
+        <v>706651</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>58176</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>362434</v>
+        <v>420610</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>57608</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>115216</v>
+        <v>172824</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>57276</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>309948</v>
+        <v>367224</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>55945</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>525983</v>
+        <v>581928</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>55901</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>111802</v>
+        <v>167703</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>54993</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>569783</v>
+        <v>624776</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>54825</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>565398</v>
+        <v>573972</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>53890</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>912226</v>
+        <v>926922</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>53653</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>780082</v>
+        <v>789722</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>50870</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>356515</v>
+        <v>368091</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>49470</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>452063</v>
+        <v>501533</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>48785</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>753041</v>
+        <v>801826</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>48086</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>670369</v>
+        <v>680009</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>47876</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>588337</v>
+        <v>609647</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>46941</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>387289</v>
+        <v>434230</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>43995</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>546644</v>
+        <v>573485</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>43416</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>126222</v>
+        <v>130538</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>43047</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>459191</v>
+        <v>498438</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>42572</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>418949</v>
+        <v>461521</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>41300</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>141643</v>
+        <v>144589</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>41270</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>156099</v>
+        <v>162378</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>40719</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>577882</v>
+        <v>586138</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>39334</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>429100</v>
+        <v>446979</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>39288</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>484371</v>
+        <v>523659</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>39193</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>137163</v>
+        <v>150878</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>38511</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>90190</v>
+        <v>128701</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>38479</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>584864</v>
+        <v>594612</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>37909</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>557847</v>
+        <v>595756</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>37246</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>193021</v>
+        <v>230267</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>36417</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>307608</v>
+        <v>324828</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>35835</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>384811</v>
+        <v>416257</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>34868</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>422345</v>
+        <v>446900</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>34616</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>64767</v>
+        <v>68625</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>34370</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>439880</v>
+        <v>474250</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>34334</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>329562</v>
+        <v>347329</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>34280</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>214921</v>
+        <v>224713</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>33783</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>459814</v>
+        <v>493597</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>33544</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>497193</v>
+        <v>520052</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>33294</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>186378</v>
+        <v>219672</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>33238</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>124071</v>
+        <v>157309</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>33063</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>410490</v>
+        <v>437891</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>32476</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>166857</v>
+        <v>199333</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>32351</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>197477</v>
+        <v>229828</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>31814</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>382196</v>
+        <v>387534</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>31199</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>258253</v>
+        <v>289452</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>30716</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>254637</v>
+        <v>285353</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>30200</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>60400</v>
+        <v>90600</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>29593</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>316510</v>
+        <v>346103</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>29540</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>59080</v>
+        <v>88620</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>29237</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>355149</v>
+        <v>374798</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>29222</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>243949</v>
+        <v>273171</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>29115</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>60169</v>
+        <v>89284</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>28689</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>249140</v>
+        <v>268305</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>28319</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>290213</v>
+        <v>304615</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>28316</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>196977</v>
+        <v>221387</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>28151</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>100387</v>
+        <v>128538</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>27693</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>373566</v>
+        <v>401259</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>27646</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>233058</v>
+        <v>260704</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>27571</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>181989</v>
+        <v>193093</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>27501</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>193491</v>
+        <v>216082</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>27294</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>230302</v>
+        <v>245920</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>27234</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>240271</v>
+        <v>267505</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>27058</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>177798</v>
+        <v>186261</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>27042</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>183439</v>
+        <v>210481</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>26996</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>155171</v>
+        <v>182167</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         <v>26814</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>336996</v>
+        <v>360365</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>26286</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>139076</v>
+        <v>142139</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>26168</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>360637</v>
+        <v>366458</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>26042</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>76198</v>
+        <v>94524</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>25641</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>140004</v>
+        <v>145901</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>25401</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>264728</v>
+        <v>266327</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>25120</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>296879</v>
+        <v>309032</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>24466</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>229060</v>
+        <v>233953</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>24373</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>201110</v>
+        <v>207984</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>24370</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>316525</v>
+        <v>324140</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>23733</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>47466</v>
+        <v>71199</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>23238</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>184485</v>
+        <v>207250</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>23055</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>174088</v>
+        <v>197143</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>22178</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>153006</v>
+        <v>175184</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>22114</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>148376</v>
+        <v>170490</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>21772</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>325944</v>
+        <v>346282</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>21731</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>225776</v>
+        <v>240889</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>21717</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>153347</v>
+        <v>156509</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>21396</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>218506</v>
+        <v>223444</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>21393</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>220552</v>
+        <v>223863</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>21350</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>146979</v>
+        <v>168329</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>21292</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>242096</v>
+        <v>256488</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>21056</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>161914</v>
+        <v>182970</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>20991</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>151302</v>
+        <v>172293</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>20958</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>222334</v>
+        <v>227475</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>20138</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>128679</v>
+        <v>136001</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>19754</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>217584</v>
+        <v>228872</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>19716</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>39432</v>
+        <v>59148</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>19651</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>148956</v>
+        <v>163498</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>19502</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>184062</v>
+        <v>193742</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>19350</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>131612</v>
+        <v>150962</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>19350</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>101700</v>
+        <v>121050</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>19271</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>150341</v>
+        <v>158054</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>19174</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>230088</v>
+        <v>249262</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>19172</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>115032</v>
+        <v>124618</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>19075</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>192902</v>
+        <v>196051</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>18517</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>170151</v>
+        <v>177484</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>18466</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>248544</v>
+        <v>254671</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>18435</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>164808</v>
+        <v>183243</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>18215</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>211869</v>
+        <v>217621</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>17796</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>179660</v>
+        <v>187759</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>17677</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>140248</v>
+        <v>157925</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>17393</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>61341</v>
+        <v>63280</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>17364</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>59136</v>
+        <v>76500</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>17025</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>196552</v>
+        <v>213577</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>16937</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>33874</v>
+        <v>50811</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>16849</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>218391</v>
+        <v>231247</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>16821</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>92499</v>
+        <v>109320</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>16587</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>148764</v>
+        <v>161385</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>16561</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>219881</v>
+        <v>225068</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>16561</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>108320</v>
+        <v>113201</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>16531</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>53329</v>
+        <v>56275</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>16494</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>114213</v>
+        <v>118446</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>16436</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>91572</v>
+        <v>96268</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>16245</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>71016</v>
+        <v>78468</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>16197</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>176369</v>
+        <v>192566</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>16166</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>181610</v>
+        <v>188244</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>16043</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>120331</v>
+        <v>125242</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>16013</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>91196</v>
+        <v>95785</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>15807</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>212923</v>
+        <v>228494</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>15527</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>220201</v>
+        <v>224906</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>15275</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>54660</v>
+        <v>69935</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>15075</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>93926</v>
+        <v>102225</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>14989</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>29978</v>
+        <v>44967</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>14953</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>124503</v>
+        <v>132213</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>14915</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>166030</v>
+        <v>168331</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>14855</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>44955</v>
+        <v>59810</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>14584</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>29168</v>
+        <v>43752</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>14436</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>125532</v>
+        <v>139968</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>14381</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>83687</v>
+        <v>98068</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>14313</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>168023</v>
+        <v>173816</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>14157</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>28314</v>
+        <v>42471</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>14153</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>138136</v>
+        <v>147895</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20784,10 +20784,10 @@
         <v>14149</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>191957</v>
+        <v>197744</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>14097</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>739070</v>
+        <v>751247</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>14042</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>98009</v>
+        <v>112051</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>14018</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>194661</v>
+        <v>204007</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>13943</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>236532</v>
+        <v>241454</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>13860</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>55428</v>
+        <v>58940</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>13832</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>60256</v>
+        <v>74088</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>13814</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>27628</v>
+        <v>41442</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>13641</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>76672</v>
+        <v>90313</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>13563</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>108755</v>
+        <v>119460</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>13541</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>162259</v>
+        <v>175800</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>13499</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>26998</v>
+        <v>40497</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>13260</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>97170</v>
+        <v>110430</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>13233</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>127433</v>
+        <v>136255</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>13172</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>172174</v>
+        <v>185346</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>13071</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>149942</v>
+        <v>159558</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>12877</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>120521</v>
+        <v>126949</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>12786</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>130789</v>
+        <v>140381</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>12715</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>73111</v>
+        <v>77879</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>12689</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>107370</v>
+        <v>113224</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>12675</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>99749</v>
+        <v>106804</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>12443</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>41766</v>
+        <v>54209</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>12382</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>29717</v>
+        <v>42099</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>12340</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>86380</v>
+        <v>98720</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>12303</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>169259</v>
+        <v>172826</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>12156</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>36556</v>
+        <v>38996</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>12088</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>137372</v>
+        <v>145618</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>11974</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>184988</v>
+        <v>190378</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>11681</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>81947</v>
+        <v>93628</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>11358</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>37434</v>
+        <v>44793</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>11226</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>79822</v>
+        <v>91048</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>10989</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>99587</v>
+        <v>105370</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>10853</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>55499</v>
+        <v>66352</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>10802</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>39280</v>
+        <v>50082</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>10675</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>21350</v>
+        <v>32025</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>10325</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>32828</v>
+        <v>43153</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>10316</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>91658</v>
+        <v>94319</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>10306</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>47547</v>
+        <v>52160</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>10268</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>79889</v>
+        <v>90157</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>10190</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>76182</v>
+        <v>82490</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>10117</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>28110</v>
+        <v>38227</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>10069</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>20138</v>
+        <v>30207</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>9898</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>135379</v>
+        <v>140426</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>9898</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>24294</v>
+        <v>31492</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>9878</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>72899</v>
+        <v>82777</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>9863</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>95106</v>
+        <v>104969</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>9823</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>65664</v>
+        <v>75487</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>9814</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>67419</v>
+        <v>74300</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>9813</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>19626</v>
+        <v>29439</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>9795</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>50448</v>
+        <v>60243</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>9712</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>118081</v>
+        <v>122923</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>9631</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>33722</v>
+        <v>43353</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>9616</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>101089</v>
+        <v>107755</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>9587</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>97523</v>
+        <v>102182</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>9587</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>19174</v>
+        <v>28761</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>9470</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>129441</v>
+        <v>137552</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>9236</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>30527</v>
+        <v>39763</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>9152</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>96596</v>
+        <v>99134</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>9047</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>63211</v>
+        <v>69113</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>9028</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>29864</v>
+        <v>38892</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>8999</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>17998</v>
+        <v>26997</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>8870</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>27380</v>
+        <v>36250</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>8847</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>115279</v>
+        <v>121487</v>
       </c>
       <c r="J303" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>8819</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>113668</v>
+        <v>119057</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>8788</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>17576</v>
+        <v>26364</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>8783</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>110706</v>
+        <v>119489</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>8748</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>23703</v>
+        <v>26243</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>8726</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>140750</v>
+        <v>143187</v>
       </c>
       <c r="J309" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8679</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>104653</v>
+        <v>113332</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>8653</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>116260</v>
+        <v>118706</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>8644</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>43153</v>
+        <v>51797</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>8585</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>71715</v>
+        <v>74594</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>8572</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>114664</v>
+        <v>119891</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
         <v>8540</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>48135</v>
+        <v>56675</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>8467</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>52683</v>
+        <v>61150</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>8399</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>49056</v>
+        <v>51131</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>8199</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>122023</v>
+        <v>123952</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>8149</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>82998</v>
+        <v>91147</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>8149</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>47453</v>
+        <v>55602</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>8137</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>16274</v>
+        <v>24411</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>8132</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>61935</v>
+        <v>65057</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>7858</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>101778</v>
+        <v>109448</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>7811</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>51822</v>
+        <v>59633</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>7713</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>94006</v>
+        <v>95934</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>7560</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>15120</v>
+        <v>22680</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>7520</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>15040</v>
+        <v>22560</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>7453</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>14906</v>
+        <v>22359</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>7428</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>41526</v>
+        <v>48954</v>
       </c>
       <c r="J343" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>7420</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>79831</v>
+        <v>87251</v>
       </c>
       <c r="J344" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>7223</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>62442</v>
+        <v>69665</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>7189</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>62783</v>
+        <v>68055</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>7172</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>40610</v>
+        <v>42985</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>7148</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>32166</v>
+        <v>39314</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>7135</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>60270</v>
+        <v>67405</v>
       </c>
       <c r="J350" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>7099</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>14198</v>
+        <v>21297</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>7093</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>50828</v>
+        <v>57921</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>7074</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>76884</v>
+        <v>79827</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>6954</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>48678</v>
+        <v>55632</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>6875</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>37318</v>
+        <v>44193</v>
       </c>
       <c r="J356" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>6834</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>79488</v>
+        <v>86322</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
@@ -34896,10 +34896,10 @@
         <v>6833</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>13666</v>
+        <v>20499</v>
       </c>
       <c r="J359" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K359" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>6752</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>51124</v>
+        <v>53536</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>6704</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>19158</v>
+        <v>22033</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>6588</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>13176</v>
+        <v>19764</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>6585</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>71486</v>
+        <v>74304</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>6585</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>35746</v>
+        <v>42331</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>6578</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>46434</v>
+        <v>50302</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -35856,10 +35856,10 @@
         <v>6554</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>16410</v>
+        <v>17818</v>
       </c>
       <c r="J369" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K369" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>6469</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>67250</v>
+        <v>68787</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>6468</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>77616</v>
+        <v>84084</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>6401</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>90951</v>
+        <v>97352</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36624,10 +36624,10 @@
         <v>6365</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>22590</v>
+        <v>28955</v>
       </c>
       <c r="J377" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>6286</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>29062</v>
+        <v>35348</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>6285</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>34096</v>
+        <v>40381</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37296,10 +37296,10 @@
         <v>6117</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>69332</v>
+        <v>70498</v>
       </c>
       <c r="J384" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
@@ -37488,10 +37488,10 @@
         <v>6056</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>45260</v>
+        <v>51316</v>
       </c>
       <c r="J386" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>6047</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>33333</v>
+        <v>34882</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37680,10 +37680,10 @@
         <v>5956</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>23627</v>
+        <v>29583</v>
       </c>
       <c r="J388" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>5925</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>79575</v>
+        <v>85500</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -37968,10 +37968,10 @@
         <v>5858</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>32166</v>
+        <v>38024</v>
       </c>
       <c r="J391" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
         <is>
@@ -38256,10 +38256,10 @@
         <v>5839</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>31587</v>
+        <v>35031</v>
       </c>
       <c r="J394" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>5834</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>58340</v>
+        <v>60316</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38448,10 +38448,10 @@
         <v>5834</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>35199</v>
+        <v>41033</v>
       </c>
       <c r="J396" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>5717</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>37160</v>
+        <v>42877</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>5674</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>59456</v>
+        <v>64153</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>5645</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>25495</v>
+        <v>31140</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -38928,10 +38928,10 @@
         <v>5642</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>61197</v>
+        <v>66839</v>
       </c>
       <c r="J401" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K401" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>5597</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>68203</v>
+        <v>72908</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>5496</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>30081</v>
+        <v>35577</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>5420</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>69423</v>
+        <v>73013</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>5400</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>32752</v>
+        <v>34728</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>5397</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>56668</v>
+        <v>58017</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39984,10 +39984,10 @@
         <v>5395</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>10790</v>
+        <v>16185</v>
       </c>
       <c r="J412" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
@@ -40272,10 +40272,10 @@
         <v>5270</v>
       </c>
       <c r="I415" s="2" t="n">
-        <v>73714</v>
+        <v>78984</v>
       </c>
       <c r="J415" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K415" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>5216</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>20864</v>
+        <v>26080</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40560,10 +40560,10 @@
         <v>5216</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>10432</v>
+        <v>15648</v>
       </c>
       <c r="J418" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>5176</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>55523</v>
+        <v>56935</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>5174</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>58136</v>
+        <v>59735</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -40944,10 +40944,10 @@
         <v>5160</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>31835</v>
+        <v>33054</v>
       </c>
       <c r="J422" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K422" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>5144</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>34473</v>
+        <v>36965</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>5027</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>48495</v>
+        <v>52956</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41328,10 +41328,10 @@
         <v>5004</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>19017</v>
+        <v>24021</v>
       </c>
       <c r="J426" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K426" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>4880</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>23814</v>
+        <v>25766</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>4853</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>57750</v>
+        <v>62603</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42096,10 +42096,10 @@
         <v>4853</v>
       </c>
       <c r="I434" s="2" t="n">
-        <v>9706</v>
+        <v>14559</v>
       </c>
       <c r="J434" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K434" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>4822</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>9644</v>
+        <v>14466</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>4762</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>52481</v>
+        <v>56101</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>4749</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>52430</v>
+        <v>54900</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43440,10 +43440,10 @@
         <v>4703</v>
       </c>
       <c r="I448" s="2" t="n">
-        <v>60767</v>
+        <v>63119</v>
       </c>
       <c r="J448" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K448" s="2" t="inlineStr">
         <is>
@@ -43632,10 +43632,10 @@
         <v>4523</v>
       </c>
       <c r="I450" s="2" t="n">
-        <v>9046</v>
+        <v>13569</v>
       </c>
       <c r="J450" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K450" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>4315</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>8630</v>
+        <v>12945</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>4260</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>8520</v>
+        <v>12780</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>4044</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>20313</v>
+        <v>24357</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>3952</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>7904</v>
+        <v>11856</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>3943</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>7886</v>
+        <v>11829</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>3941</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>7882</v>
+        <v>11823</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>3937</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>7874</v>
+        <v>11811</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -44976,10 +44976,10 @@
         <v>3928</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>31424</v>
+        <v>34370</v>
       </c>
       <c r="J464" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K464" s="2" t="inlineStr">
         <is>
@@ -45072,10 +45072,10 @@
         <v>3927</v>
       </c>
       <c r="I465" s="2" t="n">
-        <v>56413</v>
+        <v>60340</v>
       </c>
       <c r="J465" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K465" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>3925</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>7850</v>
+        <v>11775</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>3880</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>44620</v>
+        <v>48500</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>3775</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>7550</v>
+        <v>11325</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46320,10 +46320,10 @@
         <v>3764</v>
       </c>
       <c r="I478" s="2" t="n">
-        <v>26352</v>
+        <v>30116</v>
       </c>
       <c r="J478" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K478" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>3762</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>36665</v>
+        <v>40427</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>3755</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>56830</v>
+        <v>60585</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46704,10 +46704,10 @@
         <v>3736</v>
       </c>
       <c r="I482" s="2" t="n">
-        <v>42101</v>
+        <v>45215</v>
       </c>
       <c r="J482" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K482" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>3630</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>44433</v>
+        <v>48063</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>3499</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>23343</v>
+        <v>26267</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>3469</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>16888</v>
+        <v>20357</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>3427</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>51405</v>
+        <v>54832</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>3355</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>6710</v>
+        <v>10065</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48720,10 +48720,10 @@
         <v>3301</v>
       </c>
       <c r="I503" s="2" t="n">
-        <v>19629</v>
+        <v>21987</v>
       </c>
       <c r="J503" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K503" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>3144</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>24584</v>
+        <v>27728</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>3010</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>43654</v>
+        <v>46664</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2947</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>5894</v>
+        <v>8841</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2947</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>5894</v>
+        <v>8841</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2911</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>30079</v>
+        <v>32019</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -49968,10 +49968,10 @@
         <v>2909</v>
       </c>
       <c r="I516" s="2" t="n">
-        <v>18952</v>
+        <v>20421</v>
       </c>
       <c r="J516" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K516" s="2" t="inlineStr">
         <is>
@@ -50160,10 +50160,10 @@
         <v>2905</v>
       </c>
       <c r="I518" s="2" t="n">
-        <v>38252</v>
+        <v>40409</v>
       </c>
       <c r="J518" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
@@ -50256,10 +50256,10 @@
         <v>2898</v>
       </c>
       <c r="I519" s="2" t="n">
-        <v>18233</v>
+        <v>21131</v>
       </c>
       <c r="J519" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K519" s="2" t="inlineStr">
         <is>
@@ -50640,10 +50640,10 @@
         <v>2878</v>
       </c>
       <c r="I523" s="2" t="n">
-        <v>12951</v>
+        <v>15829</v>
       </c>
       <c r="J523" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K523" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>2857</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>28093</v>
+        <v>29521</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>2826</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>5652</v>
+        <v>8478</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51696,10 +51696,10 @@
         <v>2822</v>
       </c>
       <c r="I534" s="2" t="n">
-        <v>27472</v>
+        <v>29920</v>
       </c>
       <c r="J534" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>2822</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>15049</v>
+        <v>17871</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52176,10 +52176,10 @@
         <v>2822</v>
       </c>
       <c r="I539" s="2" t="n">
-        <v>5644</v>
+        <v>8466</v>
       </c>
       <c r="J539" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K539" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>2821</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>45136</v>
+        <v>47957</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>2821</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>25396</v>
+        <v>28217</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>2730</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>40835</v>
+        <v>43001</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>2700</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>5400</v>
+        <v>8100</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>2699</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>5398</v>
+        <v>8097</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53136,10 +53136,10 @@
         <v>2699</v>
       </c>
       <c r="I549" s="2" t="n">
-        <v>5398</v>
+        <v>8097</v>
       </c>
       <c r="J549" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K549" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>2698</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>7195</v>
+        <v>9893</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53328,10 +53328,10 @@
         <v>2666</v>
       </c>
       <c r="I551" s="2" t="n">
-        <v>25952</v>
+        <v>27149</v>
       </c>
       <c r="J551" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K551" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>2635</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>9222</v>
+        <v>11857</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>2631</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>25463</v>
+        <v>26779</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>2541</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>18077</v>
+        <v>20147</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>2520</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>18900</v>
+        <v>20520</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>2485</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>29246</v>
+        <v>31731</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>2471</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>4942</v>
+        <v>7413</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54096,10 +54096,10 @@
         <v>2470</v>
       </c>
       <c r="I559" s="2" t="n">
-        <v>4940</v>
+        <v>7410</v>
       </c>
       <c r="J559" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K559" s="2" t="inlineStr">
         <is>
@@ -54192,10 +54192,10 @@
         <v>2456</v>
       </c>
       <c r="I560" s="2" t="n">
-        <v>19648</v>
+        <v>22104</v>
       </c>
       <c r="J560" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
@@ -54288,10 +54288,10 @@
         <v>2441</v>
       </c>
       <c r="I561" s="2" t="n">
-        <v>17087</v>
+        <v>19528</v>
       </c>
       <c r="J561" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K561" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>2441</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>14642</v>
+        <v>17083</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54672,10 +54672,10 @@
         <v>2426</v>
       </c>
       <c r="I565" s="2" t="n">
-        <v>16982</v>
+        <v>19408</v>
       </c>
       <c r="J565" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K565" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>2425</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>23987</v>
+        <v>25516</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -55152,10 +55152,10 @@
         <v>2353</v>
       </c>
       <c r="I570" s="2" t="n">
-        <v>18824</v>
+        <v>21177</v>
       </c>
       <c r="J570" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K570" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>2352</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>22578</v>
+        <v>24459</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>2352</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>5822</v>
+        <v>8174</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>2350</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>4700</v>
+        <v>7050</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55920,10 +55920,10 @@
         <v>2248</v>
       </c>
       <c r="I578" s="2" t="n">
-        <v>4496</v>
+        <v>6744</v>
       </c>
       <c r="J578" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K578" s="2" t="inlineStr">
         <is>
@@ -56208,10 +56208,10 @@
         <v>2224</v>
       </c>
       <c r="I581" s="2" t="n">
-        <v>30570</v>
+        <v>32295</v>
       </c>
       <c r="J581" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K581" s="2" t="inlineStr">
         <is>
@@ -56304,10 +56304,10 @@
         <v>2156</v>
       </c>
       <c r="I582" s="2" t="n">
-        <v>21560</v>
+        <v>23716</v>
       </c>
       <c r="J582" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K582" s="2" t="inlineStr">
         <is>
@@ -56496,10 +56496,10 @@
         <v>2128</v>
       </c>
       <c r="I584" s="2" t="n">
-        <v>4256</v>
+        <v>6384</v>
       </c>
       <c r="J584" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
@@ -56880,10 +56880,10 @@
         <v>2057</v>
       </c>
       <c r="I588" s="2" t="n">
-        <v>4114</v>
+        <v>6171</v>
       </c>
       <c r="J588" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>2025</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>29731</v>
+        <v>30888</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1976</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>12844</v>
+        <v>14326</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57648,10 +57648,10 @@
         <v>1976</v>
       </c>
       <c r="I596" s="2" t="n">
-        <v>3952</v>
+        <v>5928</v>
       </c>
       <c r="J596" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1976</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>3952</v>
+        <v>5928</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1971</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>13522</v>
+        <v>15493</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1929</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>3858</v>
+        <v>5787</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58896,10 +58896,10 @@
         <v>1916</v>
       </c>
       <c r="I609" s="2" t="n">
-        <v>3832</v>
+        <v>5748</v>
       </c>
       <c r="J609" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K609" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1881</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>30096</v>
+        <v>31977</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1881</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>13167</v>
+        <v>15048</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>
@@ -59856,10 +59856,10 @@
         <v>1881</v>
       </c>
       <c r="I619" s="2" t="n">
-        <v>13167</v>
+        <v>15048</v>
       </c>
       <c r="J619" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K619" s="2" t="inlineStr">
         <is>
@@ -60528,10 +60528,10 @@
         <v>1799</v>
       </c>
       <c r="I626" s="2" t="n">
-        <v>12053</v>
+        <v>13582</v>
       </c>
       <c r="J626" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K626" s="2" t="inlineStr">
         <is>
@@ -60624,10 +60624,10 @@
         <v>1799</v>
       </c>
       <c r="I627" s="2" t="n">
-        <v>3598</v>
+        <v>5397</v>
       </c>
       <c r="J627" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K627" s="2" t="inlineStr">
         <is>
@@ -60912,10 +60912,10 @@
         <v>1757</v>
       </c>
       <c r="I630" s="2" t="n">
-        <v>12299</v>
+        <v>14056</v>
       </c>
       <c r="J630" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K630" s="2" t="inlineStr">
         <is>
@@ -61584,10 +61584,10 @@
         <v>1714</v>
       </c>
       <c r="I637" s="2" t="n">
-        <v>25136</v>
+        <v>26850</v>
       </c>
       <c r="J637" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K637" s="2" t="inlineStr">
         <is>
@@ -61680,10 +61680,10 @@
         <v>1711</v>
       </c>
       <c r="I638" s="2" t="n">
-        <v>3422</v>
+        <v>5133</v>
       </c>
       <c r="J638" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K638" s="2" t="inlineStr">
         <is>
@@ -62352,10 +62352,10 @@
         <v>1599</v>
       </c>
       <c r="I645" s="2" t="n">
-        <v>3198</v>
+        <v>4797</v>
       </c>
       <c r="J645" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K645" s="2" t="inlineStr">
         <is>
@@ -62928,10 +62928,10 @@
         <v>1528</v>
       </c>
       <c r="I651" s="2" t="n">
-        <v>8511</v>
+        <v>10039</v>
       </c>
       <c r="J651" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K651" s="2" t="inlineStr">
         <is>
@@ -63216,10 +63216,10 @@
         <v>1465</v>
       </c>
       <c r="I654" s="2" t="n">
-        <v>10255</v>
+        <v>11720</v>
       </c>
       <c r="J654" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K654" s="2" t="inlineStr">
         <is>
@@ -63312,10 +63312,10 @@
         <v>1464</v>
       </c>
       <c r="I655" s="2" t="n">
-        <v>2928</v>
+        <v>4392</v>
       </c>
       <c r="J655" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K655" s="2" t="inlineStr">
         <is>
@@ -63408,10 +63408,10 @@
         <v>1426</v>
       </c>
       <c r="I656" s="2" t="n">
-        <v>9982</v>
+        <v>11408</v>
       </c>
       <c r="J656" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K656" s="2" t="inlineStr">
         <is>
@@ -63792,10 +63792,10 @@
         <v>1395</v>
       </c>
       <c r="I660" s="2" t="n">
-        <v>3915</v>
+        <v>5310</v>
       </c>
       <c r="J660" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K660" s="2" t="inlineStr">
         <is>
@@ -63984,10 +63984,10 @@
         <v>1367</v>
       </c>
       <c r="I662" s="2" t="n">
-        <v>16137</v>
+        <v>17504</v>
       </c>
       <c r="J662" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K662" s="2" t="inlineStr">
         <is>
@@ -64176,10 +64176,10 @@
         <v>1347</v>
       </c>
       <c r="I664" s="2" t="n">
-        <v>8791</v>
+        <v>9819</v>
       </c>
       <c r="J664" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K664" s="2" t="inlineStr">
         <is>
@@ -64368,10 +64368,10 @@
         <v>1310</v>
       </c>
       <c r="I666" s="2" t="n">
-        <v>2620</v>
+        <v>3930</v>
       </c>
       <c r="J666" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K666" s="2" t="inlineStr">
         <is>
@@ -64464,10 +64464,10 @@
         <v>1261</v>
       </c>
       <c r="I667" s="2" t="n">
-        <v>2522</v>
+        <v>3783</v>
       </c>
       <c r="J667" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K667" s="2" t="inlineStr">
         <is>
@@ -64560,10 +64560,10 @@
         <v>1260</v>
       </c>
       <c r="I668" s="2" t="n">
-        <v>8460</v>
+        <v>9540</v>
       </c>
       <c r="J668" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K668" s="2" t="inlineStr">
         <is>
@@ -64656,10 +64656,10 @@
         <v>1260</v>
       </c>
       <c r="I669" s="2" t="n">
-        <v>2520</v>
+        <v>3780</v>
       </c>
       <c r="J669" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K669" s="2" t="inlineStr">
         <is>
@@ -64848,10 +64848,10 @@
         <v>1259</v>
       </c>
       <c r="I671" s="2" t="n">
-        <v>2518</v>
+        <v>3777</v>
       </c>
       <c r="J671" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K671" s="2" t="inlineStr">
         <is>
@@ -65232,10 +65232,10 @@
         <v>1222</v>
       </c>
       <c r="I675" s="2" t="n">
-        <v>12220</v>
+        <v>13442</v>
       </c>
       <c r="J675" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K675" s="2" t="inlineStr">
         <is>
@@ -65424,10 +65424,10 @@
         <v>1220</v>
       </c>
       <c r="I677" s="2" t="n">
-        <v>2440</v>
+        <v>3660</v>
       </c>
       <c r="J677" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K677" s="2" t="inlineStr">
         <is>
@@ -65520,10 +65520,10 @@
         <v>1156</v>
       </c>
       <c r="I678" s="2" t="n">
-        <v>2312</v>
+        <v>3468</v>
       </c>
       <c r="J678" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K678" s="2" t="inlineStr">
         <is>
@@ -65616,10 +65616,10 @@
         <v>1110</v>
       </c>
       <c r="I679" s="2" t="n">
-        <v>2220</v>
+        <v>3330</v>
       </c>
       <c r="J679" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K679" s="2" t="inlineStr">
         <is>
@@ -65712,10 +65712,10 @@
         <v>1080</v>
       </c>
       <c r="I680" s="2" t="n">
-        <v>3240</v>
+        <v>4320</v>
       </c>
       <c r="J680" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K680" s="2" t="inlineStr">
         <is>
@@ -66288,10 +66288,10 @@
         <v>1017</v>
       </c>
       <c r="I686" s="2" t="n">
-        <v>2034</v>
+        <v>3051</v>
       </c>
       <c r="J686" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K686" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9156094</v>
+        <v>9442944</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1156481</v>
+        <v>1195674</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1329028</v>
+        <v>1402655</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>162819</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2740097</v>
+        <v>2902916</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>158965</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>898030</v>
+        <v>909605</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>151478</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1959535</v>
+        <v>2082377</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1412851</v>
+        <v>1440520</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1710510</v>
+        <v>1808284</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>127846</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1426690</v>
+        <v>1554536</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>114194</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>735552</v>
+        <v>743123</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>99486</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1540911</v>
+        <v>1579304</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>88046</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>900158</v>
+        <v>980428</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>87906</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1241100</v>
+        <v>1329006</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>85649</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>374228</v>
+        <v>459877</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>84208</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1435717</v>
+        <v>1514823</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>80760</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>732880</v>
+        <v>739180</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>79502</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>648247</v>
+        <v>678825</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>76419</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>913127</v>
+        <v>937136</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>75133</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>454779</v>
+        <v>529912</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>69504</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>622072</v>
+        <v>648274</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>69234</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>980782</v>
+        <v>1034391</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>68460</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>329826</v>
+        <v>356467</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>68202</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>373451</v>
+        <v>441653</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>66703</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>461008</v>
+        <v>527711</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>65193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>712441</v>
+        <v>726425</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>65111</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>762037</v>
+        <v>766860</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>59566</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>657409</v>
+        <v>662812</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>58582</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>706651</v>
+        <v>765233</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>58176</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>420610</v>
+        <v>478786</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>57608</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>172824</v>
+        <v>230432</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>57276</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>367224</v>
+        <v>424500</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>55945</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>581928</v>
+        <v>637873</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>55901</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>167703</v>
+        <v>223604</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>54993</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>624776</v>
+        <v>679769</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>54825</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>573972</v>
+        <v>582546</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>53890</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>926922</v>
+        <v>941618</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>53653</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>789722</v>
+        <v>799362</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>50870</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>368091</v>
+        <v>379667</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>49470</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>501533</v>
+        <v>551003</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>48785</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>801826</v>
+        <v>850611</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>48086</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>680009</v>
+        <v>689649</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>47876</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>609647</v>
+        <v>630957</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>46941</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>434230</v>
+        <v>481171</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>43995</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>573485</v>
+        <v>600326</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>43416</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>130538</v>
+        <v>134854</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>43047</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>498438</v>
+        <v>537685</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>42572</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>461521</v>
+        <v>504093</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>41300</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>144589</v>
+        <v>147535</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>41270</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>162378</v>
+        <v>168657</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>40719</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>586138</v>
+        <v>594394</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>39334</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>446979</v>
+        <v>464858</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>39288</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>523659</v>
+        <v>562947</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>39193</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>150878</v>
+        <v>164593</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>38511</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>128701</v>
+        <v>167212</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>38479</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>594612</v>
+        <v>604360</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>37909</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>595756</v>
+        <v>633665</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>37246</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>230267</v>
+        <v>267513</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>36417</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>324828</v>
+        <v>342048</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>35835</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>416257</v>
+        <v>447703</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>34868</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>446900</v>
+        <v>471455</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>34616</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>68625</v>
+        <v>72483</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>34370</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>474250</v>
+        <v>508620</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>34334</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>347329</v>
+        <v>365096</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>34280</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>224713</v>
+        <v>234505</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>33783</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>493597</v>
+        <v>527380</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>33544</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>520052</v>
+        <v>542911</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>33294</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>219672</v>
+        <v>252966</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>33238</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>157309</v>
+        <v>190547</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>33063</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>437891</v>
+        <v>465292</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>32476</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>199333</v>
+        <v>231809</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>32351</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>229828</v>
+        <v>262179</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>31814</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>387534</v>
+        <v>392872</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>31199</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>289452</v>
+        <v>320651</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>30716</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>285353</v>
+        <v>316069</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>30200</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>90600</v>
+        <v>120800</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>29593</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>346103</v>
+        <v>375696</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>29540</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>88620</v>
+        <v>118160</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>29237</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>374798</v>
+        <v>394447</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>29222</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>273171</v>
+        <v>302393</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>29115</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>89284</v>
+        <v>118399</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>28689</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>268305</v>
+        <v>287470</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>28319</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>304615</v>
+        <v>319017</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>28316</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>221387</v>
+        <v>245797</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>28151</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>128538</v>
+        <v>156689</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>27693</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>401259</v>
+        <v>428952</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>27646</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>260704</v>
+        <v>288350</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>27571</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>193093</v>
+        <v>204197</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>27501</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>216082</v>
+        <v>238673</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>27294</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>245920</v>
+        <v>261538</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>27234</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>267505</v>
+        <v>294739</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>27058</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>186261</v>
+        <v>194724</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>27042</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>210481</v>
+        <v>237523</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>26996</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>182167</v>
+        <v>209163</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         <v>26814</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>360365</v>
+        <v>383734</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>26286</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>142139</v>
+        <v>145202</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>26168</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>366458</v>
+        <v>372279</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>26042</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>94524</v>
+        <v>112850</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>25641</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>145901</v>
+        <v>151798</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>25401</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>266327</v>
+        <v>267926</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>25120</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>309032</v>
+        <v>321185</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>24466</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>233953</v>
+        <v>238846</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>24373</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>207984</v>
+        <v>214858</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>24370</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>324140</v>
+        <v>331755</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>23733</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>71199</v>
+        <v>94932</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>23238</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>207250</v>
+        <v>230015</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>23055</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>197143</v>
+        <v>220198</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>22178</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>175184</v>
+        <v>197362</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>22114</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>170490</v>
+        <v>192604</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>21772</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>346282</v>
+        <v>366620</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>21731</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>240889</v>
+        <v>256002</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>21717</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>156509</v>
+        <v>159671</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>21396</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>223444</v>
+        <v>228382</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>21393</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>223863</v>
+        <v>227174</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>21350</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>168329</v>
+        <v>189679</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>21292</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>256488</v>
+        <v>270880</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>21056</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>182970</v>
+        <v>204026</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>20991</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>172293</v>
+        <v>193284</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>20958</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>227475</v>
+        <v>232616</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>20138</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>136001</v>
+        <v>143323</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>19754</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>228872</v>
+        <v>240160</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>19716</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>59148</v>
+        <v>78864</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>19651</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>163498</v>
+        <v>178040</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>19502</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>193742</v>
+        <v>203422</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>19350</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>150962</v>
+        <v>170312</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>19350</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>121050</v>
+        <v>140400</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>19271</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>158054</v>
+        <v>165767</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>19174</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>249262</v>
+        <v>268436</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>19172</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>124618</v>
+        <v>134204</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>19075</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>196051</v>
+        <v>199200</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>18517</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>177484</v>
+        <v>184817</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>18466</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>254671</v>
+        <v>260798</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>18435</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>183243</v>
+        <v>201678</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>18215</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>217621</v>
+        <v>223373</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>17796</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>187759</v>
+        <v>195858</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>17677</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>157925</v>
+        <v>175602</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>17393</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>63280</v>
+        <v>65219</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>17364</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>76500</v>
+        <v>93864</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>17025</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>213577</v>
+        <v>230602</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>16937</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>50811</v>
+        <v>67748</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>16849</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>231247</v>
+        <v>244103</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>16821</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>109320</v>
+        <v>126141</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>16587</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>161385</v>
+        <v>174006</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>16561</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>225068</v>
+        <v>230255</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>16561</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>113201</v>
+        <v>118082</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>16531</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>56275</v>
+        <v>59221</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>16494</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>118446</v>
+        <v>122679</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>16436</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>96268</v>
+        <v>100964</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>16245</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>78468</v>
+        <v>85920</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>16197</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>192566</v>
+        <v>208763</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>16166</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>188244</v>
+        <v>194878</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>16043</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>125242</v>
+        <v>130153</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>16013</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>95785</v>
+        <v>100374</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>15807</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>228494</v>
+        <v>244065</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>15527</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>224906</v>
+        <v>229611</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>15275</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>69935</v>
+        <v>85210</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>15075</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>102225</v>
+        <v>110524</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>14989</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>44967</v>
+        <v>59956</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>14953</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>132213</v>
+        <v>139923</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>14915</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>168331</v>
+        <v>170632</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>14855</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>59810</v>
+        <v>74665</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>14584</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>43752</v>
+        <v>58336</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>14436</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>139968</v>
+        <v>154404</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>14381</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>98068</v>
+        <v>112449</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>14313</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>173816</v>
+        <v>179609</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>14157</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>42471</v>
+        <v>56628</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>14153</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>147895</v>
+        <v>157654</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20784,10 +20784,10 @@
         <v>14149</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>197744</v>
+        <v>203531</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>14097</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>751247</v>
+        <v>763424</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>14042</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>112051</v>
+        <v>126093</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>14018</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>204007</v>
+        <v>213353</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>13943</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>241454</v>
+        <v>246376</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>13860</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>58940</v>
+        <v>62452</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>13832</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>74088</v>
+        <v>87920</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>13814</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>41442</v>
+        <v>55256</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>13641</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>90313</v>
+        <v>103954</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>13563</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>119460</v>
+        <v>130165</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>13541</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>175800</v>
+        <v>189341</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>13499</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>40497</v>
+        <v>53996</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>13260</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>110430</v>
+        <v>123690</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>13233</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>136255</v>
+        <v>145077</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>13172</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>185346</v>
+        <v>198518</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>13071</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>159558</v>
+        <v>169174</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>12877</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>126949</v>
+        <v>133377</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>12786</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>140381</v>
+        <v>149973</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>12715</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>77879</v>
+        <v>82647</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>12689</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>113224</v>
+        <v>119078</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>12675</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>106804</v>
+        <v>113859</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>12443</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>54209</v>
+        <v>66652</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>12382</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>42099</v>
+        <v>54481</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>12340</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>98720</v>
+        <v>111060</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>12303</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>172826</v>
+        <v>176393</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>12156</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>38996</v>
+        <v>41436</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>12088</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>145618</v>
+        <v>153864</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>11974</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>190378</v>
+        <v>195768</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>11681</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>93628</v>
+        <v>105309</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>11358</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>44793</v>
+        <v>52152</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>11226</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>91048</v>
+        <v>102274</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>10989</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>105370</v>
+        <v>111153</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>10853</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>66352</v>
+        <v>77205</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>10802</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>50082</v>
+        <v>60884</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>10675</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>32025</v>
+        <v>42700</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>10325</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>43153</v>
+        <v>53478</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>10316</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>94319</v>
+        <v>96980</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>10306</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>52160</v>
+        <v>56773</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>10268</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>90157</v>
+        <v>100425</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>10190</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>82490</v>
+        <v>88798</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>10117</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>38227</v>
+        <v>48344</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>10069</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>30207</v>
+        <v>40276</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>9898</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>140426</v>
+        <v>145473</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>9898</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>31492</v>
+        <v>38690</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>9878</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>82777</v>
+        <v>92655</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>9863</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>104969</v>
+        <v>114832</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>9823</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>75487</v>
+        <v>85310</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>9814</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>74300</v>
+        <v>81181</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>9813</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>29439</v>
+        <v>39252</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>9795</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>60243</v>
+        <v>70038</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>9712</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>122923</v>
+        <v>127765</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>9631</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>43353</v>
+        <v>52984</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>9616</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>107755</v>
+        <v>114421</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>9587</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>102182</v>
+        <v>106841</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>9587</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>28761</v>
+        <v>38348</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>9470</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>137552</v>
+        <v>145663</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>9236</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>39763</v>
+        <v>48999</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>9152</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>99134</v>
+        <v>101672</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>9047</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>69113</v>
+        <v>75015</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>9028</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>38892</v>
+        <v>47920</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>8999</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>26997</v>
+        <v>35996</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>8870</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>36250</v>
+        <v>45120</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>8847</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>121487</v>
+        <v>127695</v>
       </c>
       <c r="J303" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>8819</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>119057</v>
+        <v>124446</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>8788</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>26364</v>
+        <v>35152</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>8783</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>119489</v>
+        <v>128272</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>8748</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>26243</v>
+        <v>28783</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>8726</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>143187</v>
+        <v>145624</v>
       </c>
       <c r="J309" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8679</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>113332</v>
+        <v>122011</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>8653</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>118706</v>
+        <v>121152</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>8644</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>51797</v>
+        <v>60441</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>8585</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>74594</v>
+        <v>77473</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>8572</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>119891</v>
+        <v>125118</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
         <v>8540</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>56675</v>
+        <v>65215</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>8467</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>61150</v>
+        <v>69617</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>8399</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>51131</v>
+        <v>53206</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>8199</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>123952</v>
+        <v>125881</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>8149</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>91147</v>
+        <v>99296</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>8149</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>55602</v>
+        <v>63751</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>8137</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>24411</v>
+        <v>32548</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>8132</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>65057</v>
+        <v>68179</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>7858</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>109448</v>
+        <v>117118</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>7811</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>59633</v>
+        <v>67444</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>7713</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>95934</v>
+        <v>97862</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>7560</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>22680</v>
+        <v>30240</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>7520</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>22560</v>
+        <v>30080</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>7453</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>22359</v>
+        <v>29812</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>7428</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>48954</v>
+        <v>56382</v>
       </c>
       <c r="J343" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>7420</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>87251</v>
+        <v>94671</v>
       </c>
       <c r="J344" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>7223</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>69665</v>
+        <v>76888</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>7189</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>68055</v>
+        <v>73327</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>7172</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>42985</v>
+        <v>45360</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>7148</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>39314</v>
+        <v>46462</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>7135</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>67405</v>
+        <v>74540</v>
       </c>
       <c r="J350" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>7099</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>21297</v>
+        <v>28396</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>7093</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>57921</v>
+        <v>65014</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>7074</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>79827</v>
+        <v>82770</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>6954</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>55632</v>
+        <v>62586</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>6875</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>44193</v>
+        <v>51068</v>
       </c>
       <c r="J356" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>6834</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>86322</v>
+        <v>93156</v>
       </c>
       <c r="J358" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
         <is>
@@ -34896,10 +34896,10 @@
         <v>6833</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>20499</v>
+        <v>27332</v>
       </c>
       <c r="J359" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K359" s="2" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>6752</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>53536</v>
+        <v>55948</v>
       </c>
       <c r="J360" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>6704</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>22033</v>
+        <v>24908</v>
       </c>
       <c r="J362" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>6588</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>19764</v>
+        <v>26352</v>
       </c>
       <c r="J365" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>6585</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>74304</v>
+        <v>77122</v>
       </c>
       <c r="J366" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>6585</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>42331</v>
+        <v>48916</v>
       </c>
       <c r="J367" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>6578</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>50302</v>
+        <v>54170</v>
       </c>
       <c r="J368" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
         <is>
@@ -35856,10 +35856,10 @@
         <v>6554</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>17818</v>
+        <v>19226</v>
       </c>
       <c r="J369" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K369" s="2" t="inlineStr">
         <is>
@@ -36240,10 +36240,10 @@
         <v>6469</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>68787</v>
+        <v>70324</v>
       </c>
       <c r="J373" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
         <is>
@@ -36336,10 +36336,10 @@
         <v>6468</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>84084</v>
+        <v>90552</v>
       </c>
       <c r="J374" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>6401</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>97352</v>
+        <v>103753</v>
       </c>
       <c r="J376" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
         <is>
@@ -36624,10 +36624,10 @@
         <v>6365</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>28955</v>
+        <v>35320</v>
       </c>
       <c r="J377" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
         <is>
@@ -36816,10 +36816,10 @@
         <v>6286</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>35348</v>
+        <v>41634</v>
       </c>
       <c r="J379" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
         <is>
@@ -37008,10 +37008,10 @@
         <v>6285</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>40381</v>
+        <v>46666</v>
       </c>
       <c r="J381" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
         <is>
@@ -37296,10 +37296,10 @@
         <v>6117</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>70498</v>
+        <v>71664</v>
       </c>
       <c r="J384" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
         <is>
@@ -37488,10 +37488,10 @@
         <v>6056</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>51316</v>
+        <v>57372</v>
       </c>
       <c r="J386" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
         <is>
@@ -37584,10 +37584,10 @@
         <v>6047</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>34882</v>
+        <v>36431</v>
       </c>
       <c r="J387" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
         <is>
@@ -37680,10 +37680,10 @@
         <v>5956</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>29583</v>
+        <v>35539</v>
       </c>
       <c r="J388" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
         <is>
@@ -37872,10 +37872,10 @@
         <v>5925</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>85500</v>
+        <v>91425</v>
       </c>
       <c r="J390" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
         <is>
@@ -37968,10 +37968,10 @@
         <v>5858</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>38024</v>
+        <v>43882</v>
       </c>
       <c r="J391" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
         <is>
@@ -38256,10 +38256,10 @@
         <v>5839</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>35031</v>
+        <v>38475</v>
       </c>
       <c r="J394" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
         <is>
@@ -38352,10 +38352,10 @@
         <v>5834</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>60316</v>
+        <v>62292</v>
       </c>
       <c r="J395" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
         <is>
@@ -38448,10 +38448,10 @@
         <v>5834</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>41033</v>
+        <v>46867</v>
       </c>
       <c r="J396" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
         <is>
@@ -38640,10 +38640,10 @@
         <v>5717</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>42877</v>
+        <v>48594</v>
       </c>
       <c r="J398" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
         <is>
@@ -38736,10 +38736,10 @@
         <v>5674</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>64153</v>
+        <v>68850</v>
       </c>
       <c r="J399" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
         <is>
@@ -38832,10 +38832,10 @@
         <v>5645</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>31140</v>
+        <v>36785</v>
       </c>
       <c r="J400" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
         <is>
@@ -38928,10 +38928,10 @@
         <v>5642</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>66839</v>
+        <v>72481</v>
       </c>
       <c r="J401" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K401" s="2" t="inlineStr">
         <is>
@@ -39120,10 +39120,10 @@
         <v>5597</v>
       </c>
       <c r="I403" s="2" t="n">
-        <v>72908</v>
+        <v>77613</v>
       </c>
       <c r="J403" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
         <is>
@@ -39312,10 +39312,10 @@
         <v>5496</v>
       </c>
       <c r="I405" s="2" t="n">
-        <v>35577</v>
+        <v>41073</v>
       </c>
       <c r="J405" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
         <is>
@@ -39408,10 +39408,10 @@
         <v>5420</v>
       </c>
       <c r="I406" s="2" t="n">
-        <v>73013</v>
+        <v>76603</v>
       </c>
       <c r="J406" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
         <is>
@@ -39600,10 +39600,10 @@
         <v>5400</v>
       </c>
       <c r="I408" s="2" t="n">
-        <v>34728</v>
+        <v>36704</v>
       </c>
       <c r="J408" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         <v>5397</v>
       </c>
       <c r="I410" s="2" t="n">
-        <v>58017</v>
+        <v>59366</v>
       </c>
       <c r="J410" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
         <is>
@@ -39984,10 +39984,10 @@
         <v>5395</v>
       </c>
       <c r="I412" s="2" t="n">
-        <v>16185</v>
+        <v>21580</v>
       </c>
       <c r="J412" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
         <is>
@@ -40272,10 +40272,10 @@
         <v>5270</v>
       </c>
       <c r="I415" s="2" t="n">
-        <v>78984</v>
+        <v>84254</v>
       </c>
       <c r="J415" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K415" s="2" t="inlineStr">
         <is>
@@ -40464,10 +40464,10 @@
         <v>5216</v>
       </c>
       <c r="I417" s="2" t="n">
-        <v>26080</v>
+        <v>31296</v>
       </c>
       <c r="J417" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
         <is>
@@ -40560,10 +40560,10 @@
         <v>5216</v>
       </c>
       <c r="I418" s="2" t="n">
-        <v>15648</v>
+        <v>20864</v>
       </c>
       <c r="J418" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
         <is>
@@ -40752,10 +40752,10 @@
         <v>5176</v>
       </c>
       <c r="I420" s="2" t="n">
-        <v>56935</v>
+        <v>58347</v>
       </c>
       <c r="J420" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
         <is>
@@ -40848,10 +40848,10 @@
         <v>5174</v>
       </c>
       <c r="I421" s="2" t="n">
-        <v>59735</v>
+        <v>61334</v>
       </c>
       <c r="J421" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
         <is>
@@ -40944,10 +40944,10 @@
         <v>5160</v>
       </c>
       <c r="I422" s="2" t="n">
-        <v>33054</v>
+        <v>34273</v>
       </c>
       <c r="J422" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K422" s="2" t="inlineStr">
         <is>
@@ -41040,10 +41040,10 @@
         <v>5144</v>
       </c>
       <c r="I423" s="2" t="n">
-        <v>36965</v>
+        <v>39457</v>
       </c>
       <c r="J423" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
         <is>
@@ -41232,10 +41232,10 @@
         <v>5027</v>
       </c>
       <c r="I425" s="2" t="n">
-        <v>52956</v>
+        <v>57417</v>
       </c>
       <c r="J425" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
         <is>
@@ -41328,10 +41328,10 @@
         <v>5004</v>
       </c>
       <c r="I426" s="2" t="n">
-        <v>24021</v>
+        <v>29025</v>
       </c>
       <c r="J426" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K426" s="2" t="inlineStr">
         <is>
@@ -41712,10 +41712,10 @@
         <v>4880</v>
       </c>
       <c r="I430" s="2" t="n">
-        <v>25766</v>
+        <v>27718</v>
       </c>
       <c r="J430" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
         <is>
@@ -42000,10 +42000,10 @@
         <v>4853</v>
       </c>
       <c r="I433" s="2" t="n">
-        <v>62603</v>
+        <v>67456</v>
       </c>
       <c r="J433" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
         <is>
@@ -42096,10 +42096,10 @@
         <v>4853</v>
       </c>
       <c r="I434" s="2" t="n">
-        <v>14559</v>
+        <v>19412</v>
       </c>
       <c r="J434" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K434" s="2" t="inlineStr">
         <is>
@@ -42576,10 +42576,10 @@
         <v>4822</v>
       </c>
       <c r="I439" s="2" t="n">
-        <v>14466</v>
+        <v>19288</v>
       </c>
       <c r="J439" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
         <is>
@@ -42960,10 +42960,10 @@
         <v>4762</v>
       </c>
       <c r="I443" s="2" t="n">
-        <v>56101</v>
+        <v>59721</v>
       </c>
       <c r="J443" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
         <is>
@@ -43056,10 +43056,10 @@
         <v>4749</v>
       </c>
       <c r="I444" s="2" t="n">
-        <v>54900</v>
+        <v>57370</v>
       </c>
       <c r="J444" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
@@ -43440,10 +43440,10 @@
         <v>4703</v>
       </c>
       <c r="I448" s="2" t="n">
-        <v>63119</v>
+        <v>65471</v>
       </c>
       <c r="J448" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K448" s="2" t="inlineStr">
         <is>
@@ -43632,10 +43632,10 @@
         <v>4523</v>
       </c>
       <c r="I450" s="2" t="n">
-        <v>13569</v>
+        <v>18092</v>
       </c>
       <c r="J450" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K450" s="2" t="inlineStr">
         <is>
@@ -44016,10 +44016,10 @@
         <v>4315</v>
       </c>
       <c r="I454" s="2" t="n">
-        <v>12945</v>
+        <v>17260</v>
       </c>
       <c r="J454" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
         <is>
@@ -44208,10 +44208,10 @@
         <v>4260</v>
       </c>
       <c r="I456" s="2" t="n">
-        <v>12780</v>
+        <v>17040</v>
       </c>
       <c r="J456" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
         <is>
@@ -44304,10 +44304,10 @@
         <v>4044</v>
       </c>
       <c r="I457" s="2" t="n">
-        <v>24357</v>
+        <v>28401</v>
       </c>
       <c r="J457" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
         <is>
@@ -44496,10 +44496,10 @@
         <v>3952</v>
       </c>
       <c r="I459" s="2" t="n">
-        <v>11856</v>
+        <v>15808</v>
       </c>
       <c r="J459" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
         <is>
@@ -44592,10 +44592,10 @@
         <v>3943</v>
       </c>
       <c r="I460" s="2" t="n">
-        <v>11829</v>
+        <v>15772</v>
       </c>
       <c r="J460" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
         <is>
@@ -44784,10 +44784,10 @@
         <v>3941</v>
       </c>
       <c r="I462" s="2" t="n">
-        <v>11823</v>
+        <v>15764</v>
       </c>
       <c r="J462" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
         <is>
@@ -44880,10 +44880,10 @@
         <v>3937</v>
       </c>
       <c r="I463" s="2" t="n">
-        <v>11811</v>
+        <v>15748</v>
       </c>
       <c r="J463" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
         <is>
@@ -44976,10 +44976,10 @@
         <v>3928</v>
       </c>
       <c r="I464" s="2" t="n">
-        <v>34370</v>
+        <v>37316</v>
       </c>
       <c r="J464" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K464" s="2" t="inlineStr">
         <is>
@@ -45072,10 +45072,10 @@
         <v>3927</v>
       </c>
       <c r="I465" s="2" t="n">
-        <v>60340</v>
+        <v>64267</v>
       </c>
       <c r="J465" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K465" s="2" t="inlineStr">
         <is>
@@ -45168,10 +45168,10 @@
         <v>3925</v>
       </c>
       <c r="I466" s="2" t="n">
-        <v>11775</v>
+        <v>15700</v>
       </c>
       <c r="J466" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
         <is>
@@ -45456,10 +45456,10 @@
         <v>3880</v>
       </c>
       <c r="I469" s="2" t="n">
-        <v>48500</v>
+        <v>52380</v>
       </c>
       <c r="J469" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
         <is>
@@ -46032,10 +46032,10 @@
         <v>3775</v>
       </c>
       <c r="I475" s="2" t="n">
-        <v>11325</v>
+        <v>15100</v>
       </c>
       <c r="J475" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
         <is>
@@ -46320,10 +46320,10 @@
         <v>3764</v>
       </c>
       <c r="I478" s="2" t="n">
-        <v>30116</v>
+        <v>33880</v>
       </c>
       <c r="J478" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K478" s="2" t="inlineStr">
         <is>
@@ -46512,10 +46512,10 @@
         <v>3762</v>
       </c>
       <c r="I480" s="2" t="n">
-        <v>40427</v>
+        <v>44189</v>
       </c>
       <c r="J480" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
         <is>
@@ -46608,10 +46608,10 @@
         <v>3755</v>
       </c>
       <c r="I481" s="2" t="n">
-        <v>60585</v>
+        <v>64340</v>
       </c>
       <c r="J481" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
         <is>
@@ -46704,10 +46704,10 @@
         <v>3736</v>
       </c>
       <c r="I482" s="2" t="n">
-        <v>45215</v>
+        <v>48329</v>
       </c>
       <c r="J482" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K482" s="2" t="inlineStr">
         <is>
@@ -47088,10 +47088,10 @@
         <v>3630</v>
       </c>
       <c r="I486" s="2" t="n">
-        <v>48063</v>
+        <v>51693</v>
       </c>
       <c r="J486" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
         <is>
@@ -47376,10 +47376,10 @@
         <v>3499</v>
       </c>
       <c r="I489" s="2" t="n">
-        <v>26267</v>
+        <v>29191</v>
       </c>
       <c r="J489" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
         <is>
@@ -47472,10 +47472,10 @@
         <v>3469</v>
       </c>
       <c r="I490" s="2" t="n">
-        <v>20357</v>
+        <v>23826</v>
       </c>
       <c r="J490" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
         <is>
@@ -47568,10 +47568,10 @@
         <v>3427</v>
       </c>
       <c r="I491" s="2" t="n">
-        <v>54832</v>
+        <v>58259</v>
       </c>
       <c r="J491" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
         <is>
@@ -48240,10 +48240,10 @@
         <v>3355</v>
       </c>
       <c r="I498" s="2" t="n">
-        <v>10065</v>
+        <v>13420</v>
       </c>
       <c r="J498" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
         <is>
@@ -48720,10 +48720,10 @@
         <v>3301</v>
       </c>
       <c r="I503" s="2" t="n">
-        <v>21987</v>
+        <v>24345</v>
       </c>
       <c r="J503" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K503" s="2" t="inlineStr">
         <is>
@@ -48912,10 +48912,10 @@
         <v>3144</v>
       </c>
       <c r="I505" s="2" t="n">
-        <v>27728</v>
+        <v>30872</v>
       </c>
       <c r="J505" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
         <is>
@@ -49104,10 +49104,10 @@
         <v>3010</v>
       </c>
       <c r="I507" s="2" t="n">
-        <v>46664</v>
+        <v>49674</v>
       </c>
       <c r="J507" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         <v>2947</v>
       </c>
       <c r="I509" s="2" t="n">
-        <v>8841</v>
+        <v>11788</v>
       </c>
       <c r="J509" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
         <is>
@@ -49392,10 +49392,10 @@
         <v>2947</v>
       </c>
       <c r="I510" s="2" t="n">
-        <v>8841</v>
+        <v>11788</v>
       </c>
       <c r="J510" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
         <is>
@@ -49872,10 +49872,10 @@
         <v>2911</v>
       </c>
       <c r="I515" s="2" t="n">
-        <v>32019</v>
+        <v>33959</v>
       </c>
       <c r="J515" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
         <is>
@@ -49968,10 +49968,10 @@
         <v>2909</v>
       </c>
       <c r="I516" s="2" t="n">
-        <v>20421</v>
+        <v>21890</v>
       </c>
       <c r="J516" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K516" s="2" t="inlineStr">
         <is>
@@ -50160,10 +50160,10 @@
         <v>2905</v>
       </c>
       <c r="I518" s="2" t="n">
-        <v>40409</v>
+        <v>42566</v>
       </c>
       <c r="J518" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K518" s="2" t="inlineStr">
         <is>
@@ -50256,10 +50256,10 @@
         <v>2898</v>
       </c>
       <c r="I519" s="2" t="n">
-        <v>21131</v>
+        <v>24029</v>
       </c>
       <c r="J519" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K519" s="2" t="inlineStr">
         <is>
@@ -50640,10 +50640,10 @@
         <v>2878</v>
       </c>
       <c r="I523" s="2" t="n">
-        <v>15829</v>
+        <v>18707</v>
       </c>
       <c r="J523" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K523" s="2" t="inlineStr">
         <is>
@@ -51024,10 +51024,10 @@
         <v>2857</v>
       </c>
       <c r="I527" s="2" t="n">
-        <v>29521</v>
+        <v>30949</v>
       </c>
       <c r="J527" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         <v>2826</v>
       </c>
       <c r="I530" s="2" t="n">
-        <v>8478</v>
+        <v>11304</v>
       </c>
       <c r="J530" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
         <is>
@@ -51696,10 +51696,10 @@
         <v>2822</v>
       </c>
       <c r="I534" s="2" t="n">
-        <v>29920</v>
+        <v>32368</v>
       </c>
       <c r="J534" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K534" s="2" t="inlineStr">
         <is>
@@ -52080,10 +52080,10 @@
         <v>2822</v>
       </c>
       <c r="I538" s="2" t="n">
-        <v>17871</v>
+        <v>20693</v>
       </c>
       <c r="J538" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
         <is>
@@ -52176,10 +52176,10 @@
         <v>2822</v>
       </c>
       <c r="I539" s="2" t="n">
-        <v>8466</v>
+        <v>11288</v>
       </c>
       <c r="J539" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K539" s="2" t="inlineStr">
         <is>
@@ -52272,10 +52272,10 @@
         <v>2821</v>
       </c>
       <c r="I540" s="2" t="n">
-        <v>47957</v>
+        <v>50778</v>
       </c>
       <c r="J540" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
         <is>
@@ -52368,10 +52368,10 @@
         <v>2821</v>
       </c>
       <c r="I541" s="2" t="n">
-        <v>28217</v>
+        <v>31038</v>
       </c>
       <c r="J541" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
         <is>
@@ -52656,10 +52656,10 @@
         <v>2730</v>
       </c>
       <c r="I544" s="2" t="n">
-        <v>43001</v>
+        <v>45167</v>
       </c>
       <c r="J544" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
         <is>
@@ -52848,10 +52848,10 @@
         <v>2700</v>
       </c>
       <c r="I546" s="2" t="n">
-        <v>8100</v>
+        <v>10800</v>
       </c>
       <c r="J546" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
         <is>
@@ -53040,10 +53040,10 @@
         <v>2699</v>
       </c>
       <c r="I548" s="2" t="n">
-        <v>8097</v>
+        <v>10796</v>
       </c>
       <c r="J548" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
         <is>
@@ -53136,10 +53136,10 @@
         <v>2699</v>
       </c>
       <c r="I549" s="2" t="n">
-        <v>8097</v>
+        <v>10796</v>
       </c>
       <c r="J549" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K549" s="2" t="inlineStr">
         <is>
@@ -53232,10 +53232,10 @@
         <v>2698</v>
       </c>
       <c r="I550" s="2" t="n">
-        <v>9893</v>
+        <v>12591</v>
       </c>
       <c r="J550" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
         <is>
@@ -53328,10 +53328,10 @@
         <v>2666</v>
       </c>
       <c r="I551" s="2" t="n">
-        <v>27149</v>
+        <v>28346</v>
       </c>
       <c r="J551" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K551" s="2" t="inlineStr">
         <is>
@@ -53424,10 +53424,10 @@
         <v>2635</v>
       </c>
       <c r="I552" s="2" t="n">
-        <v>11857</v>
+        <v>14492</v>
       </c>
       <c r="J552" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
         <is>
@@ -53520,10 +53520,10 @@
         <v>2631</v>
       </c>
       <c r="I553" s="2" t="n">
-        <v>26779</v>
+        <v>28095</v>
       </c>
       <c r="J553" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
         <is>
@@ -53616,10 +53616,10 @@
         <v>2541</v>
       </c>
       <c r="I554" s="2" t="n">
-        <v>20147</v>
+        <v>22217</v>
       </c>
       <c r="J554" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
         <is>
@@ -53808,10 +53808,10 @@
         <v>2520</v>
       </c>
       <c r="I556" s="2" t="n">
-        <v>20520</v>
+        <v>22140</v>
       </c>
       <c r="J556" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
@@ -53904,10 +53904,10 @@
         <v>2485</v>
       </c>
       <c r="I557" s="2" t="n">
-        <v>31731</v>
+        <v>34216</v>
       </c>
       <c r="J557" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
         <is>
@@ -54000,10 +54000,10 @@
         <v>2471</v>
       </c>
       <c r="I558" s="2" t="n">
-        <v>7413</v>
+        <v>9884</v>
       </c>
       <c r="J558" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
@@ -54096,10 +54096,10 @@
         <v>2470</v>
       </c>
       <c r="I559" s="2" t="n">
-        <v>7410</v>
+        <v>9880</v>
       </c>
       <c r="J559" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K559" s="2" t="inlineStr">
         <is>
@@ -54192,10 +54192,10 @@
         <v>2456</v>
       </c>
       <c r="I560" s="2" t="n">
-        <v>22104</v>
+        <v>24560</v>
       </c>
       <c r="J560" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
@@ -54288,10 +54288,10 @@
         <v>2441</v>
       </c>
       <c r="I561" s="2" t="n">
-        <v>19528</v>
+        <v>21969</v>
       </c>
       <c r="J561" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K561" s="2" t="inlineStr">
         <is>
@@ -54384,10 +54384,10 @@
         <v>2441</v>
       </c>
       <c r="I562" s="2" t="n">
-        <v>17083</v>
+        <v>19524</v>
       </c>
       <c r="J562" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
@@ -54672,10 +54672,10 @@
         <v>2426</v>
       </c>
       <c r="I565" s="2" t="n">
-        <v>19408</v>
+        <v>21834</v>
       </c>
       <c r="J565" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K565" s="2" t="inlineStr">
         <is>
@@ -54768,10 +54768,10 @@
         <v>2425</v>
       </c>
       <c r="I566" s="2" t="n">
-        <v>25516</v>
+        <v>27045</v>
       </c>
       <c r="J566" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
@@ -55152,10 +55152,10 @@
         <v>2353</v>
       </c>
       <c r="I570" s="2" t="n">
-        <v>21177</v>
+        <v>23530</v>
       </c>
       <c r="J570" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K570" s="2" t="inlineStr">
         <is>
@@ -55248,10 +55248,10 @@
         <v>2352</v>
       </c>
       <c r="I571" s="2" t="n">
-        <v>24459</v>
+        <v>26340</v>
       </c>
       <c r="J571" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K571" s="2" t="inlineStr">
         <is>
@@ -55344,10 +55344,10 @@
         <v>2352</v>
       </c>
       <c r="I572" s="2" t="n">
-        <v>8174</v>
+        <v>10526</v>
       </c>
       <c r="J572" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K572" s="2" t="inlineStr">
         <is>
@@ -55536,10 +55536,10 @@
         <v>2350</v>
       </c>
       <c r="I574" s="2" t="n">
-        <v>7050</v>
+        <v>9400</v>
       </c>
       <c r="J574" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K574" s="2" t="inlineStr">
         <is>
@@ -55920,10 +55920,10 @@
         <v>2248</v>
       </c>
       <c r="I578" s="2" t="n">
-        <v>6744</v>
+        <v>8992</v>
       </c>
       <c r="J578" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K578" s="2" t="inlineStr">
         <is>
@@ -56208,10 +56208,10 @@
         <v>2224</v>
       </c>
       <c r="I581" s="2" t="n">
-        <v>32295</v>
+        <v>34020</v>
       </c>
       <c r="J581" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K581" s="2" t="inlineStr">
         <is>
@@ -56304,10 +56304,10 @@
         <v>2156</v>
       </c>
       <c r="I582" s="2" t="n">
-        <v>23716</v>
+        <v>25872</v>
       </c>
       <c r="J582" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K582" s="2" t="inlineStr">
         <is>
@@ -56496,10 +56496,10 @@
         <v>2128</v>
       </c>
       <c r="I584" s="2" t="n">
-        <v>6384</v>
+        <v>8512</v>
       </c>
       <c r="J584" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K584" s="2" t="inlineStr">
         <is>
@@ -56880,10 +56880,10 @@
         <v>2057</v>
       </c>
       <c r="I588" s="2" t="n">
-        <v>6171</v>
+        <v>8228</v>
       </c>
       <c r="J588" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K588" s="2" t="inlineStr">
         <is>
@@ -57072,10 +57072,10 @@
         <v>2025</v>
       </c>
       <c r="I590" s="2" t="n">
-        <v>30888</v>
+        <v>32045</v>
       </c>
       <c r="J590" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
@@ -57456,10 +57456,10 @@
         <v>1976</v>
       </c>
       <c r="I594" s="2" t="n">
-        <v>14326</v>
+        <v>15808</v>
       </c>
       <c r="J594" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K594" s="2" t="inlineStr">
         <is>
@@ -57648,10 +57648,10 @@
         <v>1976</v>
       </c>
       <c r="I596" s="2" t="n">
-        <v>5928</v>
+        <v>7904</v>
       </c>
       <c r="J596" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
@@ -57744,10 +57744,10 @@
         <v>1976</v>
       </c>
       <c r="I597" s="2" t="n">
-        <v>5928</v>
+        <v>7904</v>
       </c>
       <c r="J597" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K597" s="2" t="inlineStr">
         <is>
@@ -57936,10 +57936,10 @@
         <v>1971</v>
       </c>
       <c r="I599" s="2" t="n">
-        <v>15493</v>
+        <v>17464</v>
       </c>
       <c r="J599" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K599" s="2" t="inlineStr">
         <is>
@@ -58512,10 +58512,10 @@
         <v>1929</v>
       </c>
       <c r="I605" s="2" t="n">
-        <v>5787</v>
+        <v>7716</v>
       </c>
       <c r="J605" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K605" s="2" t="inlineStr">
         <is>
@@ -58896,10 +58896,10 @@
         <v>1916</v>
       </c>
       <c r="I609" s="2" t="n">
-        <v>5748</v>
+        <v>7664</v>
       </c>
       <c r="J609" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K609" s="2" t="inlineStr">
         <is>
@@ -59472,10 +59472,10 @@
         <v>1881</v>
       </c>
       <c r="I615" s="2" t="n">
-        <v>31977</v>
+        <v>33858</v>
       </c>
       <c r="J615" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K615" s="2" t="inlineStr">
         <is>
@@ -59664,10 +59664,10 @@
         <v>1881</v>
       </c>
       <c r="I617" s="2" t="n">
-        <v>15048</v>
+        <v>16929</v>
       </c>
       <c r="J617" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K617" s="2" t="inlineStr">
         <is>
@@ -59856,10 +59856,10 @@
         <v>1881</v>
       </c>
       <c r="I619" s="2" t="n">
-        <v>15048</v>
+        <v>16929</v>
       </c>
       <c r="J619" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K619" s="2" t="inlineStr">
         <is>
@@ -60528,10 +60528,10 @@
         <v>1799</v>
       </c>
       <c r="I626" s="2" t="n">
-        <v>13582</v>
+        <v>15111</v>
       </c>
       <c r="J626" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K626" s="2" t="inlineStr">
         <is>
@@ -60624,10 +60624,10 @@
         <v>1799</v>
       </c>
       <c r="I627" s="2" t="n">
-        <v>5397</v>
+        <v>7196</v>
       </c>
       <c r="J627" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K627" s="2" t="inlineStr">
         <is>
@@ -60912,10 +60912,10 @@
         <v>1757</v>
       </c>
       <c r="I630" s="2" t="n">
-        <v>14056</v>
+        <v>15813</v>
       </c>
       <c r="J630" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K630" s="2" t="inlineStr">
         <is>
@@ -61584,10 +61584,10 @@
         <v>1714</v>
       </c>
       <c r="I637" s="2" t="n">
-        <v>26850</v>
+        <v>28564</v>
       </c>
       <c r="J637" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K637" s="2" t="inlineStr">
         <is>
@@ -61680,10 +61680,10 @@
         <v>1711</v>
       </c>
       <c r="I638" s="2" t="n">
-        <v>5133</v>
+        <v>6844</v>
       </c>
       <c r="J638" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K638" s="2" t="inlineStr">
         <is>
@@ -62352,10 +62352,10 @@
         <v>1599</v>
       </c>
       <c r="I645" s="2" t="n">
-        <v>4797</v>
+        <v>6396</v>
       </c>
       <c r="J645" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K645" s="2" t="inlineStr">
         <is>
@@ -62928,10 +62928,10 @@
         <v>1528</v>
       </c>
       <c r="I651" s="2" t="n">
-        <v>10039</v>
+        <v>11567</v>
       </c>
       <c r="J651" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K651" s="2" t="inlineStr">
         <is>
@@ -63216,10 +63216,10 @@
         <v>1465</v>
       </c>
       <c r="I654" s="2" t="n">
-        <v>11720</v>
+        <v>13185</v>
       </c>
       <c r="J654" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K654" s="2" t="inlineStr">
         <is>
@@ -63312,10 +63312,10 @@
         <v>1464</v>
       </c>
       <c r="I655" s="2" t="n">
-        <v>4392</v>
+        <v>5856</v>
       </c>
       <c r="J655" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K655" s="2" t="inlineStr">
         <is>
@@ -63408,10 +63408,10 @@
         <v>1426</v>
       </c>
       <c r="I656" s="2" t="n">
-        <v>11408</v>
+        <v>12834</v>
       </c>
       <c r="J656" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K656" s="2" t="inlineStr">
         <is>
@@ -63792,10 +63792,10 @@
         <v>1395</v>
       </c>
       <c r="I660" s="2" t="n">
-        <v>5310</v>
+        <v>6705</v>
       </c>
       <c r="J660" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K660" s="2" t="inlineStr">
         <is>
@@ -63984,10 +63984,10 @@
         <v>1367</v>
       </c>
       <c r="I662" s="2" t="n">
-        <v>17504</v>
+        <v>18871</v>
       </c>
       <c r="J662" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K662" s="2" t="inlineStr">
         <is>
@@ -64176,10 +64176,10 @@
         <v>1347</v>
       </c>
       <c r="I664" s="2" t="n">
-        <v>9819</v>
+        <v>10847</v>
       </c>
       <c r="J664" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K664" s="2" t="inlineStr">
         <is>
@@ -64368,10 +64368,10 @@
         <v>1310</v>
       </c>
       <c r="I666" s="2" t="n">
-        <v>3930</v>
+        <v>5240</v>
       </c>
       <c r="J666" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K666" s="2" t="inlineStr">
         <is>
@@ -64464,10 +64464,10 @@
         <v>1261</v>
       </c>
       <c r="I667" s="2" t="n">
-        <v>3783</v>
+        <v>5044</v>
       </c>
       <c r="J667" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K667" s="2" t="inlineStr">
         <is>
@@ -64560,10 +64560,10 @@
         <v>1260</v>
       </c>
       <c r="I668" s="2" t="n">
-        <v>9540</v>
+        <v>10620</v>
       </c>
       <c r="J668" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K668" s="2" t="inlineStr">
         <is>
@@ -64656,10 +64656,10 @@
         <v>1260</v>
       </c>
       <c r="I669" s="2" t="n">
-        <v>3780</v>
+        <v>5040</v>
       </c>
       <c r="J669" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K669" s="2" t="inlineStr">
         <is>
@@ -64848,10 +64848,10 @@
         <v>1259</v>
       </c>
       <c r="I671" s="2" t="n">
-        <v>3777</v>
+        <v>5036</v>
       </c>
       <c r="J671" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K671" s="2" t="inlineStr">
         <is>
@@ -65232,10 +65232,10 @@
         <v>1222</v>
       </c>
       <c r="I675" s="2" t="n">
-        <v>13442</v>
+        <v>14664</v>
       </c>
       <c r="J675" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K675" s="2" t="inlineStr">
         <is>
@@ -65424,10 +65424,10 @@
         <v>1220</v>
       </c>
       <c r="I677" s="2" t="n">
-        <v>3660</v>
+        <v>4880</v>
       </c>
       <c r="J677" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K677" s="2" t="inlineStr">
         <is>
@@ -65520,10 +65520,10 @@
         <v>1156</v>
       </c>
       <c r="I678" s="2" t="n">
-        <v>3468</v>
+        <v>4624</v>
       </c>
       <c r="J678" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K678" s="2" t="inlineStr">
         <is>
@@ -65616,10 +65616,10 @@
         <v>1110</v>
       </c>
       <c r="I679" s="2" t="n">
-        <v>3330</v>
+        <v>4440</v>
       </c>
       <c r="J679" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K679" s="2" t="inlineStr">
         <is>
@@ -65712,10 +65712,10 @@
         <v>1080</v>
       </c>
       <c r="I680" s="2" t="n">
-        <v>4320</v>
+        <v>5400</v>
       </c>
       <c r="J680" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K680" s="2" t="inlineStr">
         <is>
@@ -66288,10 +66288,10 @@
         <v>1017</v>
       </c>
       <c r="I686" s="2" t="n">
-        <v>3051</v>
+        <v>4068</v>
       </c>
       <c r="J686" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K686" s="2" t="inlineStr">
         <is>

--- a/reports/telegram_sebi_10day_report.xlsx
+++ b/reports/telegram_sebi_10day_report.xlsx
@@ -624,10 +624,10 @@
         <v>569271</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>9442944</v>
+        <v>9729794</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>393135</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1195674</v>
+        <v>1234867</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>211523</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1402655</v>
+        <v>1476282</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>162819</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2902916</v>
+        <v>3065735</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>158965</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>909605</v>
+        <v>921180</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>151478</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2082377</v>
+        <v>2205219</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>136719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1440520</v>
+        <v>1468189</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>131492</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1808284</v>
+        <v>1906058</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>127846</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1554536</v>
+        <v>1682382</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>114194</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>743123</v>
+        <v>750694</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>99486</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1579304</v>
+        <v>1617697</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>88046</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>980428</v>
+        <v>1060698</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>87906</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1329006</v>
+        <v>1416912</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>85649</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>459877</v>
+        <v>545526</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>84208</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1514823</v>
+        <v>1593929</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>80760</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>739180</v>
+        <v>745480</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>79502</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>678825</v>
+        <v>709403</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>76419</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>937136</v>
+        <v>961145</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>75133</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>529912</v>
+        <v>605045</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>69504</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>648274</v>
+        <v>674476</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>69234</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1034391</v>
+        <v>1088000</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>68460</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>356467</v>
+        <v>383108</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>68202</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>441653</v>
+        <v>509855</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>66703</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>527711</v>
+        <v>594414</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>65193</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>726425</v>
+        <v>740409</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>65111</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>766860</v>
+        <v>771683</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>59566</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>662812</v>
+        <v>668215</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>58582</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>765233</v>
+        <v>823815</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>58176</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>478786</v>
+        <v>536962</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>57608</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>230432</v>
+        <v>288040</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>57276</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>424500</v>
+        <v>481776</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>55945</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>637873</v>
+        <v>693818</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>55901</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>223604</v>
+        <v>279505</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>54993</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>679769</v>
+        <v>734762</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>54825</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>582546</v>
+        <v>591120</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>53890</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>941618</v>
+        <v>956314</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>53653</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>799362</v>
+        <v>809002</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>50870</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>379667</v>
+        <v>391243</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>49470</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>551003</v>
+        <v>600473</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>48785</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>850611</v>
+        <v>899396</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>48086</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>689649</v>
+        <v>699289</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>47876</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>630957</v>
+        <v>652267</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>46941</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>481171</v>
+        <v>528112</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>43995</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>600326</v>
+        <v>627167</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>43416</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>134854</v>
+        <v>139170</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>43047</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>537685</v>
+        <v>576932</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>42572</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>504093</v>
+        <v>546665</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>41300</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>147535</v>
+        <v>150481</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>41270</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>168657</v>
+        <v>174936</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>40719</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>594394</v>
+        <v>602650</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>39334</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>464858</v>
+        <v>482737</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>39288</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>562947</v>
+        <v>602235</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>39193</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>164593</v>
+        <v>178308</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>38511</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>167212</v>
+        <v>205723</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>38479</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>604360</v>
+        <v>614108</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>37909</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>633665</v>
+        <v>671574</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>37246</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>267513</v>
+        <v>304759</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>36417</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>342048</v>
+        <v>359268</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>35835</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>447703</v>
+        <v>479149</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>34868</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>471455</v>
+        <v>496010</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>34616</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>72483</v>
+        <v>76341</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>34370</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>508620</v>
+        <v>542990</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>34334</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>365096</v>
+        <v>382863</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>34280</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>234505</v>
+        <v>244297</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>33783</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>527380</v>
+        <v>561163</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>33544</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>542911</v>
+        <v>565770</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>33294</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>252966</v>
+        <v>286260</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>33238</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>190547</v>
+        <v>223785</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>33063</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>465292</v>
+        <v>492693</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>32476</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>231809</v>
+        <v>264285</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>32351</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>262179</v>
+        <v>294530</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>31814</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>392872</v>
+        <v>398210</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>31199</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>320651</v>
+        <v>351850</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>30716</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>316069</v>
+        <v>346785</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>30200</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>120800</v>
+        <v>151000</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>29593</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>375696</v>
+        <v>405289</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>29540</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>118160</v>
+        <v>147700</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>29237</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>394447</v>
+        <v>414096</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>29222</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>302393</v>
+        <v>331615</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>29115</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>118399</v>
+        <v>147514</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>28689</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>287470</v>
+        <v>306635</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>28319</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>319017</v>
+        <v>333419</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>28316</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>245797</v>
+        <v>270207</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>28151</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>156689</v>
+        <v>184840</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>27693</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>428952</v>
+        <v>456645</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>27646</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>288350</v>
+        <v>315996</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>27571</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>204197</v>
+        <v>215301</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>27501</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>238673</v>
+        <v>261264</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>27294</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>261538</v>
+        <v>277156</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>27234</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>294739</v>
+        <v>321973</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>27058</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>194724</v>
+        <v>203187</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>27042</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>237523</v>
+        <v>264565</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>26996</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>209163</v>
+        <v>236159</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         <v>26814</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>383734</v>
+        <v>407103</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>26286</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>145202</v>
+        <v>148265</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>26168</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>372279</v>
+        <v>378100</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>26042</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>112850</v>
+        <v>131176</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>25641</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>151798</v>
+        <v>157695</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>25401</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>267926</v>
+        <v>269525</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>25120</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>321185</v>
+        <v>333338</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>24466</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>238846</v>
+        <v>243739</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>24373</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>214858</v>
+        <v>221732</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>24370</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>331755</v>
+        <v>339370</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>23733</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>94932</v>
+        <v>118665</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>23238</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>230015</v>
+        <v>252780</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>23055</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>220198</v>
+        <v>243253</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>22178</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>197362</v>
+        <v>219540</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>22114</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>192604</v>
+        <v>214718</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>21772</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>366620</v>
+        <v>386958</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>21731</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>256002</v>
+        <v>271115</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>21717</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>159671</v>
+        <v>162833</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>21396</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>228382</v>
+        <v>233320</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>21393</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>227174</v>
+        <v>230485</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>21350</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>189679</v>
+        <v>211029</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>21292</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>270880</v>
+        <v>285272</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>21056</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>204026</v>
+        <v>225082</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>20991</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>193284</v>
+        <v>214275</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>20958</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>232616</v>
+        <v>237757</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>20138</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>143323</v>
+        <v>150645</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>19754</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>240160</v>
+        <v>251448</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>19716</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>78864</v>
+        <v>98580</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>19651</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>178040</v>
+        <v>192582</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>19502</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>203422</v>
+        <v>213102</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>19350</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>170312</v>
+        <v>189662</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>19350</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>140400</v>
+        <v>159750</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>19271</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>165767</v>
+        <v>173480</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>19174</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>268436</v>
+        <v>287610</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>19172</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>134204</v>
+        <v>143790</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>19075</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>199200</v>
+        <v>202349</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>18517</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>184817</v>
+        <v>192150</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>18466</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>260798</v>
+        <v>266925</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>18435</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>201678</v>
+        <v>220113</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>18215</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>223373</v>
+        <v>229125</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>17796</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>195858</v>
+        <v>203957</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>17677</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>175602</v>
+        <v>193279</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>17393</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>65219</v>
+        <v>67158</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>17364</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>93864</v>
+        <v>111228</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>17025</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>230602</v>
+        <v>247627</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>16937</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>67748</v>
+        <v>84685</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>16849</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>244103</v>
+        <v>256959</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>16821</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>126141</v>
+        <v>142962</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>16587</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>174006</v>
+        <v>186627</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>16561</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>230255</v>
+        <v>235442</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>16561</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>118082</v>
+        <v>122963</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>16531</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>59221</v>
+        <v>62167</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>16494</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>122679</v>
+        <v>126912</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>16436</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>100964</v>
+        <v>105660</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>16245</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>85920</v>
+        <v>93372</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>16197</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>208763</v>
+        <v>224960</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>16166</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>194878</v>
+        <v>201512</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>16043</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>130153</v>
+        <v>135064</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>16013</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>100374</v>
+        <v>104963</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>15807</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>244065</v>
+        <v>259636</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>15527</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>229611</v>
+        <v>234316</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>15275</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>85210</v>
+        <v>100485</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>15075</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>110524</v>
+        <v>118823</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>14989</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>59956</v>
+        <v>74945</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>14953</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>139923</v>
+        <v>147633</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>14915</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>170632</v>
+        <v>172933</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>14855</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>74665</v>
+        <v>89520</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>14584</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>58336</v>
+        <v>72920</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>14436</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>154404</v>
+        <v>168840</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>14381</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>112449</v>
+        <v>126830</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>14313</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>179609</v>
+        <v>185402</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>14157</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>56628</v>
+        <v>70785</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>14153</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>157654</v>
+        <v>167413</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
@@ -20784,10 +20784,10 @@
         <v>14149</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>203531</v>
+        <v>209318</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>14097</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>763424</v>
+        <v>775601</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>14042</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>126093</v>
+        <v>140135</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>14018</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>213353</v>
+        <v>222699</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>13943</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>246376</v>
+        <v>251298</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>13860</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>62452</v>
+        <v>65964</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>13832</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>87920</v>
+        <v>101752</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>13814</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>55256</v>
+        <v>69070</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>13641</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>103954</v>
+        <v>117595</v>
       </c>
       <c r="J225" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>13563</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>130165</v>
+        <v>140870</v>
       </c>
       <c r="J226" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>13541</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>189341</v>
+        <v>202882</v>
       </c>
       <c r="J227" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>13499</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>53996</v>
+        <v>67495</v>
       </c>
       <c r="J228" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>13260</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>123690</v>
+        <v>136950</v>
       </c>
       <c r="J230" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>13233</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>145077</v>
+        <v>153899</v>
       </c>
       <c r="J231" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>13172</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>198518</v>
+        <v>211690</v>
       </c>
       <c r="J232" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>13071</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>169174</v>
+        <v>178790</v>
       </c>
       <c r="J233" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>12877</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>133377</v>
+        <v>139805</v>
       </c>
       <c r="J234" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>12786</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>149973</v>
+        <v>159565</v>
       </c>
       <c r="J235" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>12715</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>82647</v>
+        <v>87415</v>
       </c>
       <c r="J236" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>12689</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>119078</v>
+        <v>124932</v>
       </c>
       <c r="J237" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>12675</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>113859</v>
+        <v>120914</v>
       </c>
       <c r="J238" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>12443</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>66652</v>
+        <v>79095</v>
       </c>
       <c r="J239" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>12382</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>54481</v>
+        <v>66863</v>
       </c>
       <c r="J240" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>12340</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>111060</v>
+        <v>123400</v>
       </c>
       <c r="J241" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>12303</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>176393</v>
+        <v>179960</v>
       </c>
       <c r="J242" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>12156</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>41436</v>
+        <v>43876</v>
       </c>
       <c r="J243" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>12088</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>153864</v>
+        <v>162110</v>
       </c>
       <c r="J244" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>11974</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>195768</v>
+        <v>201158</v>
       </c>
       <c r="J245" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>11681</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>105309</v>
+        <v>116990</v>
       </c>
       <c r="J248" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>11358</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>52152</v>
+        <v>59511</v>
       </c>
       <c r="J250" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>11226</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>102274</v>
+        <v>113500</v>
       </c>
       <c r="J253" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>10989</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>111153</v>
+        <v>116936</v>
       </c>
       <c r="J254" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>10853</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>77205</v>
+        <v>88058</v>
       </c>
       <c r="J255" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>10802</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>60884</v>
+        <v>71686</v>
       </c>
       <c r="J256" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>10675</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>42700</v>
+        <v>53375</v>
       </c>
       <c r="J257" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>10325</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>53478</v>
+        <v>63803</v>
       </c>
       <c r="J258" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>10316</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>96980</v>
+        <v>99641</v>
       </c>
       <c r="J259" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>10306</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>56773</v>
+        <v>61386</v>
       </c>
       <c r="J260" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>10268</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>100425</v>
+        <v>110693</v>
       </c>
       <c r="J261" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>10190</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>88798</v>
+        <v>95106</v>
       </c>
       <c r="J262" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>10117</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>48344</v>
+        <v>58461</v>
       </c>
       <c r="J264" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>10069</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>40276</v>
+        <v>50345</v>
       </c>
       <c r="J265" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>9898</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>145473</v>
+        <v>150520</v>
       </c>
       <c r="J269" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>9898</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>38690</v>
+        <v>45888</v>
       </c>
       <c r="J270" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>9878</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>92655</v>
+        <v>102533</v>
       </c>
       <c r="J272" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>9863</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>114832</v>
+        <v>124695</v>
       </c>
       <c r="J273" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>9823</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>85310</v>
+        <v>95133</v>
       </c>
       <c r="J274" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>9814</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>81181</v>
+        <v>88062</v>
       </c>
       <c r="J275" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>9813</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>39252</v>
+        <v>49065</v>
       </c>
       <c r="J276" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>9795</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>70038</v>
+        <v>79833</v>
       </c>
       <c r="J277" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>9712</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>127765</v>
+        <v>132607</v>
       </c>
       <c r="J280" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>9631</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>52984</v>
+        <v>62615</v>
       </c>
       <c r="J284" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>9616</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>114421</v>
+        <v>121087</v>
       </c>
       <c r="J285" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>9587</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>106841</v>
+        <v>111500</v>
       </c>
       <c r="J287" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>9587</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>38348</v>
+        <v>47935</v>
       </c>
       <c r="J288" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>9470</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>145663</v>
+        <v>153774</v>
       </c>
       <c r="J292" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>9236</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>48999</v>
+        <v>58235</v>
       </c>
       <c r="J294" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>9152</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>101672</v>
+        <v>104210</v>
       </c>
       <c r="J295" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>9047</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>75015</v>
+        <v>80917</v>
       </c>
       <c r="J297" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>9028</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>47920</v>
+        <v>56948</v>
       </c>
       <c r="J299" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>8999</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>35996</v>
+        <v>44995</v>
       </c>
       <c r="J300" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>8870</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>45120</v>
+        <v>53990</v>
       </c>
       <c r="J302" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>8847</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>127695</v>
+        <v>133903</v>
       </c>
       <c r="J303" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>8819</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>124446</v>
+        <v>129835</v>
       </c>
       <c r="J305" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>8788</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>35152</v>
+        <v>43940</v>
       </c>
       <c r="J306" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>8783</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>128272</v>
+        <v>137055</v>
       </c>
       <c r="J307" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>8748</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>28783</v>
+        <v>31323</v>
       </c>
       <c r="J308" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>8726</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>145624</v>
+        <v>148061</v>
       </c>
       <c r="J309" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>8679</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>122011</v>
+        <v>130690</v>
       </c>
       <c r="J311" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>8653</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>121152</v>
+        <v>123598</v>
       </c>
       <c r="J312" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>8644</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>60441</v>
+        <v>69085</v>
       </c>
       <c r="J313" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>8585</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>77473</v>
+        <v>80352</v>
       </c>
       <c r="J315" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>8572</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>125118</v>
+        <v>130345</v>
       </c>
       <c r="J316" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
         <v>8540</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>65215</v>
+        <v>73755</v>
       </c>
       <c r="J318" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>8467</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>69617</v>
+        <v>78084</v>
       </c>
       <c r="J319" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>8399</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>53206</v>
+        <v>55281</v>
       </c>
       <c r="J320" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>8199</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>125881</v>
+        <v>127810</v>
       </c>
       <c r="J322" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>8149</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>99296</v>
+        <v>107445</v>
       </c>
       <c r="J324" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>8149</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>63751</v>
+        <v>71900</v>
       </c>
       <c r="J325" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>8137</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>32548</v>
+        <v>40685</v>
       </c>
       <c r="J326" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>8132</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>68179</v>
+        <v>71301</v>
       </c>
       <c r="J327" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>7858</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>117118</v>
+        <v>124788</v>
       </c>
       <c r="J331" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>7811</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>67444</v>
+        <v>75255</v>
       </c>
       <c r="J332" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>7713</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>97862</v>
+        <v>99790</v>
       </c>
       <c r="J335" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>7560</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>30240</v>
+        <v>37800</v>
       </c>
       <c r="J337" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>7520</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>30080</v>
+        <v>37600</v>
       </c>
       <c r="J340" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>7453</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>29812</v>
+        <v>37265</v>
       </c>
       <c r="J342" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>7428</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>56382</v>
+        <v>63810</v>
       </c>
       <c r="J343" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>7420</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>94671</v>
+        <v>102091</v>
       </c>
       <c r="J344" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>7223</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>76888</v>
+        <v>84111</v>
       </c>
       <c r="J345" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>7189</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>73327</v>
+        <v>78599</v>
       </c>
       <c r="J347" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>7172</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>45360</v>
+        <v>47735</v>
       </c>
       <c r="J348" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>7148</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>46462</v>
+        <v>53610</v>
       </c>
       <c r="J349" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>7135</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>74540</v>
+        <v>81675</v>
       </c>
       <c r="J350" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>7099</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>28396</v>
+        <v>35495</v>
       </c>
       <c r="J351" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>7093</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>65014</v>
+        <v>72107</v>
       </c>
       <c r="J352" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>7074</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>82770</v>
+        <v>85713</v>
       </c>
       <c r="J353" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>6954</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>62586</v>
+        <v>69540</v>
       </c>
       <c r="J354" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>6875</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>51068</v>
+        <v>57943</v>
       </c>
       <c r="J356" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>6834</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>93156</v>
+        <v>99990</v>
       </c>
       <c r="J358" s="2" t="n">
-       